--- a/events/2026/config/motions-ids.xlsx
+++ b/events/2026/config/motions-ids.xlsx
@@ -1,20 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mike\projects\work\wsw-results\events\2026\config\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61C5873-C8F0-4089-B815-72530C47C00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="motions" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="motions" sheetId="1" r:id="rId1"/>
+    <sheet name="scratch" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">motions!$A$1:$U$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">motions!$A$1:$U$86</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -23,494 +40,814 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="159">
-  <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Family Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Youth Weekend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UKWA Member</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrants Own Motion Mini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motion for Wingboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motion for Sailboard (foil)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motion for Sailboard (fin)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motion for Kiteboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motion for Boat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Craft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motion ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motion Label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael</t>
-  </si>
-  <si>
-    <t xml:space="preserve">George</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sailboard (Foil) Motion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sailboard (Fin) Motion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pettifer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jenna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gibson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stacey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiteboard Motion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eiffel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dickinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wingboard Motion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jean-Marc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">De Bruyne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dudley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meyerhoff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reeves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rob</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longstaff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rogers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crosby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mayhew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nikolaos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iliadis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingram</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonathan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salvage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lilley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gordo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brendan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lorho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francois</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fulton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bob</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spagnoletti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arnold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thompson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Watts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daffe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shellcock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burnaby Lautier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pavel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dvoulety</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Russell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boat Motion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anthony</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bernie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collenette</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arlo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dinsmore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trossell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palmer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sanderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Newman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eddie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stuart-William</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longmuir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonny</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kirton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crossley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Norman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camaret</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Twinn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Humphreys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goodwin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trevor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whatford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiernan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">carter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verrion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Davison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vickers</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="267">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Family Name</t>
+  </si>
+  <si>
+    <t>Youth Weekend</t>
+  </si>
+  <si>
+    <t>UKWA Member</t>
+  </si>
+  <si>
+    <t>Entrants Own Motion Mini</t>
+  </si>
+  <si>
+    <t>Motion for Wingboard</t>
+  </si>
+  <si>
+    <t>Motion for Sailboard (foil)</t>
+  </si>
+  <si>
+    <t>Motion for Sailboard (fin)</t>
+  </si>
+  <si>
+    <t>Motion for Kiteboard</t>
+  </si>
+  <si>
+    <t>Motion for Boat</t>
+  </si>
+  <si>
+    <t>Diff</t>
+  </si>
+  <si>
+    <t>Craft</t>
+  </si>
+  <si>
+    <t>Motion ID</t>
+  </si>
+  <si>
+    <t>Motion Label</t>
+  </si>
+  <si>
+    <t>Mr</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>George</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Sailboard (Foil) Motion</t>
+  </si>
+  <si>
+    <t>Sailboard (Fin) Motion</t>
+  </si>
+  <si>
+    <t>Simon</t>
+  </si>
+  <si>
+    <t>Pettifer</t>
+  </si>
+  <si>
+    <t>Miss</t>
+  </si>
+  <si>
+    <t>Jenna</t>
+  </si>
+  <si>
+    <t>Gibson</t>
+  </si>
+  <si>
+    <t>Stacey</t>
+  </si>
+  <si>
+    <t>Vass</t>
+  </si>
+  <si>
+    <t>Kiteboard Motion</t>
+  </si>
+  <si>
+    <t>Ms</t>
+  </si>
+  <si>
+    <t>Aya</t>
+  </si>
+  <si>
+    <t>Eiffel</t>
+  </si>
+  <si>
+    <t>Dylan</t>
+  </si>
+  <si>
+    <t>Chick</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>Richard</t>
+  </si>
+  <si>
+    <t>Henderson</t>
+  </si>
+  <si>
+    <t>Rod</t>
+  </si>
+  <si>
+    <t>Dickinson</t>
+  </si>
+  <si>
+    <t>Wingboard Motion</t>
+  </si>
+  <si>
+    <t>Jean-Marc</t>
+  </si>
+  <si>
+    <t>De Bruyne</t>
+  </si>
+  <si>
+    <t>Dudley</t>
+  </si>
+  <si>
+    <t>Ben</t>
+  </si>
+  <si>
+    <t>Meyerhoff</t>
+  </si>
+  <si>
+    <t>Jez</t>
+  </si>
+  <si>
+    <t>Milne</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>Reeves</t>
+  </si>
+  <si>
+    <t>Rob</t>
+  </si>
+  <si>
+    <t>Longstaff</t>
+  </si>
+  <si>
+    <t>Mrs</t>
+  </si>
+  <si>
+    <t>Kate</t>
+  </si>
+  <si>
+    <t>Rogers</t>
+  </si>
+  <si>
+    <t>Barry</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>Crosby</t>
+  </si>
+  <si>
+    <t>Peter</t>
+  </si>
+  <si>
+    <t>Barker</t>
+  </si>
+  <si>
+    <t>Scott</t>
+  </si>
+  <si>
+    <t>Mayhew</t>
+  </si>
+  <si>
+    <t>Nikolaos</t>
+  </si>
+  <si>
+    <t>Iliadis</t>
+  </si>
+  <si>
+    <t>Ingram</t>
+  </si>
+  <si>
+    <t>Jonathan</t>
+  </si>
+  <si>
+    <t>Salvage</t>
+  </si>
+  <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>Owen</t>
+  </si>
+  <si>
+    <t>Matthew</t>
+  </si>
+  <si>
+    <t>Lilley</t>
+  </si>
+  <si>
+    <t>Denis</t>
+  </si>
+  <si>
+    <t>Gordo</t>
+  </si>
+  <si>
+    <t>Harrison</t>
+  </si>
+  <si>
+    <t>Sian</t>
+  </si>
+  <si>
+    <t>Neil</t>
+  </si>
+  <si>
+    <t>Steve</t>
+  </si>
+  <si>
+    <t>Watson</t>
+  </si>
+  <si>
+    <t>Brendan</t>
+  </si>
+  <si>
+    <t>Lorho</t>
+  </si>
+  <si>
+    <t>Francois</t>
+  </si>
+  <si>
+    <t>Fin</t>
+  </si>
+  <si>
+    <t>Fulton</t>
+  </si>
+  <si>
+    <t>Bob</t>
+  </si>
+  <si>
+    <t>Spagnoletti</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>Arnold</t>
+  </si>
+  <si>
+    <t>Thompson</t>
+  </si>
+  <si>
+    <t>Joey</t>
+  </si>
+  <si>
+    <t>Watts</t>
+  </si>
+  <si>
+    <t>Christine</t>
+  </si>
+  <si>
+    <t>Daffe</t>
+  </si>
+  <si>
+    <t>Wills</t>
+  </si>
+  <si>
+    <t>Ian</t>
+  </si>
+  <si>
+    <t>Shellcock</t>
+  </si>
+  <si>
+    <t>Emile</t>
+  </si>
+  <si>
+    <t>Burnaby Lautier</t>
+  </si>
+  <si>
+    <t>Pavel</t>
+  </si>
+  <si>
+    <t>Dvoulety</t>
+  </si>
+  <si>
+    <t>Robin</t>
+  </si>
+  <si>
+    <t>Russell</t>
+  </si>
+  <si>
+    <t>Boat Motion</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>Brake</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Oliver</t>
+  </si>
+  <si>
+    <t>Anthony</t>
+  </si>
+  <si>
+    <t>Barber</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>Bernie</t>
+  </si>
+  <si>
+    <t>Collenette</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>Arlo</t>
+  </si>
+  <si>
+    <t>Garry</t>
+  </si>
+  <si>
+    <t>Connell</t>
+  </si>
+  <si>
+    <t>Dinsmore</t>
+  </si>
+  <si>
+    <t>Will</t>
+  </si>
+  <si>
+    <t>Trossell</t>
+  </si>
+  <si>
+    <t>Dave</t>
+  </si>
+  <si>
+    <t>Williams</t>
+  </si>
+  <si>
+    <t>Palmer</t>
+  </si>
+  <si>
+    <t>Sanderson</t>
+  </si>
+  <si>
+    <t>Newman</t>
+  </si>
+  <si>
+    <t>Eddie</t>
+  </si>
+  <si>
+    <t>Marsh</t>
+  </si>
+  <si>
+    <t>Andy</t>
+  </si>
+  <si>
+    <t>Stuart-William</t>
+  </si>
+  <si>
+    <t>Longmuir</t>
+  </si>
+  <si>
+    <t>Jonny</t>
+  </si>
+  <si>
+    <t>Kirton</t>
+  </si>
+  <si>
+    <t>Jim</t>
+  </si>
+  <si>
+    <t>Crossley</t>
+  </si>
+  <si>
+    <t>Jack</t>
+  </si>
+  <si>
+    <t>Norman</t>
+  </si>
+  <si>
+    <t>Seb</t>
+  </si>
+  <si>
+    <t>Camaret</t>
+  </si>
+  <si>
+    <t>Hill</t>
+  </si>
+  <si>
+    <t>Twinn</t>
+  </si>
+  <si>
+    <t>Tim</t>
+  </si>
+  <si>
+    <t>Humphreys</t>
+  </si>
+  <si>
+    <t>Goodwin</t>
+  </si>
+  <si>
+    <t>Trevor</t>
+  </si>
+  <si>
+    <t>Whatford</t>
+  </si>
+  <si>
+    <t>Kiernan</t>
+  </si>
+  <si>
+    <t>Iain</t>
+  </si>
+  <si>
+    <t>Neary</t>
+  </si>
+  <si>
+    <t>martin</t>
+  </si>
+  <si>
+    <t>carter</t>
+  </si>
+  <si>
+    <t>Shane</t>
+  </si>
+  <si>
+    <t>Verrion</t>
+  </si>
+  <si>
+    <t>Bran</t>
+  </si>
+  <si>
+    <t>Allan</t>
+  </si>
+  <si>
+    <t>Cross</t>
+  </si>
+  <si>
+    <t>Jay</t>
+  </si>
+  <si>
+    <t>Miller</t>
+  </si>
+  <si>
+    <t>Penna</t>
+  </si>
+  <si>
+    <t>Davison</t>
+  </si>
+  <si>
+    <t>Mitchell</t>
+  </si>
+  <si>
+    <t>Vickers</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Motion 4871</t>
+  </si>
+  <si>
+    <t>Motion 871</t>
+  </si>
+  <si>
+    <t>Motion 4822</t>
+  </si>
+  <si>
+    <t>Motion 822</t>
+  </si>
+  <si>
+    <t>Motion 4935</t>
+  </si>
+  <si>
+    <t>Motion 935</t>
+  </si>
+  <si>
+    <t>Motion 665</t>
+  </si>
+  <si>
+    <t>Motion 662</t>
+  </si>
+  <si>
+    <t>Motion 4873</t>
+  </si>
+  <si>
+    <t>Motion 873</t>
+  </si>
+  <si>
+    <t>Motion 870</t>
+  </si>
+  <si>
+    <t>Motion 940</t>
+  </si>
+  <si>
+    <t>Motion 802</t>
+  </si>
+  <si>
+    <t>Motion 4978</t>
+  </si>
+  <si>
+    <t>Motion 978</t>
+  </si>
+  <si>
+    <t>Motion 1045</t>
+  </si>
+  <si>
+    <t>Motion 642</t>
+  </si>
+  <si>
+    <t>Motion 813</t>
+  </si>
+  <si>
+    <t>Motion 4805</t>
+  </si>
+  <si>
+    <t>Motion 805</t>
+  </si>
+  <si>
+    <t>Motion 632</t>
+  </si>
+  <si>
+    <t>Motion 855</t>
+  </si>
+  <si>
+    <t>Motion 824</t>
+  </si>
+  <si>
+    <t>Motion 4952</t>
+  </si>
+  <si>
+    <t>Motion 952</t>
+  </si>
+  <si>
+    <t>Motion 849</t>
+  </si>
+  <si>
+    <t>Motion 806</t>
+  </si>
+  <si>
+    <t>Motion 4807</t>
+  </si>
+  <si>
+    <t>Motion 807</t>
+  </si>
+  <si>
+    <t>Motion 4801</t>
+  </si>
+  <si>
+    <t>Motion 801</t>
+  </si>
+  <si>
+    <t>Motion 1043</t>
+  </si>
+  <si>
+    <t>Motion 4841</t>
+  </si>
+  <si>
+    <t>Motion 841</t>
+  </si>
+  <si>
+    <t>Motion 808</t>
+  </si>
+  <si>
+    <t>Motion 804</t>
+  </si>
+  <si>
+    <t>Motion 707</t>
+  </si>
+  <si>
+    <t>Motion 852</t>
+  </si>
+  <si>
+    <t>Motion 861</t>
+  </si>
+  <si>
+    <t>Motion 1039</t>
+  </si>
+  <si>
+    <t>Motion 845</t>
+  </si>
+  <si>
+    <t>Motion 4987</t>
+  </si>
+  <si>
+    <t>Motion 987</t>
+  </si>
+  <si>
+    <t>Motion 1037</t>
+  </si>
+  <si>
+    <t>Motion 4998</t>
+  </si>
+  <si>
+    <t>Motion 998</t>
+  </si>
+  <si>
+    <t>Motion 623</t>
+  </si>
+  <si>
+    <t>Motion 815</t>
+  </si>
+  <si>
+    <t>Motion 1033</t>
+  </si>
+  <si>
+    <t>Motion 838</t>
+  </si>
+  <si>
+    <t>Motion 819</t>
+  </si>
+  <si>
+    <t>Motion 853</t>
+  </si>
+  <si>
+    <t>Motion 814</t>
+  </si>
+  <si>
+    <t>Motion 643</t>
+  </si>
+  <si>
+    <t>Motion 846</t>
+  </si>
+  <si>
+    <t>Motion 4854</t>
+  </si>
+  <si>
+    <t>Motion 854</t>
+  </si>
+  <si>
+    <t>Motion 4641</t>
+  </si>
+  <si>
+    <t>Motion 1641</t>
+  </si>
+  <si>
+    <t>Motion 1020</t>
+  </si>
+  <si>
+    <t>Motion 858</t>
+  </si>
+  <si>
+    <t>Motion 869</t>
+  </si>
+  <si>
+    <t>Motion 618</t>
+  </si>
+  <si>
+    <t>Motion 827</t>
+  </si>
+  <si>
+    <t>Motion 639</t>
+  </si>
+  <si>
+    <t>Motion 611</t>
+  </si>
+  <si>
+    <t>Motion 826</t>
+  </si>
+  <si>
+    <t>Motion 4821</t>
+  </si>
+  <si>
+    <t>Motion 821</t>
+  </si>
+  <si>
+    <t>Motion 4812</t>
+  </si>
+  <si>
+    <t>Motion 812</t>
+  </si>
+  <si>
+    <t>Motion 829</t>
+  </si>
+  <si>
+    <t>Motion 5669</t>
+  </si>
+  <si>
+    <t>Motion 2669</t>
+  </si>
+  <si>
+    <t>Motion 920</t>
+  </si>
+  <si>
+    <t>Motion 631</t>
+  </si>
+  <si>
+    <t>Motion 4810</t>
+  </si>
+  <si>
+    <t>Motion 810</t>
+  </si>
+  <si>
+    <t>Motion 817</t>
+  </si>
+  <si>
+    <t>Motion 803</t>
+  </si>
+  <si>
+    <t>Motion 699</t>
+  </si>
+  <si>
+    <t>Motion 656</t>
+  </si>
+  <si>
+    <t>Motion 651</t>
+  </si>
+  <si>
+    <t>Motion 836</t>
+  </si>
+  <si>
+    <t>Motion 818</t>
+  </si>
+  <si>
+    <t>Motion 816</t>
+  </si>
+  <si>
+    <t>Motion 4942</t>
+  </si>
+  <si>
+    <t>Motion 942</t>
+  </si>
+  <si>
+    <t>Motion 701</t>
+  </si>
+  <si>
+    <t>Motion 718</t>
+  </si>
+  <si>
+    <t>Motion 4833</t>
+  </si>
+  <si>
+    <t>Motion 833</t>
+  </si>
+  <si>
+    <t>Motion 811</t>
+  </si>
+  <si>
+    <t>Motion 1002</t>
+  </si>
+  <si>
+    <t>Motion 647</t>
+  </si>
+  <si>
+    <t>Motion 1040</t>
+  </si>
+  <si>
+    <t>Motion 676</t>
+  </si>
+  <si>
+    <t>Motion 660</t>
+  </si>
+  <si>
+    <t>Motion 704</t>
+  </si>
+  <si>
+    <t>Motion 661</t>
+  </si>
+  <si>
+    <t>Motion 4866</t>
+  </si>
+  <si>
+    <t>Motion 866</t>
+  </si>
+  <si>
+    <t>Motion 825</t>
+  </si>
+  <si>
+    <t>Motion 633</t>
+  </si>
+  <si>
+    <t>Motion 4695</t>
+  </si>
+  <si>
+    <t>Motion 2695</t>
+  </si>
+  <si>
+    <t>Motion 823</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -519,29 +856,14 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.35"/>
+      <color theme="0" tint="-0.34998626667073579"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -549,9 +871,9 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
-      <color theme="0" tint="-0.35"/>
+      <color theme="0" tint="-0.34998626667073579"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
@@ -566,13 +888,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999"/>
+        <fgColor theme="5" tint="0.79989013336588644"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.7999"/>
+        <fgColor theme="6" tint="0.79989013336588644"/>
         <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
@@ -584,7 +906,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.3999"/>
+        <fgColor theme="5" tint="0.39988402966399123"/>
         <bgColor rgb="FFFF99CC"/>
       </patternFill>
     </fill>
@@ -596,7 +918,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -604,158 +926,51 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFA6A6A6"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFBE3D6"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2AA84"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC2F1C8"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -814,64 +1029,76 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0e2841"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e8e8e8"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="e97132"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196b24"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0f9ed5"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="a02b93"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4ea72e"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607d"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -903,7 +1130,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -927,7 +1154,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -987,37 +1214,36 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U86"/>
-  <sheetFormatPr defaultColWidth="8.6015625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="2" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="3" width="11.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="3" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="3" width="17.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="4" width="13.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="4" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="19" style="4" width="13.29"/>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="5" max="7" width="9.140625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="13" max="14" width="11.140625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="13.28515625" style="4" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" style="4" customWidth="1"/>
+    <col min="19" max="21" width="13.28515625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1082,17 +1308,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>13</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="0" t="s">
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -1104,49 +1330,49 @@
       <c r="J2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="3" t="n">
-        <f aca="false">COUNTA(H2:L2)</f>
+      <c r="N2" s="3">
+        <f t="shared" ref="N2:N33" si="0">COUNTA(H2:L2)</f>
         <v>2</v>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="O2" s="3">
         <v>871</v>
       </c>
       <c r="P2" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D2,3),O2,LEFT(C2,3)))</f>
+        <f t="shared" ref="P2:P9" si="1">UPPER(_xlfn.CONCAT(LEFT(D2,3),O2,LEFT(C2,3)))</f>
         <v>GEO871MIC</v>
       </c>
       <c r="Q2" s="4" t="str">
-        <f aca="false">IF(H2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"5",""),$O2), "")</f>
+        <f t="shared" ref="Q2:Q33" si="2">IF(H2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"5",""),$O2), "")</f>
         <v/>
       </c>
       <c r="R2" s="4" t="str">
-        <f aca="false">IF(I2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"4",""),$O2), "")</f>
+        <f t="shared" ref="R2:R33" si="3">IF(I2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"4",""),$O2), "")</f>
         <v>Motion 4871</v>
       </c>
       <c r="S2" s="4" t="str">
-        <f aca="false">IF(J2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N2&gt;1,$I2=""),"4",""),$O2), "")</f>
+        <f t="shared" ref="S2:S33" si="4">IF(J2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N2&gt;1,$I2=""),"4",""),$O2), "")</f>
         <v>Motion 871</v>
       </c>
       <c r="T2" s="4" t="str">
-        <f aca="false">IF(K2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"2",""),$O2), "")</f>
+        <f t="shared" ref="T2:T33" si="5">IF(K2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"2",""),$O2), "")</f>
         <v/>
       </c>
       <c r="U2" s="4" t="str">
-        <f aca="false">IF(L2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"1",""),$O2), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+        <f t="shared" ref="U2:U33" si="6">IF(L2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"1",""),$O2), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>14</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="0" t="s">
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" t="s">
         <v>23</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -1160,52 +1386,52 @@
         <v>21</v>
       </c>
       <c r="M3" s="3" t="str">
-        <f aca="false">IF(A3-A2&lt;&gt;1,A3-A2,"")</f>
-        <v/>
-      </c>
-      <c r="N3" s="3" t="n">
-        <f aca="false">COUNTA(H3:L3)</f>
+        <f t="shared" ref="M3:M34" si="7">IF(A3-A2&lt;&gt;1,A3-A2,"")</f>
+        <v/>
+      </c>
+      <c r="N3" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="O3" s="3">
         <v>822</v>
       </c>
       <c r="P3" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D3,3),O3,LEFT(C3,3)))</f>
+        <f t="shared" si="1"/>
         <v>PET822SIM</v>
       </c>
       <c r="Q3" s="4" t="str">
-        <f aca="false">IF(H3&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N3&gt;1,"5",""),$O3), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R3" s="4" t="str">
-        <f aca="false">IF(I3&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N3&gt;1,"4",""),$O3), "")</f>
+        <f t="shared" si="3"/>
         <v>Motion 4822</v>
       </c>
       <c r="S3" s="4" t="str">
-        <f aca="false">IF(J3&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N3&gt;1,$I3=""),"4",""),$O3), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 822</v>
       </c>
       <c r="T3" s="4" t="str">
-        <f aca="false">IF(K3&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N3&gt;1,"2",""),$O3), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U3" s="4" t="str">
-        <f aca="false">IF(L3&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N3&gt;1,"1",""),$O3), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>15</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -1219,156 +1445,156 @@
         <v>21</v>
       </c>
       <c r="M4" s="3" t="str">
-        <f aca="false">IF(A4-A3&lt;&gt;1,A4-A3,"")</f>
-        <v/>
-      </c>
-      <c r="N4" s="3" t="n">
-        <f aca="false">COUNTA(H4:L4)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N4" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="O4" s="3" t="n">
+      <c r="O4" s="3">
         <v>935</v>
       </c>
       <c r="P4" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D4,3),O4,LEFT(C4,3)))</f>
+        <f t="shared" si="1"/>
         <v>GIB935JEN</v>
       </c>
       <c r="Q4" s="4" t="str">
-        <f aca="false">IF(H4&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N4&gt;1,"5",""),$O4), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R4" s="4" t="str">
-        <f aca="false">IF(I4&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N4&gt;1,"4",""),$O4), "")</f>
+        <f t="shared" si="3"/>
         <v>Motion 4935</v>
       </c>
       <c r="S4" s="4" t="str">
-        <f aca="false">IF(J4&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N4&gt;1,$I4=""),"4",""),$O4), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 935</v>
       </c>
       <c r="T4" s="4" t="str">
-        <f aca="false">IF(K4&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N4&gt;1,"2",""),$O4), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U4" s="4" t="str">
-        <f aca="false">IF(L4&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N4&gt;1,"1",""),$O4), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
-        <v>16</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="0" t="s">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>28</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="M5" s="3" t="str">
-        <f aca="false">IF(A5-A4&lt;&gt;1,A5-A4,"")</f>
-        <v/>
-      </c>
-      <c r="N5" s="3" t="n">
-        <f aca="false">COUNTA(H5:L5)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N5" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O5" s="3" t="n">
+      <c r="O5" s="3">
         <v>665</v>
       </c>
       <c r="P5" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D5,3),O5,LEFT(C5,3)))</f>
+        <f t="shared" si="1"/>
         <v>VAS665STA</v>
       </c>
       <c r="Q5" s="4" t="str">
-        <f aca="false">IF(H5&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N5&gt;1,"5",""),$O5), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R5" s="4" t="str">
-        <f aca="false">IF(I5&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N5&gt;1,"4",""),$O5), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S5" s="4" t="str">
-        <f aca="false">IF(J5&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N5&gt;1,$I5=""),"4",""),$O5), "")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T5" s="4" t="str">
-        <f aca="false">IF(K5&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N5&gt;1,"2",""),$O5), "")</f>
+        <f t="shared" si="5"/>
         <v>Motion 665</v>
       </c>
       <c r="U5" s="4" t="str">
-        <f aca="false">IF(L5&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N5&gt;1,"1",""),$O5), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6">
         <v>17</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" t="s">
         <v>32</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="M6" s="3" t="str">
-        <f aca="false">IF(A6-A5&lt;&gt;1,A6-A5,"")</f>
-        <v/>
-      </c>
-      <c r="N6" s="3" t="n">
-        <f aca="false">COUNTA(H6:L6)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N6" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="O6" s="3">
         <v>662</v>
       </c>
       <c r="P6" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D6,3),O6,LEFT(C6,3)))</f>
+        <f t="shared" si="1"/>
         <v>EIF662AYA</v>
       </c>
       <c r="Q6" s="4" t="str">
-        <f aca="false">IF(H6&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N6&gt;1,"5",""),$O6), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R6" s="4" t="str">
-        <f aca="false">IF(I6&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N6&gt;1,"4",""),$O6), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S6" s="4" t="str">
-        <f aca="false">IF(J6&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N6&gt;1,$I6=""),"4",""),$O6), "")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T6" s="4" t="str">
-        <f aca="false">IF(K6&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N6&gt;1,"2",""),$O6), "")</f>
+        <f t="shared" si="5"/>
         <v>Motion 662</v>
       </c>
       <c r="U6" s="4" t="str">
-        <f aca="false">IF(L6&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N6&gt;1,"1",""),$O6), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7">
         <v>18</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="0" t="s">
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -1384,52 +1610,52 @@
         <v>21</v>
       </c>
       <c r="M7" s="3" t="str">
-        <f aca="false">IF(A7-A6&lt;&gt;1,A7-A6,"")</f>
-        <v/>
-      </c>
-      <c r="N7" s="3" t="n">
-        <f aca="false">COUNTA(H7:L7)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N7" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="O7" s="3" t="n">
+      <c r="O7" s="3">
         <v>873</v>
       </c>
       <c r="P7" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D7,3),O7,LEFT(C7,3)))</f>
+        <f t="shared" si="1"/>
         <v>CHI873DYL</v>
       </c>
       <c r="Q7" s="4" t="str">
-        <f aca="false">IF(H7&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N7&gt;1,"5",""),$O7), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R7" s="4" t="str">
-        <f aca="false">IF(I7&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N7&gt;1,"4",""),$O7), "")</f>
+        <f t="shared" si="3"/>
         <v>Motion 4873</v>
       </c>
       <c r="S7" s="4" t="str">
-        <f aca="false">IF(J7&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N7&gt;1,$I7=""),"4",""),$O7), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 873</v>
       </c>
       <c r="T7" s="4" t="str">
-        <f aca="false">IF(K7&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N7&gt;1,"2",""),$O7), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U7" s="4" t="str">
-        <f aca="false">IF(L7&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N7&gt;1,"1",""),$O7), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>19</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="0" t="s">
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" t="s">
         <v>37</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -1439,110 +1665,110 @@
         <v>21</v>
       </c>
       <c r="M8" s="3" t="str">
-        <f aca="false">IF(A8-A7&lt;&gt;1,A8-A7,"")</f>
-        <v/>
-      </c>
-      <c r="N8" s="3" t="n">
-        <f aca="false">COUNTA(H8:L8)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N8" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="O8" s="3">
         <v>870</v>
       </c>
       <c r="P8" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D8,3),O8,LEFT(C8,3)))</f>
+        <f t="shared" si="1"/>
         <v>HEN870RIC</v>
       </c>
       <c r="Q8" s="4" t="str">
-        <f aca="false">IF(H8&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N8&gt;1,"5",""),$O8), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R8" s="4" t="str">
-        <f aca="false">IF(I8&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N8&gt;1,"4",""),$O8), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S8" s="4" t="str">
-        <f aca="false">IF(J8&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N8&gt;1,$I8=""),"4",""),$O8), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 870</v>
       </c>
       <c r="T8" s="4" t="str">
-        <f aca="false">IF(K8&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N8&gt;1,"2",""),$O8), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U8" s="4" t="str">
-        <f aca="false">IF(L8&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N8&gt;1,"1",""),$O8), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>20</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="0" t="s">
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" t="s">
         <v>39</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="10">
         <v>940</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>40</v>
       </c>
       <c r="M9" s="3" t="str">
-        <f aca="false">IF(A9-A8&lt;&gt;1,A9-A8,"")</f>
-        <v/>
-      </c>
-      <c r="N9" s="3" t="n">
-        <f aca="false">COUNTA(H9:L9)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N9" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O9" s="11" t="n">
+      <c r="O9" s="11">
         <v>940</v>
       </c>
       <c r="P9" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D9,3),O9,LEFT(C9,3)))</f>
+        <f t="shared" si="1"/>
         <v>DIC940ROD</v>
       </c>
       <c r="Q9" s="4" t="str">
-        <f aca="false">IF(H9&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N9&gt;1,"5",""),$O9), "")</f>
+        <f t="shared" si="2"/>
         <v>Motion 940</v>
       </c>
       <c r="R9" s="4" t="str">
-        <f aca="false">IF(I9&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N9&gt;1,"4",""),$O9), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S9" s="4" t="str">
-        <f aca="false">IF(J9&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N9&gt;1,$I9=""),"4",""),$O9), "")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T9" s="4" t="str">
-        <f aca="false">IF(K9&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N9&gt;1,"2",""),$O9), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U9" s="4" t="str">
-        <f aca="false">IF(L9&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N9&gt;1,"1",""),$O9), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>21</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="0" t="s">
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" t="s">
         <v>42</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -1552,52 +1778,52 @@
         <v>21</v>
       </c>
       <c r="M10" s="3" t="str">
-        <f aca="false">IF(A10-A9&lt;&gt;1,A10-A9,"")</f>
-        <v/>
-      </c>
-      <c r="N10" s="3" t="n">
-        <f aca="false">COUNTA(H10:L10)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N10" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O10" s="3" t="n">
+      <c r="O10" s="3">
         <v>802</v>
       </c>
       <c r="P10" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT("BRU",O10,LEFT(C10,3)))</f>
+        <f>UPPER(_xlfn.CONCAT("BRU",O10,LEFT(C10,3)))</f>
         <v>BRU802JEA</v>
       </c>
       <c r="Q10" s="4" t="str">
-        <f aca="false">IF(H10&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N10&gt;1,"5",""),$O10), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R10" s="4" t="str">
-        <f aca="false">IF(I10&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N10&gt;1,"4",""),$O10), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S10" s="4" t="str">
-        <f aca="false">IF(J10&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N10&gt;1,$I10=""),"4",""),$O10), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 802</v>
       </c>
       <c r="T10" s="4" t="str">
-        <f aca="false">IF(K10&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N10&gt;1,"2",""),$O10), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U10" s="4" t="str">
-        <f aca="false">IF(L10&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N10&gt;1,"1",""),$O10), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>22</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="0" t="s">
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" t="s">
         <v>43</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -1610,52 +1836,52 @@
         <v>21</v>
       </c>
       <c r="M11" s="3" t="str">
-        <f aca="false">IF(A11-A10&lt;&gt;1,A11-A10,"")</f>
-        <v/>
-      </c>
-      <c r="N11" s="3" t="n">
-        <f aca="false">COUNTA(H11:L11)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N11" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="O11" s="3" t="n">
+      <c r="O11" s="3">
         <v>978</v>
       </c>
       <c r="P11" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D11,3),O11,LEFT(C11,3)))</f>
+        <f t="shared" ref="P11:P42" si="8">UPPER(_xlfn.CONCAT(LEFT(D11,3),O11,LEFT(C11,3)))</f>
         <v>DUD978RIC</v>
       </c>
       <c r="Q11" s="4" t="str">
-        <f aca="false">IF(H11&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N11&gt;1,"5",""),$O11), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R11" s="4" t="str">
-        <f aca="false">IF(I11&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N11&gt;1,"4",""),$O11), "")</f>
+        <f t="shared" si="3"/>
         <v>Motion 4978</v>
       </c>
       <c r="S11" s="4" t="str">
-        <f aca="false">IF(J11&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N11&gt;1,$I11=""),"4",""),$O11), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 978</v>
       </c>
       <c r="T11" s="4" t="str">
-        <f aca="false">IF(K11&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N11&gt;1,"2",""),$O11), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U11" s="4" t="str">
-        <f aca="false">IF(L11&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N11&gt;1,"1",""),$O11), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>23</v>
       </c>
-      <c r="B12" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="0" t="s">
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" t="s">
         <v>45</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -1665,52 +1891,52 @@
         <v>21</v>
       </c>
       <c r="M12" s="3" t="str">
-        <f aca="false">IF(A12-A11&lt;&gt;1,A12-A11,"")</f>
-        <v/>
-      </c>
-      <c r="N12" s="3" t="n">
-        <f aca="false">COUNTA(H12:L12)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N12" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O12" s="3" t="n">
+      <c r="O12" s="3">
         <v>1045</v>
       </c>
       <c r="P12" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D12,3),O12,LEFT(C12,3)))</f>
+        <f t="shared" si="8"/>
         <v>MEY1045BEN</v>
       </c>
       <c r="Q12" s="4" t="str">
-        <f aca="false">IF(H12&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N12&gt;1,"5",""),$O12), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R12" s="4" t="str">
-        <f aca="false">IF(I12&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N12&gt;1,"4",""),$O12), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S12" s="4" t="str">
-        <f aca="false">IF(J12&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N12&gt;1,$I12=""),"4",""),$O12), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 1045</v>
       </c>
       <c r="T12" s="4" t="str">
-        <f aca="false">IF(K12&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N12&gt;1,"2",""),$O12), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U12" s="4" t="str">
-        <f aca="false">IF(L12&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N12&gt;1,"1",""),$O12), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13">
         <v>24</v>
       </c>
-      <c r="B13" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="0" t="s">
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" t="s">
         <v>47</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -1720,52 +1946,52 @@
         <v>40</v>
       </c>
       <c r="M13" s="3" t="str">
-        <f aca="false">IF(A13-A12&lt;&gt;1,A13-A12,"")</f>
-        <v/>
-      </c>
-      <c r="N13" s="3" t="n">
-        <f aca="false">COUNTA(H13:L13)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N13" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O13" s="3" t="n">
+      <c r="O13" s="3">
         <v>642</v>
       </c>
       <c r="P13" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D13,3),O13,LEFT(C13,3)))</f>
+        <f t="shared" si="8"/>
         <v>MIL642JEZ</v>
       </c>
       <c r="Q13" s="4" t="str">
-        <f aca="false">IF(H13&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N13&gt;1,"5",""),$O13), "")</f>
+        <f t="shared" si="2"/>
         <v>Motion 642</v>
       </c>
       <c r="R13" s="4" t="str">
-        <f aca="false">IF(I13&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N13&gt;1,"4",""),$O13), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S13" s="4" t="str">
-        <f aca="false">IF(J13&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N13&gt;1,$I13=""),"4",""),$O13), "")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T13" s="4" t="str">
-        <f aca="false">IF(K13&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N13&gt;1,"2",""),$O13), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U13" s="4" t="str">
-        <f aca="false">IF(L13&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N13&gt;1,"1",""),$O13), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14">
         <v>25</v>
       </c>
-      <c r="B14" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="0" t="s">
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" t="s">
         <v>49</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -1775,52 +2001,52 @@
         <v>21</v>
       </c>
       <c r="M14" s="3" t="str">
-        <f aca="false">IF(A14-A13&lt;&gt;1,A14-A13,"")</f>
-        <v/>
-      </c>
-      <c r="N14" s="3" t="n">
-        <f aca="false">COUNTA(H14:L14)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N14" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O14" s="3" t="n">
+      <c r="O14" s="3">
         <v>813</v>
       </c>
       <c r="P14" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D14,3),O14,LEFT(C14,3)))</f>
+        <f t="shared" si="8"/>
         <v>REE813MAR</v>
       </c>
       <c r="Q14" s="4" t="str">
-        <f aca="false">IF(H14&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N14&gt;1,"5",""),$O14), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R14" s="4" t="str">
-        <f aca="false">IF(I14&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N14&gt;1,"4",""),$O14), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S14" s="4" t="str">
-        <f aca="false">IF(J14&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N14&gt;1,$I14=""),"4",""),$O14), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 813</v>
       </c>
       <c r="T14" s="4" t="str">
-        <f aca="false">IF(K14&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N14&gt;1,"2",""),$O14), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U14" s="4" t="str">
-        <f aca="false">IF(L14&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N14&gt;1,"1",""),$O14), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15">
         <v>26</v>
       </c>
-      <c r="B15" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="0" t="s">
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" t="s">
         <v>51</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -1833,52 +2059,52 @@
         <v>21</v>
       </c>
       <c r="M15" s="3" t="str">
-        <f aca="false">IF(A15-A14&lt;&gt;1,A15-A14,"")</f>
-        <v/>
-      </c>
-      <c r="N15" s="3" t="n">
-        <f aca="false">COUNTA(H15:L15)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N15" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="O15" s="3" t="n">
+      <c r="O15" s="3">
         <v>805</v>
       </c>
       <c r="P15" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D15,3),O15,LEFT(C15,3)))</f>
+        <f t="shared" si="8"/>
         <v>LON805ROB</v>
       </c>
       <c r="Q15" s="4" t="str">
-        <f aca="false">IF(H15&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N15&gt;1,"5",""),$O15), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R15" s="4" t="str">
-        <f aca="false">IF(I15&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N15&gt;1,"4",""),$O15), "")</f>
+        <f t="shared" si="3"/>
         <v>Motion 4805</v>
       </c>
       <c r="S15" s="4" t="str">
-        <f aca="false">IF(J15&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N15&gt;1,$I15=""),"4",""),$O15), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 805</v>
       </c>
       <c r="T15" s="4" t="str">
-        <f aca="false">IF(K15&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N15&gt;1,"2",""),$O15), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U15" s="4" t="str">
-        <f aca="false">IF(L15&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N15&gt;1,"1",""),$O15), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>27</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" t="s">
         <v>54</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -1888,52 +2114,52 @@
         <v>40</v>
       </c>
       <c r="M16" s="3" t="str">
-        <f aca="false">IF(A16-A15&lt;&gt;1,A16-A15,"")</f>
-        <v/>
-      </c>
-      <c r="N16" s="3" t="n">
-        <f aca="false">COUNTA(H16:L16)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N16" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O16" s="3" t="n">
+      <c r="O16" s="3">
         <v>632</v>
       </c>
       <c r="P16" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D16,3),O16,LEFT(C16,3)))</f>
+        <f t="shared" si="8"/>
         <v>ROG632KAT</v>
       </c>
       <c r="Q16" s="4" t="str">
-        <f aca="false">IF(H16&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N16&gt;1,"5",""),$O16), "")</f>
+        <f t="shared" si="2"/>
         <v>Motion 632</v>
       </c>
       <c r="R16" s="4" t="str">
-        <f aca="false">IF(I16&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N16&gt;1,"4",""),$O16), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S16" s="4" t="str">
-        <f aca="false">IF(J16&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N16&gt;1,$I16=""),"4",""),$O16), "")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T16" s="4" t="str">
-        <f aca="false">IF(K16&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N16&gt;1,"2",""),$O16), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U16" s="4" t="str">
-        <f aca="false">IF(L16&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N16&gt;1,"1",""),$O16), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>28</v>
       </c>
-      <c r="B17" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="0" t="s">
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" t="s">
         <v>56</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -1943,52 +2169,52 @@
         <v>21</v>
       </c>
       <c r="M17" s="3" t="str">
-        <f aca="false">IF(A17-A16&lt;&gt;1,A17-A16,"")</f>
-        <v/>
-      </c>
-      <c r="N17" s="3" t="n">
-        <f aca="false">COUNTA(H17:L17)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N17" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O17" s="3" t="n">
+      <c r="O17" s="3">
         <v>855</v>
       </c>
       <c r="P17" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D17,3),O17,LEFT(C17,3)))</f>
+        <f t="shared" si="8"/>
         <v>SMI855BAR</v>
       </c>
       <c r="Q17" s="4" t="str">
-        <f aca="false">IF(H17&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N17&gt;1,"5",""),$O17), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R17" s="4" t="str">
-        <f aca="false">IF(I17&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N17&gt;1,"4",""),$O17), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S17" s="4" t="str">
-        <f aca="false">IF(J17&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N17&gt;1,$I17=""),"4",""),$O17), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 855</v>
       </c>
       <c r="T17" s="4" t="str">
-        <f aca="false">IF(K17&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N17&gt;1,"2",""),$O17), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U17" s="4" t="str">
-        <f aca="false">IF(L17&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N17&gt;1,"1",""),$O17), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18">
         <v>29</v>
       </c>
-      <c r="B18" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="0" t="s">
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" t="s">
         <v>57</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -1998,52 +2224,52 @@
         <v>21</v>
       </c>
       <c r="M18" s="3" t="str">
-        <f aca="false">IF(A18-A17&lt;&gt;1,A18-A17,"")</f>
-        <v/>
-      </c>
-      <c r="N18" s="3" t="n">
-        <f aca="false">COUNTA(H18:L18)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N18" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O18" s="3" t="n">
+      <c r="O18" s="3">
         <v>824</v>
       </c>
       <c r="P18" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D18,3),O18,LEFT(C18,3)))</f>
+        <f t="shared" si="8"/>
         <v>CRO824RIC</v>
       </c>
       <c r="Q18" s="4" t="str">
-        <f aca="false">IF(H18&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N18&gt;1,"5",""),$O18), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R18" s="4" t="str">
-        <f aca="false">IF(I18&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N18&gt;1,"4",""),$O18), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S18" s="4" t="str">
-        <f aca="false">IF(J18&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N18&gt;1,$I18=""),"4",""),$O18), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 824</v>
       </c>
       <c r="T18" s="4" t="str">
-        <f aca="false">IF(K18&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N18&gt;1,"2",""),$O18), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U18" s="4" t="str">
-        <f aca="false">IF(L18&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N18&gt;1,"1",""),$O18), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19">
         <v>30</v>
       </c>
-      <c r="B19" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="0" t="s">
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" t="s">
         <v>57</v>
       </c>
       <c r="F19" s="1" t="s">
@@ -2056,52 +2282,52 @@
         <v>21</v>
       </c>
       <c r="M19" s="3" t="str">
-        <f aca="false">IF(A19-A18&lt;&gt;1,A19-A18,"")</f>
-        <v/>
-      </c>
-      <c r="N19" s="3" t="n">
-        <f aca="false">COUNTA(H19:L19)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N19" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="O19" s="3" t="n">
+      <c r="O19" s="3">
         <v>952</v>
       </c>
       <c r="P19" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D19,3),O19,LEFT(C19,3)))</f>
+        <f t="shared" si="8"/>
         <v>CRO952PET</v>
       </c>
       <c r="Q19" s="4" t="str">
-        <f aca="false">IF(H19&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N19&gt;1,"5",""),$O19), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R19" s="4" t="str">
-        <f aca="false">IF(I19&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N19&gt;1,"4",""),$O19), "")</f>
+        <f t="shared" si="3"/>
         <v>Motion 4952</v>
       </c>
       <c r="S19" s="4" t="str">
-        <f aca="false">IF(J19&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N19&gt;1,$I19=""),"4",""),$O19), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 952</v>
       </c>
       <c r="T19" s="4" t="str">
-        <f aca="false">IF(K19&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N19&gt;1,"2",""),$O19), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U19" s="4" t="str">
-        <f aca="false">IF(L19&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N19&gt;1,"1",""),$O19), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20">
         <v>31</v>
       </c>
-      <c r="B20" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="0" t="s">
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" t="s">
         <v>59</v>
       </c>
       <c r="F20" s="1" t="s">
@@ -2111,52 +2337,52 @@
         <v>21</v>
       </c>
       <c r="M20" s="3" t="str">
-        <f aca="false">IF(A20-A19&lt;&gt;1,A20-A19,"")</f>
-        <v/>
-      </c>
-      <c r="N20" s="3" t="n">
-        <f aca="false">COUNTA(H20:L20)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N20" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O20" s="3" t="n">
+      <c r="O20" s="3">
         <v>849</v>
       </c>
       <c r="P20" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D20,3),O20,LEFT(C20,3)))</f>
+        <f t="shared" si="8"/>
         <v>BAR849SIM</v>
       </c>
       <c r="Q20" s="4" t="str">
-        <f aca="false">IF(H20&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N20&gt;1,"5",""),$O20), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R20" s="4" t="str">
-        <f aca="false">IF(I20&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N20&gt;1,"4",""),$O20), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S20" s="4" t="str">
-        <f aca="false">IF(J20&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N20&gt;1,$I20=""),"4",""),$O20), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 849</v>
       </c>
       <c r="T20" s="4" t="str">
-        <f aca="false">IF(K20&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N20&gt;1,"2",""),$O20), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U20" s="4" t="str">
-        <f aca="false">IF(L20&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N20&gt;1,"1",""),$O20), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21">
         <v>32</v>
       </c>
-      <c r="B21" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="0" t="s">
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" t="s">
         <v>61</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -2166,52 +2392,52 @@
         <v>21</v>
       </c>
       <c r="M21" s="3" t="str">
-        <f aca="false">IF(A21-A20&lt;&gt;1,A21-A20,"")</f>
-        <v/>
-      </c>
-      <c r="N21" s="3" t="n">
-        <f aca="false">COUNTA(H21:L21)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N21" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O21" s="3" t="n">
+      <c r="O21" s="3">
         <v>806</v>
       </c>
       <c r="P21" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D21,3),O21,LEFT(C21,3)))</f>
+        <f t="shared" si="8"/>
         <v>MAY806SCO</v>
       </c>
       <c r="Q21" s="4" t="str">
-        <f aca="false">IF(H21&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N21&gt;1,"5",""),$O21), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R21" s="4" t="str">
-        <f aca="false">IF(I21&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N21&gt;1,"4",""),$O21), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S21" s="4" t="str">
-        <f aca="false">IF(J21&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N21&gt;1,$I21=""),"4",""),$O21), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 806</v>
       </c>
       <c r="T21" s="4" t="str">
-        <f aca="false">IF(K21&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N21&gt;1,"2",""),$O21), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U21" s="4" t="str">
-        <f aca="false">IF(L21&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N21&gt;1,"1",""),$O21), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>33</v>
       </c>
-      <c r="B22" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="0" t="s">
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" t="s">
         <v>63</v>
       </c>
       <c r="F22" s="1" t="s">
@@ -2224,52 +2450,52 @@
         <v>21</v>
       </c>
       <c r="M22" s="3" t="str">
-        <f aca="false">IF(A22-A21&lt;&gt;1,A22-A21,"")</f>
-        <v/>
-      </c>
-      <c r="N22" s="3" t="n">
-        <f aca="false">COUNTA(H22:L22)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N22" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="O22" s="3" t="n">
+      <c r="O22" s="3">
         <v>807</v>
       </c>
       <c r="P22" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D22,3),O22,LEFT(C22,3)))</f>
+        <f t="shared" si="8"/>
         <v>ILI807NIK</v>
       </c>
       <c r="Q22" s="4" t="str">
-        <f aca="false">IF(H22&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N22&gt;1,"5",""),$O22), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R22" s="4" t="str">
-        <f aca="false">IF(I22&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N22&gt;1,"4",""),$O22), "")</f>
+        <f t="shared" si="3"/>
         <v>Motion 4807</v>
       </c>
       <c r="S22" s="4" t="str">
-        <f aca="false">IF(J22&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N22&gt;1,$I22=""),"4",""),$O22), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 807</v>
       </c>
       <c r="T22" s="4" t="str">
-        <f aca="false">IF(K22&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N22&gt;1,"2",""),$O22), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U22" s="4" t="str">
-        <f aca="false">IF(L22&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N22&gt;1,"1",""),$O22), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23">
         <v>34</v>
       </c>
-      <c r="B23" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="0" t="s">
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" t="s">
         <v>64</v>
       </c>
       <c r="F23" s="1" t="s">
@@ -2282,52 +2508,52 @@
         <v>21</v>
       </c>
       <c r="M23" s="3" t="str">
-        <f aca="false">IF(A23-A22&lt;&gt;1,A23-A22,"")</f>
-        <v/>
-      </c>
-      <c r="N23" s="3" t="n">
-        <f aca="false">COUNTA(H23:L23)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N23" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="O23" s="3" t="n">
+      <c r="O23" s="3">
         <v>801</v>
       </c>
       <c r="P23" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D23,3),O23,LEFT(C23,3)))</f>
+        <f t="shared" si="8"/>
         <v>ING801MAR</v>
       </c>
       <c r="Q23" s="4" t="str">
-        <f aca="false">IF(H23&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N23&gt;1,"5",""),$O23), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R23" s="4" t="str">
-        <f aca="false">IF(I23&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N23&gt;1,"4",""),$O23), "")</f>
+        <f t="shared" si="3"/>
         <v>Motion 4801</v>
       </c>
       <c r="S23" s="4" t="str">
-        <f aca="false">IF(J23&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N23&gt;1,$I23=""),"4",""),$O23), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 801</v>
       </c>
       <c r="T23" s="4" t="str">
-        <f aca="false">IF(K23&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N23&gt;1,"2",""),$O23), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U23" s="4" t="str">
-        <f aca="false">IF(L23&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N23&gt;1,"1",""),$O23), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24">
         <v>35</v>
       </c>
-      <c r="B24" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="0" t="s">
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" t="s">
         <v>64</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -2337,52 +2563,52 @@
         <v>21</v>
       </c>
       <c r="M24" s="3" t="str">
-        <f aca="false">IF(A24-A23&lt;&gt;1,A24-A23,"")</f>
-        <v/>
-      </c>
-      <c r="N24" s="3" t="n">
-        <f aca="false">COUNTA(H24:L24)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N24" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O24" s="3" t="n">
+      <c r="O24" s="3">
         <v>1043</v>
       </c>
       <c r="P24" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D24,3),O24,LEFT(C24,3)))</f>
+        <f t="shared" si="8"/>
         <v>ING1043JON</v>
       </c>
       <c r="Q24" s="4" t="str">
-        <f aca="false">IF(H24&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N24&gt;1,"5",""),$O24), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R24" s="4" t="str">
-        <f aca="false">IF(I24&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N24&gt;1,"4",""),$O24), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S24" s="4" t="str">
-        <f aca="false">IF(J24&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N24&gt;1,$I24=""),"4",""),$O24), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 1043</v>
       </c>
       <c r="T24" s="4" t="str">
-        <f aca="false">IF(K24&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N24&gt;1,"2",""),$O24), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U24" s="4" t="str">
-        <f aca="false">IF(L24&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N24&gt;1,"1",""),$O24), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25">
         <v>36</v>
       </c>
-      <c r="B25" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="0" t="s">
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" t="s">
         <v>66</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -2395,52 +2621,52 @@
         <v>21</v>
       </c>
       <c r="M25" s="3" t="str">
-        <f aca="false">IF(A25-A24&lt;&gt;1,A25-A24,"")</f>
-        <v/>
-      </c>
-      <c r="N25" s="3" t="n">
-        <f aca="false">COUNTA(H25:L25)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N25" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="O25" s="3" t="n">
+      <c r="O25" s="3">
         <v>841</v>
       </c>
       <c r="P25" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D25,3),O25,LEFT(C25,3)))</f>
+        <f t="shared" si="8"/>
         <v>SAL841MAR</v>
       </c>
       <c r="Q25" s="4" t="str">
-        <f aca="false">IF(H25&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N25&gt;1,"5",""),$O25), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R25" s="4" t="str">
-        <f aca="false">IF(I25&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N25&gt;1,"4",""),$O25), "")</f>
+        <f t="shared" si="3"/>
         <v>Motion 4841</v>
       </c>
       <c r="S25" s="4" t="str">
-        <f aca="false">IF(J25&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N25&gt;1,$I25=""),"4",""),$O25), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 841</v>
       </c>
       <c r="T25" s="4" t="str">
-        <f aca="false">IF(K25&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N25&gt;1,"2",""),$O25), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U25" s="4" t="str">
-        <f aca="false">IF(L25&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N25&gt;1,"1",""),$O25), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>37</v>
       </c>
-      <c r="B26" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" s="0" t="s">
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" t="s">
         <v>68</v>
       </c>
       <c r="F26" s="1" t="s">
@@ -2450,52 +2676,52 @@
         <v>21</v>
       </c>
       <c r="M26" s="3" t="str">
-        <f aca="false">IF(A26-A25&lt;&gt;1,A26-A25,"")</f>
-        <v/>
-      </c>
-      <c r="N26" s="3" t="n">
-        <f aca="false">COUNTA(H26:L26)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N26" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O26" s="3" t="n">
+      <c r="O26" s="3">
         <v>808</v>
       </c>
       <c r="P26" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D26,3),O26,LEFT(C26,3)))</f>
+        <f t="shared" si="8"/>
         <v>OWE808AND</v>
       </c>
       <c r="Q26" s="4" t="str">
-        <f aca="false">IF(H26&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N26&gt;1,"5",""),$O26), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R26" s="4" t="str">
-        <f aca="false">IF(I26&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N26&gt;1,"4",""),$O26), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S26" s="4" t="str">
-        <f aca="false">IF(J26&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N26&gt;1,$I26=""),"4",""),$O26), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 808</v>
       </c>
       <c r="T26" s="4" t="str">
-        <f aca="false">IF(K26&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N26&gt;1,"2",""),$O26), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U26" s="4" t="str">
-        <f aca="false">IF(L26&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N26&gt;1,"1",""),$O26), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27">
         <v>38</v>
       </c>
-      <c r="B27" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="0" t="s">
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" t="s">
         <v>70</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -2505,111 +2731,111 @@
         <v>21</v>
       </c>
       <c r="M27" s="3" t="str">
-        <f aca="false">IF(A27-A26&lt;&gt;1,A27-A26,"")</f>
-        <v/>
-      </c>
-      <c r="N27" s="3" t="n">
-        <f aca="false">COUNTA(H27:L27)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N27" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O27" s="3" t="n">
+      <c r="O27" s="3">
         <v>804</v>
       </c>
       <c r="P27" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D27,3),O27,LEFT(C27,3)))</f>
+        <f t="shared" si="8"/>
         <v>LIL804MAT</v>
       </c>
       <c r="Q27" s="4" t="str">
-        <f aca="false">IF(H27&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N27&gt;1,"5",""),$O27), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R27" s="4" t="str">
-        <f aca="false">IF(I27&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N27&gt;1,"4",""),$O27), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S27" s="4" t="str">
-        <f aca="false">IF(J27&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N27&gt;1,$I27=""),"4",""),$O27), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 804</v>
       </c>
       <c r="T27" s="4" t="str">
-        <f aca="false">IF(K27&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N27&gt;1,"2",""),$O27), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U27" s="4" t="str">
-        <f aca="false">IF(L27&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N27&gt;1,"1",""),$O27), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28">
         <v>39</v>
       </c>
-      <c r="B28" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="0" t="s">
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" t="s">
         <v>72</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="1" t="n">
+      <c r="G28" s="1">
         <v>707</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>40</v>
       </c>
       <c r="M28" s="3" t="str">
-        <f aca="false">IF(A28-A27&lt;&gt;1,A28-A27,"")</f>
-        <v/>
-      </c>
-      <c r="N28" s="3" t="n">
-        <f aca="false">COUNTA(H28:L28)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N28" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O28" s="11" t="n">
-        <f aca="false">G28</f>
+      <c r="O28" s="11">
+        <f>G28</f>
         <v>707</v>
       </c>
       <c r="P28" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D28,3),O28,LEFT(C28,3)))</f>
+        <f t="shared" si="8"/>
         <v>GOR707DEN</v>
       </c>
       <c r="Q28" s="4" t="str">
-        <f aca="false">IF(H28&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N28&gt;1,"5",""),$O28), "")</f>
+        <f t="shared" si="2"/>
         <v>Motion 707</v>
       </c>
       <c r="R28" s="4" t="str">
-        <f aca="false">IF(I28&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N28&gt;1,"4",""),$O28), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S28" s="4" t="str">
-        <f aca="false">IF(J28&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N28&gt;1,$I28=""),"4",""),$O28), "")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T28" s="4" t="str">
-        <f aca="false">IF(K28&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N28&gt;1,"2",""),$O28), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U28" s="4" t="str">
-        <f aca="false">IF(L28&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N28&gt;1,"1",""),$O28), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29">
         <v>40</v>
       </c>
-      <c r="B29" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="0" t="s">
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" t="s">
         <v>73</v>
       </c>
       <c r="F29" s="1" t="s">
@@ -2619,52 +2845,52 @@
         <v>21</v>
       </c>
       <c r="M29" s="3" t="str">
-        <f aca="false">IF(A29-A28&lt;&gt;1,A29-A28,"")</f>
-        <v/>
-      </c>
-      <c r="N29" s="3" t="n">
-        <f aca="false">COUNTA(H29:L29)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N29" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O29" s="3" t="n">
+      <c r="O29" s="3">
         <v>852</v>
       </c>
       <c r="P29" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D29,3),O29,LEFT(C29,3)))</f>
+        <f t="shared" si="8"/>
         <v>HAR852SCO</v>
       </c>
       <c r="Q29" s="4" t="str">
-        <f aca="false">IF(H29&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N29&gt;1,"5",""),$O29), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R29" s="4" t="str">
-        <f aca="false">IF(I29&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N29&gt;1,"4",""),$O29), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S29" s="4" t="str">
-        <f aca="false">IF(J29&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N29&gt;1,$I29=""),"4",""),$O29), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 852</v>
       </c>
       <c r="T29" s="4" t="str">
-        <f aca="false">IF(K29&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N29&gt;1,"2",""),$O29), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U29" s="4" t="str">
-        <f aca="false">IF(L29&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N29&gt;1,"1",""),$O29), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30">
         <v>41</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" t="s">
         <v>52</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" t="s">
         <v>73</v>
       </c>
       <c r="F30" s="1" t="s">
@@ -2674,52 +2900,52 @@
         <v>21</v>
       </c>
       <c r="M30" s="3" t="str">
-        <f aca="false">IF(A30-A29&lt;&gt;1,A30-A29,"")</f>
-        <v/>
-      </c>
-      <c r="N30" s="3" t="n">
-        <f aca="false">COUNTA(H30:L30)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N30" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O30" s="3" t="n">
+      <c r="O30" s="3">
         <v>861</v>
       </c>
       <c r="P30" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D30,3),O30,LEFT(C30,3)))</f>
+        <f t="shared" si="8"/>
         <v>HAR861SIA</v>
       </c>
       <c r="Q30" s="4" t="str">
-        <f aca="false">IF(H30&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N30&gt;1,"5",""),$O30), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R30" s="4" t="str">
-        <f aca="false">IF(I30&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N30&gt;1,"4",""),$O30), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S30" s="4" t="str">
-        <f aca="false">IF(J30&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N30&gt;1,$I30=""),"4",""),$O30), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 861</v>
       </c>
       <c r="T30" s="4" t="str">
-        <f aca="false">IF(K30&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N30&gt;1,"2",""),$O30), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U30" s="4" t="str">
-        <f aca="false">IF(L30&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N30&gt;1,"1",""),$O30), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31">
         <v>42</v>
       </c>
-      <c r="B31" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" s="0" t="s">
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" t="s">
         <v>45</v>
       </c>
       <c r="F31" s="1" t="s">
@@ -2729,52 +2955,52 @@
         <v>21</v>
       </c>
       <c r="M31" s="3" t="str">
-        <f aca="false">IF(A31-A30&lt;&gt;1,A31-A30,"")</f>
-        <v/>
-      </c>
-      <c r="N31" s="3" t="n">
-        <f aca="false">COUNTA(H31:L31)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N31" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O31" s="3" t="n">
+      <c r="O31" s="3">
         <v>1039</v>
       </c>
       <c r="P31" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D31,3),O31,LEFT(C31,3)))</f>
+        <f t="shared" si="8"/>
         <v>MEY1039NEI</v>
       </c>
       <c r="Q31" s="4" t="str">
-        <f aca="false">IF(H31&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N31&gt;1,"5",""),$O31), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R31" s="4" t="str">
-        <f aca="false">IF(I31&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N31&gt;1,"4",""),$O31), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S31" s="4" t="str">
-        <f aca="false">IF(J31&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N31&gt;1,$I31=""),"4",""),$O31), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 1039</v>
       </c>
       <c r="T31" s="4" t="str">
-        <f aca="false">IF(K31&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N31&gt;1,"2",""),$O31), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U31" s="4" t="str">
-        <f aca="false">IF(L31&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N31&gt;1,"1",""),$O31), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32">
         <v>43</v>
       </c>
-      <c r="B32" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" s="0" t="s">
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" t="s">
         <v>77</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -2784,52 +3010,52 @@
         <v>21</v>
       </c>
       <c r="M32" s="3" t="str">
-        <f aca="false">IF(A32-A31&lt;&gt;1,A32-A31,"")</f>
-        <v/>
-      </c>
-      <c r="N32" s="3" t="n">
-        <f aca="false">COUNTA(H32:L32)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N32" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O32" s="3" t="n">
+      <c r="O32" s="3">
         <v>845</v>
       </c>
       <c r="P32" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D32,3),O32,LEFT(C32,3)))</f>
+        <f t="shared" si="8"/>
         <v>WAT845STE</v>
       </c>
       <c r="Q32" s="4" t="str">
-        <f aca="false">IF(H32&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N32&gt;1,"5",""),$O32), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R32" s="4" t="str">
-        <f aca="false">IF(I32&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N32&gt;1,"4",""),$O32), "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S32" s="4" t="str">
-        <f aca="false">IF(J32&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N32&gt;1,$I32=""),"4",""),$O32), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 845</v>
       </c>
       <c r="T32" s="4" t="str">
-        <f aca="false">IF(K32&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N32&gt;1,"2",""),$O32), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U32" s="4" t="str">
-        <f aca="false">IF(L32&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N32&gt;1,"1",""),$O32), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A33">
         <v>44</v>
       </c>
-      <c r="B33" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" s="0" t="s">
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="s">
         <v>78</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" t="s">
         <v>79</v>
       </c>
       <c r="F33" s="1" t="s">
@@ -2842,52 +3068,52 @@
         <v>21</v>
       </c>
       <c r="M33" s="3" t="str">
-        <f aca="false">IF(A33-A32&lt;&gt;1,A33-A32,"")</f>
-        <v/>
-      </c>
-      <c r="N33" s="3" t="n">
-        <f aca="false">COUNTA(H33:L33)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N33" s="3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="O33" s="3" t="n">
+      <c r="O33" s="3">
         <v>987</v>
       </c>
       <c r="P33" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D33,3),O33,LEFT(C33,3)))</f>
+        <f t="shared" si="8"/>
         <v>LOR987BRE</v>
       </c>
       <c r="Q33" s="4" t="str">
-        <f aca="false">IF(H33&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N33&gt;1,"5",""),$O33), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R33" s="4" t="str">
-        <f aca="false">IF(I33&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N33&gt;1,"4",""),$O33), "")</f>
+        <f t="shared" si="3"/>
         <v>Motion 4987</v>
       </c>
       <c r="S33" s="4" t="str">
-        <f aca="false">IF(J33&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N33&gt;1,$I33=""),"4",""),$O33), "")</f>
+        <f t="shared" si="4"/>
         <v>Motion 987</v>
       </c>
       <c r="T33" s="4" t="str">
-        <f aca="false">IF(K33&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N33&gt;1,"2",""),$O33), "")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U33" s="4" t="str">
-        <f aca="false">IF(L33&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N33&gt;1,"1",""),$O33), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="n">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A34">
         <v>45</v>
       </c>
-      <c r="B34" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" s="0" t="s">
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="s">
         <v>80</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" t="s">
         <v>79</v>
       </c>
       <c r="F34" s="1" t="s">
@@ -2897,52 +3123,52 @@
         <v>21</v>
       </c>
       <c r="M34" s="3" t="str">
-        <f aca="false">IF(A34-A33&lt;&gt;1,A34-A33,"")</f>
-        <v/>
-      </c>
-      <c r="N34" s="3" t="n">
-        <f aca="false">COUNTA(H34:L34)</f>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N34" s="3">
+        <f t="shared" ref="N34:N65" si="9">COUNTA(H34:L34)</f>
         <v>1</v>
       </c>
-      <c r="O34" s="3" t="n">
+      <c r="O34" s="3">
         <v>1037</v>
       </c>
       <c r="P34" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D34,3),O34,LEFT(C34,3)))</f>
+        <f t="shared" si="8"/>
         <v>LOR1037FRA</v>
       </c>
       <c r="Q34" s="4" t="str">
-        <f aca="false">IF(H34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N34&gt;1,"5",""),$O34), "")</f>
+        <f t="shared" ref="Q34:Q65" si="10">IF(H34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N34&gt;1,"5",""),$O34), "")</f>
         <v/>
       </c>
       <c r="R34" s="4" t="str">
-        <f aca="false">IF(I34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N34&gt;1,"4",""),$O34), "")</f>
+        <f t="shared" ref="R34:R65" si="11">IF(I34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N34&gt;1,"4",""),$O34), "")</f>
         <v/>
       </c>
       <c r="S34" s="4" t="str">
-        <f aca="false">IF(J34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N34&gt;1,$I34=""),"4",""),$O34), "")</f>
+        <f t="shared" ref="S34:S65" si="12">IF(J34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N34&gt;1,$I34=""),"4",""),$O34), "")</f>
         <v>Motion 1037</v>
       </c>
       <c r="T34" s="4" t="str">
-        <f aca="false">IF(K34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N34&gt;1,"2",""),$O34), "")</f>
+        <f t="shared" ref="T34:T65" si="13">IF(K34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N34&gt;1,"2",""),$O34), "")</f>
         <v/>
       </c>
       <c r="U34" s="4" t="str">
-        <f aca="false">IF(L34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N34&gt;1,"1",""),$O34), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="n">
+        <f t="shared" ref="U34:U65" si="14">IF(L34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N34&gt;1,"1",""),$O34), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A35">
         <v>46</v>
       </c>
-      <c r="B35" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" s="0" t="s">
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="s">
         <v>81</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" t="s">
         <v>39</v>
       </c>
       <c r="F35" s="1" t="s">
@@ -2955,111 +3181,111 @@
         <v>21</v>
       </c>
       <c r="M35" s="3" t="str">
-        <f aca="false">IF(A35-A34&lt;&gt;1,A35-A34,"")</f>
-        <v/>
-      </c>
-      <c r="N35" s="3" t="n">
-        <f aca="false">COUNTA(H35:L35)</f>
+        <f t="shared" ref="M35:M66" si="15">IF(A35-A34&lt;&gt;1,A35-A34,"")</f>
+        <v/>
+      </c>
+      <c r="N35" s="3">
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="O35" s="3" t="n">
+      <c r="O35" s="3">
         <v>998</v>
       </c>
       <c r="P35" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D35,3),O35,LEFT(C35,3)))</f>
+        <f t="shared" si="8"/>
         <v>DIC998FIN</v>
       </c>
       <c r="Q35" s="4" t="str">
-        <f aca="false">IF(H35&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N35&gt;1,"5",""),$O35), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R35" s="4" t="str">
-        <f aca="false">IF(I35&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N35&gt;1,"4",""),$O35), "")</f>
+        <f t="shared" si="11"/>
         <v>Motion 4998</v>
       </c>
       <c r="S35" s="4" t="str">
-        <f aca="false">IF(J35&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N35&gt;1,$I35=""),"4",""),$O35), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 998</v>
       </c>
       <c r="T35" s="4" t="str">
-        <f aca="false">IF(K35&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N35&gt;1,"2",""),$O35), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U35" s="4" t="str">
-        <f aca="false">IF(L35&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N35&gt;1,"1",""),$O35), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36">
         <v>47</v>
       </c>
-      <c r="B36" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="0" t="s">
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="s">
         <v>18</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" t="s">
         <v>82</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G36" s="10" t="n">
+      <c r="G36" s="10">
         <v>623</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>21</v>
       </c>
       <c r="M36" s="3" t="str">
-        <f aca="false">IF(A36-A35&lt;&gt;1,A36-A35,"")</f>
-        <v/>
-      </c>
-      <c r="N36" s="3" t="n">
-        <f aca="false">COUNTA(H36:L36)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N36" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O36" s="11" t="n">
-        <f aca="false">G36</f>
+      <c r="O36" s="11">
+        <f>G36</f>
         <v>623</v>
       </c>
       <c r="P36" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D36,3),O36,LEFT(C36,3)))</f>
+        <f t="shared" si="8"/>
         <v>FUL623GEO</v>
       </c>
       <c r="Q36" s="4" t="str">
-        <f aca="false">IF(H36&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N36&gt;1,"5",""),$O36), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R36" s="4" t="str">
-        <f aca="false">IF(I36&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N36&gt;1,"4",""),$O36), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S36" s="4" t="str">
-        <f aca="false">IF(J36&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N36&gt;1,$I36=""),"4",""),$O36), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 623</v>
       </c>
       <c r="T36" s="4" t="str">
-        <f aca="false">IF(K36&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N36&gt;1,"2",""),$O36), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U36" s="4" t="str">
-        <f aca="false">IF(L36&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N36&gt;1,"1",""),$O36), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37">
         <v>48</v>
       </c>
-      <c r="B37" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" s="0" t="s">
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" t="s">
         <v>84</v>
       </c>
       <c r="F37" s="1" t="s">
@@ -3069,52 +3295,52 @@
         <v>21</v>
       </c>
       <c r="M37" s="3" t="str">
-        <f aca="false">IF(A37-A36&lt;&gt;1,A37-A36,"")</f>
-        <v/>
-      </c>
-      <c r="N37" s="3" t="n">
-        <f aca="false">COUNTA(H37:L37)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N37" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O37" s="3" t="n">
+      <c r="O37" s="3">
         <v>815</v>
       </c>
       <c r="P37" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D37,3),O37,LEFT(C37,3)))</f>
+        <f t="shared" si="8"/>
         <v>SPA815BOB</v>
       </c>
       <c r="Q37" s="4" t="str">
-        <f aca="false">IF(H37&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N37&gt;1,"5",""),$O37), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R37" s="4" t="str">
-        <f aca="false">IF(I37&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N37&gt;1,"4",""),$O37), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S37" s="4" t="str">
-        <f aca="false">IF(J37&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N37&gt;1,$I37=""),"4",""),$O37), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 815</v>
       </c>
       <c r="T37" s="4" t="str">
-        <f aca="false">IF(K37&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N37&gt;1,"2",""),$O37), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U37" s="4" t="str">
-        <f aca="false">IF(L37&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N37&gt;1,"1",""),$O37), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A38">
         <v>49</v>
       </c>
-      <c r="B38" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" s="0" t="s">
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="s">
         <v>85</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" t="s">
         <v>86</v>
       </c>
       <c r="F38" s="1" t="s">
@@ -3124,52 +3350,52 @@
         <v>21</v>
       </c>
       <c r="M38" s="3" t="str">
-        <f aca="false">IF(A38-A37&lt;&gt;1,A38-A37,"")</f>
-        <v/>
-      </c>
-      <c r="N38" s="3" t="n">
-        <f aca="false">COUNTA(H38:L38)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N38" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O38" s="3" t="n">
+      <c r="O38" s="3">
         <v>1033</v>
       </c>
       <c r="P38" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D38,3),O38,LEFT(C38,3)))</f>
+        <f t="shared" si="8"/>
         <v>ARN1033PAU</v>
       </c>
       <c r="Q38" s="4" t="str">
-        <f aca="false">IF(H38&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N38&gt;1,"5",""),$O38), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R38" s="4" t="str">
-        <f aca="false">IF(I38&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N38&gt;1,"4",""),$O38), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S38" s="4" t="str">
-        <f aca="false">IF(J38&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N38&gt;1,$I38=""),"4",""),$O38), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 1033</v>
       </c>
       <c r="T38" s="4" t="str">
-        <f aca="false">IF(K38&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N38&gt;1,"2",""),$O38), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U38" s="4" t="str">
-        <f aca="false">IF(L38&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N38&gt;1,"1",""),$O38), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A39">
         <v>50</v>
       </c>
-      <c r="B39" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" s="0" t="s">
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="s">
         <v>76</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" t="s">
         <v>87</v>
       </c>
       <c r="F39" s="1" t="s">
@@ -3179,52 +3405,52 @@
         <v>21</v>
       </c>
       <c r="M39" s="3" t="str">
-        <f aca="false">IF(A39-A38&lt;&gt;1,A39-A38,"")</f>
-        <v/>
-      </c>
-      <c r="N39" s="3" t="n">
-        <f aca="false">COUNTA(H39:L39)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N39" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O39" s="3" t="n">
+      <c r="O39" s="3">
         <v>838</v>
       </c>
       <c r="P39" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D39,3),O39,LEFT(C39,3)))</f>
+        <f t="shared" si="8"/>
         <v>THO838STE</v>
       </c>
       <c r="Q39" s="4" t="str">
-        <f aca="false">IF(H39&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N39&gt;1,"5",""),$O39), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R39" s="4" t="str">
-        <f aca="false">IF(I39&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N39&gt;1,"4",""),$O39), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S39" s="4" t="str">
-        <f aca="false">IF(J39&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N39&gt;1,$I39=""),"4",""),$O39), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 838</v>
       </c>
       <c r="T39" s="4" t="str">
-        <f aca="false">IF(K39&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N39&gt;1,"2",""),$O39), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U39" s="4" t="str">
-        <f aca="false">IF(L39&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N39&gt;1,"1",""),$O39), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A40">
         <v>51</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" t="s">
         <v>52</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" t="s">
         <v>88</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" t="s">
         <v>89</v>
       </c>
       <c r="F40" s="1" t="s">
@@ -3234,52 +3460,52 @@
         <v>21</v>
       </c>
       <c r="M40" s="3" t="str">
-        <f aca="false">IF(A40-A39&lt;&gt;1,A40-A39,"")</f>
-        <v/>
-      </c>
-      <c r="N40" s="3" t="n">
-        <f aca="false">COUNTA(H40:L40)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N40" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O40" s="3" t="n">
+      <c r="O40" s="3">
         <v>819</v>
       </c>
       <c r="P40" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D40,3),O40,LEFT(C40,3)))</f>
+        <f t="shared" si="8"/>
         <v>WAT819JOE</v>
       </c>
       <c r="Q40" s="4" t="str">
-        <f aca="false">IF(H40&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N40&gt;1,"5",""),$O40), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R40" s="4" t="str">
-        <f aca="false">IF(I40&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N40&gt;1,"4",""),$O40), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S40" s="4" t="str">
-        <f aca="false">IF(J40&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N40&gt;1,$I40=""),"4",""),$O40), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 819</v>
       </c>
       <c r="T40" s="4" t="str">
-        <f aca="false">IF(K40&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N40&gt;1,"2",""),$O40), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U40" s="4" t="str">
-        <f aca="false">IF(L40&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N40&gt;1,"1",""),$O40), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A41">
         <v>52</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" t="s">
         <v>90</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" t="s">
         <v>91</v>
       </c>
       <c r="F41" s="1" t="s">
@@ -3289,52 +3515,52 @@
         <v>21</v>
       </c>
       <c r="M41" s="3" t="str">
-        <f aca="false">IF(A41-A40&lt;&gt;1,A41-A40,"")</f>
-        <v/>
-      </c>
-      <c r="N41" s="3" t="n">
-        <f aca="false">COUNTA(H41:L41)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N41" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O41" s="3" t="n">
+      <c r="O41" s="3">
         <v>853</v>
       </c>
       <c r="P41" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D41,3),O41,LEFT(C41,3)))</f>
+        <f t="shared" si="8"/>
         <v>DAF853CHR</v>
       </c>
       <c r="Q41" s="4" t="str">
-        <f aca="false">IF(H41&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N41&gt;1,"5",""),$O41), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R41" s="4" t="str">
-        <f aca="false">IF(I41&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N41&gt;1,"4",""),$O41), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S41" s="4" t="str">
-        <f aca="false">IF(J41&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N41&gt;1,$I41=""),"4",""),$O41), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 853</v>
       </c>
       <c r="T41" s="4" t="str">
-        <f aca="false">IF(K41&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N41&gt;1,"2",""),$O41), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U41" s="4" t="str">
-        <f aca="false">IF(L41&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N41&gt;1,"1",""),$O41), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A42">
         <v>53</v>
       </c>
-      <c r="B42" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" s="0" t="s">
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="s">
         <v>65</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="D42" t="s">
         <v>92</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -3344,52 +3570,52 @@
         <v>21</v>
       </c>
       <c r="M42" s="3" t="str">
-        <f aca="false">IF(A42-A41&lt;&gt;1,A42-A41,"")</f>
-        <v/>
-      </c>
-      <c r="N42" s="3" t="n">
-        <f aca="false">COUNTA(H42:L42)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N42" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O42" s="3" t="n">
+      <c r="O42" s="3">
         <v>814</v>
       </c>
       <c r="P42" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D42,3),O42,LEFT(C42,3)))</f>
+        <f t="shared" si="8"/>
         <v>WIL814JON</v>
       </c>
       <c r="Q42" s="4" t="str">
-        <f aca="false">IF(H42&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N42&gt;1,"5",""),$O42), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R42" s="4" t="str">
-        <f aca="false">IF(I42&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N42&gt;1,"4",""),$O42), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S42" s="4" t="str">
-        <f aca="false">IF(J42&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N42&gt;1,$I42=""),"4",""),$O42), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 814</v>
       </c>
       <c r="T42" s="4" t="str">
-        <f aca="false">IF(K42&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N42&gt;1,"2",""),$O42), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U42" s="4" t="str">
-        <f aca="false">IF(L42&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N42&gt;1,"1",""),$O42), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A43">
         <v>54</v>
       </c>
-      <c r="B43" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="0" t="s">
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="s">
         <v>93</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" t="s">
         <v>94</v>
       </c>
       <c r="F43" s="1" t="s">
@@ -3399,108 +3625,108 @@
         <v>40</v>
       </c>
       <c r="M43" s="3" t="str">
-        <f aca="false">IF(A43-A42&lt;&gt;1,A43-A42,"")</f>
-        <v/>
-      </c>
-      <c r="N43" s="3" t="n">
-        <f aca="false">COUNTA(H43:L43)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N43" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O43" s="3" t="n">
+      <c r="O43" s="3">
         <v>643</v>
       </c>
       <c r="P43" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D43,3),O43,LEFT(C43,3)))</f>
+        <f t="shared" ref="P43:P74" si="16">UPPER(_xlfn.CONCAT(LEFT(D43,3),O43,LEFT(C43,3)))</f>
         <v>SHE643IAN</v>
       </c>
       <c r="Q43" s="4" t="str">
-        <f aca="false">IF(H43&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N43&gt;1,"5",""),$O43), "")</f>
+        <f t="shared" si="10"/>
         <v>Motion 643</v>
       </c>
       <c r="R43" s="4" t="str">
-        <f aca="false">IF(I43&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N43&gt;1,"4",""),$O43), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S43" s="4" t="str">
-        <f aca="false">IF(J43&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N43&gt;1,$I43=""),"4",""),$O43), "")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T43" s="4" t="str">
-        <f aca="false">IF(K43&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N43&gt;1,"2",""),$O43), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U43" s="4" t="str">
-        <f aca="false">IF(L43&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N43&gt;1,"1",""),$O43), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A44">
         <v>55</v>
       </c>
-      <c r="B44" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" s="0" t="s">
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="s">
         <v>95</v>
       </c>
-      <c r="D44" s="0" t="s">
+      <c r="D44" t="s">
         <v>96</v>
       </c>
-      <c r="G44" s="10" t="n">
+      <c r="G44" s="10">
         <v>846</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>29</v>
       </c>
       <c r="M44" s="3" t="str">
-        <f aca="false">IF(A44-A43&lt;&gt;1,A44-A43,"")</f>
-        <v/>
-      </c>
-      <c r="N44" s="3" t="n">
-        <f aca="false">COUNTA(H44:L44)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N44" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O44" s="11" t="n">
-        <f aca="false">G44</f>
+      <c r="O44" s="11">
+        <f>G44</f>
         <v>846</v>
       </c>
       <c r="P44" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D44,3),O44,LEFT(C44,3)))</f>
+        <f t="shared" si="16"/>
         <v>BUR846EMI</v>
       </c>
       <c r="Q44" s="4" t="str">
-        <f aca="false">IF(H44&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N44&gt;1,"5",""),$O44), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R44" s="4" t="str">
-        <f aca="false">IF(I44&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N44&gt;1,"4",""),$O44), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S44" s="4" t="str">
-        <f aca="false">IF(J44&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N44&gt;1,$I44=""),"4",""),$O44), "")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T44" s="4" t="str">
-        <f aca="false">IF(K44&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N44&gt;1,"2",""),$O44), "")</f>
+        <f t="shared" si="13"/>
         <v>Motion 846</v>
       </c>
       <c r="U44" s="4" t="str">
-        <f aca="false">IF(L44&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N44&gt;1,"1",""),$O44), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A45">
         <v>56</v>
       </c>
-      <c r="B45" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" s="0" t="s">
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="s">
         <v>97</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="D45" t="s">
         <v>98</v>
       </c>
       <c r="F45" s="1" t="s">
@@ -3513,52 +3739,52 @@
         <v>21</v>
       </c>
       <c r="M45" s="3" t="str">
-        <f aca="false">IF(A45-A44&lt;&gt;1,A45-A44,"")</f>
-        <v/>
-      </c>
-      <c r="N45" s="3" t="n">
-        <f aca="false">COUNTA(H45:L45)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N45" s="3">
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="O45" s="3" t="n">
+      <c r="O45" s="3">
         <v>854</v>
       </c>
       <c r="P45" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D45,3),O45,LEFT(C45,3)))</f>
+        <f t="shared" si="16"/>
         <v>DVO854PAV</v>
       </c>
       <c r="Q45" s="4" t="str">
-        <f aca="false">IF(H45&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N45&gt;1,"5",""),$O45), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R45" s="4" t="str">
-        <f aca="false">IF(I45&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N45&gt;1,"4",""),$O45), "")</f>
+        <f t="shared" si="11"/>
         <v>Motion 4854</v>
       </c>
       <c r="S45" s="4" t="str">
-        <f aca="false">IF(J45&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N45&gt;1,$I45=""),"4",""),$O45), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 854</v>
       </c>
       <c r="T45" s="4" t="str">
-        <f aca="false">IF(K45&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N45&gt;1,"2",""),$O45), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U45" s="4" t="str">
-        <f aca="false">IF(L45&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N45&gt;1,"1",""),$O45), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A46">
         <v>57</v>
       </c>
-      <c r="B46" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" s="0" t="s">
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="s">
         <v>99</v>
       </c>
-      <c r="D46" s="0" t="s">
+      <c r="D46" t="s">
         <v>100</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -3571,52 +3797,52 @@
         <v>101</v>
       </c>
       <c r="M46" s="3" t="str">
-        <f aca="false">IF(A46-A45&lt;&gt;1,A46-A45,"")</f>
-        <v/>
-      </c>
-      <c r="N46" s="3" t="n">
-        <f aca="false">COUNTA(H46:L46)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N46" s="3">
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="O46" s="3" t="n">
+      <c r="O46" s="3">
         <v>641</v>
       </c>
       <c r="P46" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D46,3),O46,LEFT(C46,3)))</f>
+        <f t="shared" si="16"/>
         <v>RUS641ROB</v>
       </c>
       <c r="Q46" s="4" t="str">
-        <f aca="false">IF(H46&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N46&gt;1,"5",""),$O46), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R46" s="4" t="str">
-        <f aca="false">IF(I46&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N46&gt;1,"4",""),$O46), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S46" s="4" t="str">
-        <f aca="false">IF(J46&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N46&gt;1,$I46=""),"4",""),$O46), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 4641</v>
       </c>
       <c r="T46" s="4" t="str">
-        <f aca="false">IF(K46&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N46&gt;1,"2",""),$O46), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U46" s="4" t="str">
-        <f aca="false">IF(L46&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N46&gt;1,"1",""),$O46), "")</f>
+        <f t="shared" si="14"/>
         <v>Motion 1641</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="n">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A47">
         <v>58</v>
       </c>
-      <c r="B47" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" s="0" t="s">
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="s">
         <v>102</v>
       </c>
-      <c r="D47" s="0" t="s">
+      <c r="D47" t="s">
         <v>103</v>
       </c>
       <c r="F47" s="1" t="s">
@@ -3626,52 +3852,52 @@
         <v>21</v>
       </c>
       <c r="M47" s="3" t="str">
-        <f aca="false">IF(A47-A46&lt;&gt;1,A47-A46,"")</f>
-        <v/>
-      </c>
-      <c r="N47" s="3" t="n">
-        <f aca="false">COUNTA(H47:L47)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N47" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O47" s="3" t="n">
+      <c r="O47" s="3">
         <v>1020</v>
       </c>
       <c r="P47" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D47,3),O47,LEFT(C47,3)))</f>
+        <f t="shared" si="16"/>
         <v>BRA1020JAM</v>
       </c>
       <c r="Q47" s="4" t="str">
-        <f aca="false">IF(H47&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N47&gt;1,"5",""),$O47), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R47" s="4" t="str">
-        <f aca="false">IF(I47&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N47&gt;1,"4",""),$O47), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S47" s="4" t="str">
-        <f aca="false">IF(J47&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N47&gt;1,$I47=""),"4",""),$O47), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 1020</v>
       </c>
       <c r="T47" s="4" t="str">
-        <f aca="false">IF(K47&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N47&gt;1,"2",""),$O47), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U47" s="4" t="str">
-        <f aca="false">IF(L47&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N47&gt;1,"1",""),$O47), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A48">
         <v>59</v>
       </c>
-      <c r="B48" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" s="0" t="s">
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="s">
         <v>104</v>
       </c>
-      <c r="D48" s="0" t="s">
+      <c r="D48" t="s">
         <v>105</v>
       </c>
       <c r="F48" s="1" t="s">
@@ -3681,52 +3907,52 @@
         <v>21</v>
       </c>
       <c r="M48" s="3" t="str">
-        <f aca="false">IF(A48-A47&lt;&gt;1,A48-A47,"")</f>
-        <v/>
-      </c>
-      <c r="N48" s="3" t="n">
-        <f aca="false">COUNTA(H48:L48)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N48" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O48" s="3" t="n">
+      <c r="O48" s="3">
         <v>858</v>
       </c>
       <c r="P48" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D48,3),O48,LEFT(C48,3)))</f>
+        <f t="shared" si="16"/>
         <v>OLI858JOH</v>
       </c>
       <c r="Q48" s="4" t="str">
-        <f aca="false">IF(H48&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N48&gt;1,"5",""),$O48), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R48" s="4" t="str">
-        <f aca="false">IF(I48&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N48&gt;1,"4",""),$O48), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S48" s="4" t="str">
-        <f aca="false">IF(J48&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N48&gt;1,$I48=""),"4",""),$O48), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 858</v>
       </c>
       <c r="T48" s="4" t="str">
-        <f aca="false">IF(K48&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N48&gt;1,"2",""),$O48), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U48" s="4" t="str">
-        <f aca="false">IF(L48&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N48&gt;1,"1",""),$O48), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A49">
         <v>60</v>
       </c>
-      <c r="B49" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" s="0" t="s">
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="s">
         <v>106</v>
       </c>
-      <c r="D49" s="0" t="s">
+      <c r="D49" t="s">
         <v>107</v>
       </c>
       <c r="F49" s="1" t="s">
@@ -3736,104 +3962,104 @@
         <v>21</v>
       </c>
       <c r="M49" s="3" t="str">
-        <f aca="false">IF(A49-A48&lt;&gt;1,A49-A48,"")</f>
-        <v/>
-      </c>
-      <c r="N49" s="3" t="n">
-        <f aca="false">COUNTA(H49:L49)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N49" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O49" s="3" t="n">
+      <c r="O49" s="3">
         <v>869</v>
       </c>
       <c r="P49" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D49,3),O49,LEFT(C49,3)))</f>
+        <f t="shared" si="16"/>
         <v>BAR869ANT</v>
       </c>
       <c r="Q49" s="4" t="str">
-        <f aca="false">IF(H49&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N49&gt;1,"5",""),$O49), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R49" s="4" t="str">
-        <f aca="false">IF(I49&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N49&gt;1,"4",""),$O49), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S49" s="4" t="str">
-        <f aca="false">IF(J49&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N49&gt;1,$I49=""),"4",""),$O49), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 869</v>
       </c>
       <c r="T49" s="4" t="str">
-        <f aca="false">IF(K49&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N49&gt;1,"2",""),$O49), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U49" s="4" t="str">
-        <f aca="false">IF(L49&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N49&gt;1,"1",""),$O49), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A50">
         <v>61</v>
       </c>
-      <c r="B50" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" s="0" t="s">
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="s">
         <v>58</v>
       </c>
-      <c r="D50" s="0" t="s">
+      <c r="D50" t="s">
         <v>108</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>101</v>
       </c>
       <c r="M50" s="3" t="str">
-        <f aca="false">IF(A50-A49&lt;&gt;1,A50-A49,"")</f>
-        <v/>
-      </c>
-      <c r="N50" s="3" t="n">
-        <f aca="false">COUNTA(H50:L50)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N50" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O50" s="3" t="n">
+      <c r="O50" s="3">
         <v>618</v>
       </c>
       <c r="P50" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D50,3),O50,LEFT(C50,3)))</f>
+        <f t="shared" si="16"/>
         <v>MAR618PET</v>
       </c>
       <c r="Q50" s="4" t="str">
-        <f aca="false">IF(H50&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N50&gt;1,"5",""),$O50), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R50" s="4" t="str">
-        <f aca="false">IF(I50&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N50&gt;1,"4",""),$O50), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S50" s="4" t="str">
-        <f aca="false">IF(J50&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N50&gt;1,$I50=""),"4",""),$O50), "")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T50" s="4" t="str">
-        <f aca="false">IF(K50&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N50&gt;1,"2",""),$O50), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U50" s="4" t="str">
-        <f aca="false">IF(L50&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N50&gt;1,"1",""),$O50), "")</f>
+        <f t="shared" si="14"/>
         <v>Motion 618</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="n">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A51">
         <v>63</v>
       </c>
-      <c r="B51" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" s="0" t="s">
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="s">
         <v>81</v>
       </c>
-      <c r="D51" s="0" t="s">
+      <c r="D51" t="s">
         <v>109</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -3845,53 +4071,53 @@
       <c r="H51" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M51" s="12" t="n">
-        <f aca="false">IF(A51-A50&lt;&gt;1,A51-A50,"")</f>
+      <c r="M51" s="12">
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
-      <c r="N51" s="3" t="n">
-        <f aca="false">COUNTA(H51:L51)</f>
+      <c r="N51" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O51" s="3" t="n">
+      <c r="O51" s="3">
         <v>827</v>
       </c>
       <c r="P51" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D51,3),O51,LEFT(C51,3)))</f>
+        <f t="shared" si="16"/>
         <v>BER827FIN</v>
       </c>
       <c r="Q51" s="4" t="str">
-        <f aca="false">IF(H51&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N51&gt;1,"5",""),$O51), "")</f>
+        <f t="shared" si="10"/>
         <v>Motion 827</v>
       </c>
       <c r="R51" s="4" t="str">
-        <f aca="false">IF(I51&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N51&gt;1,"4",""),$O51), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S51" s="4" t="str">
-        <f aca="false">IF(J51&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N51&gt;1,$I51=""),"4",""),$O51), "")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T51" s="4" t="str">
-        <f aca="false">IF(K51&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N51&gt;1,"2",""),$O51), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U51" s="4" t="str">
-        <f aca="false">IF(L51&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N51&gt;1,"1",""),$O51), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A52">
         <v>64</v>
       </c>
-      <c r="B52" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" s="0" t="s">
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="s">
         <v>67</v>
       </c>
-      <c r="D52" s="0" t="s">
+      <c r="D52" t="s">
         <v>110</v>
       </c>
       <c r="F52" s="1" t="s">
@@ -3901,52 +4127,52 @@
         <v>40</v>
       </c>
       <c r="M52" s="3" t="str">
-        <f aca="false">IF(A52-A51&lt;&gt;1,A52-A51,"")</f>
-        <v/>
-      </c>
-      <c r="N52" s="3" t="n">
-        <f aca="false">COUNTA(H52:L52)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N52" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O52" s="3" t="n">
+      <c r="O52" s="3">
         <v>639</v>
       </c>
       <c r="P52" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D52,3),O52,LEFT(C52,3)))</f>
+        <f t="shared" si="16"/>
         <v>COL639AND</v>
       </c>
       <c r="Q52" s="4" t="str">
-        <f aca="false">IF(H52&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N52&gt;1,"5",""),$O52), "")</f>
+        <f t="shared" si="10"/>
         <v>Motion 639</v>
       </c>
       <c r="R52" s="4" t="str">
-        <f aca="false">IF(I52&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N52&gt;1,"4",""),$O52), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S52" s="4" t="str">
-        <f aca="false">IF(J52&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N52&gt;1,$I52=""),"4",""),$O52), "")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T52" s="4" t="str">
-        <f aca="false">IF(K52&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N52&gt;1,"2",""),$O52), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U52" s="4" t="str">
-        <f aca="false">IF(L52&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N52&gt;1,"1",""),$O52), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A53">
         <v>65</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" t="s">
         <v>30</v>
       </c>
-      <c r="C53" s="0" t="s">
+      <c r="C53" t="s">
         <v>111</v>
       </c>
-      <c r="D53" s="0" t="s">
+      <c r="D53" t="s">
         <v>110</v>
       </c>
       <c r="F53" s="1" t="s">
@@ -3956,52 +4182,52 @@
         <v>40</v>
       </c>
       <c r="M53" s="3" t="str">
-        <f aca="false">IF(A53-A52&lt;&gt;1,A53-A52,"")</f>
-        <v/>
-      </c>
-      <c r="N53" s="3" t="n">
-        <f aca="false">COUNTA(H53:L53)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N53" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O53" s="3" t="n">
+      <c r="O53" s="3">
         <v>611</v>
       </c>
       <c r="P53" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D53,3),O53,LEFT(C53,3)))</f>
+        <f t="shared" si="16"/>
         <v>COL611ANN</v>
       </c>
       <c r="Q53" s="4" t="str">
-        <f aca="false">IF(H53&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N53&gt;1,"5",""),$O53), "")</f>
+        <f t="shared" si="10"/>
         <v>Motion 611</v>
       </c>
       <c r="R53" s="4" t="str">
-        <f aca="false">IF(I53&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N53&gt;1,"4",""),$O53), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S53" s="4" t="str">
-        <f aca="false">IF(J53&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N53&gt;1,$I53=""),"4",""),$O53), "")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T53" s="4" t="str">
-        <f aca="false">IF(K53&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N53&gt;1,"2",""),$O53), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U53" s="4" t="str">
-        <f aca="false">IF(L53&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N53&gt;1,"1",""),$O53), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A54">
         <v>66</v>
       </c>
-      <c r="B54" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" s="0" t="s">
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="s">
         <v>112</v>
       </c>
-      <c r="D54" s="0" t="s">
+      <c r="D54" t="s">
         <v>109</v>
       </c>
       <c r="E54" s="1" t="s">
@@ -4014,52 +4240,52 @@
         <v>40</v>
       </c>
       <c r="M54" s="3" t="str">
-        <f aca="false">IF(A54-A53&lt;&gt;1,A54-A53,"")</f>
-        <v/>
-      </c>
-      <c r="N54" s="3" t="n">
-        <f aca="false">COUNTA(H54:L54)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N54" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O54" s="3" t="n">
+      <c r="O54" s="3">
         <v>826</v>
       </c>
       <c r="P54" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D54,3),O54,LEFT(C54,3)))</f>
+        <f t="shared" si="16"/>
         <v>BER826ARL</v>
       </c>
       <c r="Q54" s="4" t="str">
-        <f aca="false">IF(H54&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N54&gt;1,"5",""),$O54), "")</f>
+        <f t="shared" si="10"/>
         <v>Motion 826</v>
       </c>
       <c r="R54" s="4" t="str">
-        <f aca="false">IF(I54&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N54&gt;1,"4",""),$O54), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S54" s="4" t="str">
-        <f aca="false">IF(J54&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N54&gt;1,$I54=""),"4",""),$O54), "")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T54" s="4" t="str">
-        <f aca="false">IF(K54&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N54&gt;1,"2",""),$O54), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U54" s="4" t="str">
-        <f aca="false">IF(L54&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N54&gt;1,"1",""),$O54), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A55">
         <v>67</v>
       </c>
-      <c r="B55" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" s="0" t="s">
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="s">
         <v>113</v>
       </c>
-      <c r="D55" s="0" t="s">
+      <c r="D55" t="s">
         <v>114</v>
       </c>
       <c r="F55" s="1" t="s">
@@ -4072,52 +4298,52 @@
         <v>21</v>
       </c>
       <c r="M55" s="3" t="str">
-        <f aca="false">IF(A55-A54&lt;&gt;1,A55-A54,"")</f>
-        <v/>
-      </c>
-      <c r="N55" s="3" t="n">
-        <f aca="false">COUNTA(H55:L55)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N55" s="3">
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="O55" s="3" t="n">
+      <c r="O55" s="3">
         <v>821</v>
       </c>
       <c r="P55" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D55,3),O55,LEFT(C55,3)))</f>
+        <f t="shared" si="16"/>
         <v>CON821GAR</v>
       </c>
       <c r="Q55" s="4" t="str">
-        <f aca="false">IF(H55&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N55&gt;1,"5",""),$O55), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R55" s="4" t="str">
-        <f aca="false">IF(I55&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N55&gt;1,"4",""),$O55), "")</f>
+        <f t="shared" si="11"/>
         <v>Motion 4821</v>
       </c>
       <c r="S55" s="4" t="str">
-        <f aca="false">IF(J55&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N55&gt;1,$I55=""),"4",""),$O55), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 821</v>
       </c>
       <c r="T55" s="4" t="str">
-        <f aca="false">IF(K55&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N55&gt;1,"2",""),$O55), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U55" s="4" t="str">
-        <f aca="false">IF(L55&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N55&gt;1,"1",""),$O55), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A56">
         <v>68</v>
       </c>
-      <c r="B56" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" s="0" t="s">
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="s">
         <v>102</v>
       </c>
-      <c r="D56" s="0" t="s">
+      <c r="D56" t="s">
         <v>115</v>
       </c>
       <c r="F56" s="1" t="s">
@@ -4130,52 +4356,52 @@
         <v>21</v>
       </c>
       <c r="M56" s="3" t="str">
-        <f aca="false">IF(A56-A55&lt;&gt;1,A56-A55,"")</f>
-        <v/>
-      </c>
-      <c r="N56" s="3" t="n">
-        <f aca="false">COUNTA(H56:L56)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N56" s="3">
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="O56" s="3" t="n">
+      <c r="O56" s="3">
         <v>812</v>
       </c>
       <c r="P56" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D56,3),O56,LEFT(C56,3)))</f>
+        <f t="shared" si="16"/>
         <v>DIN812JAM</v>
       </c>
       <c r="Q56" s="4" t="str">
-        <f aca="false">IF(H56&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N56&gt;1,"5",""),$O56), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R56" s="4" t="str">
-        <f aca="false">IF(I56&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N56&gt;1,"4",""),$O56), "")</f>
+        <f t="shared" si="11"/>
         <v>Motion 4812</v>
       </c>
       <c r="S56" s="4" t="str">
-        <f aca="false">IF(J56&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N56&gt;1,$I56=""),"4",""),$O56), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 812</v>
       </c>
       <c r="T56" s="4" t="str">
-        <f aca="false">IF(K56&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N56&gt;1,"2",""),$O56), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U56" s="4" t="str">
-        <f aca="false">IF(L56&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N56&gt;1,"1",""),$O56), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A57">
         <v>69</v>
       </c>
-      <c r="B57" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" s="0" t="s">
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="s">
         <v>116</v>
       </c>
-      <c r="D57" s="0" t="s">
+      <c r="D57" t="s">
         <v>117</v>
       </c>
       <c r="F57" s="1" t="s">
@@ -4185,52 +4411,52 @@
         <v>21</v>
       </c>
       <c r="M57" s="3" t="str">
-        <f aca="false">IF(A57-A56&lt;&gt;1,A57-A56,"")</f>
-        <v/>
-      </c>
-      <c r="N57" s="3" t="n">
-        <f aca="false">COUNTA(H57:L57)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N57" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O57" s="3" t="n">
+      <c r="O57" s="3">
         <v>829</v>
       </c>
       <c r="P57" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D57,3),O57,LEFT(C57,3)))</f>
+        <f t="shared" si="16"/>
         <v>TRO829WIL</v>
       </c>
       <c r="Q57" s="4" t="str">
-        <f aca="false">IF(H57&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N57&gt;1,"5",""),$O57), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R57" s="4" t="str">
-        <f aca="false">IF(I57&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N57&gt;1,"4",""),$O57), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S57" s="4" t="str">
-        <f aca="false">IF(J57&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N57&gt;1,$I57=""),"4",""),$O57), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 829</v>
       </c>
       <c r="T57" s="4" t="str">
-        <f aca="false">IF(K57&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N57&gt;1,"2",""),$O57), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U57" s="4" t="str">
-        <f aca="false">IF(L57&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N57&gt;1,"1",""),$O57), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A58">
         <v>70</v>
       </c>
-      <c r="B58" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" s="0" t="s">
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="s">
         <v>118</v>
       </c>
-      <c r="D58" s="0" t="s">
+      <c r="D58" t="s">
         <v>119</v>
       </c>
       <c r="F58" s="1" t="s">
@@ -4243,111 +4469,111 @@
         <v>29</v>
       </c>
       <c r="M58" s="3" t="str">
-        <f aca="false">IF(A58-A57&lt;&gt;1,A58-A57,"")</f>
-        <v/>
-      </c>
-      <c r="N58" s="3" t="n">
-        <f aca="false">COUNTA(H58:L58)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N58" s="3">
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="O58" s="3" t="n">
+      <c r="O58" s="3">
         <v>669</v>
       </c>
       <c r="P58" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D58,3),O58,LEFT(C58,3)))</f>
+        <f t="shared" si="16"/>
         <v>WIL669DAV</v>
       </c>
       <c r="Q58" s="4" t="str">
-        <f aca="false">IF(H58&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N58&gt;1,"5",""),$O58), "")</f>
+        <f t="shared" si="10"/>
         <v>Motion 5669</v>
       </c>
       <c r="R58" s="4" t="str">
-        <f aca="false">IF(I58&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N58&gt;1,"4",""),$O58), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S58" s="4" t="str">
-        <f aca="false">IF(J58&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N58&gt;1,$I58=""),"4",""),$O58), "")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T58" s="4" t="str">
-        <f aca="false">IF(K58&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N58&gt;1,"2",""),$O58), "")</f>
+        <f t="shared" si="13"/>
         <v>Motion 2669</v>
       </c>
       <c r="U58" s="4" t="str">
-        <f aca="false">IF(L58&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N58&gt;1,"1",""),$O58), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A59">
         <v>71</v>
       </c>
-      <c r="B59" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" s="0" t="s">
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="s">
         <v>48</v>
       </c>
-      <c r="D59" s="0" t="s">
+      <c r="D59" t="s">
         <v>120</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G59" s="1" t="n">
+      <c r="G59" s="1">
         <v>920</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>21</v>
       </c>
       <c r="M59" s="3" t="str">
-        <f aca="false">IF(A59-A58&lt;&gt;1,A59-A58,"")</f>
-        <v/>
-      </c>
-      <c r="N59" s="3" t="n">
-        <f aca="false">COUNTA(H59:L59)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N59" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O59" s="11" t="n">
-        <f aca="false">G59</f>
+      <c r="O59" s="11">
+        <f>G59</f>
         <v>920</v>
       </c>
       <c r="P59" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D59,3),O59,LEFT(C59,3)))</f>
+        <f t="shared" si="16"/>
         <v>PAL920MAR</v>
       </c>
       <c r="Q59" s="4" t="str">
-        <f aca="false">IF(H59&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N59&gt;1,"5",""),$O59), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R59" s="4" t="str">
-        <f aca="false">IF(I59&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N59&gt;1,"4",""),$O59), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S59" s="4" t="str">
-        <f aca="false">IF(J59&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N59&gt;1,$I59=""),"4",""),$O59), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 920</v>
       </c>
       <c r="T59" s="4" t="str">
-        <f aca="false">IF(K59&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N59&gt;1,"2",""),$O59), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U59" s="4" t="str">
-        <f aca="false">IF(L59&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N59&gt;1,"1",""),$O59), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A60">
         <v>72</v>
       </c>
-      <c r="B60" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" s="0" t="s">
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="s">
         <v>22</v>
       </c>
-      <c r="D60" s="0" t="s">
+      <c r="D60" t="s">
         <v>121</v>
       </c>
       <c r="F60" s="1" t="s">
@@ -4357,52 +4583,52 @@
         <v>40</v>
       </c>
       <c r="M60" s="3" t="str">
-        <f aca="false">IF(A60-A59&lt;&gt;1,A60-A59,"")</f>
-        <v/>
-      </c>
-      <c r="N60" s="3" t="n">
-        <f aca="false">COUNTA(H60:L60)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N60" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O60" s="3" t="n">
+      <c r="O60" s="3">
         <v>631</v>
       </c>
       <c r="P60" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D60,3),O60,LEFT(C60,3)))</f>
+        <f t="shared" si="16"/>
         <v>SAN631SIM</v>
       </c>
       <c r="Q60" s="4" t="str">
-        <f aca="false">IF(H60&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N60&gt;1,"5",""),$O60), "")</f>
+        <f t="shared" si="10"/>
         <v>Motion 631</v>
       </c>
       <c r="R60" s="4" t="str">
-        <f aca="false">IF(I60&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N60&gt;1,"4",""),$O60), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S60" s="4" t="str">
-        <f aca="false">IF(J60&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N60&gt;1,$I60=""),"4",""),$O60), "")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T60" s="4" t="str">
-        <f aca="false">IF(K60&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N60&gt;1,"2",""),$O60), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U60" s="4" t="str">
-        <f aca="false">IF(L60&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N60&gt;1,"1",""),$O60), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A61">
         <v>73</v>
       </c>
-      <c r="B61" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" s="0" t="s">
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="s">
         <v>48</v>
       </c>
-      <c r="D61" s="0" t="s">
+      <c r="D61" t="s">
         <v>122</v>
       </c>
       <c r="F61" s="1" t="s">
@@ -4415,52 +4641,52 @@
         <v>21</v>
       </c>
       <c r="M61" s="3" t="str">
-        <f aca="false">IF(A61-A60&lt;&gt;1,A61-A60,"")</f>
-        <v/>
-      </c>
-      <c r="N61" s="3" t="n">
-        <f aca="false">COUNTA(H61:L61)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N61" s="3">
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="O61" s="3" t="n">
+      <c r="O61" s="3">
         <v>810</v>
       </c>
       <c r="P61" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D61,3),O61,LEFT(C61,3)))</f>
+        <f t="shared" si="16"/>
         <v>NEW810MAR</v>
       </c>
       <c r="Q61" s="4" t="str">
-        <f aca="false">IF(H61&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N61&gt;1,"5",""),$O61), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R61" s="4" t="str">
-        <f aca="false">IF(I61&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N61&gt;1,"4",""),$O61), "")</f>
+        <f t="shared" si="11"/>
         <v>Motion 4810</v>
       </c>
       <c r="S61" s="4" t="str">
-        <f aca="false">IF(J61&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N61&gt;1,$I61=""),"4",""),$O61), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 810</v>
       </c>
       <c r="T61" s="4" t="str">
-        <f aca="false">IF(K61&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N61&gt;1,"2",""),$O61), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U61" s="4" t="str">
-        <f aca="false">IF(L61&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N61&gt;1,"1",""),$O61), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A62">
         <v>75</v>
       </c>
-      <c r="B62" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" s="0" t="s">
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="s">
         <v>123</v>
       </c>
-      <c r="D62" s="0" t="s">
+      <c r="D62" t="s">
         <v>124</v>
       </c>
       <c r="F62" s="1" t="s">
@@ -4469,53 +4695,53 @@
       <c r="J62" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M62" s="12" t="n">
-        <f aca="false">IF(A62-A61&lt;&gt;1,A62-A61,"")</f>
+      <c r="M62" s="12">
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
-      <c r="N62" s="3" t="n">
-        <f aca="false">COUNTA(H62:L62)</f>
+      <c r="N62" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O62" s="3" t="n">
+      <c r="O62" s="3">
         <v>817</v>
       </c>
       <c r="P62" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D62,3),O62,LEFT(C62,3)))</f>
+        <f t="shared" si="16"/>
         <v>MAR817EDD</v>
       </c>
       <c r="Q62" s="4" t="str">
-        <f aca="false">IF(H62&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N62&gt;1,"5",""),$O62), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R62" s="4" t="str">
-        <f aca="false">IF(I62&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N62&gt;1,"4",""),$O62), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S62" s="4" t="str">
-        <f aca="false">IF(J62&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N62&gt;1,$I62=""),"4",""),$O62), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 817</v>
       </c>
       <c r="T62" s="4" t="str">
-        <f aca="false">IF(K62&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N62&gt;1,"2",""),$O62), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U62" s="4" t="str">
-        <f aca="false">IF(L62&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N62&gt;1,"1",""),$O62), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A63">
         <v>76</v>
       </c>
-      <c r="B63" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" s="0" t="s">
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="s">
         <v>125</v>
       </c>
-      <c r="D63" s="0" t="s">
+      <c r="D63" t="s">
         <v>126</v>
       </c>
       <c r="F63" s="1" t="s">
@@ -4525,104 +4751,104 @@
         <v>21</v>
       </c>
       <c r="M63" s="3" t="str">
-        <f aca="false">IF(A63-A62&lt;&gt;1,A63-A62,"")</f>
-        <v/>
-      </c>
-      <c r="N63" s="3" t="n">
-        <f aca="false">COUNTA(H63:L63)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N63" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O63" s="3" t="n">
+      <c r="O63" s="3">
         <v>803</v>
       </c>
       <c r="P63" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D63,3),O63,LEFT(C63,3)))</f>
+        <f t="shared" si="16"/>
         <v>STU803AND</v>
       </c>
       <c r="Q63" s="4" t="str">
-        <f aca="false">IF(H63&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N63&gt;1,"5",""),$O63), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R63" s="4" t="str">
-        <f aca="false">IF(I63&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N63&gt;1,"4",""),$O63), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S63" s="4" t="str">
-        <f aca="false">IF(J63&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N63&gt;1,$I63=""),"4",""),$O63), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 803</v>
       </c>
       <c r="T63" s="4" t="str">
-        <f aca="false">IF(K63&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N63&gt;1,"2",""),$O63), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U63" s="4" t="str">
-        <f aca="false">IF(L63&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N63&gt;1,"1",""),$O63), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A64">
         <v>77</v>
       </c>
-      <c r="B64" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" s="0" t="s">
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="s">
         <v>102</v>
       </c>
-      <c r="D64" s="0" t="s">
+      <c r="D64" t="s">
         <v>127</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>29</v>
       </c>
       <c r="M64" s="3" t="str">
-        <f aca="false">IF(A64-A63&lt;&gt;1,A64-A63,"")</f>
-        <v/>
-      </c>
-      <c r="N64" s="3" t="n">
-        <f aca="false">COUNTA(H64:L64)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N64" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O64" s="3" t="n">
+      <c r="O64" s="3">
         <v>699</v>
       </c>
       <c r="P64" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D64,3),O64,LEFT(C64,3)))</f>
+        <f t="shared" si="16"/>
         <v>LON699JAM</v>
       </c>
       <c r="Q64" s="4" t="str">
-        <f aca="false">IF(H64&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N64&gt;1,"5",""),$O64), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R64" s="4" t="str">
-        <f aca="false">IF(I64&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N64&gt;1,"4",""),$O64), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S64" s="4" t="str">
-        <f aca="false">IF(J64&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N64&gt;1,$I64=""),"4",""),$O64), "")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T64" s="4" t="str">
-        <f aca="false">IF(K64&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N64&gt;1,"2",""),$O64), "")</f>
+        <f t="shared" si="13"/>
         <v>Motion 699</v>
       </c>
       <c r="U64" s="4" t="str">
-        <f aca="false">IF(L64&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N64&gt;1,"1",""),$O64), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A65">
         <v>78</v>
       </c>
-      <c r="B65" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" s="0" t="s">
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="s">
         <v>100</v>
       </c>
-      <c r="D65" s="0" t="s">
+      <c r="D65" t="s">
         <v>87</v>
       </c>
       <c r="F65" s="1" t="s">
@@ -4632,52 +4858,52 @@
         <v>21</v>
       </c>
       <c r="M65" s="3" t="str">
-        <f aca="false">IF(A65-A64&lt;&gt;1,A65-A64,"")</f>
-        <v/>
-      </c>
-      <c r="N65" s="3" t="n">
-        <f aca="false">COUNTA(H65:L65)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N65" s="3">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="O65" s="3" t="n">
+      <c r="O65" s="3">
         <v>656</v>
       </c>
       <c r="P65" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D65,3),O65,LEFT(C65,3)))</f>
+        <f t="shared" si="16"/>
         <v>THO656RUS</v>
       </c>
       <c r="Q65" s="4" t="str">
-        <f aca="false">IF(H65&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N65&gt;1,"5",""),$O65), "")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R65" s="4" t="str">
-        <f aca="false">IF(I65&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N65&gt;1,"4",""),$O65), "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="S65" s="4" t="str">
-        <f aca="false">IF(J65&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N65&gt;1,$I65=""),"4",""),$O65), "")</f>
+        <f t="shared" si="12"/>
         <v>Motion 656</v>
       </c>
       <c r="T65" s="4" t="str">
-        <f aca="false">IF(K65&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N65&gt;1,"2",""),$O65), "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="U65" s="4" t="str">
-        <f aca="false">IF(L65&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N65&gt;1,"1",""),$O65), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="n">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A66">
         <v>79</v>
       </c>
-      <c r="B66" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" s="0" t="s">
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="s">
         <v>128</v>
       </c>
-      <c r="D66" s="0" t="s">
+      <c r="D66" t="s">
         <v>129</v>
       </c>
       <c r="F66" s="1" t="s">
@@ -4687,52 +4913,52 @@
         <v>21</v>
       </c>
       <c r="M66" s="3" t="str">
-        <f aca="false">IF(A66-A65&lt;&gt;1,A66-A65,"")</f>
-        <v/>
-      </c>
-      <c r="N66" s="3" t="n">
-        <f aca="false">COUNTA(H66:L66)</f>
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N66" s="3">
+        <f t="shared" ref="N66:N86" si="17">COUNTA(H66:L66)</f>
         <v>1</v>
       </c>
-      <c r="O66" s="3" t="n">
+      <c r="O66" s="3">
         <v>651</v>
       </c>
       <c r="P66" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D66,3),O66,LEFT(C66,3)))</f>
+        <f t="shared" si="16"/>
         <v>KIR651JON</v>
       </c>
       <c r="Q66" s="4" t="str">
-        <f aca="false">IF(H66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"5",""),$O66), "")</f>
+        <f t="shared" ref="Q66:Q86" si="18">IF(H66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"5",""),$O66), "")</f>
         <v/>
       </c>
       <c r="R66" s="4" t="str">
-        <f aca="false">IF(I66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"4",""),$O66), "")</f>
+        <f t="shared" ref="R66:R86" si="19">IF(I66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"4",""),$O66), "")</f>
         <v/>
       </c>
       <c r="S66" s="4" t="str">
-        <f aca="false">IF(J66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N66&gt;1,$I66=""),"4",""),$O66), "")</f>
+        <f t="shared" ref="S66:S86" si="20">IF(J66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N66&gt;1,$I66=""),"4",""),$O66), "")</f>
         <v>Motion 651</v>
       </c>
       <c r="T66" s="4" t="str">
-        <f aca="false">IF(K66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"2",""),$O66), "")</f>
+        <f t="shared" ref="T66:T86" si="21">IF(K66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"2",""),$O66), "")</f>
         <v/>
       </c>
       <c r="U66" s="4" t="str">
-        <f aca="false">IF(L66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"1",""),$O66), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="n">
+        <f t="shared" ref="U66:U86" si="22">IF(L66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"1",""),$O66), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A67">
         <v>80</v>
       </c>
-      <c r="B67" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" s="0" t="s">
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="s">
         <v>130</v>
       </c>
-      <c r="D67" s="0" t="s">
+      <c r="D67" t="s">
         <v>131</v>
       </c>
       <c r="F67" s="1" t="s">
@@ -4742,52 +4968,52 @@
         <v>21</v>
       </c>
       <c r="M67" s="3" t="str">
-        <f aca="false">IF(A67-A66&lt;&gt;1,A67-A66,"")</f>
-        <v/>
-      </c>
-      <c r="N67" s="3" t="n">
-        <f aca="false">COUNTA(H67:L67)</f>
+        <f t="shared" ref="M67:M86" si="23">IF(A67-A66&lt;&gt;1,A67-A66,"")</f>
+        <v/>
+      </c>
+      <c r="N67" s="3">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O67" s="3" t="n">
+      <c r="O67" s="3">
         <v>836</v>
       </c>
       <c r="P67" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D67,3),O67,LEFT(C67,3)))</f>
+        <f t="shared" si="16"/>
         <v>CRO836JIM</v>
       </c>
       <c r="Q67" s="4" t="str">
-        <f aca="false">IF(H67&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N67&gt;1,"5",""),$O67), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R67" s="4" t="str">
-        <f aca="false">IF(I67&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N67&gt;1,"4",""),$O67), "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S67" s="4" t="str">
-        <f aca="false">IF(J67&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N67&gt;1,$I67=""),"4",""),$O67), "")</f>
+        <f t="shared" si="20"/>
         <v>Motion 836</v>
       </c>
       <c r="T67" s="4" t="str">
-        <f aca="false">IF(K67&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N67&gt;1,"2",""),$O67), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U67" s="4" t="str">
-        <f aca="false">IF(L67&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N67&gt;1,"1",""),$O67), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A68">
         <v>81</v>
       </c>
-      <c r="B68" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" s="0" t="s">
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="s">
         <v>18</v>
       </c>
-      <c r="D68" s="0" t="s">
+      <c r="D68" t="s">
         <v>131</v>
       </c>
       <c r="E68" s="1" t="s">
@@ -4800,52 +5026,52 @@
         <v>21</v>
       </c>
       <c r="M68" s="3" t="str">
-        <f aca="false">IF(A68-A67&lt;&gt;1,A68-A67,"")</f>
-        <v/>
-      </c>
-      <c r="N68" s="3" t="n">
-        <f aca="false">COUNTA(H68:L68)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N68" s="3">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O68" s="3" t="n">
+      <c r="O68" s="3">
         <v>818</v>
       </c>
       <c r="P68" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D68,3),O68,LEFT(C68,3)))</f>
+        <f t="shared" si="16"/>
         <v>CRO818GEO</v>
       </c>
       <c r="Q68" s="4" t="str">
-        <f aca="false">IF(H68&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N68&gt;1,"5",""),$O68), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R68" s="4" t="str">
-        <f aca="false">IF(I68&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N68&gt;1,"4",""),$O68), "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S68" s="4" t="str">
-        <f aca="false">IF(J68&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N68&gt;1,$I68=""),"4",""),$O68), "")</f>
+        <f t="shared" si="20"/>
         <v>Motion 818</v>
       </c>
       <c r="T68" s="4" t="str">
-        <f aca="false">IF(K68&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N68&gt;1,"2",""),$O68), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U68" s="4" t="str">
-        <f aca="false">IF(L68&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N68&gt;1,"1",""),$O68), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A69">
         <v>82</v>
       </c>
-      <c r="B69" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" s="0" t="s">
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="s">
         <v>132</v>
       </c>
-      <c r="D69" s="0" t="s">
+      <c r="D69" t="s">
         <v>131</v>
       </c>
       <c r="E69" s="1" t="s">
@@ -4858,52 +5084,52 @@
         <v>21</v>
       </c>
       <c r="M69" s="3" t="str">
-        <f aca="false">IF(A69-A68&lt;&gt;1,A69-A68,"")</f>
-        <v/>
-      </c>
-      <c r="N69" s="3" t="n">
-        <f aca="false">COUNTA(H69:L69)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N69" s="3">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O69" s="3" t="n">
+      <c r="O69" s="3">
         <v>816</v>
       </c>
       <c r="P69" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D69,3),O69,LEFT(C69,3)))</f>
+        <f t="shared" si="16"/>
         <v>CRO816JAC</v>
       </c>
       <c r="Q69" s="4" t="str">
-        <f aca="false">IF(H69&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N69&gt;1,"5",""),$O69), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R69" s="4" t="str">
-        <f aca="false">IF(I69&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N69&gt;1,"4",""),$O69), "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S69" s="4" t="str">
-        <f aca="false">IF(J69&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N69&gt;1,$I69=""),"4",""),$O69), "")</f>
+        <f t="shared" si="20"/>
         <v>Motion 816</v>
       </c>
       <c r="T69" s="4" t="str">
-        <f aca="false">IF(K69&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N69&gt;1,"2",""),$O69), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U69" s="4" t="str">
-        <f aca="false">IF(L69&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N69&gt;1,"1",""),$O69), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A70">
         <v>83</v>
       </c>
-      <c r="B70" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" s="0" t="s">
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="s">
         <v>60</v>
       </c>
-      <c r="D70" s="0" t="s">
+      <c r="D70" t="s">
         <v>133</v>
       </c>
       <c r="F70" s="1" t="s">
@@ -4916,104 +5142,104 @@
         <v>21</v>
       </c>
       <c r="M70" s="3" t="str">
-        <f aca="false">IF(A70-A69&lt;&gt;1,A70-A69,"")</f>
-        <v/>
-      </c>
-      <c r="N70" s="3" t="n">
-        <f aca="false">COUNTA(H70:L70)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N70" s="3">
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
-      <c r="O70" s="3" t="n">
+      <c r="O70" s="3">
         <v>942</v>
       </c>
       <c r="P70" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D70,3),O70,LEFT(C70,3)))</f>
+        <f t="shared" si="16"/>
         <v>NOR942SCO</v>
       </c>
       <c r="Q70" s="4" t="str">
-        <f aca="false">IF(H70&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N70&gt;1,"5",""),$O70), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R70" s="4" t="str">
-        <f aca="false">IF(I70&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N70&gt;1,"4",""),$O70), "")</f>
+        <f t="shared" si="19"/>
         <v>Motion 4942</v>
       </c>
       <c r="S70" s="4" t="str">
-        <f aca="false">IF(J70&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N70&gt;1,$I70=""),"4",""),$O70), "")</f>
+        <f t="shared" si="20"/>
         <v>Motion 942</v>
       </c>
       <c r="T70" s="4" t="str">
-        <f aca="false">IF(K70&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N70&gt;1,"2",""),$O70), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U70" s="4" t="str">
-        <f aca="false">IF(L70&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N70&gt;1,"1",""),$O70), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A71">
         <v>84</v>
       </c>
-      <c r="B71" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" s="0" t="s">
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="s">
         <v>134</v>
       </c>
-      <c r="D71" s="0" t="s">
+      <c r="D71" t="s">
         <v>135</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>29</v>
       </c>
       <c r="M71" s="3" t="str">
-        <f aca="false">IF(A71-A70&lt;&gt;1,A71-A70,"")</f>
-        <v/>
-      </c>
-      <c r="N71" s="3" t="n">
-        <f aca="false">COUNTA(H71:L71)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N71" s="3">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O71" s="3" t="n">
+      <c r="O71" s="3">
         <v>701</v>
       </c>
       <c r="P71" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D71,3),O71,LEFT(C71,3)))</f>
+        <f t="shared" si="16"/>
         <v>CAM701SEB</v>
       </c>
       <c r="Q71" s="4" t="str">
-        <f aca="false">IF(H71&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N71&gt;1,"5",""),$O71), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R71" s="4" t="str">
-        <f aca="false">IF(I71&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N71&gt;1,"4",""),$O71), "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S71" s="4" t="str">
-        <f aca="false">IF(J71&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N71&gt;1,$I71=""),"4",""),$O71), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="T71" s="4" t="str">
-        <f aca="false">IF(K71&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N71&gt;1,"2",""),$O71), "")</f>
+        <f t="shared" si="21"/>
         <v>Motion 701</v>
       </c>
       <c r="U71" s="4" t="str">
-        <f aca="false">IF(L71&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N71&gt;1,"1",""),$O71), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A72">
         <v>85</v>
       </c>
-      <c r="B72" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" s="0" t="s">
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="s">
         <v>93</v>
       </c>
-      <c r="D72" s="0" t="s">
+      <c r="D72" t="s">
         <v>136</v>
       </c>
       <c r="F72" s="1" t="s">
@@ -5023,52 +5249,52 @@
         <v>21</v>
       </c>
       <c r="M72" s="3" t="str">
-        <f aca="false">IF(A72-A71&lt;&gt;1,A72-A71,"")</f>
-        <v/>
-      </c>
-      <c r="N72" s="3" t="n">
-        <f aca="false">COUNTA(H72:L72)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N72" s="3">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O72" s="3" t="n">
+      <c r="O72" s="3">
         <v>718</v>
       </c>
       <c r="P72" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D72,3),O72,LEFT(C72,3)))</f>
+        <f t="shared" si="16"/>
         <v>HIL718IAN</v>
       </c>
       <c r="Q72" s="4" t="str">
-        <f aca="false">IF(H72&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N72&gt;1,"5",""),$O72), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R72" s="4" t="str">
-        <f aca="false">IF(I72&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N72&gt;1,"4",""),$O72), "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S72" s="4" t="str">
-        <f aca="false">IF(J72&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N72&gt;1,$I72=""),"4",""),$O72), "")</f>
+        <f t="shared" si="20"/>
         <v>Motion 718</v>
       </c>
       <c r="T72" s="4" t="str">
-        <f aca="false">IF(K72&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N72&gt;1,"2",""),$O72), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U72" s="4" t="str">
-        <f aca="false">IF(L72&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N72&gt;1,"1",""),$O72), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A73">
         <v>86</v>
       </c>
-      <c r="B73" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" s="0" t="s">
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="s">
         <v>67</v>
       </c>
-      <c r="D73" s="0" t="s">
+      <c r="D73" t="s">
         <v>137</v>
       </c>
       <c r="F73" s="1" t="s">
@@ -5081,52 +5307,52 @@
         <v>21</v>
       </c>
       <c r="M73" s="3" t="str">
-        <f aca="false">IF(A73-A72&lt;&gt;1,A73-A72,"")</f>
-        <v/>
-      </c>
-      <c r="N73" s="3" t="n">
-        <f aca="false">COUNTA(H73:L73)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N73" s="3">
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
-      <c r="O73" s="3" t="n">
+      <c r="O73" s="3">
         <v>833</v>
       </c>
       <c r="P73" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D73,3),O73,LEFT(C73,3)))</f>
+        <f t="shared" si="16"/>
         <v>TWI833AND</v>
       </c>
       <c r="Q73" s="4" t="str">
-        <f aca="false">IF(H73&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N73&gt;1,"5",""),$O73), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R73" s="4" t="str">
-        <f aca="false">IF(I73&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N73&gt;1,"4",""),$O73), "")</f>
+        <f t="shared" si="19"/>
         <v>Motion 4833</v>
       </c>
       <c r="S73" s="4" t="str">
-        <f aca="false">IF(J73&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N73&gt;1,$I73=""),"4",""),$O73), "")</f>
+        <f t="shared" si="20"/>
         <v>Motion 833</v>
       </c>
       <c r="T73" s="4" t="str">
-        <f aca="false">IF(K73&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N73&gt;1,"2",""),$O73), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U73" s="4" t="str">
-        <f aca="false">IF(L73&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N73&gt;1,"1",""),$O73), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A74">
         <v>87</v>
       </c>
-      <c r="B74" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" s="0" t="s">
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="s">
         <v>138</v>
       </c>
-      <c r="D74" s="0" t="s">
+      <c r="D74" t="s">
         <v>139</v>
       </c>
       <c r="F74" s="1" t="s">
@@ -5136,111 +5362,111 @@
         <v>21</v>
       </c>
       <c r="M74" s="3" t="str">
-        <f aca="false">IF(A74-A73&lt;&gt;1,A74-A73,"")</f>
-        <v/>
-      </c>
-      <c r="N74" s="3" t="n">
-        <f aca="false">COUNTA(H74:L74)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N74" s="3">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O74" s="3" t="n">
+      <c r="O74" s="3">
         <v>811</v>
       </c>
       <c r="P74" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D74,3),O74,LEFT(C74,3)))</f>
+        <f t="shared" si="16"/>
         <v>HUM811TIM</v>
       </c>
       <c r="Q74" s="4" t="str">
-        <f aca="false">IF(H74&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N74&gt;1,"5",""),$O74), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R74" s="4" t="str">
-        <f aca="false">IF(I74&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N74&gt;1,"4",""),$O74), "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S74" s="4" t="str">
-        <f aca="false">IF(J74&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N74&gt;1,$I74=""),"4",""),$O74), "")</f>
+        <f t="shared" si="20"/>
         <v>Motion 811</v>
       </c>
       <c r="T74" s="4" t="str">
-        <f aca="false">IF(K74&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N74&gt;1,"2",""),$O74), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U74" s="4" t="str">
-        <f aca="false">IF(L74&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N74&gt;1,"1",""),$O74), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A75">
         <v>88</v>
       </c>
-      <c r="B75" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" s="0" t="s">
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="s">
         <v>113</v>
       </c>
-      <c r="D75" s="0" t="s">
+      <c r="D75" t="s">
         <v>140</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G75" s="1" t="n">
+      <c r="G75" s="1">
         <v>1002</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>21</v>
       </c>
       <c r="M75" s="3" t="str">
-        <f aca="false">IF(A75-A74&lt;&gt;1,A75-A74,"")</f>
-        <v/>
-      </c>
-      <c r="N75" s="3" t="n">
-        <f aca="false">COUNTA(H75:L75)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N75" s="3">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O75" s="11" t="n">
-        <f aca="false">G75</f>
+      <c r="O75" s="11">
+        <f>G75</f>
         <v>1002</v>
       </c>
       <c r="P75" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D75,3),O75,LEFT(C75,3)))</f>
+        <f t="shared" ref="P75:P106" si="24">UPPER(_xlfn.CONCAT(LEFT(D75,3),O75,LEFT(C75,3)))</f>
         <v>GOO1002GAR</v>
       </c>
       <c r="Q75" s="4" t="str">
-        <f aca="false">IF(H75&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N75&gt;1,"5",""),$O75), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R75" s="4" t="str">
-        <f aca="false">IF(I75&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N75&gt;1,"4",""),$O75), "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S75" s="4" t="str">
-        <f aca="false">IF(J75&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N75&gt;1,$I75=""),"4",""),$O75), "")</f>
+        <f t="shared" si="20"/>
         <v>Motion 1002</v>
       </c>
       <c r="T75" s="4" t="str">
-        <f aca="false">IF(K75&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N75&gt;1,"2",""),$O75), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U75" s="4" t="str">
-        <f aca="false">IF(L75&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N75&gt;1,"1",""),$O75), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A76">
         <v>89</v>
       </c>
-      <c r="B76" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" s="0" t="s">
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="s">
         <v>141</v>
       </c>
-      <c r="D76" s="0" t="s">
+      <c r="D76" t="s">
         <v>142</v>
       </c>
       <c r="F76" s="1" t="s">
@@ -5250,52 +5476,52 @@
         <v>21</v>
       </c>
       <c r="M76" s="3" t="str">
-        <f aca="false">IF(A76-A75&lt;&gt;1,A76-A75,"")</f>
-        <v/>
-      </c>
-      <c r="N76" s="3" t="n">
-        <f aca="false">COUNTA(H76:L76)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N76" s="3">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O76" s="3" t="n">
+      <c r="O76" s="3">
         <v>647</v>
       </c>
       <c r="P76" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D76,3),O76,LEFT(C76,3)))</f>
+        <f t="shared" si="24"/>
         <v>WHA647TRE</v>
       </c>
       <c r="Q76" s="4" t="str">
-        <f aca="false">IF(H76&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N76&gt;1,"5",""),$O76), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R76" s="4" t="str">
-        <f aca="false">IF(I76&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N76&gt;1,"4",""),$O76), "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S76" s="4" t="str">
-        <f aca="false">IF(J76&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N76&gt;1,$I76=""),"4",""),$O76), "")</f>
+        <f t="shared" si="20"/>
         <v>Motion 647</v>
       </c>
       <c r="T76" s="4" t="str">
-        <f aca="false">IF(K76&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N76&gt;1,"2",""),$O76), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U76" s="4" t="str">
-        <f aca="false">IF(L76&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N76&gt;1,"1",""),$O76), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A77">
         <v>90</v>
       </c>
-      <c r="B77" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" s="0" t="s">
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="s">
         <v>105</v>
       </c>
-      <c r="D77" s="0" t="s">
+      <c r="D77" t="s">
         <v>143</v>
       </c>
       <c r="E77" s="1" t="s">
@@ -5308,222 +5534,222 @@
         <v>21</v>
       </c>
       <c r="M77" s="3" t="str">
-        <f aca="false">IF(A77-A76&lt;&gt;1,A77-A76,"")</f>
-        <v/>
-      </c>
-      <c r="N77" s="3" t="n">
-        <f aca="false">COUNTA(H77:L77)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N77" s="3">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O77" s="3" t="n">
+      <c r="O77" s="3">
         <v>1040</v>
       </c>
       <c r="P77" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D77,3),O77,LEFT(C77,3)))</f>
+        <f t="shared" si="24"/>
         <v>KIE1040OLI</v>
       </c>
       <c r="Q77" s="4" t="str">
-        <f aca="false">IF(H77&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N77&gt;1,"5",""),$O77), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R77" s="4" t="str">
-        <f aca="false">IF(I77&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N77&gt;1,"4",""),$O77), "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S77" s="4" t="str">
-        <f aca="false">IF(J77&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N77&gt;1,$I77=""),"4",""),$O77), "")</f>
+        <f t="shared" si="20"/>
         <v>Motion 1040</v>
       </c>
       <c r="T77" s="4" t="str">
-        <f aca="false">IF(K77&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N77&gt;1,"2",""),$O77), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U77" s="4" t="str">
-        <f aca="false">IF(L77&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N77&gt;1,"1",""),$O77), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A78">
         <v>91</v>
       </c>
-      <c r="B78" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" s="0" t="s">
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="s">
         <v>144</v>
       </c>
-      <c r="D78" s="0" t="s">
+      <c r="D78" t="s">
         <v>145</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G78" s="1" t="n">
+      <c r="G78" s="1">
         <v>676</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>21</v>
       </c>
       <c r="M78" s="3" t="str">
-        <f aca="false">IF(A78-A77&lt;&gt;1,A78-A77,"")</f>
-        <v/>
-      </c>
-      <c r="N78" s="3" t="n">
-        <f aca="false">COUNTA(H78:L78)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N78" s="3">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O78" s="11" t="n">
-        <f aca="false">G78</f>
+      <c r="O78" s="11">
+        <f>G78</f>
         <v>676</v>
       </c>
       <c r="P78" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D78,3),O78,LEFT(C78,3)))</f>
+        <f t="shared" si="24"/>
         <v>NEA676IAI</v>
       </c>
       <c r="Q78" s="4" t="str">
-        <f aca="false">IF(H78&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N78&gt;1,"5",""),$O78), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R78" s="4" t="str">
-        <f aca="false">IF(I78&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N78&gt;1,"4",""),$O78), "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S78" s="4" t="str">
-        <f aca="false">IF(J78&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N78&gt;1,$I78=""),"4",""),$O78), "")</f>
+        <f t="shared" si="20"/>
         <v>Motion 676</v>
       </c>
       <c r="T78" s="4" t="str">
-        <f aca="false">IF(K78&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N78&gt;1,"2",""),$O78), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U78" s="4" t="str">
-        <f aca="false">IF(L78&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N78&gt;1,"1",""),$O78), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A79">
         <v>92</v>
       </c>
-      <c r="B79" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" s="0" t="s">
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="s">
         <v>146</v>
       </c>
-      <c r="D79" s="0" t="s">
+      <c r="D79" t="s">
         <v>147</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>29</v>
       </c>
       <c r="M79" s="3" t="str">
-        <f aca="false">IF(A79-A78&lt;&gt;1,A79-A78,"")</f>
-        <v/>
-      </c>
-      <c r="N79" s="3" t="n">
-        <f aca="false">COUNTA(H79:L79)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N79" s="3">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O79" s="3" t="n">
+      <c r="O79" s="3">
         <v>660</v>
       </c>
       <c r="P79" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D79,3),O79,LEFT(C79,3)))</f>
+        <f t="shared" si="24"/>
         <v>CAR660MAR</v>
       </c>
       <c r="Q79" s="4" t="str">
-        <f aca="false">IF(H79&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N79&gt;1,"5",""),$O79), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R79" s="4" t="str">
-        <f aca="false">IF(I79&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N79&gt;1,"4",""),$O79), "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S79" s="4" t="str">
-        <f aca="false">IF(J79&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N79&gt;1,$I79=""),"4",""),$O79), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="T79" s="4" t="str">
-        <f aca="false">IF(K79&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N79&gt;1,"2",""),$O79), "")</f>
+        <f t="shared" si="21"/>
         <v>Motion 660</v>
       </c>
       <c r="U79" s="4" t="str">
-        <f aca="false">IF(L79&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N79&gt;1,"1",""),$O79), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A80">
         <v>93</v>
       </c>
-      <c r="B80" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" s="0" t="s">
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="s">
         <v>148</v>
       </c>
-      <c r="D80" s="0" t="s">
+      <c r="D80" t="s">
         <v>149</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G80" s="1" t="n">
+      <c r="G80" s="1">
         <v>704</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>21</v>
       </c>
       <c r="M80" s="3" t="str">
-        <f aca="false">IF(A80-A79&lt;&gt;1,A80-A79,"")</f>
-        <v/>
-      </c>
-      <c r="N80" s="3" t="n">
-        <f aca="false">COUNTA(H80:L80)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N80" s="3">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O80" s="11" t="n">
-        <f aca="false">G80</f>
+      <c r="O80" s="11">
+        <f>G80</f>
         <v>704</v>
       </c>
       <c r="P80" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D80,3),O80,LEFT(C80,3)))</f>
+        <f t="shared" si="24"/>
         <v>VER704SHA</v>
       </c>
       <c r="Q80" s="4" t="str">
-        <f aca="false">IF(H80&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N80&gt;1,"5",""),$O80), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R80" s="4" t="str">
-        <f aca="false">IF(I80&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N80&gt;1,"4",""),$O80), "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S80" s="4" t="str">
-        <f aca="false">IF(J80&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N80&gt;1,$I80=""),"4",""),$O80), "")</f>
+        <f t="shared" si="20"/>
         <v>Motion 704</v>
       </c>
       <c r="T80" s="4" t="str">
-        <f aca="false">IF(K80&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N80&gt;1,"2",""),$O80), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U80" s="4" t="str">
-        <f aca="false">IF(L80&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N80&gt;1,"1",""),$O80), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A81">
         <v>94</v>
       </c>
-      <c r="B81" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" s="0" t="s">
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="s">
         <v>85</v>
       </c>
-      <c r="D81" s="0" t="s">
+      <c r="D81" t="s">
         <v>150</v>
       </c>
       <c r="F81" s="1" t="s">
@@ -5533,52 +5759,52 @@
         <v>21</v>
       </c>
       <c r="M81" s="3" t="str">
-        <f aca="false">IF(A81-A80&lt;&gt;1,A81-A80,"")</f>
-        <v/>
-      </c>
-      <c r="N81" s="3" t="n">
-        <f aca="false">COUNTA(H81:L81)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N81" s="3">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O81" s="3" t="n">
+      <c r="O81" s="3">
         <v>661</v>
       </c>
       <c r="P81" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D81,3),O81,LEFT(C81,3)))</f>
+        <f t="shared" si="24"/>
         <v>BRA661PAU</v>
       </c>
       <c r="Q81" s="4" t="str">
-        <f aca="false">IF(H81&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N81&gt;1,"5",""),$O81), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R81" s="4" t="str">
-        <f aca="false">IF(I81&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N81&gt;1,"4",""),$O81), "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S81" s="4" t="str">
-        <f aca="false">IF(J81&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N81&gt;1,$I81=""),"4",""),$O81), "")</f>
+        <f t="shared" si="20"/>
         <v>Motion 661</v>
       </c>
       <c r="T81" s="4" t="str">
-        <f aca="false">IF(K81&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N81&gt;1,"2",""),$O81), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U81" s="4" t="str">
-        <f aca="false">IF(L81&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N81&gt;1,"1",""),$O81), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A82">
         <v>96</v>
       </c>
-      <c r="B82" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" s="0" t="s">
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="s">
         <v>151</v>
       </c>
-      <c r="D82" s="0" t="s">
+      <c r="D82" t="s">
         <v>152</v>
       </c>
       <c r="F82" s="1" t="s">
@@ -5590,53 +5816,53 @@
       <c r="J82" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M82" s="12" t="n">
-        <f aca="false">IF(A82-A81&lt;&gt;1,A82-A81,"")</f>
+      <c r="M82" s="12">
+        <f t="shared" si="23"/>
         <v>2</v>
       </c>
-      <c r="N82" s="3" t="n">
-        <f aca="false">COUNTA(H82:L82)</f>
+      <c r="N82" s="3">
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
-      <c r="O82" s="3" t="n">
+      <c r="O82" s="3">
         <v>866</v>
       </c>
       <c r="P82" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D82,3),O82,LEFT(C82,3)))</f>
+        <f t="shared" si="24"/>
         <v>CRO866ALL</v>
       </c>
       <c r="Q82" s="4" t="str">
-        <f aca="false">IF(H82&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N82&gt;1,"5",""),$O82), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R82" s="4" t="str">
-        <f aca="false">IF(I82&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N82&gt;1,"4",""),$O82), "")</f>
+        <f t="shared" si="19"/>
         <v>Motion 4866</v>
       </c>
       <c r="S82" s="4" t="str">
-        <f aca="false">IF(J82&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N82&gt;1,$I82=""),"4",""),$O82), "")</f>
+        <f t="shared" si="20"/>
         <v>Motion 866</v>
       </c>
       <c r="T82" s="4" t="str">
-        <f aca="false">IF(K82&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N82&gt;1,"2",""),$O82), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U82" s="4" t="str">
-        <f aca="false">IF(L82&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N82&gt;1,"1",""),$O82), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A83">
         <v>97</v>
       </c>
-      <c r="B83" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" s="0" t="s">
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="s">
         <v>153</v>
       </c>
-      <c r="D83" s="0" t="s">
+      <c r="D83" t="s">
         <v>154</v>
       </c>
       <c r="E83" s="1" t="s">
@@ -5649,52 +5875,52 @@
         <v>40</v>
       </c>
       <c r="M83" s="3" t="str">
-        <f aca="false">IF(A83-A82&lt;&gt;1,A83-A82,"")</f>
-        <v/>
-      </c>
-      <c r="N83" s="3" t="n">
-        <f aca="false">COUNTA(H83:L83)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N83" s="3">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O83" s="3" t="n">
+      <c r="O83" s="3">
         <v>825</v>
       </c>
       <c r="P83" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D83,3),O83,LEFT(C83,3)))</f>
+        <f t="shared" si="24"/>
         <v>MIL825JAY</v>
       </c>
       <c r="Q83" s="4" t="str">
-        <f aca="false">IF(H83&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N83&gt;1,"5",""),$O83), "")</f>
+        <f t="shared" si="18"/>
         <v>Motion 825</v>
       </c>
       <c r="R83" s="4" t="str">
-        <f aca="false">IF(I83&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N83&gt;1,"4",""),$O83), "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S83" s="4" t="str">
-        <f aca="false">IF(J83&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N83&gt;1,$I83=""),"4",""),$O83), "")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="T83" s="4" t="str">
-        <f aca="false">IF(K83&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N83&gt;1,"2",""),$O83), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U83" s="4" t="str">
-        <f aca="false">IF(L83&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N83&gt;1,"1",""),$O83), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A84">
         <v>98</v>
       </c>
-      <c r="B84" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" s="0" t="s">
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="s">
         <v>99</v>
       </c>
-      <c r="D84" s="0" t="s">
+      <c r="D84" t="s">
         <v>155</v>
       </c>
       <c r="F84" s="1" t="s">
@@ -5704,52 +5930,52 @@
         <v>21</v>
       </c>
       <c r="M84" s="3" t="str">
-        <f aca="false">IF(A84-A83&lt;&gt;1,A84-A83,"")</f>
-        <v/>
-      </c>
-      <c r="N84" s="3" t="n">
-        <f aca="false">COUNTA(H84:L84)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N84" s="3">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O84" s="3" t="n">
+      <c r="O84" s="3">
         <v>633</v>
       </c>
       <c r="P84" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D84,3),O84,LEFT(C84,3)))</f>
+        <f t="shared" si="24"/>
         <v>PEN633ROB</v>
       </c>
       <c r="Q84" s="4" t="str">
-        <f aca="false">IF(H84&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N84&gt;1,"5",""),$O84), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R84" s="4" t="str">
-        <f aca="false">IF(I84&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N84&gt;1,"4",""),$O84), "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S84" s="4" t="str">
-        <f aca="false">IF(J84&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N84&gt;1,$I84=""),"4",""),$O84), "")</f>
+        <f t="shared" si="20"/>
         <v>Motion 633</v>
       </c>
       <c r="T84" s="4" t="str">
-        <f aca="false">IF(K84&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N84&gt;1,"2",""),$O84), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U84" s="4" t="str">
-        <f aca="false">IF(L84&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N84&gt;1,"1",""),$O84), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A85">
         <v>99</v>
       </c>
-      <c r="B85" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" s="0" t="s">
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="s">
         <v>76</v>
       </c>
-      <c r="D85" s="0" t="s">
+      <c r="D85" t="s">
         <v>156</v>
       </c>
       <c r="F85" s="1" t="s">
@@ -5762,52 +5988,52 @@
         <v>29</v>
       </c>
       <c r="M85" s="3" t="str">
-        <f aca="false">IF(A85-A84&lt;&gt;1,A85-A84,"")</f>
-        <v/>
-      </c>
-      <c r="N85" s="3" t="n">
-        <f aca="false">COUNTA(H85:L85)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N85" s="3">
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
-      <c r="O85" s="3" t="n">
+      <c r="O85" s="3">
         <v>695</v>
       </c>
       <c r="P85" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D85,3),O85,LEFT(C85,3)))</f>
+        <f t="shared" si="24"/>
         <v>DAV695STE</v>
       </c>
       <c r="Q85" s="4" t="str">
-        <f aca="false">IF(H85&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N85&gt;1,"5",""),$O85), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R85" s="4" t="str">
-        <f aca="false">IF(I85&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N85&gt;1,"4",""),$O85), "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S85" s="4" t="str">
-        <f aca="false">IF(J85&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N85&gt;1,$I85=""),"4",""),$O85), "")</f>
+        <f t="shared" si="20"/>
         <v>Motion 4695</v>
       </c>
       <c r="T85" s="4" t="str">
-        <f aca="false">IF(K85&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N85&gt;1,"2",""),$O85), "")</f>
+        <f t="shared" si="21"/>
         <v>Motion 2695</v>
       </c>
       <c r="U85" s="4" t="str">
-        <f aca="false">IF(L85&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N85&gt;1,"1",""),$O85), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="n">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A86">
         <v>100</v>
       </c>
-      <c r="B86" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" s="0" t="s">
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="s">
         <v>157</v>
       </c>
-      <c r="D86" s="0" t="s">
+      <c r="D86" t="s">
         <v>158</v>
       </c>
       <c r="E86" s="1" t="s">
@@ -5820,50 +6046,1777 @@
         <v>21</v>
       </c>
       <c r="M86" s="3" t="str">
-        <f aca="false">IF(A86-A85&lt;&gt;1,A86-A85,"")</f>
-        <v/>
-      </c>
-      <c r="N86" s="3" t="n">
-        <f aca="false">COUNTA(H86:L86)</f>
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N86" s="3">
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O86" s="3" t="n">
+      <c r="O86" s="3">
         <v>823</v>
       </c>
       <c r="P86" s="3" t="str">
-        <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D86,3),O86,LEFT(C86,3)))</f>
+        <f t="shared" si="24"/>
         <v>VIC823MIT</v>
       </c>
       <c r="Q86" s="4" t="str">
-        <f aca="false">IF(H86&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N86&gt;1,"5",""),$O86), "")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R86" s="4" t="str">
-        <f aca="false">IF(I86&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N86&gt;1,"4",""),$O86), "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S86" s="4" t="str">
-        <f aca="false">IF(J86&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N86&gt;1,$I86=""),"4",""),$O86), "")</f>
+        <f t="shared" si="20"/>
         <v>Motion 823</v>
       </c>
       <c r="T86" s="4" t="str">
-        <f aca="false">IF(K86&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N86&gt;1,"2",""),$O86), "")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="U86" s="4" t="str">
-        <f aca="false">IF(L86&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N86&gt;1,"1",""),$O86), "")</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U86"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:U86" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76855B16-A584-4DC9-9954-AFD12940DB0D}">
+  <dimension ref="A1:F86"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E7" t="s">
+        <v>159</v>
+      </c>
+      <c r="F7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E8" t="s">
+        <v>159</v>
+      </c>
+      <c r="F8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D10" t="s">
+        <v>172</v>
+      </c>
+      <c r="E10" t="s">
+        <v>159</v>
+      </c>
+      <c r="F10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" t="s">
+        <v>174</v>
+      </c>
+      <c r="E11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E12" t="s">
+        <v>159</v>
+      </c>
+      <c r="F12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>176</v>
+      </c>
+      <c r="C13" t="s">
+        <v>159</v>
+      </c>
+      <c r="D13" t="s">
+        <v>159</v>
+      </c>
+      <c r="E13" t="s">
+        <v>159</v>
+      </c>
+      <c r="F13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" t="s">
+        <v>177</v>
+      </c>
+      <c r="E14" t="s">
+        <v>159</v>
+      </c>
+      <c r="F14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" t="s">
+        <v>178</v>
+      </c>
+      <c r="D15" t="s">
+        <v>179</v>
+      </c>
+      <c r="E15" t="s">
+        <v>159</v>
+      </c>
+      <c r="F15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>180</v>
+      </c>
+      <c r="C16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D16" t="s">
+        <v>159</v>
+      </c>
+      <c r="E16" t="s">
+        <v>159</v>
+      </c>
+      <c r="F16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" t="s">
+        <v>181</v>
+      </c>
+      <c r="E17" t="s">
+        <v>159</v>
+      </c>
+      <c r="F17" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D18" t="s">
+        <v>182</v>
+      </c>
+      <c r="E18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>30</v>
+      </c>
+      <c r="B19" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19" t="s">
+        <v>183</v>
+      </c>
+      <c r="D19" t="s">
+        <v>184</v>
+      </c>
+      <c r="E19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" t="s">
+        <v>159</v>
+      </c>
+      <c r="D20" t="s">
+        <v>185</v>
+      </c>
+      <c r="E20" t="s">
+        <v>159</v>
+      </c>
+      <c r="F20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21" t="s">
+        <v>159</v>
+      </c>
+      <c r="D21" t="s">
+        <v>186</v>
+      </c>
+      <c r="E21" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22" t="s">
+        <v>187</v>
+      </c>
+      <c r="D22" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22" t="s">
+        <v>159</v>
+      </c>
+      <c r="F22" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>34</v>
+      </c>
+      <c r="B23" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" t="s">
+        <v>189</v>
+      </c>
+      <c r="D23" t="s">
+        <v>190</v>
+      </c>
+      <c r="E23" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>35</v>
+      </c>
+      <c r="B24" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" t="s">
+        <v>191</v>
+      </c>
+      <c r="E24" t="s">
+        <v>159</v>
+      </c>
+      <c r="F24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" t="s">
+        <v>192</v>
+      </c>
+      <c r="D25" t="s">
+        <v>193</v>
+      </c>
+      <c r="E25" t="s">
+        <v>159</v>
+      </c>
+      <c r="F25" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>37</v>
+      </c>
+      <c r="B26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" t="s">
+        <v>159</v>
+      </c>
+      <c r="D26" t="s">
+        <v>194</v>
+      </c>
+      <c r="E26" t="s">
+        <v>159</v>
+      </c>
+      <c r="F26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" t="s">
+        <v>159</v>
+      </c>
+      <c r="D27" t="s">
+        <v>195</v>
+      </c>
+      <c r="E27" t="s">
+        <v>159</v>
+      </c>
+      <c r="F27" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>39</v>
+      </c>
+      <c r="B28" t="s">
+        <v>196</v>
+      </c>
+      <c r="C28" t="s">
+        <v>159</v>
+      </c>
+      <c r="D28" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" t="s">
+        <v>159</v>
+      </c>
+      <c r="F28" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>40</v>
+      </c>
+      <c r="B29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C29" t="s">
+        <v>159</v>
+      </c>
+      <c r="D29" t="s">
+        <v>197</v>
+      </c>
+      <c r="E29" t="s">
+        <v>159</v>
+      </c>
+      <c r="F29" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" t="s">
+        <v>159</v>
+      </c>
+      <c r="D30" t="s">
+        <v>198</v>
+      </c>
+      <c r="E30" t="s">
+        <v>159</v>
+      </c>
+      <c r="F30" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>42</v>
+      </c>
+      <c r="B31" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" t="s">
+        <v>159</v>
+      </c>
+      <c r="D31" t="s">
+        <v>199</v>
+      </c>
+      <c r="E31" t="s">
+        <v>159</v>
+      </c>
+      <c r="F31" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>43</v>
+      </c>
+      <c r="B32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" t="s">
+        <v>159</v>
+      </c>
+      <c r="D32" t="s">
+        <v>200</v>
+      </c>
+      <c r="E32" t="s">
+        <v>159</v>
+      </c>
+      <c r="F32" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>44</v>
+      </c>
+      <c r="B33" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" t="s">
+        <v>201</v>
+      </c>
+      <c r="D33" t="s">
+        <v>202</v>
+      </c>
+      <c r="E33" t="s">
+        <v>159</v>
+      </c>
+      <c r="F33" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>45</v>
+      </c>
+      <c r="B34" t="s">
+        <v>159</v>
+      </c>
+      <c r="C34" t="s">
+        <v>159</v>
+      </c>
+      <c r="D34" t="s">
+        <v>203</v>
+      </c>
+      <c r="E34" t="s">
+        <v>159</v>
+      </c>
+      <c r="F34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>46</v>
+      </c>
+      <c r="B35" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" t="s">
+        <v>204</v>
+      </c>
+      <c r="D35" t="s">
+        <v>205</v>
+      </c>
+      <c r="E35" t="s">
+        <v>159</v>
+      </c>
+      <c r="F35" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>47</v>
+      </c>
+      <c r="B36" t="s">
+        <v>159</v>
+      </c>
+      <c r="C36" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" t="s">
+        <v>206</v>
+      </c>
+      <c r="E36" t="s">
+        <v>159</v>
+      </c>
+      <c r="F36" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>48</v>
+      </c>
+      <c r="B37" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" t="s">
+        <v>159</v>
+      </c>
+      <c r="D37" t="s">
+        <v>207</v>
+      </c>
+      <c r="E37" t="s">
+        <v>159</v>
+      </c>
+      <c r="F37" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>49</v>
+      </c>
+      <c r="B38" t="s">
+        <v>159</v>
+      </c>
+      <c r="C38" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38" t="s">
+        <v>208</v>
+      </c>
+      <c r="E38" t="s">
+        <v>159</v>
+      </c>
+      <c r="F38" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>50</v>
+      </c>
+      <c r="B39" t="s">
+        <v>159</v>
+      </c>
+      <c r="C39" t="s">
+        <v>159</v>
+      </c>
+      <c r="D39" t="s">
+        <v>209</v>
+      </c>
+      <c r="E39" t="s">
+        <v>159</v>
+      </c>
+      <c r="F39" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>51</v>
+      </c>
+      <c r="B40" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" t="s">
+        <v>159</v>
+      </c>
+      <c r="D40" t="s">
+        <v>210</v>
+      </c>
+      <c r="E40" t="s">
+        <v>159</v>
+      </c>
+      <c r="F40" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>52</v>
+      </c>
+      <c r="B41" t="s">
+        <v>159</v>
+      </c>
+      <c r="C41" t="s">
+        <v>159</v>
+      </c>
+      <c r="D41" t="s">
+        <v>211</v>
+      </c>
+      <c r="E41" t="s">
+        <v>159</v>
+      </c>
+      <c r="F41" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>53</v>
+      </c>
+      <c r="B42" t="s">
+        <v>159</v>
+      </c>
+      <c r="C42" t="s">
+        <v>159</v>
+      </c>
+      <c r="D42" t="s">
+        <v>212</v>
+      </c>
+      <c r="E42" t="s">
+        <v>159</v>
+      </c>
+      <c r="F42" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>54</v>
+      </c>
+      <c r="B43" t="s">
+        <v>213</v>
+      </c>
+      <c r="C43" t="s">
+        <v>159</v>
+      </c>
+      <c r="D43" t="s">
+        <v>159</v>
+      </c>
+      <c r="E43" t="s">
+        <v>159</v>
+      </c>
+      <c r="F43" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>55</v>
+      </c>
+      <c r="B44" t="s">
+        <v>159</v>
+      </c>
+      <c r="C44" t="s">
+        <v>159</v>
+      </c>
+      <c r="D44" t="s">
+        <v>159</v>
+      </c>
+      <c r="E44" t="s">
+        <v>214</v>
+      </c>
+      <c r="F44" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>56</v>
+      </c>
+      <c r="B45" t="s">
+        <v>159</v>
+      </c>
+      <c r="C45" t="s">
+        <v>215</v>
+      </c>
+      <c r="D45" t="s">
+        <v>216</v>
+      </c>
+      <c r="E45" t="s">
+        <v>159</v>
+      </c>
+      <c r="F45" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>57</v>
+      </c>
+      <c r="B46" t="s">
+        <v>159</v>
+      </c>
+      <c r="C46" t="s">
+        <v>159</v>
+      </c>
+      <c r="D46" t="s">
+        <v>217</v>
+      </c>
+      <c r="E46" t="s">
+        <v>159</v>
+      </c>
+      <c r="F46" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>58</v>
+      </c>
+      <c r="B47" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" t="s">
+        <v>159</v>
+      </c>
+      <c r="D47" t="s">
+        <v>219</v>
+      </c>
+      <c r="E47" t="s">
+        <v>159</v>
+      </c>
+      <c r="F47" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>59</v>
+      </c>
+      <c r="B48" t="s">
+        <v>159</v>
+      </c>
+      <c r="C48" t="s">
+        <v>159</v>
+      </c>
+      <c r="D48" t="s">
+        <v>220</v>
+      </c>
+      <c r="E48" t="s">
+        <v>159</v>
+      </c>
+      <c r="F48" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>60</v>
+      </c>
+      <c r="B49" t="s">
+        <v>159</v>
+      </c>
+      <c r="C49" t="s">
+        <v>159</v>
+      </c>
+      <c r="D49" t="s">
+        <v>221</v>
+      </c>
+      <c r="E49" t="s">
+        <v>159</v>
+      </c>
+      <c r="F49" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>61</v>
+      </c>
+      <c r="B50" t="s">
+        <v>159</v>
+      </c>
+      <c r="C50" t="s">
+        <v>159</v>
+      </c>
+      <c r="D50" t="s">
+        <v>159</v>
+      </c>
+      <c r="E50" t="s">
+        <v>159</v>
+      </c>
+      <c r="F50" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>63</v>
+      </c>
+      <c r="B51" t="s">
+        <v>223</v>
+      </c>
+      <c r="C51" t="s">
+        <v>159</v>
+      </c>
+      <c r="D51" t="s">
+        <v>159</v>
+      </c>
+      <c r="E51" t="s">
+        <v>159</v>
+      </c>
+      <c r="F51" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>64</v>
+      </c>
+      <c r="B52" t="s">
+        <v>224</v>
+      </c>
+      <c r="C52" t="s">
+        <v>159</v>
+      </c>
+      <c r="D52" t="s">
+        <v>159</v>
+      </c>
+      <c r="E52" t="s">
+        <v>159</v>
+      </c>
+      <c r="F52" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>65</v>
+      </c>
+      <c r="B53" t="s">
+        <v>225</v>
+      </c>
+      <c r="C53" t="s">
+        <v>159</v>
+      </c>
+      <c r="D53" t="s">
+        <v>159</v>
+      </c>
+      <c r="E53" t="s">
+        <v>159</v>
+      </c>
+      <c r="F53" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>66</v>
+      </c>
+      <c r="B54" t="s">
+        <v>226</v>
+      </c>
+      <c r="C54" t="s">
+        <v>159</v>
+      </c>
+      <c r="D54" t="s">
+        <v>159</v>
+      </c>
+      <c r="E54" t="s">
+        <v>159</v>
+      </c>
+      <c r="F54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>67</v>
+      </c>
+      <c r="B55" t="s">
+        <v>159</v>
+      </c>
+      <c r="C55" t="s">
+        <v>227</v>
+      </c>
+      <c r="D55" t="s">
+        <v>228</v>
+      </c>
+      <c r="E55" t="s">
+        <v>159</v>
+      </c>
+      <c r="F55" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>68</v>
+      </c>
+      <c r="B56" t="s">
+        <v>159</v>
+      </c>
+      <c r="C56" t="s">
+        <v>229</v>
+      </c>
+      <c r="D56" t="s">
+        <v>230</v>
+      </c>
+      <c r="E56" t="s">
+        <v>159</v>
+      </c>
+      <c r="F56" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>69</v>
+      </c>
+      <c r="B57" t="s">
+        <v>159</v>
+      </c>
+      <c r="C57" t="s">
+        <v>159</v>
+      </c>
+      <c r="D57" t="s">
+        <v>231</v>
+      </c>
+      <c r="E57" t="s">
+        <v>159</v>
+      </c>
+      <c r="F57" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>70</v>
+      </c>
+      <c r="B58" t="s">
+        <v>232</v>
+      </c>
+      <c r="C58" t="s">
+        <v>159</v>
+      </c>
+      <c r="D58" t="s">
+        <v>159</v>
+      </c>
+      <c r="E58" t="s">
+        <v>233</v>
+      </c>
+      <c r="F58" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>71</v>
+      </c>
+      <c r="B59" t="s">
+        <v>159</v>
+      </c>
+      <c r="C59" t="s">
+        <v>159</v>
+      </c>
+      <c r="D59" t="s">
+        <v>234</v>
+      </c>
+      <c r="E59" t="s">
+        <v>159</v>
+      </c>
+      <c r="F59" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>72</v>
+      </c>
+      <c r="B60" t="s">
+        <v>235</v>
+      </c>
+      <c r="C60" t="s">
+        <v>159</v>
+      </c>
+      <c r="D60" t="s">
+        <v>159</v>
+      </c>
+      <c r="E60" t="s">
+        <v>159</v>
+      </c>
+      <c r="F60" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>73</v>
+      </c>
+      <c r="B61" t="s">
+        <v>159</v>
+      </c>
+      <c r="C61" t="s">
+        <v>236</v>
+      </c>
+      <c r="D61" t="s">
+        <v>237</v>
+      </c>
+      <c r="E61" t="s">
+        <v>159</v>
+      </c>
+      <c r="F61" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>75</v>
+      </c>
+      <c r="B62" t="s">
+        <v>159</v>
+      </c>
+      <c r="C62" t="s">
+        <v>159</v>
+      </c>
+      <c r="D62" t="s">
+        <v>238</v>
+      </c>
+      <c r="E62" t="s">
+        <v>159</v>
+      </c>
+      <c r="F62" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>76</v>
+      </c>
+      <c r="B63" t="s">
+        <v>159</v>
+      </c>
+      <c r="C63" t="s">
+        <v>159</v>
+      </c>
+      <c r="D63" t="s">
+        <v>239</v>
+      </c>
+      <c r="E63" t="s">
+        <v>159</v>
+      </c>
+      <c r="F63" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>77</v>
+      </c>
+      <c r="B64" t="s">
+        <v>159</v>
+      </c>
+      <c r="C64" t="s">
+        <v>159</v>
+      </c>
+      <c r="D64" t="s">
+        <v>159</v>
+      </c>
+      <c r="E64" t="s">
+        <v>240</v>
+      </c>
+      <c r="F64" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>78</v>
+      </c>
+      <c r="B65" t="s">
+        <v>159</v>
+      </c>
+      <c r="C65" t="s">
+        <v>159</v>
+      </c>
+      <c r="D65" t="s">
+        <v>241</v>
+      </c>
+      <c r="E65" t="s">
+        <v>159</v>
+      </c>
+      <c r="F65" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>79</v>
+      </c>
+      <c r="B66" t="s">
+        <v>159</v>
+      </c>
+      <c r="C66" t="s">
+        <v>159</v>
+      </c>
+      <c r="D66" t="s">
+        <v>242</v>
+      </c>
+      <c r="E66" t="s">
+        <v>159</v>
+      </c>
+      <c r="F66" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>80</v>
+      </c>
+      <c r="B67" t="s">
+        <v>159</v>
+      </c>
+      <c r="C67" t="s">
+        <v>159</v>
+      </c>
+      <c r="D67" t="s">
+        <v>243</v>
+      </c>
+      <c r="E67" t="s">
+        <v>159</v>
+      </c>
+      <c r="F67" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>81</v>
+      </c>
+      <c r="B68" t="s">
+        <v>159</v>
+      </c>
+      <c r="C68" t="s">
+        <v>159</v>
+      </c>
+      <c r="D68" t="s">
+        <v>244</v>
+      </c>
+      <c r="E68" t="s">
+        <v>159</v>
+      </c>
+      <c r="F68" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>82</v>
+      </c>
+      <c r="B69" t="s">
+        <v>159</v>
+      </c>
+      <c r="C69" t="s">
+        <v>159</v>
+      </c>
+      <c r="D69" t="s">
+        <v>245</v>
+      </c>
+      <c r="E69" t="s">
+        <v>159</v>
+      </c>
+      <c r="F69" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>83</v>
+      </c>
+      <c r="B70" t="s">
+        <v>159</v>
+      </c>
+      <c r="C70" t="s">
+        <v>246</v>
+      </c>
+      <c r="D70" t="s">
+        <v>247</v>
+      </c>
+      <c r="E70" t="s">
+        <v>159</v>
+      </c>
+      <c r="F70" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>84</v>
+      </c>
+      <c r="B71" t="s">
+        <v>159</v>
+      </c>
+      <c r="C71" t="s">
+        <v>159</v>
+      </c>
+      <c r="D71" t="s">
+        <v>159</v>
+      </c>
+      <c r="E71" t="s">
+        <v>248</v>
+      </c>
+      <c r="F71" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>85</v>
+      </c>
+      <c r="B72" t="s">
+        <v>159</v>
+      </c>
+      <c r="C72" t="s">
+        <v>159</v>
+      </c>
+      <c r="D72" t="s">
+        <v>249</v>
+      </c>
+      <c r="E72" t="s">
+        <v>159</v>
+      </c>
+      <c r="F72" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>86</v>
+      </c>
+      <c r="B73" t="s">
+        <v>159</v>
+      </c>
+      <c r="C73" t="s">
+        <v>250</v>
+      </c>
+      <c r="D73" t="s">
+        <v>251</v>
+      </c>
+      <c r="E73" t="s">
+        <v>159</v>
+      </c>
+      <c r="F73" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>87</v>
+      </c>
+      <c r="B74" t="s">
+        <v>159</v>
+      </c>
+      <c r="C74" t="s">
+        <v>159</v>
+      </c>
+      <c r="D74" t="s">
+        <v>252</v>
+      </c>
+      <c r="E74" t="s">
+        <v>159</v>
+      </c>
+      <c r="F74" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>88</v>
+      </c>
+      <c r="B75" t="s">
+        <v>159</v>
+      </c>
+      <c r="C75" t="s">
+        <v>159</v>
+      </c>
+      <c r="D75" t="s">
+        <v>253</v>
+      </c>
+      <c r="E75" t="s">
+        <v>159</v>
+      </c>
+      <c r="F75" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>89</v>
+      </c>
+      <c r="B76" t="s">
+        <v>159</v>
+      </c>
+      <c r="C76" t="s">
+        <v>159</v>
+      </c>
+      <c r="D76" t="s">
+        <v>254</v>
+      </c>
+      <c r="E76" t="s">
+        <v>159</v>
+      </c>
+      <c r="F76" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>90</v>
+      </c>
+      <c r="B77" t="s">
+        <v>159</v>
+      </c>
+      <c r="C77" t="s">
+        <v>159</v>
+      </c>
+      <c r="D77" t="s">
+        <v>255</v>
+      </c>
+      <c r="E77" t="s">
+        <v>159</v>
+      </c>
+      <c r="F77" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>91</v>
+      </c>
+      <c r="B78" t="s">
+        <v>159</v>
+      </c>
+      <c r="C78" t="s">
+        <v>159</v>
+      </c>
+      <c r="D78" t="s">
+        <v>256</v>
+      </c>
+      <c r="E78" t="s">
+        <v>159</v>
+      </c>
+      <c r="F78" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>92</v>
+      </c>
+      <c r="B79" t="s">
+        <v>159</v>
+      </c>
+      <c r="C79" t="s">
+        <v>159</v>
+      </c>
+      <c r="D79" t="s">
+        <v>159</v>
+      </c>
+      <c r="E79" t="s">
+        <v>257</v>
+      </c>
+      <c r="F79" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>93</v>
+      </c>
+      <c r="B80" t="s">
+        <v>159</v>
+      </c>
+      <c r="C80" t="s">
+        <v>159</v>
+      </c>
+      <c r="D80" t="s">
+        <v>258</v>
+      </c>
+      <c r="E80" t="s">
+        <v>159</v>
+      </c>
+      <c r="F80" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>94</v>
+      </c>
+      <c r="B81" t="s">
+        <v>159</v>
+      </c>
+      <c r="C81" t="s">
+        <v>159</v>
+      </c>
+      <c r="D81" t="s">
+        <v>259</v>
+      </c>
+      <c r="E81" t="s">
+        <v>159</v>
+      </c>
+      <c r="F81" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>96</v>
+      </c>
+      <c r="B82" t="s">
+        <v>159</v>
+      </c>
+      <c r="C82" t="s">
+        <v>260</v>
+      </c>
+      <c r="D82" t="s">
+        <v>261</v>
+      </c>
+      <c r="E82" t="s">
+        <v>159</v>
+      </c>
+      <c r="F82" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>97</v>
+      </c>
+      <c r="B83" t="s">
+        <v>262</v>
+      </c>
+      <c r="C83" t="s">
+        <v>159</v>
+      </c>
+      <c r="D83" t="s">
+        <v>159</v>
+      </c>
+      <c r="E83" t="s">
+        <v>159</v>
+      </c>
+      <c r="F83" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>98</v>
+      </c>
+      <c r="B84" t="s">
+        <v>159</v>
+      </c>
+      <c r="C84" t="s">
+        <v>159</v>
+      </c>
+      <c r="D84" t="s">
+        <v>263</v>
+      </c>
+      <c r="E84" t="s">
+        <v>159</v>
+      </c>
+      <c r="F84" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>99</v>
+      </c>
+      <c r="B85" t="s">
+        <v>159</v>
+      </c>
+      <c r="C85" t="s">
+        <v>159</v>
+      </c>
+      <c r="D85" t="s">
+        <v>264</v>
+      </c>
+      <c r="E85" t="s">
+        <v>265</v>
+      </c>
+      <c r="F85" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>100</v>
+      </c>
+      <c r="B86" t="s">
+        <v>159</v>
+      </c>
+      <c r="C86" t="s">
+        <v>159</v>
+      </c>
+      <c r="D86" t="s">
+        <v>266</v>
+      </c>
+      <c r="E86" t="s">
+        <v>159</v>
+      </c>
+      <c r="F86" t="s">
+        <v>159</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/events/2026/config/motions-ids.xlsx
+++ b/events/2026/config/motions-ids.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mike\projects\work\wsw-results\events\2026\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61C5873-C8F0-4089-B815-72530C47C00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E73A60A-F035-4671-B120-F6FB21145667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="motions" sheetId="1" r:id="rId1"/>
@@ -693,9 +693,6 @@
     <t>Motion 854</t>
   </si>
   <si>
-    <t>Motion 4641</t>
-  </si>
-  <si>
     <t>Motion 1641</t>
   </si>
   <si>
@@ -834,20 +831,23 @@
     <t>Motion 633</t>
   </si>
   <si>
-    <t>Motion 4695</t>
-  </si>
-  <si>
     <t>Motion 2695</t>
   </si>
   <si>
     <t>Motion 823</t>
+  </si>
+  <si>
+    <t>Motion 641</t>
+  </si>
+  <si>
+    <t>Motion 695</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -877,6 +877,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -929,7 +936,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -965,6 +972,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1350,15 +1361,15 @@
         <v>Motion 4871</v>
       </c>
       <c r="S2" s="4" t="str">
-        <f t="shared" ref="S2:S33" si="4">IF(J2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N2&gt;1,$I2=""),"4",""),$O2), "")</f>
+        <f>IF(J2&lt;&gt;"", _xlfn.CONCAT("Motion ",$O2), "")</f>
         <v>Motion 871</v>
       </c>
       <c r="T2" s="4" t="str">
-        <f t="shared" ref="T2:T33" si="5">IF(K2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"2",""),$O2), "")</f>
+        <f t="shared" ref="T2:T33" si="4">IF(K2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"2",""),$O2), "")</f>
         <v/>
       </c>
       <c r="U2" s="4" t="str">
-        <f t="shared" ref="U2:U33" si="6">IF(L2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"1",""),$O2), "")</f>
+        <f t="shared" ref="U2:U33" si="5">IF(L2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"1",""),$O2), "")</f>
         <v/>
       </c>
     </row>
@@ -1386,7 +1397,7 @@
         <v>21</v>
       </c>
       <c r="M3" s="3" t="str">
-        <f t="shared" ref="M3:M34" si="7">IF(A3-A2&lt;&gt;1,A3-A2,"")</f>
+        <f t="shared" ref="M3:M34" si="6">IF(A3-A2&lt;&gt;1,A3-A2,"")</f>
         <v/>
       </c>
       <c r="N3" s="3">
@@ -1409,15 +1420,15 @@
         <v>Motion 4822</v>
       </c>
       <c r="S3" s="4" t="str">
+        <f t="shared" ref="S3:S66" si="7">IF(J3&lt;&gt;"", _xlfn.CONCAT("Motion ",$O3), "")</f>
+        <v>Motion 822</v>
+      </c>
+      <c r="T3" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 822</v>
-      </c>
-      <c r="T3" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U3" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U3" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -1445,7 +1456,7 @@
         <v>21</v>
       </c>
       <c r="M4" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N4" s="3">
@@ -1468,15 +1479,15 @@
         <v>Motion 4935</v>
       </c>
       <c r="S4" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 935</v>
+      </c>
+      <c r="T4" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 935</v>
-      </c>
-      <c r="T4" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U4" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U4" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -1497,7 +1508,7 @@
         <v>29</v>
       </c>
       <c r="M5" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N5" s="3">
@@ -1520,15 +1531,15 @@
         <v/>
       </c>
       <c r="S5" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="T5" s="4" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="T5" s="4" t="str">
+        <v>Motion 665</v>
+      </c>
+      <c r="U5" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>Motion 665</v>
-      </c>
-      <c r="U5" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -1549,7 +1560,7 @@
         <v>29</v>
       </c>
       <c r="M6" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N6" s="3">
@@ -1572,15 +1583,15 @@
         <v/>
       </c>
       <c r="S6" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="T6" s="4" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="T6" s="4" t="str">
+        <v>Motion 662</v>
+      </c>
+      <c r="U6" s="4" t="str">
         <f t="shared" si="5"/>
-        <v>Motion 662</v>
-      </c>
-      <c r="U6" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -1610,7 +1621,7 @@
         <v>21</v>
       </c>
       <c r="M7" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N7" s="3">
@@ -1633,15 +1644,15 @@
         <v>Motion 4873</v>
       </c>
       <c r="S7" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 873</v>
+      </c>
+      <c r="T7" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 873</v>
-      </c>
-      <c r="T7" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U7" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U7" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -1665,7 +1676,7 @@
         <v>21</v>
       </c>
       <c r="M8" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N8" s="3">
@@ -1688,15 +1699,15 @@
         <v/>
       </c>
       <c r="S8" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 870</v>
+      </c>
+      <c r="T8" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 870</v>
-      </c>
-      <c r="T8" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U8" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U8" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -1723,7 +1734,7 @@
         <v>40</v>
       </c>
       <c r="M9" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N9" s="3">
@@ -1746,15 +1757,15 @@
         <v/>
       </c>
       <c r="S9" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="T9" s="4" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T9" s="4" t="str">
+      <c r="U9" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U9" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -1778,7 +1789,7 @@
         <v>21</v>
       </c>
       <c r="M10" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N10" s="3">
@@ -1801,15 +1812,15 @@
         <v/>
       </c>
       <c r="S10" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 802</v>
+      </c>
+      <c r="T10" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 802</v>
-      </c>
-      <c r="T10" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U10" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U10" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -1836,7 +1847,7 @@
         <v>21</v>
       </c>
       <c r="M11" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N11" s="3">
@@ -1859,15 +1870,15 @@
         <v>Motion 4978</v>
       </c>
       <c r="S11" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 978</v>
+      </c>
+      <c r="T11" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 978</v>
-      </c>
-      <c r="T11" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U11" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U11" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -1891,7 +1902,7 @@
         <v>21</v>
       </c>
       <c r="M12" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N12" s="3">
@@ -1914,15 +1925,15 @@
         <v/>
       </c>
       <c r="S12" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 1045</v>
+      </c>
+      <c r="T12" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 1045</v>
-      </c>
-      <c r="T12" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U12" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U12" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -1946,7 +1957,7 @@
         <v>40</v>
       </c>
       <c r="M13" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N13" s="3">
@@ -1969,15 +1980,15 @@
         <v/>
       </c>
       <c r="S13" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="T13" s="4" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T13" s="4" t="str">
+      <c r="U13" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U13" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2001,7 +2012,7 @@
         <v>21</v>
       </c>
       <c r="M14" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N14" s="3">
@@ -2024,15 +2035,15 @@
         <v/>
       </c>
       <c r="S14" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 813</v>
+      </c>
+      <c r="T14" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 813</v>
-      </c>
-      <c r="T14" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U14" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U14" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2059,7 +2070,7 @@
         <v>21</v>
       </c>
       <c r="M15" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N15" s="3">
@@ -2082,15 +2093,15 @@
         <v>Motion 4805</v>
       </c>
       <c r="S15" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 805</v>
+      </c>
+      <c r="T15" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 805</v>
-      </c>
-      <c r="T15" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U15" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U15" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2114,7 +2125,7 @@
         <v>40</v>
       </c>
       <c r="M16" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N16" s="3">
@@ -2137,15 +2148,15 @@
         <v/>
       </c>
       <c r="S16" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="T16" s="4" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T16" s="4" t="str">
+      <c r="U16" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U16" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2169,7 +2180,7 @@
         <v>21</v>
       </c>
       <c r="M17" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N17" s="3">
@@ -2192,15 +2203,15 @@
         <v/>
       </c>
       <c r="S17" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 855</v>
+      </c>
+      <c r="T17" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 855</v>
-      </c>
-      <c r="T17" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U17" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U17" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2224,7 +2235,7 @@
         <v>21</v>
       </c>
       <c r="M18" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N18" s="3">
@@ -2247,15 +2258,15 @@
         <v/>
       </c>
       <c r="S18" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 824</v>
+      </c>
+      <c r="T18" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 824</v>
-      </c>
-      <c r="T18" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U18" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U18" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2282,7 +2293,7 @@
         <v>21</v>
       </c>
       <c r="M19" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N19" s="3">
@@ -2305,15 +2316,15 @@
         <v>Motion 4952</v>
       </c>
       <c r="S19" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 952</v>
+      </c>
+      <c r="T19" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 952</v>
-      </c>
-      <c r="T19" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U19" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U19" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2337,7 +2348,7 @@
         <v>21</v>
       </c>
       <c r="M20" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N20" s="3">
@@ -2360,15 +2371,15 @@
         <v/>
       </c>
       <c r="S20" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 849</v>
+      </c>
+      <c r="T20" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 849</v>
-      </c>
-      <c r="T20" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U20" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U20" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2392,7 +2403,7 @@
         <v>21</v>
       </c>
       <c r="M21" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N21" s="3">
@@ -2415,15 +2426,15 @@
         <v/>
       </c>
       <c r="S21" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 806</v>
+      </c>
+      <c r="T21" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 806</v>
-      </c>
-      <c r="T21" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U21" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U21" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2450,7 +2461,7 @@
         <v>21</v>
       </c>
       <c r="M22" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N22" s="3">
@@ -2473,15 +2484,15 @@
         <v>Motion 4807</v>
       </c>
       <c r="S22" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 807</v>
+      </c>
+      <c r="T22" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 807</v>
-      </c>
-      <c r="T22" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U22" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U22" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2508,7 +2519,7 @@
         <v>21</v>
       </c>
       <c r="M23" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N23" s="3">
@@ -2531,15 +2542,15 @@
         <v>Motion 4801</v>
       </c>
       <c r="S23" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 801</v>
+      </c>
+      <c r="T23" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 801</v>
-      </c>
-      <c r="T23" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U23" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U23" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2563,7 +2574,7 @@
         <v>21</v>
       </c>
       <c r="M24" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N24" s="3">
@@ -2586,15 +2597,15 @@
         <v/>
       </c>
       <c r="S24" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 1043</v>
+      </c>
+      <c r="T24" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 1043</v>
-      </c>
-      <c r="T24" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U24" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U24" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2621,7 +2632,7 @@
         <v>21</v>
       </c>
       <c r="M25" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N25" s="3">
@@ -2644,15 +2655,15 @@
         <v>Motion 4841</v>
       </c>
       <c r="S25" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 841</v>
+      </c>
+      <c r="T25" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 841</v>
-      </c>
-      <c r="T25" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U25" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U25" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2676,7 +2687,7 @@
         <v>21</v>
       </c>
       <c r="M26" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N26" s="3">
@@ -2699,15 +2710,15 @@
         <v/>
       </c>
       <c r="S26" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 808</v>
+      </c>
+      <c r="T26" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 808</v>
-      </c>
-      <c r="T26" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U26" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U26" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2731,7 +2742,7 @@
         <v>21</v>
       </c>
       <c r="M27" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N27" s="3">
@@ -2754,15 +2765,15 @@
         <v/>
       </c>
       <c r="S27" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 804</v>
+      </c>
+      <c r="T27" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 804</v>
-      </c>
-      <c r="T27" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U27" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U27" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2789,7 +2800,7 @@
         <v>40</v>
       </c>
       <c r="M28" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N28" s="3">
@@ -2813,15 +2824,15 @@
         <v/>
       </c>
       <c r="S28" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="T28" s="4" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T28" s="4" t="str">
+      <c r="U28" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U28" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2845,7 +2856,7 @@
         <v>21</v>
       </c>
       <c r="M29" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N29" s="3">
@@ -2868,15 +2879,15 @@
         <v/>
       </c>
       <c r="S29" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 852</v>
+      </c>
+      <c r="T29" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 852</v>
-      </c>
-      <c r="T29" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U29" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U29" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2900,7 +2911,7 @@
         <v>21</v>
       </c>
       <c r="M30" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N30" s="3">
@@ -2923,15 +2934,15 @@
         <v/>
       </c>
       <c r="S30" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 861</v>
+      </c>
+      <c r="T30" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 861</v>
-      </c>
-      <c r="T30" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U30" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U30" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -2955,7 +2966,7 @@
         <v>21</v>
       </c>
       <c r="M31" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N31" s="3">
@@ -2978,15 +2989,15 @@
         <v/>
       </c>
       <c r="S31" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 1039</v>
+      </c>
+      <c r="T31" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 1039</v>
-      </c>
-      <c r="T31" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U31" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U31" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -3010,7 +3021,7 @@
         <v>21</v>
       </c>
       <c r="M32" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N32" s="3">
@@ -3033,15 +3044,15 @@
         <v/>
       </c>
       <c r="S32" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 845</v>
+      </c>
+      <c r="T32" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 845</v>
-      </c>
-      <c r="T32" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U32" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U32" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -3068,7 +3079,7 @@
         <v>21</v>
       </c>
       <c r="M33" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N33" s="3">
@@ -3091,15 +3102,15 @@
         <v>Motion 4987</v>
       </c>
       <c r="S33" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 987</v>
+      </c>
+      <c r="T33" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>Motion 987</v>
-      </c>
-      <c r="T33" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U33" s="4" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U33" s="4" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -3123,7 +3134,7 @@
         <v>21</v>
       </c>
       <c r="M34" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N34" s="3">
@@ -3146,15 +3157,15 @@
         <v/>
       </c>
       <c r="S34" s="4" t="str">
-        <f t="shared" ref="S34:S65" si="12">IF(J34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N34&gt;1,$I34=""),"4",""),$O34), "")</f>
+        <f t="shared" si="7"/>
         <v>Motion 1037</v>
       </c>
       <c r="T34" s="4" t="str">
-        <f t="shared" ref="T34:T65" si="13">IF(K34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N34&gt;1,"2",""),$O34), "")</f>
+        <f t="shared" ref="T34:T65" si="12">IF(K34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N34&gt;1,"2",""),$O34), "")</f>
         <v/>
       </c>
       <c r="U34" s="4" t="str">
-        <f t="shared" ref="U34:U65" si="14">IF(L34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N34&gt;1,"1",""),$O34), "")</f>
+        <f t="shared" ref="U34:U65" si="13">IF(L34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N34&gt;1,"1",""),$O34), "")</f>
         <v/>
       </c>
     </row>
@@ -3181,7 +3192,7 @@
         <v>21</v>
       </c>
       <c r="M35" s="3" t="str">
-        <f t="shared" ref="M35:M66" si="15">IF(A35-A34&lt;&gt;1,A35-A34,"")</f>
+        <f t="shared" ref="M35:M66" si="14">IF(A35-A34&lt;&gt;1,A35-A34,"")</f>
         <v/>
       </c>
       <c r="N35" s="3">
@@ -3204,15 +3215,15 @@
         <v>Motion 4998</v>
       </c>
       <c r="S35" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 998</v>
+      </c>
+      <c r="T35" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 998</v>
-      </c>
-      <c r="T35" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U35" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U35" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -3239,7 +3250,7 @@
         <v>21</v>
       </c>
       <c r="M36" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N36" s="3">
@@ -3263,15 +3274,15 @@
         <v/>
       </c>
       <c r="S36" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 623</v>
+      </c>
+      <c r="T36" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 623</v>
-      </c>
-      <c r="T36" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U36" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U36" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -3295,7 +3306,7 @@
         <v>21</v>
       </c>
       <c r="M37" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N37" s="3">
@@ -3318,15 +3329,15 @@
         <v/>
       </c>
       <c r="S37" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 815</v>
+      </c>
+      <c r="T37" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 815</v>
-      </c>
-      <c r="T37" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U37" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U37" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -3350,7 +3361,7 @@
         <v>21</v>
       </c>
       <c r="M38" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N38" s="3">
@@ -3373,15 +3384,15 @@
         <v/>
       </c>
       <c r="S38" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 1033</v>
+      </c>
+      <c r="T38" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 1033</v>
-      </c>
-      <c r="T38" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U38" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U38" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -3405,7 +3416,7 @@
         <v>21</v>
       </c>
       <c r="M39" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N39" s="3">
@@ -3428,15 +3439,15 @@
         <v/>
       </c>
       <c r="S39" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 838</v>
+      </c>
+      <c r="T39" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 838</v>
-      </c>
-      <c r="T39" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U39" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U39" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -3460,7 +3471,7 @@
         <v>21</v>
       </c>
       <c r="M40" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N40" s="3">
@@ -3483,15 +3494,15 @@
         <v/>
       </c>
       <c r="S40" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 819</v>
+      </c>
+      <c r="T40" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 819</v>
-      </c>
-      <c r="T40" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U40" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U40" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -3515,7 +3526,7 @@
         <v>21</v>
       </c>
       <c r="M41" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N41" s="3">
@@ -3538,15 +3549,15 @@
         <v/>
       </c>
       <c r="S41" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 853</v>
+      </c>
+      <c r="T41" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 853</v>
-      </c>
-      <c r="T41" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U41" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U41" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -3570,7 +3581,7 @@
         <v>21</v>
       </c>
       <c r="M42" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N42" s="3">
@@ -3593,15 +3604,15 @@
         <v/>
       </c>
       <c r="S42" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 814</v>
+      </c>
+      <c r="T42" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 814</v>
-      </c>
-      <c r="T42" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U42" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U42" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -3625,7 +3636,7 @@
         <v>40</v>
       </c>
       <c r="M43" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N43" s="3">
@@ -3636,7 +3647,7 @@
         <v>643</v>
       </c>
       <c r="P43" s="3" t="str">
-        <f t="shared" ref="P43:P74" si="16">UPPER(_xlfn.CONCAT(LEFT(D43,3),O43,LEFT(C43,3)))</f>
+        <f t="shared" ref="P43:P74" si="15">UPPER(_xlfn.CONCAT(LEFT(D43,3),O43,LEFT(C43,3)))</f>
         <v>SHE643IAN</v>
       </c>
       <c r="Q43" s="4" t="str">
@@ -3648,15 +3659,15 @@
         <v/>
       </c>
       <c r="S43" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="T43" s="4" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="T43" s="4" t="str">
+      <c r="U43" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U43" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -3680,7 +3691,7 @@
         <v>29</v>
       </c>
       <c r="M44" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N44" s="3">
@@ -3692,7 +3703,7 @@
         <v>846</v>
       </c>
       <c r="P44" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>BUR846EMI</v>
       </c>
       <c r="Q44" s="4" t="str">
@@ -3704,15 +3715,15 @@
         <v/>
       </c>
       <c r="S44" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="T44" s="4" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="T44" s="4" t="str">
+        <v>Motion 846</v>
+      </c>
+      <c r="U44" s="4" t="str">
         <f t="shared" si="13"/>
-        <v>Motion 846</v>
-      </c>
-      <c r="U44" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -3739,7 +3750,7 @@
         <v>21</v>
       </c>
       <c r="M45" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N45" s="3">
@@ -3750,7 +3761,7 @@
         <v>854</v>
       </c>
       <c r="P45" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>DVO854PAV</v>
       </c>
       <c r="Q45" s="4" t="str">
@@ -3762,15 +3773,15 @@
         <v>Motion 4854</v>
       </c>
       <c r="S45" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 854</v>
+      </c>
+      <c r="T45" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 854</v>
-      </c>
-      <c r="T45" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U45" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U45" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -3797,7 +3808,7 @@
         <v>101</v>
       </c>
       <c r="M46" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N46" s="3">
@@ -3808,7 +3819,7 @@
         <v>641</v>
       </c>
       <c r="P46" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>RUS641ROB</v>
       </c>
       <c r="Q46" s="4" t="str">
@@ -3820,15 +3831,15 @@
         <v/>
       </c>
       <c r="S46" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 641</v>
+      </c>
+      <c r="T46" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 4641</v>
-      </c>
-      <c r="T46" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U46" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U46" s="4" t="str">
-        <f t="shared" si="14"/>
         <v>Motion 1641</v>
       </c>
     </row>
@@ -3852,7 +3863,7 @@
         <v>21</v>
       </c>
       <c r="M47" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N47" s="3">
@@ -3863,7 +3874,7 @@
         <v>1020</v>
       </c>
       <c r="P47" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>BRA1020JAM</v>
       </c>
       <c r="Q47" s="4" t="str">
@@ -3875,15 +3886,15 @@
         <v/>
       </c>
       <c r="S47" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 1020</v>
+      </c>
+      <c r="T47" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 1020</v>
-      </c>
-      <c r="T47" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U47" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U47" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -3907,7 +3918,7 @@
         <v>21</v>
       </c>
       <c r="M48" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N48" s="3">
@@ -3918,7 +3929,7 @@
         <v>858</v>
       </c>
       <c r="P48" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>OLI858JOH</v>
       </c>
       <c r="Q48" s="4" t="str">
@@ -3930,15 +3941,15 @@
         <v/>
       </c>
       <c r="S48" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 858</v>
+      </c>
+      <c r="T48" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 858</v>
-      </c>
-      <c r="T48" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U48" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U48" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -3962,7 +3973,7 @@
         <v>21</v>
       </c>
       <c r="M49" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N49" s="3">
@@ -3973,7 +3984,7 @@
         <v>869</v>
       </c>
       <c r="P49" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>BAR869ANT</v>
       </c>
       <c r="Q49" s="4" t="str">
@@ -3985,15 +3996,15 @@
         <v/>
       </c>
       <c r="S49" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 869</v>
+      </c>
+      <c r="T49" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 869</v>
-      </c>
-      <c r="T49" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U49" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U49" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -4014,7 +4025,7 @@
         <v>101</v>
       </c>
       <c r="M50" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N50" s="3">
@@ -4025,7 +4036,7 @@
         <v>618</v>
       </c>
       <c r="P50" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>MAR618PET</v>
       </c>
       <c r="Q50" s="4" t="str">
@@ -4037,15 +4048,15 @@
         <v/>
       </c>
       <c r="S50" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="T50" s="4" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="T50" s="4" t="str">
+      <c r="U50" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U50" s="4" t="str">
-        <f t="shared" si="14"/>
         <v>Motion 618</v>
       </c>
     </row>
@@ -4072,7 +4083,7 @@
         <v>40</v>
       </c>
       <c r="M51" s="12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="N51" s="3">
@@ -4083,7 +4094,7 @@
         <v>827</v>
       </c>
       <c r="P51" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>BER827FIN</v>
       </c>
       <c r="Q51" s="4" t="str">
@@ -4095,15 +4106,15 @@
         <v/>
       </c>
       <c r="S51" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="T51" s="4" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="T51" s="4" t="str">
+      <c r="U51" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U51" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -4127,7 +4138,7 @@
         <v>40</v>
       </c>
       <c r="M52" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N52" s="3">
@@ -4138,7 +4149,7 @@
         <v>639</v>
       </c>
       <c r="P52" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>COL639AND</v>
       </c>
       <c r="Q52" s="4" t="str">
@@ -4150,15 +4161,15 @@
         <v/>
       </c>
       <c r="S52" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="T52" s="4" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="T52" s="4" t="str">
+      <c r="U52" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U52" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -4182,7 +4193,7 @@
         <v>40</v>
       </c>
       <c r="M53" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N53" s="3">
@@ -4193,7 +4204,7 @@
         <v>611</v>
       </c>
       <c r="P53" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>COL611ANN</v>
       </c>
       <c r="Q53" s="4" t="str">
@@ -4205,15 +4216,15 @@
         <v/>
       </c>
       <c r="S53" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="T53" s="4" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="T53" s="4" t="str">
+      <c r="U53" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U53" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -4240,7 +4251,7 @@
         <v>40</v>
       </c>
       <c r="M54" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N54" s="3">
@@ -4251,7 +4262,7 @@
         <v>826</v>
       </c>
       <c r="P54" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>BER826ARL</v>
       </c>
       <c r="Q54" s="4" t="str">
@@ -4263,15 +4274,15 @@
         <v/>
       </c>
       <c r="S54" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="T54" s="4" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="T54" s="4" t="str">
+      <c r="U54" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U54" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -4298,7 +4309,7 @@
         <v>21</v>
       </c>
       <c r="M55" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N55" s="3">
@@ -4309,7 +4320,7 @@
         <v>821</v>
       </c>
       <c r="P55" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>CON821GAR</v>
       </c>
       <c r="Q55" s="4" t="str">
@@ -4321,15 +4332,15 @@
         <v>Motion 4821</v>
       </c>
       <c r="S55" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 821</v>
+      </c>
+      <c r="T55" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 821</v>
-      </c>
-      <c r="T55" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U55" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U55" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -4356,7 +4367,7 @@
         <v>21</v>
       </c>
       <c r="M56" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N56" s="3">
@@ -4367,7 +4378,7 @@
         <v>812</v>
       </c>
       <c r="P56" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>DIN812JAM</v>
       </c>
       <c r="Q56" s="4" t="str">
@@ -4379,15 +4390,15 @@
         <v>Motion 4812</v>
       </c>
       <c r="S56" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 812</v>
+      </c>
+      <c r="T56" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 812</v>
-      </c>
-      <c r="T56" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U56" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U56" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -4411,7 +4422,7 @@
         <v>21</v>
       </c>
       <c r="M57" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N57" s="3">
@@ -4422,7 +4433,7 @@
         <v>829</v>
       </c>
       <c r="P57" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>TRO829WIL</v>
       </c>
       <c r="Q57" s="4" t="str">
@@ -4434,15 +4445,15 @@
         <v/>
       </c>
       <c r="S57" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 829</v>
+      </c>
+      <c r="T57" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 829</v>
-      </c>
-      <c r="T57" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U57" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U57" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -4469,7 +4480,7 @@
         <v>29</v>
       </c>
       <c r="M58" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N58" s="3">
@@ -4480,7 +4491,7 @@
         <v>669</v>
       </c>
       <c r="P58" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>WIL669DAV</v>
       </c>
       <c r="Q58" s="4" t="str">
@@ -4492,15 +4503,15 @@
         <v/>
       </c>
       <c r="S58" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="T58" s="4" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="T58" s="4" t="str">
+        <v>Motion 2669</v>
+      </c>
+      <c r="U58" s="4" t="str">
         <f t="shared" si="13"/>
-        <v>Motion 2669</v>
-      </c>
-      <c r="U58" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -4527,7 +4538,7 @@
         <v>21</v>
       </c>
       <c r="M59" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N59" s="3">
@@ -4539,7 +4550,7 @@
         <v>920</v>
       </c>
       <c r="P59" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>PAL920MAR</v>
       </c>
       <c r="Q59" s="4" t="str">
@@ -4551,15 +4562,15 @@
         <v/>
       </c>
       <c r="S59" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 920</v>
+      </c>
+      <c r="T59" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 920</v>
-      </c>
-      <c r="T59" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U59" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U59" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -4583,7 +4594,7 @@
         <v>40</v>
       </c>
       <c r="M60" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N60" s="3">
@@ -4594,7 +4605,7 @@
         <v>631</v>
       </c>
       <c r="P60" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>SAN631SIM</v>
       </c>
       <c r="Q60" s="4" t="str">
@@ -4606,15 +4617,15 @@
         <v/>
       </c>
       <c r="S60" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="T60" s="4" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="T60" s="4" t="str">
+      <c r="U60" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U60" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -4641,7 +4652,7 @@
         <v>21</v>
       </c>
       <c r="M61" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N61" s="3">
@@ -4652,7 +4663,7 @@
         <v>810</v>
       </c>
       <c r="P61" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NEW810MAR</v>
       </c>
       <c r="Q61" s="4" t="str">
@@ -4664,15 +4675,15 @@
         <v>Motion 4810</v>
       </c>
       <c r="S61" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 810</v>
+      </c>
+      <c r="T61" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 810</v>
-      </c>
-      <c r="T61" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U61" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U61" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -4696,7 +4707,7 @@
         <v>21</v>
       </c>
       <c r="M62" s="12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="N62" s="3">
@@ -4707,7 +4718,7 @@
         <v>817</v>
       </c>
       <c r="P62" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>MAR817EDD</v>
       </c>
       <c r="Q62" s="4" t="str">
@@ -4719,15 +4730,15 @@
         <v/>
       </c>
       <c r="S62" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 817</v>
+      </c>
+      <c r="T62" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 817</v>
-      </c>
-      <c r="T62" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U62" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U62" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -4751,7 +4762,7 @@
         <v>21</v>
       </c>
       <c r="M63" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N63" s="3">
@@ -4762,7 +4773,7 @@
         <v>803</v>
       </c>
       <c r="P63" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>STU803AND</v>
       </c>
       <c r="Q63" s="4" t="str">
@@ -4774,15 +4785,15 @@
         <v/>
       </c>
       <c r="S63" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 803</v>
+      </c>
+      <c r="T63" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 803</v>
-      </c>
-      <c r="T63" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U63" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U63" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -4803,7 +4814,7 @@
         <v>29</v>
       </c>
       <c r="M64" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N64" s="3">
@@ -4814,7 +4825,7 @@
         <v>699</v>
       </c>
       <c r="P64" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>LON699JAM</v>
       </c>
       <c r="Q64" s="4" t="str">
@@ -4826,15 +4837,15 @@
         <v/>
       </c>
       <c r="S64" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="T64" s="4" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="T64" s="4" t="str">
+        <v>Motion 699</v>
+      </c>
+      <c r="U64" s="4" t="str">
         <f t="shared" si="13"/>
-        <v>Motion 699</v>
-      </c>
-      <c r="U64" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -4858,7 +4869,7 @@
         <v>21</v>
       </c>
       <c r="M65" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N65" s="3">
@@ -4869,7 +4880,7 @@
         <v>656</v>
       </c>
       <c r="P65" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>THO656RUS</v>
       </c>
       <c r="Q65" s="4" t="str">
@@ -4881,15 +4892,15 @@
         <v/>
       </c>
       <c r="S65" s="4" t="str">
+        <f t="shared" si="7"/>
+        <v>Motion 656</v>
+      </c>
+      <c r="T65" s="4" t="str">
         <f t="shared" si="12"/>
-        <v>Motion 656</v>
-      </c>
-      <c r="T65" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U65" s="4" t="str">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U65" s="4" t="str">
-        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -4913,38 +4924,38 @@
         <v>21</v>
       </c>
       <c r="M66" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N66" s="3">
-        <f t="shared" ref="N66:N86" si="17">COUNTA(H66:L66)</f>
+        <f t="shared" ref="N66:N86" si="16">COUNTA(H66:L66)</f>
         <v>1</v>
       </c>
       <c r="O66" s="3">
         <v>651</v>
       </c>
       <c r="P66" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>KIR651JON</v>
       </c>
       <c r="Q66" s="4" t="str">
-        <f t="shared" ref="Q66:Q86" si="18">IF(H66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"5",""),$O66), "")</f>
+        <f t="shared" ref="Q66:Q86" si="17">IF(H66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"5",""),$O66), "")</f>
         <v/>
       </c>
       <c r="R66" s="4" t="str">
-        <f t="shared" ref="R66:R86" si="19">IF(I66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"4",""),$O66), "")</f>
+        <f t="shared" ref="R66:R86" si="18">IF(I66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"4",""),$O66), "")</f>
         <v/>
       </c>
       <c r="S66" s="4" t="str">
-        <f t="shared" ref="S66:S86" si="20">IF(J66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N66&gt;1,$I66=""),"4",""),$O66), "")</f>
+        <f t="shared" si="7"/>
         <v>Motion 651</v>
       </c>
       <c r="T66" s="4" t="str">
-        <f t="shared" ref="T66:T86" si="21">IF(K66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"2",""),$O66), "")</f>
+        <f t="shared" ref="T66:T86" si="19">IF(K66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"2",""),$O66), "")</f>
         <v/>
       </c>
       <c r="U66" s="4" t="str">
-        <f t="shared" ref="U66:U86" si="22">IF(L66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"1",""),$O66), "")</f>
+        <f t="shared" ref="U66:U86" si="20">IF(L66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"1",""),$O66), "")</f>
         <v/>
       </c>
     </row>
@@ -4968,38 +4979,38 @@
         <v>21</v>
       </c>
       <c r="M67" s="3" t="str">
-        <f t="shared" ref="M67:M86" si="23">IF(A67-A66&lt;&gt;1,A67-A66,"")</f>
+        <f t="shared" ref="M67:M86" si="21">IF(A67-A66&lt;&gt;1,A67-A66,"")</f>
         <v/>
       </c>
       <c r="N67" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O67" s="3">
         <v>836</v>
       </c>
       <c r="P67" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>CRO836JIM</v>
       </c>
       <c r="Q67" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R67" s="4" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="R67" s="4" t="str">
+      <c r="S67" s="4" t="str">
+        <f t="shared" ref="S67:S86" si="22">IF(J67&lt;&gt;"", _xlfn.CONCAT("Motion ",$O67), "")</f>
+        <v>Motion 836</v>
+      </c>
+      <c r="T67" s="4" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="S67" s="4" t="str">
+      <c r="U67" s="4" t="str">
         <f t="shared" si="20"/>
-        <v>Motion 836</v>
-      </c>
-      <c r="T67" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U67" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5026,38 +5037,38 @@
         <v>21</v>
       </c>
       <c r="M68" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N68" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O68" s="3">
         <v>818</v>
       </c>
       <c r="P68" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>CRO818GEO</v>
       </c>
       <c r="Q68" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R68" s="4" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="R68" s="4" t="str">
+      <c r="S68" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v>Motion 818</v>
+      </c>
+      <c r="T68" s="4" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="S68" s="4" t="str">
+      <c r="U68" s="4" t="str">
         <f t="shared" si="20"/>
-        <v>Motion 818</v>
-      </c>
-      <c r="T68" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U68" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5084,38 +5095,38 @@
         <v>21</v>
       </c>
       <c r="M69" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N69" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O69" s="3">
         <v>816</v>
       </c>
       <c r="P69" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>CRO816JAC</v>
       </c>
       <c r="Q69" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R69" s="4" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="R69" s="4" t="str">
+      <c r="S69" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v>Motion 816</v>
+      </c>
+      <c r="T69" s="4" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="S69" s="4" t="str">
+      <c r="U69" s="4" t="str">
         <f t="shared" si="20"/>
-        <v>Motion 816</v>
-      </c>
-      <c r="T69" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U69" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5142,38 +5153,38 @@
         <v>21</v>
       </c>
       <c r="M70" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N70" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="O70" s="3">
         <v>942</v>
       </c>
       <c r="P70" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NOR942SCO</v>
       </c>
       <c r="Q70" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R70" s="4" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="R70" s="4" t="str">
+        <v>Motion 4942</v>
+      </c>
+      <c r="S70" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v>Motion 942</v>
+      </c>
+      <c r="T70" s="4" t="str">
         <f t="shared" si="19"/>
-        <v>Motion 4942</v>
-      </c>
-      <c r="S70" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U70" s="4" t="str">
         <f t="shared" si="20"/>
-        <v>Motion 942</v>
-      </c>
-      <c r="T70" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U70" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5194,38 +5205,38 @@
         <v>29</v>
       </c>
       <c r="M71" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N71" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O71" s="3">
         <v>701</v>
       </c>
       <c r="P71" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>CAM701SEB</v>
       </c>
       <c r="Q71" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R71" s="4" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="R71" s="4" t="str">
+      <c r="S71" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="T71" s="4" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="S71" s="4" t="str">
+        <v>Motion 701</v>
+      </c>
+      <c r="U71" s="4" t="str">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="T71" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>Motion 701</v>
-      </c>
-      <c r="U71" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5249,38 +5260,38 @@
         <v>21</v>
       </c>
       <c r="M72" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N72" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O72" s="3">
         <v>718</v>
       </c>
       <c r="P72" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>HIL718IAN</v>
       </c>
       <c r="Q72" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R72" s="4" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="R72" s="4" t="str">
+      <c r="S72" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v>Motion 718</v>
+      </c>
+      <c r="T72" s="4" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="S72" s="4" t="str">
+      <c r="U72" s="4" t="str">
         <f t="shared" si="20"/>
-        <v>Motion 718</v>
-      </c>
-      <c r="T72" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U72" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5307,38 +5318,38 @@
         <v>21</v>
       </c>
       <c r="M73" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N73" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="O73" s="3">
         <v>833</v>
       </c>
       <c r="P73" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>TWI833AND</v>
       </c>
       <c r="Q73" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R73" s="4" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="R73" s="4" t="str">
+        <v>Motion 4833</v>
+      </c>
+      <c r="S73" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v>Motion 833</v>
+      </c>
+      <c r="T73" s="4" t="str">
         <f t="shared" si="19"/>
-        <v>Motion 4833</v>
-      </c>
-      <c r="S73" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U73" s="4" t="str">
         <f t="shared" si="20"/>
-        <v>Motion 833</v>
-      </c>
-      <c r="T73" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U73" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5362,38 +5373,38 @@
         <v>21</v>
       </c>
       <c r="M74" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N74" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O74" s="3">
         <v>811</v>
       </c>
       <c r="P74" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>HUM811TIM</v>
       </c>
       <c r="Q74" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R74" s="4" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="R74" s="4" t="str">
+      <c r="S74" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v>Motion 811</v>
+      </c>
+      <c r="T74" s="4" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="S74" s="4" t="str">
+      <c r="U74" s="4" t="str">
         <f t="shared" si="20"/>
-        <v>Motion 811</v>
-      </c>
-      <c r="T74" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U74" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5420,11 +5431,11 @@
         <v>21</v>
       </c>
       <c r="M75" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N75" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O75" s="11">
@@ -5432,27 +5443,27 @@
         <v>1002</v>
       </c>
       <c r="P75" s="3" t="str">
-        <f t="shared" ref="P75:P106" si="24">UPPER(_xlfn.CONCAT(LEFT(D75,3),O75,LEFT(C75,3)))</f>
+        <f t="shared" ref="P75:P86" si="23">UPPER(_xlfn.CONCAT(LEFT(D75,3),O75,LEFT(C75,3)))</f>
         <v>GOO1002GAR</v>
       </c>
       <c r="Q75" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R75" s="4" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="R75" s="4" t="str">
+      <c r="S75" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v>Motion 1002</v>
+      </c>
+      <c r="T75" s="4" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="S75" s="4" t="str">
+      <c r="U75" s="4" t="str">
         <f t="shared" si="20"/>
-        <v>Motion 1002</v>
-      </c>
-      <c r="T75" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U75" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5476,38 +5487,38 @@
         <v>21</v>
       </c>
       <c r="M76" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N76" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O76" s="3">
         <v>647</v>
       </c>
       <c r="P76" s="3" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>WHA647TRE</v>
       </c>
       <c r="Q76" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R76" s="4" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="R76" s="4" t="str">
+      <c r="S76" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v>Motion 647</v>
+      </c>
+      <c r="T76" s="4" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="S76" s="4" t="str">
+      <c r="U76" s="4" t="str">
         <f t="shared" si="20"/>
-        <v>Motion 647</v>
-      </c>
-      <c r="T76" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U76" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5534,38 +5545,38 @@
         <v>21</v>
       </c>
       <c r="M77" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N77" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O77" s="3">
         <v>1040</v>
       </c>
       <c r="P77" s="3" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>KIE1040OLI</v>
       </c>
       <c r="Q77" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R77" s="4" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="R77" s="4" t="str">
+      <c r="S77" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v>Motion 1040</v>
+      </c>
+      <c r="T77" s="4" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="S77" s="4" t="str">
+      <c r="U77" s="4" t="str">
         <f t="shared" si="20"/>
-        <v>Motion 1040</v>
-      </c>
-      <c r="T77" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U77" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5592,11 +5603,11 @@
         <v>21</v>
       </c>
       <c r="M78" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N78" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O78" s="11">
@@ -5604,27 +5615,27 @@
         <v>676</v>
       </c>
       <c r="P78" s="3" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>NEA676IAI</v>
       </c>
       <c r="Q78" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R78" s="4" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="R78" s="4" t="str">
+      <c r="S78" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v>Motion 676</v>
+      </c>
+      <c r="T78" s="4" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="S78" s="4" t="str">
+      <c r="U78" s="4" t="str">
         <f t="shared" si="20"/>
-        <v>Motion 676</v>
-      </c>
-      <c r="T78" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U78" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5645,38 +5656,38 @@
         <v>29</v>
       </c>
       <c r="M79" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N79" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O79" s="3">
         <v>660</v>
       </c>
       <c r="P79" s="3" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>CAR660MAR</v>
       </c>
       <c r="Q79" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R79" s="4" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="R79" s="4" t="str">
+      <c r="S79" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="T79" s="4" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="S79" s="4" t="str">
+        <v>Motion 660</v>
+      </c>
+      <c r="U79" s="4" t="str">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="T79" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>Motion 660</v>
-      </c>
-      <c r="U79" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5703,11 +5714,11 @@
         <v>21</v>
       </c>
       <c r="M80" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N80" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O80" s="11">
@@ -5715,27 +5726,27 @@
         <v>704</v>
       </c>
       <c r="P80" s="3" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>VER704SHA</v>
       </c>
       <c r="Q80" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R80" s="4" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="R80" s="4" t="str">
+      <c r="S80" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v>Motion 704</v>
+      </c>
+      <c r="T80" s="4" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="S80" s="4" t="str">
+      <c r="U80" s="4" t="str">
         <f t="shared" si="20"/>
-        <v>Motion 704</v>
-      </c>
-      <c r="T80" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U80" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5759,38 +5770,38 @@
         <v>21</v>
       </c>
       <c r="M81" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N81" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O81" s="3">
         <v>661</v>
       </c>
       <c r="P81" s="3" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>BRA661PAU</v>
       </c>
       <c r="Q81" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R81" s="4" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="R81" s="4" t="str">
+      <c r="S81" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v>Motion 661</v>
+      </c>
+      <c r="T81" s="4" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="S81" s="4" t="str">
+      <c r="U81" s="4" t="str">
         <f t="shared" si="20"/>
-        <v>Motion 661</v>
-      </c>
-      <c r="T81" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U81" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5817,38 +5828,38 @@
         <v>21</v>
       </c>
       <c r="M82" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>2</v>
       </c>
       <c r="N82" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="O82" s="3">
         <v>866</v>
       </c>
       <c r="P82" s="3" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>CRO866ALL</v>
       </c>
       <c r="Q82" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R82" s="4" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="R82" s="4" t="str">
+        <v>Motion 4866</v>
+      </c>
+      <c r="S82" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v>Motion 866</v>
+      </c>
+      <c r="T82" s="4" t="str">
         <f t="shared" si="19"/>
-        <v>Motion 4866</v>
-      </c>
-      <c r="S82" s="4" t="str">
+        <v/>
+      </c>
+      <c r="U82" s="4" t="str">
         <f t="shared" si="20"/>
-        <v>Motion 866</v>
-      </c>
-      <c r="T82" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U82" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5875,38 +5886,38 @@
         <v>40</v>
       </c>
       <c r="M83" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N83" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O83" s="3">
         <v>825</v>
       </c>
       <c r="P83" s="3" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>MIL825JAY</v>
       </c>
       <c r="Q83" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v>Motion 825</v>
+      </c>
+      <c r="R83" s="4" t="str">
         <f t="shared" si="18"/>
-        <v>Motion 825</v>
-      </c>
-      <c r="R83" s="4" t="str">
+        <v/>
+      </c>
+      <c r="S83" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="T83" s="4" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="S83" s="4" t="str">
+      <c r="U83" s="4" t="str">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="T83" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U83" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5930,38 +5941,38 @@
         <v>21</v>
       </c>
       <c r="M84" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N84" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O84" s="3">
         <v>633</v>
       </c>
       <c r="P84" s="3" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>PEN633ROB</v>
       </c>
       <c r="Q84" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R84" s="4" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="R84" s="4" t="str">
+      <c r="S84" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v>Motion 633</v>
+      </c>
+      <c r="T84" s="4" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="S84" s="4" t="str">
+      <c r="U84" s="4" t="str">
         <f t="shared" si="20"/>
-        <v>Motion 633</v>
-      </c>
-      <c r="T84" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U84" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -5988,38 +5999,38 @@
         <v>29</v>
       </c>
       <c r="M85" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N85" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="O85" s="3">
         <v>695</v>
       </c>
       <c r="P85" s="3" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>DAV695STE</v>
       </c>
       <c r="Q85" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R85" s="4" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="R85" s="4" t="str">
+      <c r="S85" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v>Motion 695</v>
+      </c>
+      <c r="T85" s="4" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="S85" s="4" t="str">
+        <v>Motion 2695</v>
+      </c>
+      <c r="U85" s="4" t="str">
         <f t="shared" si="20"/>
-        <v>Motion 4695</v>
-      </c>
-      <c r="T85" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v>Motion 2695</v>
-      </c>
-      <c r="U85" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -6046,38 +6057,38 @@
         <v>21</v>
       </c>
       <c r="M86" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N86" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O86" s="3">
         <v>823</v>
       </c>
       <c r="P86" s="3" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>VIC823MIT</v>
       </c>
       <c r="Q86" s="4" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R86" s="4" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="R86" s="4" t="str">
+      <c r="S86" s="4" t="str">
+        <f t="shared" si="22"/>
+        <v>Motion 823</v>
+      </c>
+      <c r="T86" s="4" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="S86" s="4" t="str">
+      <c r="U86" s="4" t="str">
         <f t="shared" si="20"/>
-        <v>Motion 823</v>
-      </c>
-      <c r="T86" s="4" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="U86" s="4" t="str">
-        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -6093,1726 +6104,1731 @@
   <dimension ref="A1:F86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="13" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="A3" s="1">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E4" t="s">
-        <v>159</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E4" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D5" t="s">
-        <v>159</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="B6" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="E7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="1">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" t="s">
-        <v>159</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="B8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E8" t="s">
-        <v>159</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="E8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="1">
         <v>20</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C9" t="s">
-        <v>159</v>
-      </c>
-      <c r="D9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E9" t="s">
-        <v>159</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="C9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="A10" s="1">
         <v>21</v>
       </c>
-      <c r="B10" t="s">
-        <v>159</v>
-      </c>
-      <c r="C10" t="s">
-        <v>159</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="B10" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E10" t="s">
-        <v>159</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="E10" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="A11" s="1">
         <v>22</v>
       </c>
-      <c r="B11" t="s">
-        <v>159</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B11" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E11" t="s">
-        <v>159</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="E11" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="A12" s="1">
         <v>23</v>
       </c>
-      <c r="B12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C12" t="s">
-        <v>159</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="B12" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E12" t="s">
-        <v>159</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="E12" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="A13" s="1">
         <v>24</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C13" t="s">
-        <v>159</v>
-      </c>
-      <c r="D13" t="s">
-        <v>159</v>
-      </c>
-      <c r="E13" t="s">
-        <v>159</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="C13" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="A14" s="1">
         <v>25</v>
       </c>
-      <c r="B14" t="s">
-        <v>159</v>
-      </c>
-      <c r="C14" t="s">
-        <v>159</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="B14" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E14" t="s">
-        <v>159</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="E14" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="A15" s="1">
         <v>26</v>
       </c>
-      <c r="B15" t="s">
-        <v>159</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B15" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E15" t="s">
-        <v>159</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="E15" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="A16" s="1">
         <v>27</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D16" t="s">
-        <v>159</v>
-      </c>
-      <c r="E16" t="s">
-        <v>159</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="C16" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="A17" s="1">
         <v>28</v>
       </c>
-      <c r="B17" t="s">
-        <v>159</v>
-      </c>
-      <c r="C17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="B17" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E17" t="s">
-        <v>159</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="E17" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="A18" s="1">
         <v>29</v>
       </c>
-      <c r="B18" t="s">
-        <v>159</v>
-      </c>
-      <c r="C18" t="s">
-        <v>159</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="B18" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E18" t="s">
-        <v>159</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="E18" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="A19" s="1">
         <v>30</v>
       </c>
-      <c r="B19" t="s">
-        <v>159</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B19" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E19" t="s">
-        <v>159</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="E19" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="A20" s="1">
         <v>31</v>
       </c>
-      <c r="B20" t="s">
-        <v>159</v>
-      </c>
-      <c r="C20" t="s">
-        <v>159</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="B20" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E20" t="s">
-        <v>159</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="E20" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="A21" s="1">
         <v>32</v>
       </c>
-      <c r="B21" t="s">
-        <v>159</v>
-      </c>
-      <c r="C21" t="s">
-        <v>159</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="B21" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E21" t="s">
-        <v>159</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="E21" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="A22" s="1">
         <v>33</v>
       </c>
-      <c r="B22" t="s">
-        <v>159</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B22" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E22" t="s">
-        <v>159</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="E22" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="A23" s="1">
         <v>34</v>
       </c>
-      <c r="B23" t="s">
-        <v>159</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B23" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E23" t="s">
-        <v>159</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="E23" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="A24" s="1">
         <v>35</v>
       </c>
-      <c r="B24" t="s">
-        <v>159</v>
-      </c>
-      <c r="C24" t="s">
-        <v>159</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="B24" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E24" t="s">
-        <v>159</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="E24" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="A25" s="1">
         <v>36</v>
       </c>
-      <c r="B25" t="s">
-        <v>159</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B25" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E25" t="s">
-        <v>159</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="E25" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26">
+      <c r="A26" s="1">
         <v>37</v>
       </c>
-      <c r="B26" t="s">
-        <v>159</v>
-      </c>
-      <c r="C26" t="s">
-        <v>159</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="B26" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E26" t="s">
-        <v>159</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="E26" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="A27" s="1">
         <v>38</v>
       </c>
-      <c r="B27" t="s">
-        <v>159</v>
-      </c>
-      <c r="C27" t="s">
-        <v>159</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="B27" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E27" t="s">
-        <v>159</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="E27" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28">
+      <c r="A28" s="1">
         <v>39</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C28" t="s">
-        <v>159</v>
-      </c>
-      <c r="D28" t="s">
-        <v>159</v>
-      </c>
-      <c r="E28" t="s">
-        <v>159</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="C28" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29">
+      <c r="A29" s="1">
         <v>40</v>
       </c>
-      <c r="B29" t="s">
-        <v>159</v>
-      </c>
-      <c r="C29" t="s">
-        <v>159</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="B29" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E29" t="s">
-        <v>159</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="E29" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30">
+      <c r="A30" s="1">
         <v>41</v>
       </c>
-      <c r="B30" t="s">
-        <v>159</v>
-      </c>
-      <c r="C30" t="s">
-        <v>159</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="B30" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E30" t="s">
-        <v>159</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="E30" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31">
+      <c r="A31" s="1">
         <v>42</v>
       </c>
-      <c r="B31" t="s">
-        <v>159</v>
-      </c>
-      <c r="C31" t="s">
-        <v>159</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="B31" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E31" t="s">
-        <v>159</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="E31" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32">
+      <c r="A32" s="1">
         <v>43</v>
       </c>
-      <c r="B32" t="s">
-        <v>159</v>
-      </c>
-      <c r="C32" t="s">
-        <v>159</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="B32" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E32" t="s">
-        <v>159</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="E32" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33">
+      <c r="A33" s="1">
         <v>44</v>
       </c>
-      <c r="B33" t="s">
-        <v>159</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B33" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E33" t="s">
-        <v>159</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="E33" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34">
+      <c r="A34" s="1">
         <v>45</v>
       </c>
-      <c r="B34" t="s">
-        <v>159</v>
-      </c>
-      <c r="C34" t="s">
-        <v>159</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="B34" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E34" t="s">
-        <v>159</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="E34" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35">
+      <c r="A35" s="1">
         <v>46</v>
       </c>
-      <c r="B35" t="s">
-        <v>159</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="B35" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E35" t="s">
-        <v>159</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="E35" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36">
+      <c r="A36" s="1">
         <v>47</v>
       </c>
-      <c r="B36" t="s">
-        <v>159</v>
-      </c>
-      <c r="C36" t="s">
-        <v>159</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="B36" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E36" t="s">
-        <v>159</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="E36" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37">
+      <c r="A37" s="1">
         <v>48</v>
       </c>
-      <c r="B37" t="s">
-        <v>159</v>
-      </c>
-      <c r="C37" t="s">
-        <v>159</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="B37" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E37" t="s">
-        <v>159</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="E37" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38">
+      <c r="A38" s="1">
         <v>49</v>
       </c>
-      <c r="B38" t="s">
-        <v>159</v>
-      </c>
-      <c r="C38" t="s">
-        <v>159</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="B38" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="E38" t="s">
-        <v>159</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="E38" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39">
+      <c r="A39" s="1">
         <v>50</v>
       </c>
-      <c r="B39" t="s">
-        <v>159</v>
-      </c>
-      <c r="C39" t="s">
-        <v>159</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="B39" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E39" t="s">
-        <v>159</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="E39" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40">
+      <c r="A40" s="1">
         <v>51</v>
       </c>
-      <c r="B40" t="s">
-        <v>159</v>
-      </c>
-      <c r="C40" t="s">
-        <v>159</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="B40" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E40" t="s">
-        <v>159</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="E40" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41">
+      <c r="A41" s="1">
         <v>52</v>
       </c>
-      <c r="B41" t="s">
-        <v>159</v>
-      </c>
-      <c r="C41" t="s">
-        <v>159</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="B41" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E41" t="s">
-        <v>159</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="E41" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42">
+      <c r="A42" s="1">
         <v>53</v>
       </c>
-      <c r="B42" t="s">
-        <v>159</v>
-      </c>
-      <c r="C42" t="s">
-        <v>159</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="B42" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E42" t="s">
-        <v>159</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="E42" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43">
+      <c r="A43" s="1">
         <v>54</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C43" t="s">
-        <v>159</v>
-      </c>
-      <c r="D43" t="s">
-        <v>159</v>
-      </c>
-      <c r="E43" t="s">
-        <v>159</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="C43" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44">
+      <c r="A44" s="1">
         <v>55</v>
       </c>
-      <c r="B44" t="s">
-        <v>159</v>
-      </c>
-      <c r="C44" t="s">
-        <v>159</v>
-      </c>
-      <c r="D44" t="s">
-        <v>159</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="B44" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45">
+      <c r="A45" s="1">
         <v>56</v>
       </c>
-      <c r="B45" t="s">
-        <v>159</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B45" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E45" t="s">
-        <v>159</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="E45" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46">
+      <c r="A46" s="1">
         <v>57</v>
       </c>
-      <c r="B46" t="s">
-        <v>159</v>
-      </c>
-      <c r="C46" t="s">
-        <v>159</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="B46" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E46" t="s">
-        <v>159</v>
-      </c>
-      <c r="F46" t="s">
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>58</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>58</v>
-      </c>
-      <c r="B47" t="s">
-        <v>159</v>
-      </c>
-      <c r="C47" t="s">
-        <v>159</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="E47" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>59</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E47" t="s">
-        <v>159</v>
-      </c>
-      <c r="F47" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>59</v>
-      </c>
-      <c r="B48" t="s">
-        <v>159</v>
-      </c>
-      <c r="C48" t="s">
-        <v>159</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="E48" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>60</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E48" t="s">
-        <v>159</v>
-      </c>
-      <c r="F48" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>60</v>
-      </c>
-      <c r="B49" t="s">
-        <v>159</v>
-      </c>
-      <c r="C49" t="s">
-        <v>159</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="E49" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>61</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="E49" t="s">
-        <v>159</v>
-      </c>
-      <c r="F49" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>61</v>
-      </c>
-      <c r="B50" t="s">
-        <v>159</v>
-      </c>
-      <c r="C50" t="s">
-        <v>159</v>
-      </c>
-      <c r="D50" t="s">
-        <v>159</v>
-      </c>
-      <c r="E50" t="s">
-        <v>159</v>
-      </c>
-      <c r="F50" t="s">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>63</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>63</v>
-      </c>
-      <c r="B51" t="s">
+      <c r="C51" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>64</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C51" t="s">
-        <v>159</v>
-      </c>
-      <c r="D51" t="s">
-        <v>159</v>
-      </c>
-      <c r="E51" t="s">
-        <v>159</v>
-      </c>
-      <c r="F51" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>64</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="C52" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>65</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C52" t="s">
-        <v>159</v>
-      </c>
-      <c r="D52" t="s">
-        <v>159</v>
-      </c>
-      <c r="E52" t="s">
-        <v>159</v>
-      </c>
-      <c r="F52" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>65</v>
-      </c>
-      <c r="B53" t="s">
+      <c r="C53" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>66</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C53" t="s">
-        <v>159</v>
-      </c>
-      <c r="D53" t="s">
-        <v>159</v>
-      </c>
-      <c r="E53" t="s">
-        <v>159</v>
-      </c>
-      <c r="F53" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>66</v>
-      </c>
-      <c r="B54" t="s">
+      <c r="C54" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>67</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C54" t="s">
-        <v>159</v>
-      </c>
-      <c r="D54" t="s">
-        <v>159</v>
-      </c>
-      <c r="E54" t="s">
-        <v>159</v>
-      </c>
-      <c r="F54" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>67</v>
-      </c>
-      <c r="B55" t="s">
-        <v>159</v>
-      </c>
-      <c r="C55" t="s">
+      <c r="D55" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>68</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="E55" t="s">
-        <v>159</v>
-      </c>
-      <c r="F55" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>68</v>
-      </c>
-      <c r="B56" t="s">
-        <v>159</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="D56" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>69</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E56" t="s">
-        <v>159</v>
-      </c>
-      <c r="F56" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>69</v>
-      </c>
-      <c r="B57" t="s">
-        <v>159</v>
-      </c>
-      <c r="C57" t="s">
-        <v>159</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="E57" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>70</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E57" t="s">
-        <v>159</v>
-      </c>
-      <c r="F57" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>70</v>
-      </c>
-      <c r="B58" t="s">
+      <c r="C58" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C58" t="s">
-        <v>159</v>
-      </c>
-      <c r="D58" t="s">
-        <v>159</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="F58" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>71</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F58" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>71</v>
-      </c>
-      <c r="B59" t="s">
-        <v>159</v>
-      </c>
-      <c r="C59" t="s">
-        <v>159</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="E59" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>72</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E59" t="s">
-        <v>159</v>
-      </c>
-      <c r="F59" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>72</v>
-      </c>
-      <c r="B60" t="s">
+      <c r="C60" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>73</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C60" t="s">
-        <v>159</v>
-      </c>
-      <c r="D60" t="s">
-        <v>159</v>
-      </c>
-      <c r="E60" t="s">
-        <v>159</v>
-      </c>
-      <c r="F60" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>73</v>
-      </c>
-      <c r="B61" t="s">
-        <v>159</v>
-      </c>
-      <c r="C61" t="s">
+      <c r="D61" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>75</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="E61" t="s">
-        <v>159</v>
-      </c>
-      <c r="F61" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>75</v>
-      </c>
-      <c r="B62" t="s">
-        <v>159</v>
-      </c>
-      <c r="C62" t="s">
-        <v>159</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="E62" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>76</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="E62" t="s">
-        <v>159</v>
-      </c>
-      <c r="F62" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>76</v>
-      </c>
-      <c r="B63" t="s">
-        <v>159</v>
-      </c>
-      <c r="C63" t="s">
-        <v>159</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="E63" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>77</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E63" t="s">
-        <v>159</v>
-      </c>
-      <c r="F63" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>77</v>
-      </c>
-      <c r="B64" t="s">
-        <v>159</v>
-      </c>
-      <c r="C64" t="s">
-        <v>159</v>
-      </c>
-      <c r="D64" t="s">
-        <v>159</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="F64" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>78</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="F64" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>78</v>
-      </c>
-      <c r="B65" t="s">
-        <v>159</v>
-      </c>
-      <c r="C65" t="s">
-        <v>159</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="E65" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>79</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E65" t="s">
-        <v>159</v>
-      </c>
-      <c r="F65" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>79</v>
-      </c>
-      <c r="B66" t="s">
-        <v>159</v>
-      </c>
-      <c r="C66" t="s">
-        <v>159</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="E66" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>80</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E66" t="s">
-        <v>159</v>
-      </c>
-      <c r="F66" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>80</v>
-      </c>
-      <c r="B67" t="s">
-        <v>159</v>
-      </c>
-      <c r="C67" t="s">
-        <v>159</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="E67" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>81</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E67" t="s">
-        <v>159</v>
-      </c>
-      <c r="F67" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>81</v>
-      </c>
-      <c r="B68" t="s">
-        <v>159</v>
-      </c>
-      <c r="C68" t="s">
-        <v>159</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="E68" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>82</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E68" t="s">
-        <v>159</v>
-      </c>
-      <c r="F68" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>82</v>
-      </c>
-      <c r="B69" t="s">
-        <v>159</v>
-      </c>
-      <c r="C69" t="s">
-        <v>159</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="E69" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>83</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E69" t="s">
-        <v>159</v>
-      </c>
-      <c r="F69" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>83</v>
-      </c>
-      <c r="B70" t="s">
-        <v>159</v>
-      </c>
-      <c r="C70" t="s">
+      <c r="D70" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>84</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="E70" t="s">
-        <v>159</v>
-      </c>
-      <c r="F70" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>84</v>
-      </c>
-      <c r="B71" t="s">
-        <v>159</v>
-      </c>
-      <c r="C71" t="s">
-        <v>159</v>
-      </c>
-      <c r="D71" t="s">
-        <v>159</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="F71" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>85</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F71" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>85</v>
-      </c>
-      <c r="B72" t="s">
-        <v>159</v>
-      </c>
-      <c r="C72" t="s">
-        <v>159</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="E72" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>86</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="E72" t="s">
-        <v>159</v>
-      </c>
-      <c r="F72" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>86</v>
-      </c>
-      <c r="B73" t="s">
-        <v>159</v>
-      </c>
-      <c r="C73" t="s">
+      <c r="D73" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>87</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E73" t="s">
-        <v>159</v>
-      </c>
-      <c r="F73" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>87</v>
-      </c>
-      <c r="B74" t="s">
-        <v>159</v>
-      </c>
-      <c r="C74" t="s">
-        <v>159</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="E74" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>88</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="E74" t="s">
-        <v>159</v>
-      </c>
-      <c r="F74" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>88</v>
-      </c>
-      <c r="B75" t="s">
-        <v>159</v>
-      </c>
-      <c r="C75" t="s">
-        <v>159</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="E75" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>89</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="E75" t="s">
-        <v>159</v>
-      </c>
-      <c r="F75" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>89</v>
-      </c>
-      <c r="B76" t="s">
-        <v>159</v>
-      </c>
-      <c r="C76" t="s">
-        <v>159</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="E76" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>90</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E76" t="s">
-        <v>159</v>
-      </c>
-      <c r="F76" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>90</v>
-      </c>
-      <c r="B77" t="s">
-        <v>159</v>
-      </c>
-      <c r="C77" t="s">
-        <v>159</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="E77" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>91</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="E77" t="s">
-        <v>159</v>
-      </c>
-      <c r="F77" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>91</v>
-      </c>
-      <c r="B78" t="s">
-        <v>159</v>
-      </c>
-      <c r="C78" t="s">
-        <v>159</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="E78" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>92</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="E78" t="s">
-        <v>159</v>
-      </c>
-      <c r="F78" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>92</v>
-      </c>
-      <c r="B79" t="s">
-        <v>159</v>
-      </c>
-      <c r="C79" t="s">
-        <v>159</v>
-      </c>
-      <c r="D79" t="s">
-        <v>159</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="F79" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>93</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="F79" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>93</v>
-      </c>
-      <c r="B80" t="s">
-        <v>159</v>
-      </c>
-      <c r="C80" t="s">
-        <v>159</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="E80" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>94</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="E80" t="s">
-        <v>159</v>
-      </c>
-      <c r="F80" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>94</v>
-      </c>
-      <c r="B81" t="s">
-        <v>159</v>
-      </c>
-      <c r="C81" t="s">
-        <v>159</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="E81" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>96</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E81" t="s">
-        <v>159</v>
-      </c>
-      <c r="F81" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>96</v>
-      </c>
-      <c r="B82" t="s">
-        <v>159</v>
-      </c>
-      <c r="C82" t="s">
+      <c r="D82" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>97</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="E82" t="s">
-        <v>159</v>
-      </c>
-      <c r="F82" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>97</v>
-      </c>
-      <c r="B83" t="s">
+      <c r="C83" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>98</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C83" t="s">
-        <v>159</v>
-      </c>
-      <c r="D83" t="s">
-        <v>159</v>
-      </c>
-      <c r="E83" t="s">
-        <v>159</v>
-      </c>
-      <c r="F83" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>98</v>
-      </c>
-      <c r="B84" t="s">
-        <v>159</v>
-      </c>
-      <c r="C84" t="s">
-        <v>159</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="E84" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>99</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="E84" t="s">
-        <v>159</v>
-      </c>
-      <c r="F84" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>99</v>
-      </c>
-      <c r="B85" t="s">
-        <v>159</v>
-      </c>
-      <c r="C85" t="s">
-        <v>159</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="F85" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>100</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="E85" t="s">
-        <v>265</v>
-      </c>
-      <c r="F85" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>100</v>
-      </c>
-      <c r="B86" t="s">
-        <v>159</v>
-      </c>
-      <c r="C86" t="s">
-        <v>159</v>
-      </c>
-      <c r="D86" t="s">
-        <v>266</v>
-      </c>
-      <c r="E86" t="s">
-        <v>159</v>
-      </c>
-      <c r="F86" t="s">
+      <c r="E86" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>159</v>
       </c>
     </row>

--- a/events/2026/config/motions-ids.xlsx
+++ b/events/2026/config/motions-ids.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mike\projects\work\wsw-results\events\2026\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E73A60A-F035-4671-B120-F6FB21145667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{758D61B0-4B8F-4FBD-B0D0-43E23F450EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="motions" sheetId="1" r:id="rId1"/>
@@ -1237,6 +1237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:U86"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1491,7 +1492,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>16</v>
       </c>
@@ -1543,7 +1544,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>17</v>
       </c>
@@ -1656,7 +1657,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>19</v>
       </c>
@@ -1711,7 +1712,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>20</v>
       </c>
@@ -1769,7 +1770,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>21</v>
       </c>
@@ -1882,7 +1883,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>23</v>
       </c>
@@ -1937,7 +1938,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>24</v>
       </c>
@@ -1992,7 +1993,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25</v>
       </c>
@@ -2105,7 +2106,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>27</v>
       </c>
@@ -2160,7 +2161,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>28</v>
       </c>
@@ -2215,7 +2216,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>29</v>
       </c>
@@ -2328,7 +2329,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>31</v>
       </c>
@@ -2383,7 +2384,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>32</v>
       </c>
@@ -2554,7 +2555,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>35</v>
       </c>
@@ -2667,7 +2668,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>37</v>
       </c>
@@ -2722,7 +2723,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>38</v>
       </c>
@@ -2777,7 +2778,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>39</v>
       </c>
@@ -2836,7 +2837,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>40</v>
       </c>
@@ -2891,7 +2892,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>41</v>
       </c>
@@ -2946,7 +2947,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>42</v>
       </c>
@@ -3001,7 +3002,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>43</v>
       </c>
@@ -3114,7 +3115,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>45</v>
       </c>
@@ -3227,7 +3228,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>47</v>
       </c>
@@ -3286,7 +3287,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>48</v>
       </c>
@@ -3341,7 +3342,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>49</v>
       </c>
@@ -3396,7 +3397,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>50</v>
       </c>
@@ -3451,7 +3452,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>51</v>
       </c>
@@ -3506,7 +3507,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>52</v>
       </c>
@@ -3561,7 +3562,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>53</v>
       </c>
@@ -3616,7 +3617,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>54</v>
       </c>
@@ -3671,7 +3672,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>55</v>
       </c>
@@ -3843,7 +3844,7 @@
         <v>Motion 1641</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>58</v>
       </c>
@@ -3898,7 +3899,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>59</v>
       </c>
@@ -3953,7 +3954,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>60</v>
       </c>
@@ -4008,7 +4009,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>61</v>
       </c>
@@ -4060,7 +4061,7 @@
         <v>Motion 618</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>63</v>
       </c>
@@ -4118,7 +4119,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>64</v>
       </c>
@@ -4173,7 +4174,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>65</v>
       </c>
@@ -4228,7 +4229,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>66</v>
       </c>
@@ -4402,7 +4403,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>69</v>
       </c>
@@ -4515,7 +4516,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>71</v>
       </c>
@@ -4574,7 +4575,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>72</v>
       </c>
@@ -4687,7 +4688,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>75</v>
       </c>
@@ -4742,7 +4743,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>76</v>
       </c>
@@ -4797,7 +4798,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>77</v>
       </c>
@@ -4849,7 +4850,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>78</v>
       </c>
@@ -4904,7 +4905,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>79</v>
       </c>
@@ -4959,7 +4960,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>80</v>
       </c>
@@ -5014,7 +5015,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>81</v>
       </c>
@@ -5072,7 +5073,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>82</v>
       </c>
@@ -5188,7 +5189,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>84</v>
       </c>
@@ -5240,7 +5241,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>85</v>
       </c>
@@ -5353,7 +5354,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>87</v>
       </c>
@@ -5408,7 +5409,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>88</v>
       </c>
@@ -5467,7 +5468,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>89</v>
       </c>
@@ -5522,7 +5523,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>90</v>
       </c>
@@ -5580,7 +5581,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>91</v>
       </c>
@@ -5639,7 +5640,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>92</v>
       </c>
@@ -5691,7 +5692,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>93</v>
       </c>
@@ -5750,7 +5751,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>94</v>
       </c>
@@ -5863,7 +5864,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>97</v>
       </c>
@@ -5921,7 +5922,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>98</v>
       </c>
@@ -6034,7 +6035,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>100</v>
       </c>
@@ -6093,7 +6094,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U86" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:U86" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="13">
+      <filters>
+        <filter val="2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/events/2026/config/motions-ids.xlsx
+++ b/events/2026/config/motions-ids.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mike\projects\work\wsw-results\events\2026\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{758D61B0-4B8F-4FBD-B0D0-43E23F450EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA0B88F-99CD-4B16-9EBC-2226B3933F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1237,7 +1237,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:U86"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1492,7 +1491,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>16</v>
       </c>
@@ -1544,7 +1543,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>17</v>
       </c>
@@ -1657,7 +1656,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>19</v>
       </c>
@@ -1712,7 +1711,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>20</v>
       </c>
@@ -1770,7 +1769,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>21</v>
       </c>
@@ -1883,7 +1882,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>23</v>
       </c>
@@ -1938,7 +1937,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>24</v>
       </c>
@@ -1993,7 +1992,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25</v>
       </c>
@@ -2106,7 +2105,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>27</v>
       </c>
@@ -2161,7 +2160,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>28</v>
       </c>
@@ -2216,7 +2215,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>29</v>
       </c>
@@ -2329,7 +2328,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>31</v>
       </c>
@@ -2384,7 +2383,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>32</v>
       </c>
@@ -2555,7 +2554,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>35</v>
       </c>
@@ -2668,7 +2667,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>37</v>
       </c>
@@ -2723,7 +2722,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>38</v>
       </c>
@@ -2778,7 +2777,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>39</v>
       </c>
@@ -2837,7 +2836,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>40</v>
       </c>
@@ -2892,7 +2891,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>41</v>
       </c>
@@ -2947,7 +2946,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>42</v>
       </c>
@@ -3002,7 +3001,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>43</v>
       </c>
@@ -3115,7 +3114,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>45</v>
       </c>
@@ -3228,7 +3227,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>47</v>
       </c>
@@ -3287,7 +3286,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>48</v>
       </c>
@@ -3342,7 +3341,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>49</v>
       </c>
@@ -3397,7 +3396,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>50</v>
       </c>
@@ -3452,7 +3451,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>51</v>
       </c>
@@ -3507,7 +3506,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>52</v>
       </c>
@@ -3562,7 +3561,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>53</v>
       </c>
@@ -3617,7 +3616,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>54</v>
       </c>
@@ -3672,7 +3671,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>55</v>
       </c>
@@ -3844,7 +3843,7 @@
         <v>Motion 1641</v>
       </c>
     </row>
-    <row r="47" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>58</v>
       </c>
@@ -3899,7 +3898,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>59</v>
       </c>
@@ -3954,7 +3953,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>60</v>
       </c>
@@ -4009,7 +4008,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>61</v>
       </c>
@@ -4061,7 +4060,7 @@
         <v>Motion 618</v>
       </c>
     </row>
-    <row r="51" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>63</v>
       </c>
@@ -4119,7 +4118,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>64</v>
       </c>
@@ -4174,7 +4173,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>65</v>
       </c>
@@ -4229,7 +4228,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>66</v>
       </c>
@@ -4403,7 +4402,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>69</v>
       </c>
@@ -4516,7 +4515,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>71</v>
       </c>
@@ -4575,7 +4574,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>72</v>
       </c>
@@ -4688,7 +4687,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>75</v>
       </c>
@@ -4743,7 +4742,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>76</v>
       </c>
@@ -4798,7 +4797,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>77</v>
       </c>
@@ -4850,7 +4849,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>78</v>
       </c>
@@ -4905,7 +4904,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>79</v>
       </c>
@@ -4960,7 +4959,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>80</v>
       </c>
@@ -5015,7 +5014,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>81</v>
       </c>
@@ -5073,7 +5072,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>82</v>
       </c>
@@ -5189,7 +5188,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>84</v>
       </c>
@@ -5241,7 +5240,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>85</v>
       </c>
@@ -5354,7 +5353,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>87</v>
       </c>
@@ -5409,7 +5408,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>88</v>
       </c>
@@ -5468,7 +5467,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>89</v>
       </c>
@@ -5523,7 +5522,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>90</v>
       </c>
@@ -5581,7 +5580,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>91</v>
       </c>
@@ -5640,7 +5639,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>92</v>
       </c>
@@ -5692,7 +5691,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>93</v>
       </c>
@@ -5751,7 +5750,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>94</v>
       </c>
@@ -5864,7 +5863,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>97</v>
       </c>
@@ -5922,7 +5921,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>98</v>
       </c>
@@ -6035,7 +6034,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>100</v>
       </c>
@@ -6094,13 +6093,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U86" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="13">
-      <filters>
-        <filter val="2"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:U86" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/events/2026/config/motions-ids.xlsx
+++ b/events/2026/config/motions-ids.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mike\projects\work\wsw-results\events\2026\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA0B88F-99CD-4B16-9EBC-2226B3933F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBC6D0D-0983-44E1-BF47-52BA18A243A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="270">
   <si>
     <t>ID</t>
   </si>
@@ -841,6 +841,15 @@
   </si>
   <si>
     <t>Motion 695</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>Dempsey</t>
+  </si>
+  <si>
+    <t>Motion 601</t>
   </si>
 </sst>
 </file>
@@ -1237,7 +1246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U86"/>
+  <dimension ref="A1:U87"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -4928,7 +4937,7 @@
         <v/>
       </c>
       <c r="N66" s="3">
-        <f t="shared" ref="N66:N86" si="16">COUNTA(H66:L66)</f>
+        <f t="shared" ref="N66:N87" si="16">COUNTA(H66:L66)</f>
         <v>1</v>
       </c>
       <c r="O66" s="3">
@@ -5443,7 +5452,7 @@
         <v>1002</v>
       </c>
       <c r="P75" s="3" t="str">
-        <f t="shared" ref="P75:P86" si="23">UPPER(_xlfn.CONCAT(LEFT(D75,3),O75,LEFT(C75,3)))</f>
+        <f t="shared" ref="P75:P87" si="23">UPPER(_xlfn.CONCAT(LEFT(D75,3),O75,LEFT(C75,3)))</f>
         <v>GOO1002GAR</v>
       </c>
       <c r="Q75" s="4" t="str">
@@ -6089,6 +6098,56 @@
       </c>
       <c r="U86" s="4" t="str">
         <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>101</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="s">
+        <v>267</v>
+      </c>
+      <c r="D87" t="s">
+        <v>268</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N87" s="3">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="O87" s="3">
+        <v>601</v>
+      </c>
+      <c r="P87" s="3" t="str">
+        <f t="shared" si="23"/>
+        <v>DEM601OSC</v>
+      </c>
+      <c r="Q87" s="4" t="str">
+        <f t="shared" ref="Q87:S87" si="24">IF(H87&lt;&gt;"", _xlfn.CONCAT("Motion ",$O87), "")</f>
+        <v>Motion 601</v>
+      </c>
+      <c r="R87" s="4" t="str">
+        <f t="shared" ref="R87" si="25">IF(I87&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N87&gt;1,"4",""),$O87), "")</f>
+        <v/>
+      </c>
+      <c r="T87" s="4" t="str">
+        <f t="shared" ref="T87" si="26">IF(K87&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N87&gt;1,"2",""),$O87), "")</f>
+        <v/>
+      </c>
+      <c r="U87" s="4" t="str">
+        <f t="shared" ref="U87" si="27">IF(L87&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N87&gt;1,"1",""),$O87), "")</f>
         <v/>
       </c>
     </row>
@@ -6101,7 +6160,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76855B16-A584-4DC9-9954-AFD12940DB0D}">
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
@@ -7832,6 +7891,23 @@
         <v>159</v>
       </c>
     </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>101</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/events/2026/config/motions-ids.xlsx
+++ b/events/2026/config/motions-ids.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mike\projects\work\wsw-results\events\2026\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBC6D0D-0983-44E1-BF47-52BA18A243A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F010C9AC-A04C-4B33-A6C3-27B7B2E76E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5448,12 +5448,11 @@
         <v>1</v>
       </c>
       <c r="O75" s="11">
-        <f>G75</f>
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="P75" s="3" t="str">
         <f t="shared" ref="P75:P87" si="23">UPPER(_xlfn.CONCAT(LEFT(D75,3),O75,LEFT(C75,3)))</f>
-        <v>GOO1002GAR</v>
+        <v>GOO1001GAR</v>
       </c>
       <c r="Q75" s="4" t="str">
         <f t="shared" si="17"/>
@@ -5465,7 +5464,7 @@
       </c>
       <c r="S75" s="4" t="str">
         <f t="shared" si="22"/>
-        <v>Motion 1002</v>
+        <v>Motion 1001</v>
       </c>
       <c r="T75" s="4" t="str">
         <f t="shared" si="19"/>
@@ -6135,7 +6134,7 @@
         <v>DEM601OSC</v>
       </c>
       <c r="Q87" s="4" t="str">
-        <f t="shared" ref="Q87:S87" si="24">IF(H87&lt;&gt;"", _xlfn.CONCAT("Motion ",$O87), "")</f>
+        <f t="shared" ref="Q87" si="24">IF(H87&lt;&gt;"", _xlfn.CONCAT("Motion ",$O87), "")</f>
         <v>Motion 601</v>
       </c>
       <c r="R87" s="4" t="str">

--- a/events/2026/config/motions-ids.xlsx
+++ b/events/2026/config/motions-ids.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="278">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -528,6 +528,12 @@
   </si>
   <si>
     <t xml:space="preserve">Hobson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lilia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yelland</t>
   </si>
   <si>
     <t xml:space="preserve">Motion 4871</t>
@@ -981,60 +987,64 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1356,4954 +1366,4969 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U97"/>
+  <dimension ref="A1:U102"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="2" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="3" width="11.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="3" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="3" width="17.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="4" width="13.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="4" width="12.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="19" style="4" width="13.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="2" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="3" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="4" width="11.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="4" width="14.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="4" width="17.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="5" width="13.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="5" width="12.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="19" style="5" width="13.29"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="S1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="T1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="U1" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="0" t="s">
+      <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" s="4" t="n">
         <f aca="false">COUNTA(H2:L2)</f>
         <v>2</v>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="O2" s="4" t="n">
         <v>871</v>
       </c>
-      <c r="P2" s="3" t="str">
+      <c r="P2" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D2,3),O2,LEFT(C2,3)))</f>
         <v>GEO871MIC</v>
       </c>
-      <c r="Q2" s="4" t="str">
+      <c r="Q2" s="5" t="str">
         <f aca="false">IF(H2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"5",""),$O2), "")</f>
         <v/>
       </c>
-      <c r="R2" s="4" t="str">
+      <c r="R2" s="5" t="str">
         <f aca="false">IF(I2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"4",""),$O2), "")</f>
         <v>Motion 4871</v>
       </c>
-      <c r="S2" s="4" t="str">
+      <c r="S2" s="5" t="str">
         <f aca="false">IF(J2&lt;&gt;"", _xlfn.CONCAT("Motion ",$O2), "")</f>
         <v>Motion 871</v>
       </c>
-      <c r="T2" s="4" t="str">
+      <c r="T2" s="5" t="str">
         <f aca="false">IF(K2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"2",""),$O2), "")</f>
         <v/>
       </c>
-      <c r="U2" s="4" t="str">
+      <c r="U2" s="5" t="str">
         <f aca="false">IF(L2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"1",""),$O2), "")</f>
         <v/>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="0" t="s">
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="I3" s="2" t="s">
+      <c r="G3" s="11"/>
+      <c r="I3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="3" t="str">
+      <c r="M3" s="4" t="str">
         <f aca="false">IF(A3-A2&lt;&gt;1,A3-A2,"")</f>
         <v/>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" s="4" t="n">
         <f aca="false">COUNTA(H3:L3)</f>
         <v>2</v>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="O3" s="4" t="n">
         <v>822</v>
       </c>
-      <c r="P3" s="3" t="str">
+      <c r="P3" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D3,3),O3,LEFT(C3,3)))</f>
         <v>PET822SIM</v>
       </c>
-      <c r="Q3" s="4" t="str">
+      <c r="Q3" s="5" t="str">
         <f aca="false">IF(H3&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N3&gt;1,"5",""),$O3), "")</f>
         <v/>
       </c>
-      <c r="R3" s="4" t="str">
+      <c r="R3" s="5" t="str">
         <f aca="false">IF(I3&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N3&gt;1,"4",""),$O3), "")</f>
         <v>Motion 4822</v>
       </c>
-      <c r="S3" s="4" t="str">
+      <c r="S3" s="5" t="str">
         <f aca="false">IF(J3&lt;&gt;"", _xlfn.CONCAT("Motion ",$O3), "")</f>
         <v>Motion 822</v>
       </c>
-      <c r="T3" s="4" t="str">
+      <c r="T3" s="5" t="str">
         <f aca="false">IF(K3&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N3&gt;1,"2",""),$O3), "")</f>
         <v/>
       </c>
-      <c r="U3" s="4" t="str">
+      <c r="U3" s="5" t="str">
         <f aca="false">IF(L3&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N3&gt;1,"1",""),$O3), "")</f>
         <v/>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="I4" s="2" t="s">
+      <c r="G4" s="11"/>
+      <c r="I4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="3" t="str">
+      <c r="M4" s="4" t="str">
         <f aca="false">IF(A4-A3&lt;&gt;1,A4-A3,"")</f>
         <v/>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="N4" s="4" t="n">
         <f aca="false">COUNTA(H4:L4)</f>
         <v>2</v>
       </c>
-      <c r="O4" s="3" t="n">
+      <c r="O4" s="4" t="n">
         <v>935</v>
       </c>
-      <c r="P4" s="3" t="str">
+      <c r="P4" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D4,3),O4,LEFT(C4,3)))</f>
         <v>GIB935JEN</v>
       </c>
-      <c r="Q4" s="4" t="str">
+      <c r="Q4" s="5" t="str">
         <f aca="false">IF(H4&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N4&gt;1,"5",""),$O4), "")</f>
         <v/>
       </c>
-      <c r="R4" s="4" t="str">
+      <c r="R4" s="5" t="str">
         <f aca="false">IF(I4&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N4&gt;1,"4",""),$O4), "")</f>
         <v>Motion 4935</v>
       </c>
-      <c r="S4" s="4" t="str">
+      <c r="S4" s="5" t="str">
         <f aca="false">IF(J4&lt;&gt;"", _xlfn.CONCAT("Motion ",$O4), "")</f>
         <v>Motion 935</v>
       </c>
-      <c r="T4" s="4" t="str">
+      <c r="T4" s="5" t="str">
         <f aca="false">IF(K4&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N4&gt;1,"2",""),$O4), "")</f>
         <v/>
       </c>
-      <c r="U4" s="4" t="str">
+      <c r="U4" s="5" t="str">
         <f aca="false">IF(L4&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N4&gt;1,"1",""),$O4), "")</f>
         <v/>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
-        <v>16</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="0" t="s">
+      <c r="A5" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M5" s="3" t="str">
+      <c r="M5" s="4" t="str">
         <f aca="false">IF(A5-A4&lt;&gt;1,A5-A4,"")</f>
         <v/>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="4" t="n">
         <f aca="false">COUNTA(H5:L5)</f>
         <v>1</v>
       </c>
-      <c r="O5" s="3" t="n">
+      <c r="O5" s="4" t="n">
         <v>665</v>
       </c>
-      <c r="P5" s="3" t="str">
+      <c r="P5" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D5,3),O5,LEFT(C5,3)))</f>
         <v>VAS665STA</v>
       </c>
-      <c r="Q5" s="4" t="str">
+      <c r="Q5" s="5" t="str">
         <f aca="false">IF(H5&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N5&gt;1,"5",""),$O5), "")</f>
         <v/>
       </c>
-      <c r="R5" s="4" t="str">
+      <c r="R5" s="5" t="str">
         <f aca="false">IF(I5&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N5&gt;1,"4",""),$O5), "")</f>
         <v/>
       </c>
-      <c r="S5" s="4" t="str">
+      <c r="S5" s="5" t="str">
         <f aca="false">IF(J5&lt;&gt;"", _xlfn.CONCAT("Motion ",$O5), "")</f>
         <v/>
       </c>
-      <c r="T5" s="4" t="str">
+      <c r="T5" s="5" t="str">
         <f aca="false">IF(K5&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N5&gt;1,"2",""),$O5), "")</f>
         <v>Motion 665</v>
       </c>
-      <c r="U5" s="4" t="str">
+      <c r="U5" s="5" t="str">
         <f aca="false">IF(L5&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N5&gt;1,"1",""),$O5), "")</f>
         <v/>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="3" t="str">
+      <c r="M6" s="4" t="str">
         <f aca="false">IF(A6-A5&lt;&gt;1,A6-A5,"")</f>
         <v/>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="4" t="n">
         <f aca="false">COUNTA(H6:L6)</f>
         <v>1</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="O6" s="4" t="n">
         <v>662</v>
       </c>
-      <c r="P6" s="3" t="str">
+      <c r="P6" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D6,3),O6,LEFT(C6,3)))</f>
         <v>EIF662AYA</v>
       </c>
-      <c r="Q6" s="4" t="str">
+      <c r="Q6" s="5" t="str">
         <f aca="false">IF(H6&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N6&gt;1,"5",""),$O6), "")</f>
         <v/>
       </c>
-      <c r="R6" s="4" t="str">
+      <c r="R6" s="5" t="str">
         <f aca="false">IF(I6&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N6&gt;1,"4",""),$O6), "")</f>
         <v/>
       </c>
-      <c r="S6" s="4" t="str">
+      <c r="S6" s="5" t="str">
         <f aca="false">IF(J6&lt;&gt;"", _xlfn.CONCAT("Motion ",$O6), "")</f>
         <v/>
       </c>
-      <c r="T6" s="4" t="str">
+      <c r="T6" s="5" t="str">
         <f aca="false">IF(K6&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N6&gt;1,"2",""),$O6), "")</f>
         <v>Motion 662</v>
       </c>
-      <c r="U6" s="4" t="str">
+      <c r="U6" s="5" t="str">
         <f aca="false">IF(L6&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N6&gt;1,"1",""),$O6), "")</f>
         <v/>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="0" t="s">
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M7" s="3" t="str">
+      <c r="M7" s="4" t="str">
         <f aca="false">IF(A7-A6&lt;&gt;1,A7-A6,"")</f>
         <v/>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" s="4" t="n">
         <f aca="false">COUNTA(H7:L7)</f>
         <v>2</v>
       </c>
-      <c r="O7" s="3" t="n">
+      <c r="O7" s="4" t="n">
         <v>873</v>
       </c>
-      <c r="P7" s="3" t="str">
+      <c r="P7" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D7,3),O7,LEFT(C7,3)))</f>
         <v>CHI873DYL</v>
       </c>
-      <c r="Q7" s="4" t="str">
+      <c r="Q7" s="5" t="str">
         <f aca="false">IF(H7&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N7&gt;1,"5",""),$O7), "")</f>
         <v/>
       </c>
-      <c r="R7" s="4" t="str">
+      <c r="R7" s="5" t="str">
         <f aca="false">IF(I7&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N7&gt;1,"4",""),$O7), "")</f>
         <v>Motion 4873</v>
       </c>
-      <c r="S7" s="4" t="str">
+      <c r="S7" s="5" t="str">
         <f aca="false">IF(J7&lt;&gt;"", _xlfn.CONCAT("Motion ",$O7), "")</f>
         <v>Motion 873</v>
       </c>
-      <c r="T7" s="4" t="str">
+      <c r="T7" s="5" t="str">
         <f aca="false">IF(K7&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N7&gt;1,"2",""),$O7), "")</f>
         <v/>
       </c>
-      <c r="U7" s="4" t="str">
+      <c r="U7" s="5" t="str">
         <f aca="false">IF(L7&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N7&gt;1,"1",""),$O7), "")</f>
         <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="0" t="s">
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="3" t="str">
+      <c r="M8" s="4" t="str">
         <f aca="false">IF(A8-A7&lt;&gt;1,A8-A7,"")</f>
         <v/>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N8" s="4" t="n">
         <f aca="false">COUNTA(H8:L8)</f>
         <v>1</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="O8" s="4" t="n">
         <v>870</v>
       </c>
-      <c r="P8" s="3" t="str">
+      <c r="P8" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D8,3),O8,LEFT(C8,3)))</f>
         <v>HEN870RIC</v>
       </c>
-      <c r="Q8" s="4" t="str">
+      <c r="Q8" s="5" t="str">
         <f aca="false">IF(H8&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N8&gt;1,"5",""),$O8), "")</f>
         <v/>
       </c>
-      <c r="R8" s="4" t="str">
+      <c r="R8" s="5" t="str">
         <f aca="false">IF(I8&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N8&gt;1,"4",""),$O8), "")</f>
         <v/>
       </c>
-      <c r="S8" s="4" t="str">
+      <c r="S8" s="5" t="str">
         <f aca="false">IF(J8&lt;&gt;"", _xlfn.CONCAT("Motion ",$O8), "")</f>
         <v>Motion 870</v>
       </c>
-      <c r="T8" s="4" t="str">
+      <c r="T8" s="5" t="str">
         <f aca="false">IF(K8&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N8&gt;1,"2",""),$O8), "")</f>
         <v/>
       </c>
-      <c r="U8" s="4" t="str">
+      <c r="U8" s="5" t="str">
         <f aca="false">IF(L8&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N8&gt;1,"1",""),$O8), "")</f>
         <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="0" t="s">
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="11" t="n">
         <v>940</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M9" s="3" t="str">
+      <c r="M9" s="4" t="str">
         <f aca="false">IF(A9-A8&lt;&gt;1,A9-A8,"")</f>
         <v/>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="N9" s="4" t="n">
         <f aca="false">COUNTA(H9:L9)</f>
         <v>1</v>
       </c>
-      <c r="O9" s="11" t="n">
+      <c r="O9" s="12" t="n">
         <v>940</v>
       </c>
-      <c r="P9" s="3" t="str">
+      <c r="P9" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D9,3),O9,LEFT(C9,3)))</f>
         <v>DIC940ROD</v>
       </c>
-      <c r="Q9" s="4" t="str">
+      <c r="Q9" s="5" t="str">
         <f aca="false">IF(H9&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N9&gt;1,"5",""),$O9), "")</f>
         <v>Motion 940</v>
       </c>
-      <c r="R9" s="4" t="str">
+      <c r="R9" s="5" t="str">
         <f aca="false">IF(I9&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N9&gt;1,"4",""),$O9), "")</f>
         <v/>
       </c>
-      <c r="S9" s="4" t="str">
+      <c r="S9" s="5" t="str">
         <f aca="false">IF(J9&lt;&gt;"", _xlfn.CONCAT("Motion ",$O9), "")</f>
         <v/>
       </c>
-      <c r="T9" s="4" t="str">
+      <c r="T9" s="5" t="str">
         <f aca="false">IF(K9&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N9&gt;1,"2",""),$O9), "")</f>
         <v/>
       </c>
-      <c r="U9" s="4" t="str">
+      <c r="U9" s="5" t="str">
         <f aca="false">IF(L9&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N9&gt;1,"1",""),$O9), "")</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="0" t="s">
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="3" t="str">
+      <c r="M10" s="4" t="str">
         <f aca="false">IF(A10-A9&lt;&gt;1,A10-A9,"")</f>
         <v/>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="N10" s="4" t="n">
         <f aca="false">COUNTA(H10:L10)</f>
         <v>1</v>
       </c>
-      <c r="O10" s="3" t="n">
+      <c r="O10" s="4" t="n">
         <v>802</v>
       </c>
-      <c r="P10" s="3" t="str">
+      <c r="P10" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT("BRU",O10,LEFT(C10,3)))</f>
         <v>BRU802JEA</v>
       </c>
-      <c r="Q10" s="4" t="str">
+      <c r="Q10" s="5" t="str">
         <f aca="false">IF(H10&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N10&gt;1,"5",""),$O10), "")</f>
         <v/>
       </c>
-      <c r="R10" s="4" t="str">
+      <c r="R10" s="5" t="str">
         <f aca="false">IF(I10&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N10&gt;1,"4",""),$O10), "")</f>
         <v/>
       </c>
-      <c r="S10" s="4" t="str">
+      <c r="S10" s="5" t="str">
         <f aca="false">IF(J10&lt;&gt;"", _xlfn.CONCAT("Motion ",$O10), "")</f>
         <v>Motion 802</v>
       </c>
-      <c r="T10" s="4" t="str">
+      <c r="T10" s="5" t="str">
         <f aca="false">IF(K10&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N10&gt;1,"2",""),$O10), "")</f>
         <v/>
       </c>
-      <c r="U10" s="4" t="str">
+      <c r="U10" s="5" t="str">
         <f aca="false">IF(L10&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N10&gt;1,"1",""),$O10), "")</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="0" t="s">
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M11" s="3" t="str">
+      <c r="M11" s="4" t="str">
         <f aca="false">IF(A11-A10&lt;&gt;1,A11-A10,"")</f>
         <v/>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N11" s="4" t="n">
         <f aca="false">COUNTA(H11:L11)</f>
         <v>2</v>
       </c>
-      <c r="O11" s="3" t="n">
+      <c r="O11" s="4" t="n">
         <v>978</v>
       </c>
-      <c r="P11" s="3" t="str">
+      <c r="P11" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D11,3),O11,LEFT(C11,3)))</f>
         <v>DUD978RIC</v>
       </c>
-      <c r="Q11" s="4" t="str">
+      <c r="Q11" s="5" t="str">
         <f aca="false">IF(H11&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N11&gt;1,"5",""),$O11), "")</f>
         <v/>
       </c>
-      <c r="R11" s="4" t="str">
+      <c r="R11" s="5" t="str">
         <f aca="false">IF(I11&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N11&gt;1,"4",""),$O11), "")</f>
         <v>Motion 4978</v>
       </c>
-      <c r="S11" s="4" t="str">
+      <c r="S11" s="5" t="str">
         <f aca="false">IF(J11&lt;&gt;"", _xlfn.CONCAT("Motion ",$O11), "")</f>
         <v>Motion 978</v>
       </c>
-      <c r="T11" s="4" t="str">
+      <c r="T11" s="5" t="str">
         <f aca="false">IF(K11&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N11&gt;1,"2",""),$O11), "")</f>
         <v/>
       </c>
-      <c r="U11" s="4" t="str">
+      <c r="U11" s="5" t="str">
         <f aca="false">IF(L11&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N11&gt;1,"1",""),$O11), "")</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B12" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="0" t="s">
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M12" s="3" t="str">
+      <c r="M12" s="4" t="str">
         <f aca="false">IF(A12-A11&lt;&gt;1,A12-A11,"")</f>
         <v/>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" s="4" t="n">
         <f aca="false">COUNTA(H12:L12)</f>
         <v>1</v>
       </c>
-      <c r="O12" s="3" t="n">
+      <c r="O12" s="4" t="n">
         <v>1045</v>
       </c>
-      <c r="P12" s="3" t="str">
+      <c r="P12" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D12,3),O12,LEFT(C12,3)))</f>
         <v>MEY1045BEN</v>
       </c>
-      <c r="Q12" s="4" t="str">
+      <c r="Q12" s="5" t="str">
         <f aca="false">IF(H12&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N12&gt;1,"5",""),$O12), "")</f>
         <v/>
       </c>
-      <c r="R12" s="4" t="str">
+      <c r="R12" s="5" t="str">
         <f aca="false">IF(I12&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N12&gt;1,"4",""),$O12), "")</f>
         <v/>
       </c>
-      <c r="S12" s="4" t="str">
+      <c r="S12" s="5" t="str">
         <f aca="false">IF(J12&lt;&gt;"", _xlfn.CONCAT("Motion ",$O12), "")</f>
         <v>Motion 1045</v>
       </c>
-      <c r="T12" s="4" t="str">
+      <c r="T12" s="5" t="str">
         <f aca="false">IF(K12&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N12&gt;1,"2",""),$O12), "")</f>
         <v/>
       </c>
-      <c r="U12" s="4" t="str">
+      <c r="U12" s="5" t="str">
         <f aca="false">IF(L12&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N12&gt;1,"1",""),$O12), "")</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B13" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="0" t="s">
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M13" s="3" t="str">
+      <c r="M13" s="4" t="str">
         <f aca="false">IF(A13-A12&lt;&gt;1,A13-A12,"")</f>
         <v/>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="N13" s="4" t="n">
         <f aca="false">COUNTA(H13:L13)</f>
         <v>1</v>
       </c>
-      <c r="O13" s="3" t="n">
+      <c r="O13" s="4" t="n">
         <v>642</v>
       </c>
-      <c r="P13" s="3" t="str">
+      <c r="P13" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D13,3),O13,LEFT(C13,3)))</f>
         <v>MIL642JEZ</v>
       </c>
-      <c r="Q13" s="4" t="str">
+      <c r="Q13" s="5" t="str">
         <f aca="false">IF(H13&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N13&gt;1,"5",""),$O13), "")</f>
         <v>Motion 642</v>
       </c>
-      <c r="R13" s="4" t="str">
+      <c r="R13" s="5" t="str">
         <f aca="false">IF(I13&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N13&gt;1,"4",""),$O13), "")</f>
         <v/>
       </c>
-      <c r="S13" s="4" t="str">
+      <c r="S13" s="5" t="str">
         <f aca="false">IF(J13&lt;&gt;"", _xlfn.CONCAT("Motion ",$O13), "")</f>
         <v/>
       </c>
-      <c r="T13" s="4" t="str">
+      <c r="T13" s="5" t="str">
         <f aca="false">IF(K13&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N13&gt;1,"2",""),$O13), "")</f>
         <v/>
       </c>
-      <c r="U13" s="4" t="str">
+      <c r="U13" s="5" t="str">
         <f aca="false">IF(L13&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N13&gt;1,"1",""),$O13), "")</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B14" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="0" t="s">
+      <c r="B14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="3" t="str">
+      <c r="M14" s="4" t="str">
         <f aca="false">IF(A14-A13&lt;&gt;1,A14-A13,"")</f>
         <v/>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" s="4" t="n">
         <f aca="false">COUNTA(H14:L14)</f>
         <v>1</v>
       </c>
-      <c r="O14" s="3" t="n">
+      <c r="O14" s="4" t="n">
         <v>813</v>
       </c>
-      <c r="P14" s="3" t="str">
+      <c r="P14" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D14,3),O14,LEFT(C14,3)))</f>
         <v>REE813MAR</v>
       </c>
-      <c r="Q14" s="4" t="str">
+      <c r="Q14" s="5" t="str">
         <f aca="false">IF(H14&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N14&gt;1,"5",""),$O14), "")</f>
         <v/>
       </c>
-      <c r="R14" s="4" t="str">
+      <c r="R14" s="5" t="str">
         <f aca="false">IF(I14&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N14&gt;1,"4",""),$O14), "")</f>
         <v/>
       </c>
-      <c r="S14" s="4" t="str">
+      <c r="S14" s="5" t="str">
         <f aca="false">IF(J14&lt;&gt;"", _xlfn.CONCAT("Motion ",$O14), "")</f>
         <v>Motion 813</v>
       </c>
-      <c r="T14" s="4" t="str">
+      <c r="T14" s="5" t="str">
         <f aca="false">IF(K14&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N14&gt;1,"2",""),$O14), "")</f>
         <v/>
       </c>
-      <c r="U14" s="4" t="str">
+      <c r="U14" s="5" t="str">
         <f aca="false">IF(L14&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N14&gt;1,"1",""),$O14), "")</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B15" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="0" t="s">
+      <c r="B15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M15" s="3" t="str">
+      <c r="M15" s="4" t="str">
         <f aca="false">IF(A15-A14&lt;&gt;1,A15-A14,"")</f>
         <v/>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="N15" s="4" t="n">
         <f aca="false">COUNTA(H15:L15)</f>
         <v>2</v>
       </c>
-      <c r="O15" s="3" t="n">
+      <c r="O15" s="4" t="n">
         <v>805</v>
       </c>
-      <c r="P15" s="3" t="str">
+      <c r="P15" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D15,3),O15,LEFT(C15,3)))</f>
         <v>LON805ROB</v>
       </c>
-      <c r="Q15" s="4" t="str">
+      <c r="Q15" s="5" t="str">
         <f aca="false">IF(H15&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N15&gt;1,"5",""),$O15), "")</f>
         <v/>
       </c>
-      <c r="R15" s="4" t="str">
+      <c r="R15" s="5" t="str">
         <f aca="false">IF(I15&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N15&gt;1,"4",""),$O15), "")</f>
         <v>Motion 4805</v>
       </c>
-      <c r="S15" s="4" t="str">
+      <c r="S15" s="5" t="str">
         <f aca="false">IF(J15&lt;&gt;"", _xlfn.CONCAT("Motion ",$O15), "")</f>
         <v>Motion 805</v>
       </c>
-      <c r="T15" s="4" t="str">
+      <c r="T15" s="5" t="str">
         <f aca="false">IF(K15&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N15&gt;1,"2",""),$O15), "")</f>
         <v/>
       </c>
-      <c r="U15" s="4" t="str">
+      <c r="U15" s="5" t="str">
         <f aca="false">IF(L15&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N15&gt;1,"1",""),$O15), "")</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M16" s="3" t="str">
+      <c r="M16" s="4" t="str">
         <f aca="false">IF(A16-A15&lt;&gt;1,A16-A15,"")</f>
         <v/>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="N16" s="4" t="n">
         <f aca="false">COUNTA(H16:L16)</f>
         <v>1</v>
       </c>
-      <c r="O16" s="3" t="n">
+      <c r="O16" s="4" t="n">
         <v>632</v>
       </c>
-      <c r="P16" s="3" t="str">
+      <c r="P16" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D16,3),O16,LEFT(C16,3)))</f>
         <v>ROG632KAT</v>
       </c>
-      <c r="Q16" s="4" t="str">
+      <c r="Q16" s="5" t="str">
         <f aca="false">IF(H16&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N16&gt;1,"5",""),$O16), "")</f>
         <v>Motion 632</v>
       </c>
-      <c r="R16" s="4" t="str">
+      <c r="R16" s="5" t="str">
         <f aca="false">IF(I16&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N16&gt;1,"4",""),$O16), "")</f>
         <v/>
       </c>
-      <c r="S16" s="4" t="str">
+      <c r="S16" s="5" t="str">
         <f aca="false">IF(J16&lt;&gt;"", _xlfn.CONCAT("Motion ",$O16), "")</f>
         <v/>
       </c>
-      <c r="T16" s="4" t="str">
+      <c r="T16" s="5" t="str">
         <f aca="false">IF(K16&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N16&gt;1,"2",""),$O16), "")</f>
         <v/>
       </c>
-      <c r="U16" s="4" t="str">
+      <c r="U16" s="5" t="str">
         <f aca="false">IF(L16&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N16&gt;1,"1",""),$O16), "")</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B17" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="0" t="s">
+      <c r="B17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M17" s="3" t="str">
+      <c r="M17" s="4" t="str">
         <f aca="false">IF(A17-A16&lt;&gt;1,A17-A16,"")</f>
         <v/>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="N17" s="4" t="n">
         <f aca="false">COUNTA(H17:L17)</f>
         <v>1</v>
       </c>
-      <c r="O17" s="3" t="n">
+      <c r="O17" s="4" t="n">
         <v>855</v>
       </c>
-      <c r="P17" s="3" t="str">
+      <c r="P17" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D17,3),O17,LEFT(C17,3)))</f>
         <v>SMI855BAR</v>
       </c>
-      <c r="Q17" s="4" t="str">
+      <c r="Q17" s="5" t="str">
         <f aca="false">IF(H17&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N17&gt;1,"5",""),$O17), "")</f>
         <v/>
       </c>
-      <c r="R17" s="4" t="str">
+      <c r="R17" s="5" t="str">
         <f aca="false">IF(I17&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N17&gt;1,"4",""),$O17), "")</f>
         <v/>
       </c>
-      <c r="S17" s="4" t="str">
+      <c r="S17" s="5" t="str">
         <f aca="false">IF(J17&lt;&gt;"", _xlfn.CONCAT("Motion ",$O17), "")</f>
         <v>Motion 855</v>
       </c>
-      <c r="T17" s="4" t="str">
+      <c r="T17" s="5" t="str">
         <f aca="false">IF(K17&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N17&gt;1,"2",""),$O17), "")</f>
         <v/>
       </c>
-      <c r="U17" s="4" t="str">
+      <c r="U17" s="5" t="str">
         <f aca="false">IF(L17&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N17&gt;1,"1",""),$O17), "")</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B18" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="0" t="s">
+      <c r="B18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M18" s="3" t="str">
+      <c r="M18" s="4" t="str">
         <f aca="false">IF(A18-A17&lt;&gt;1,A18-A17,"")</f>
         <v/>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N18" s="4" t="n">
         <f aca="false">COUNTA(H18:L18)</f>
         <v>1</v>
       </c>
-      <c r="O18" s="3" t="n">
+      <c r="O18" s="4" t="n">
         <v>824</v>
       </c>
-      <c r="P18" s="3" t="str">
+      <c r="P18" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D18,3),O18,LEFT(C18,3)))</f>
         <v>CRO824RIC</v>
       </c>
-      <c r="Q18" s="4" t="str">
+      <c r="Q18" s="5" t="str">
         <f aca="false">IF(H18&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N18&gt;1,"5",""),$O18), "")</f>
         <v/>
       </c>
-      <c r="R18" s="4" t="str">
+      <c r="R18" s="5" t="str">
         <f aca="false">IF(I18&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N18&gt;1,"4",""),$O18), "")</f>
         <v/>
       </c>
-      <c r="S18" s="4" t="str">
+      <c r="S18" s="5" t="str">
         <f aca="false">IF(J18&lt;&gt;"", _xlfn.CONCAT("Motion ",$O18), "")</f>
         <v>Motion 824</v>
       </c>
-      <c r="T18" s="4" t="str">
+      <c r="T18" s="5" t="str">
         <f aca="false">IF(K18&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N18&gt;1,"2",""),$O18), "")</f>
         <v/>
       </c>
-      <c r="U18" s="4" t="str">
+      <c r="U18" s="5" t="str">
         <f aca="false">IF(L18&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N18&gt;1,"1",""),$O18), "")</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B19" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="0" t="s">
+      <c r="B19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="I19" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M19" s="3" t="str">
+      <c r="M19" s="4" t="str">
         <f aca="false">IF(A19-A18&lt;&gt;1,A19-A18,"")</f>
         <v/>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" s="4" t="n">
         <f aca="false">COUNTA(H19:L19)</f>
         <v>2</v>
       </c>
-      <c r="O19" s="3" t="n">
+      <c r="O19" s="4" t="n">
         <v>952</v>
       </c>
-      <c r="P19" s="3" t="str">
+      <c r="P19" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D19,3),O19,LEFT(C19,3)))</f>
         <v>CRO952PET</v>
       </c>
-      <c r="Q19" s="4" t="str">
+      <c r="Q19" s="5" t="str">
         <f aca="false">IF(H19&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N19&gt;1,"5",""),$O19), "")</f>
         <v/>
       </c>
-      <c r="R19" s="4" t="str">
+      <c r="R19" s="5" t="str">
         <f aca="false">IF(I19&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N19&gt;1,"4",""),$O19), "")</f>
         <v>Motion 4952</v>
       </c>
-      <c r="S19" s="4" t="str">
+      <c r="S19" s="5" t="str">
         <f aca="false">IF(J19&lt;&gt;"", _xlfn.CONCAT("Motion ",$O19), "")</f>
         <v>Motion 952</v>
       </c>
-      <c r="T19" s="4" t="str">
+      <c r="T19" s="5" t="str">
         <f aca="false">IF(K19&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N19&gt;1,"2",""),$O19), "")</f>
         <v/>
       </c>
-      <c r="U19" s="4" t="str">
+      <c r="U19" s="5" t="str">
         <f aca="false">IF(L19&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N19&gt;1,"1",""),$O19), "")</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B20" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="0" t="s">
+      <c r="B20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="J20" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M20" s="3" t="str">
+      <c r="M20" s="4" t="str">
         <f aca="false">IF(A20-A19&lt;&gt;1,A20-A19,"")</f>
         <v/>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N20" s="4" t="n">
         <f aca="false">COUNTA(H20:L20)</f>
         <v>1</v>
       </c>
-      <c r="O20" s="3" t="n">
+      <c r="O20" s="4" t="n">
         <v>849</v>
       </c>
-      <c r="P20" s="3" t="str">
+      <c r="P20" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D20,3),O20,LEFT(C20,3)))</f>
         <v>BAR849SIM</v>
       </c>
-      <c r="Q20" s="4" t="str">
+      <c r="Q20" s="5" t="str">
         <f aca="false">IF(H20&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N20&gt;1,"5",""),$O20), "")</f>
         <v/>
       </c>
-      <c r="R20" s="4" t="str">
+      <c r="R20" s="5" t="str">
         <f aca="false">IF(I20&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N20&gt;1,"4",""),$O20), "")</f>
         <v/>
       </c>
-      <c r="S20" s="4" t="str">
+      <c r="S20" s="5" t="str">
         <f aca="false">IF(J20&lt;&gt;"", _xlfn.CONCAT("Motion ",$O20), "")</f>
         <v>Motion 849</v>
       </c>
-      <c r="T20" s="4" t="str">
+      <c r="T20" s="5" t="str">
         <f aca="false">IF(K20&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N20&gt;1,"2",""),$O20), "")</f>
         <v/>
       </c>
-      <c r="U20" s="4" t="str">
+      <c r="U20" s="5" t="str">
         <f aca="false">IF(L20&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N20&gt;1,"1",""),$O20), "")</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B21" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="0" t="s">
+      <c r="B21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="J21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M21" s="3" t="str">
+      <c r="M21" s="4" t="str">
         <f aca="false">IF(A21-A20&lt;&gt;1,A21-A20,"")</f>
         <v/>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" s="4" t="n">
         <f aca="false">COUNTA(H21:L21)</f>
         <v>1</v>
       </c>
-      <c r="O21" s="3" t="n">
+      <c r="O21" s="4" t="n">
         <v>806</v>
       </c>
-      <c r="P21" s="3" t="str">
+      <c r="P21" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D21,3),O21,LEFT(C21,3)))</f>
         <v>MAY806SCO</v>
       </c>
-      <c r="Q21" s="4" t="str">
+      <c r="Q21" s="5" t="str">
         <f aca="false">IF(H21&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N21&gt;1,"5",""),$O21), "")</f>
         <v/>
       </c>
-      <c r="R21" s="4" t="str">
+      <c r="R21" s="5" t="str">
         <f aca="false">IF(I21&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N21&gt;1,"4",""),$O21), "")</f>
         <v/>
       </c>
-      <c r="S21" s="4" t="str">
+      <c r="S21" s="5" t="str">
         <f aca="false">IF(J21&lt;&gt;"", _xlfn.CONCAT("Motion ",$O21), "")</f>
         <v>Motion 806</v>
       </c>
-      <c r="T21" s="4" t="str">
+      <c r="T21" s="5" t="str">
         <f aca="false">IF(K21&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N21&gt;1,"2",""),$O21), "")</f>
         <v/>
       </c>
-      <c r="U21" s="4" t="str">
+      <c r="U21" s="5" t="str">
         <f aca="false">IF(L21&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N21&gt;1,"1",""),$O21), "")</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B22" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="0" t="s">
+      <c r="B22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="I22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="J22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M22" s="3" t="str">
+      <c r="M22" s="4" t="str">
         <f aca="false">IF(A22-A21&lt;&gt;1,A22-A21,"")</f>
         <v/>
       </c>
-      <c r="N22" s="3" t="n">
+      <c r="N22" s="4" t="n">
         <f aca="false">COUNTA(H22:L22)</f>
         <v>2</v>
       </c>
-      <c r="O22" s="3" t="n">
+      <c r="O22" s="4" t="n">
         <v>807</v>
       </c>
-      <c r="P22" s="3" t="str">
+      <c r="P22" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D22,3),O22,LEFT(C22,3)))</f>
         <v>ILI807NIK</v>
       </c>
-      <c r="Q22" s="4" t="str">
+      <c r="Q22" s="5" t="str">
         <f aca="false">IF(H22&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N22&gt;1,"5",""),$O22), "")</f>
         <v/>
       </c>
-      <c r="R22" s="4" t="str">
+      <c r="R22" s="5" t="str">
         <f aca="false">IF(I22&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N22&gt;1,"4",""),$O22), "")</f>
         <v>Motion 4807</v>
       </c>
-      <c r="S22" s="4" t="str">
+      <c r="S22" s="5" t="str">
         <f aca="false">IF(J22&lt;&gt;"", _xlfn.CONCAT("Motion ",$O22), "")</f>
         <v>Motion 807</v>
       </c>
-      <c r="T22" s="4" t="str">
+      <c r="T22" s="5" t="str">
         <f aca="false">IF(K22&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N22&gt;1,"2",""),$O22), "")</f>
         <v/>
       </c>
-      <c r="U22" s="4" t="str">
+      <c r="U22" s="5" t="str">
         <f aca="false">IF(L22&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N22&gt;1,"1",""),$O22), "")</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B23" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="0" t="s">
+      <c r="B23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="I23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="J23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M23" s="3" t="str">
+      <c r="M23" s="4" t="str">
         <f aca="false">IF(A23-A22&lt;&gt;1,A23-A22,"")</f>
         <v/>
       </c>
-      <c r="N23" s="3" t="n">
+      <c r="N23" s="4" t="n">
         <f aca="false">COUNTA(H23:L23)</f>
         <v>2</v>
       </c>
-      <c r="O23" s="3" t="n">
+      <c r="O23" s="4" t="n">
         <v>801</v>
       </c>
-      <c r="P23" s="3" t="str">
+      <c r="P23" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D23,3),O23,LEFT(C23,3)))</f>
         <v>ING801MAR</v>
       </c>
-      <c r="Q23" s="4" t="str">
+      <c r="Q23" s="5" t="str">
         <f aca="false">IF(H23&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N23&gt;1,"5",""),$O23), "")</f>
         <v/>
       </c>
-      <c r="R23" s="4" t="str">
+      <c r="R23" s="5" t="str">
         <f aca="false">IF(I23&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N23&gt;1,"4",""),$O23), "")</f>
         <v>Motion 4801</v>
       </c>
-      <c r="S23" s="4" t="str">
+      <c r="S23" s="5" t="str">
         <f aca="false">IF(J23&lt;&gt;"", _xlfn.CONCAT("Motion ",$O23), "")</f>
         <v>Motion 801</v>
       </c>
-      <c r="T23" s="4" t="str">
+      <c r="T23" s="5" t="str">
         <f aca="false">IF(K23&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N23&gt;1,"2",""),$O23), "")</f>
         <v/>
       </c>
-      <c r="U23" s="4" t="str">
+      <c r="U23" s="5" t="str">
         <f aca="false">IF(L23&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N23&gt;1,"1",""),$O23), "")</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B24" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="0" t="s">
+      <c r="B24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="J24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M24" s="3" t="str">
+      <c r="M24" s="4" t="str">
         <f aca="false">IF(A24-A23&lt;&gt;1,A24-A23,"")</f>
         <v/>
       </c>
-      <c r="N24" s="3" t="n">
+      <c r="N24" s="4" t="n">
         <f aca="false">COUNTA(H24:L24)</f>
         <v>1</v>
       </c>
-      <c r="O24" s="3" t="n">
+      <c r="O24" s="4" t="n">
         <v>1043</v>
       </c>
-      <c r="P24" s="3" t="str">
+      <c r="P24" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D24,3),O24,LEFT(C24,3)))</f>
         <v>ING1043JON</v>
       </c>
-      <c r="Q24" s="4" t="str">
+      <c r="Q24" s="5" t="str">
         <f aca="false">IF(H24&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N24&gt;1,"5",""),$O24), "")</f>
         <v/>
       </c>
-      <c r="R24" s="4" t="str">
+      <c r="R24" s="5" t="str">
         <f aca="false">IF(I24&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N24&gt;1,"4",""),$O24), "")</f>
         <v/>
       </c>
-      <c r="S24" s="4" t="str">
+      <c r="S24" s="5" t="str">
         <f aca="false">IF(J24&lt;&gt;"", _xlfn.CONCAT("Motion ",$O24), "")</f>
         <v>Motion 1043</v>
       </c>
-      <c r="T24" s="4" t="str">
+      <c r="T24" s="5" t="str">
         <f aca="false">IF(K24&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N24&gt;1,"2",""),$O24), "")</f>
         <v/>
       </c>
-      <c r="U24" s="4" t="str">
+      <c r="U24" s="5" t="str">
         <f aca="false">IF(L24&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N24&gt;1,"1",""),$O24), "")</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B25" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="0" t="s">
+      <c r="B25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="I25" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="J25" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M25" s="3" t="str">
+      <c r="M25" s="4" t="str">
         <f aca="false">IF(A25-A24&lt;&gt;1,A25-A24,"")</f>
         <v/>
       </c>
-      <c r="N25" s="3" t="n">
+      <c r="N25" s="4" t="n">
         <f aca="false">COUNTA(H25:L25)</f>
         <v>2</v>
       </c>
-      <c r="O25" s="3" t="n">
+      <c r="O25" s="4" t="n">
         <v>841</v>
       </c>
-      <c r="P25" s="3" t="str">
+      <c r="P25" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D25,3),O25,LEFT(C25,3)))</f>
         <v>SAL841MAR</v>
       </c>
-      <c r="Q25" s="4" t="str">
+      <c r="Q25" s="5" t="str">
         <f aca="false">IF(H25&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N25&gt;1,"5",""),$O25), "")</f>
         <v/>
       </c>
-      <c r="R25" s="4" t="str">
+      <c r="R25" s="5" t="str">
         <f aca="false">IF(I25&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N25&gt;1,"4",""),$O25), "")</f>
         <v>Motion 4841</v>
       </c>
-      <c r="S25" s="4" t="str">
+      <c r="S25" s="5" t="str">
         <f aca="false">IF(J25&lt;&gt;"", _xlfn.CONCAT("Motion ",$O25), "")</f>
         <v>Motion 841</v>
       </c>
-      <c r="T25" s="4" t="str">
+      <c r="T25" s="5" t="str">
         <f aca="false">IF(K25&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N25&gt;1,"2",""),$O25), "")</f>
         <v/>
       </c>
-      <c r="U25" s="4" t="str">
+      <c r="U25" s="5" t="str">
         <f aca="false">IF(L25&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N25&gt;1,"1",""),$O25), "")</f>
         <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B26" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" s="0" t="s">
+      <c r="B26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="J26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M26" s="3" t="str">
+      <c r="M26" s="4" t="str">
         <f aca="false">IF(A26-A25&lt;&gt;1,A26-A25,"")</f>
         <v/>
       </c>
-      <c r="N26" s="3" t="n">
+      <c r="N26" s="4" t="n">
         <f aca="false">COUNTA(H26:L26)</f>
         <v>1</v>
       </c>
-      <c r="O26" s="3" t="n">
+      <c r="O26" s="4" t="n">
         <v>808</v>
       </c>
-      <c r="P26" s="3" t="str">
+      <c r="P26" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D26,3),O26,LEFT(C26,3)))</f>
         <v>OWE808AND</v>
       </c>
-      <c r="Q26" s="4" t="str">
+      <c r="Q26" s="5" t="str">
         <f aca="false">IF(H26&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N26&gt;1,"5",""),$O26), "")</f>
         <v/>
       </c>
-      <c r="R26" s="4" t="str">
+      <c r="R26" s="5" t="str">
         <f aca="false">IF(I26&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N26&gt;1,"4",""),$O26), "")</f>
         <v/>
       </c>
-      <c r="S26" s="4" t="str">
+      <c r="S26" s="5" t="str">
         <f aca="false">IF(J26&lt;&gt;"", _xlfn.CONCAT("Motion ",$O26), "")</f>
         <v>Motion 808</v>
       </c>
-      <c r="T26" s="4" t="str">
+      <c r="T26" s="5" t="str">
         <f aca="false">IF(K26&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N26&gt;1,"2",""),$O26), "")</f>
         <v/>
       </c>
-      <c r="U26" s="4" t="str">
+      <c r="U26" s="5" t="str">
         <f aca="false">IF(L26&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N26&gt;1,"1",""),$O26), "")</f>
         <v/>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="A27" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B27" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="0" t="s">
+      <c r="B27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="J27" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M27" s="3" t="str">
+      <c r="M27" s="4" t="str">
         <f aca="false">IF(A27-A26&lt;&gt;1,A27-A26,"")</f>
         <v/>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="N27" s="4" t="n">
         <f aca="false">COUNTA(H27:L27)</f>
         <v>1</v>
       </c>
-      <c r="O27" s="3" t="n">
+      <c r="O27" s="4" t="n">
         <v>804</v>
       </c>
-      <c r="P27" s="3" t="str">
+      <c r="P27" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D27,3),O27,LEFT(C27,3)))</f>
         <v>LIL804MAT</v>
       </c>
-      <c r="Q27" s="4" t="str">
+      <c r="Q27" s="5" t="str">
         <f aca="false">IF(H27&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N27&gt;1,"5",""),$O27), "")</f>
         <v/>
       </c>
-      <c r="R27" s="4" t="str">
+      <c r="R27" s="5" t="str">
         <f aca="false">IF(I27&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N27&gt;1,"4",""),$O27), "")</f>
         <v/>
       </c>
-      <c r="S27" s="4" t="str">
+      <c r="S27" s="5" t="str">
         <f aca="false">IF(J27&lt;&gt;"", _xlfn.CONCAT("Motion ",$O27), "")</f>
         <v>Motion 804</v>
       </c>
-      <c r="T27" s="4" t="str">
+      <c r="T27" s="5" t="str">
         <f aca="false">IF(K27&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N27&gt;1,"2",""),$O27), "")</f>
         <v/>
       </c>
-      <c r="U27" s="4" t="str">
+      <c r="U27" s="5" t="str">
         <f aca="false">IF(L27&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N27&gt;1,"1",""),$O27), "")</f>
         <v/>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="A28" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B28" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="0" t="s">
+      <c r="B28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="1" t="n">
+      <c r="G28" s="2" t="n">
         <v>707</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M28" s="3" t="str">
+      <c r="M28" s="4" t="str">
         <f aca="false">IF(A28-A27&lt;&gt;1,A28-A27,"")</f>
         <v/>
       </c>
-      <c r="N28" s="3" t="n">
+      <c r="N28" s="4" t="n">
         <f aca="false">COUNTA(H28:L28)</f>
         <v>1</v>
       </c>
-      <c r="O28" s="11" t="n">
+      <c r="O28" s="12" t="n">
         <f aca="false">G28</f>
         <v>707</v>
       </c>
-      <c r="P28" s="3" t="str">
+      <c r="P28" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D28,3),O28,LEFT(C28,3)))</f>
         <v>GOR707DEN</v>
       </c>
-      <c r="Q28" s="4" t="str">
+      <c r="Q28" s="5" t="str">
         <f aca="false">IF(H28&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N28&gt;1,"5",""),$O28), "")</f>
         <v>Motion 707</v>
       </c>
-      <c r="R28" s="4" t="str">
+      <c r="R28" s="5" t="str">
         <f aca="false">IF(I28&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N28&gt;1,"4",""),$O28), "")</f>
         <v/>
       </c>
-      <c r="S28" s="4" t="str">
+      <c r="S28" s="5" t="str">
         <f aca="false">IF(J28&lt;&gt;"", _xlfn.CONCAT("Motion ",$O28), "")</f>
         <v/>
       </c>
-      <c r="T28" s="4" t="str">
+      <c r="T28" s="5" t="str">
         <f aca="false">IF(K28&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N28&gt;1,"2",""),$O28), "")</f>
         <v/>
       </c>
-      <c r="U28" s="4" t="str">
+      <c r="U28" s="5" t="str">
         <f aca="false">IF(L28&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N28&gt;1,"1",""),$O28), "")</f>
         <v/>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
+      <c r="A29" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B29" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="0" t="s">
+      <c r="B29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="J29" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M29" s="3" t="str">
+      <c r="M29" s="4" t="str">
         <f aca="false">IF(A29-A28&lt;&gt;1,A29-A28,"")</f>
         <v/>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="4" t="n">
         <f aca="false">COUNTA(H29:L29)</f>
         <v>1</v>
       </c>
-      <c r="O29" s="3" t="n">
+      <c r="O29" s="4" t="n">
         <v>852</v>
       </c>
-      <c r="P29" s="3" t="str">
+      <c r="P29" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D29,3),O29,LEFT(C29,3)))</f>
         <v>HAR852SCO</v>
       </c>
-      <c r="Q29" s="4" t="str">
+      <c r="Q29" s="5" t="str">
         <f aca="false">IF(H29&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N29&gt;1,"5",""),$O29), "")</f>
         <v/>
       </c>
-      <c r="R29" s="4" t="str">
+      <c r="R29" s="5" t="str">
         <f aca="false">IF(I29&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N29&gt;1,"4",""),$O29), "")</f>
         <v/>
       </c>
-      <c r="S29" s="4" t="str">
+      <c r="S29" s="5" t="str">
         <f aca="false">IF(J29&lt;&gt;"", _xlfn.CONCAT("Motion ",$O29), "")</f>
         <v>Motion 852</v>
       </c>
-      <c r="T29" s="4" t="str">
+      <c r="T29" s="5" t="str">
         <f aca="false">IF(K29&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N29&gt;1,"2",""),$O29), "")</f>
         <v/>
       </c>
-      <c r="U29" s="4" t="str">
+      <c r="U29" s="5" t="str">
         <f aca="false">IF(L29&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N29&gt;1,"1",""),$O29), "")</f>
         <v/>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+      <c r="A30" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="J30" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M30" s="3" t="str">
+      <c r="M30" s="4" t="str">
         <f aca="false">IF(A30-A29&lt;&gt;1,A30-A29,"")</f>
         <v/>
       </c>
-      <c r="N30" s="3" t="n">
+      <c r="N30" s="4" t="n">
         <f aca="false">COUNTA(H30:L30)</f>
         <v>1</v>
       </c>
-      <c r="O30" s="3" t="n">
+      <c r="O30" s="4" t="n">
         <v>861</v>
       </c>
-      <c r="P30" s="3" t="str">
+      <c r="P30" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D30,3),O30,LEFT(C30,3)))</f>
         <v>HAR861SIA</v>
       </c>
-      <c r="Q30" s="4" t="str">
+      <c r="Q30" s="5" t="str">
         <f aca="false">IF(H30&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N30&gt;1,"5",""),$O30), "")</f>
         <v/>
       </c>
-      <c r="R30" s="4" t="str">
+      <c r="R30" s="5" t="str">
         <f aca="false">IF(I30&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N30&gt;1,"4",""),$O30), "")</f>
         <v/>
       </c>
-      <c r="S30" s="4" t="str">
+      <c r="S30" s="5" t="str">
         <f aca="false">IF(J30&lt;&gt;"", _xlfn.CONCAT("Motion ",$O30), "")</f>
         <v>Motion 861</v>
       </c>
-      <c r="T30" s="4" t="str">
+      <c r="T30" s="5" t="str">
         <f aca="false">IF(K30&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N30&gt;1,"2",""),$O30), "")</f>
         <v/>
       </c>
-      <c r="U30" s="4" t="str">
+      <c r="U30" s="5" t="str">
         <f aca="false">IF(L30&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N30&gt;1,"1",""),$O30), "")</f>
         <v/>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
+      <c r="A31" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B31" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" s="0" t="s">
+      <c r="B31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="J31" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M31" s="3" t="str">
+      <c r="M31" s="4" t="str">
         <f aca="false">IF(A31-A30&lt;&gt;1,A31-A30,"")</f>
         <v/>
       </c>
-      <c r="N31" s="3" t="n">
+      <c r="N31" s="4" t="n">
         <f aca="false">COUNTA(H31:L31)</f>
         <v>1</v>
       </c>
-      <c r="O31" s="3" t="n">
+      <c r="O31" s="4" t="n">
         <v>1039</v>
       </c>
-      <c r="P31" s="3" t="str">
+      <c r="P31" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D31,3),O31,LEFT(C31,3)))</f>
         <v>MEY1039NEI</v>
       </c>
-      <c r="Q31" s="4" t="str">
+      <c r="Q31" s="5" t="str">
         <f aca="false">IF(H31&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N31&gt;1,"5",""),$O31), "")</f>
         <v/>
       </c>
-      <c r="R31" s="4" t="str">
+      <c r="R31" s="5" t="str">
         <f aca="false">IF(I31&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N31&gt;1,"4",""),$O31), "")</f>
         <v/>
       </c>
-      <c r="S31" s="4" t="str">
+      <c r="S31" s="5" t="str">
         <f aca="false">IF(J31&lt;&gt;"", _xlfn.CONCAT("Motion ",$O31), "")</f>
         <v>Motion 1039</v>
       </c>
-      <c r="T31" s="4" t="str">
+      <c r="T31" s="5" t="str">
         <f aca="false">IF(K31&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N31&gt;1,"2",""),$O31), "")</f>
         <v/>
       </c>
-      <c r="U31" s="4" t="str">
+      <c r="U31" s="5" t="str">
         <f aca="false">IF(L31&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N31&gt;1,"1",""),$O31), "")</f>
         <v/>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="n">
+      <c r="A32" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B32" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" s="0" t="s">
+      <c r="B32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="J32" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M32" s="3" t="str">
+      <c r="M32" s="4" t="str">
         <f aca="false">IF(A32-A31&lt;&gt;1,A32-A31,"")</f>
         <v/>
       </c>
-      <c r="N32" s="3" t="n">
+      <c r="N32" s="4" t="n">
         <f aca="false">COUNTA(H32:L32)</f>
         <v>1</v>
       </c>
-      <c r="O32" s="3" t="n">
+      <c r="O32" s="4" t="n">
         <v>845</v>
       </c>
-      <c r="P32" s="3" t="str">
+      <c r="P32" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D32,3),O32,LEFT(C32,3)))</f>
         <v>WAT845STE</v>
       </c>
-      <c r="Q32" s="4" t="str">
+      <c r="Q32" s="5" t="str">
         <f aca="false">IF(H32&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N32&gt;1,"5",""),$O32), "")</f>
         <v/>
       </c>
-      <c r="R32" s="4" t="str">
+      <c r="R32" s="5" t="str">
         <f aca="false">IF(I32&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N32&gt;1,"4",""),$O32), "")</f>
         <v/>
       </c>
-      <c r="S32" s="4" t="str">
+      <c r="S32" s="5" t="str">
         <f aca="false">IF(J32&lt;&gt;"", _xlfn.CONCAT("Motion ",$O32), "")</f>
         <v>Motion 845</v>
       </c>
-      <c r="T32" s="4" t="str">
+      <c r="T32" s="5" t="str">
         <f aca="false">IF(K32&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N32&gt;1,"2",""),$O32), "")</f>
         <v/>
       </c>
-      <c r="U32" s="4" t="str">
+      <c r="U32" s="5" t="str">
         <f aca="false">IF(L32&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N32&gt;1,"1",""),$O32), "")</f>
         <v/>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="n">
+      <c r="A33" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B33" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" s="0" t="s">
+      <c r="B33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I33" s="2" t="s">
+      <c r="I33" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="J33" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M33" s="3" t="str">
+      <c r="M33" s="4" t="str">
         <f aca="false">IF(A33-A32&lt;&gt;1,A33-A32,"")</f>
         <v/>
       </c>
-      <c r="N33" s="3" t="n">
+      <c r="N33" s="4" t="n">
         <f aca="false">COUNTA(H33:L33)</f>
         <v>2</v>
       </c>
-      <c r="O33" s="3" t="n">
+      <c r="O33" s="4" t="n">
         <v>872</v>
       </c>
-      <c r="P33" s="3" t="str">
+      <c r="P33" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D33,3),O33,LEFT(C33,3)))</f>
         <v>LOR872BRE</v>
       </c>
-      <c r="Q33" s="4" t="str">
+      <c r="Q33" s="5" t="str">
         <f aca="false">IF(H33&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N33&gt;1,"5",""),$O33), "")</f>
         <v/>
       </c>
-      <c r="R33" s="4" t="str">
+      <c r="R33" s="5" t="str">
         <f aca="false">IF(I33&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N33&gt;1,"4",""),$O33), "")</f>
         <v>Motion 4872</v>
       </c>
-      <c r="S33" s="4" t="str">
+      <c r="S33" s="5" t="str">
         <f aca="false">IF(J33&lt;&gt;"", _xlfn.CONCAT("Motion ",$O33), "")</f>
         <v>Motion 872</v>
       </c>
-      <c r="T33" s="4" t="str">
+      <c r="T33" s="5" t="str">
         <f aca="false">IF(K33&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N33&gt;1,"2",""),$O33), "")</f>
         <v/>
       </c>
-      <c r="U33" s="4" t="str">
+      <c r="U33" s="5" t="str">
         <f aca="false">IF(L33&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N33&gt;1,"1",""),$O33), "")</f>
         <v/>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="n">
+      <c r="A34" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B34" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" s="0" t="s">
+      <c r="B34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="J34" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M34" s="3" t="str">
+      <c r="M34" s="4" t="str">
         <f aca="false">IF(A34-A33&lt;&gt;1,A34-A33,"")</f>
         <v/>
       </c>
-      <c r="N34" s="3" t="n">
+      <c r="N34" s="4" t="n">
         <f aca="false">COUNTA(H34:L34)</f>
         <v>1</v>
       </c>
-      <c r="O34" s="3" t="n">
+      <c r="O34" s="4" t="n">
         <v>1037</v>
       </c>
-      <c r="P34" s="3" t="str">
+      <c r="P34" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D34,3),O34,LEFT(C34,3)))</f>
         <v>LOR1037FRA</v>
       </c>
-      <c r="Q34" s="4" t="str">
+      <c r="Q34" s="5" t="str">
         <f aca="false">IF(H34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N34&gt;1,"5",""),$O34), "")</f>
         <v/>
       </c>
-      <c r="R34" s="4" t="str">
+      <c r="R34" s="5" t="str">
         <f aca="false">IF(I34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N34&gt;1,"4",""),$O34), "")</f>
         <v/>
       </c>
-      <c r="S34" s="4" t="str">
+      <c r="S34" s="5" t="str">
         <f aca="false">IF(J34&lt;&gt;"", _xlfn.CONCAT("Motion ",$O34), "")</f>
         <v>Motion 1037</v>
       </c>
-      <c r="T34" s="4" t="str">
+      <c r="T34" s="5" t="str">
         <f aca="false">IF(K34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N34&gt;1,"2",""),$O34), "")</f>
         <v/>
       </c>
-      <c r="U34" s="4" t="str">
+      <c r="U34" s="5" t="str">
         <f aca="false">IF(L34&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N34&gt;1,"1",""),$O34), "")</f>
         <v/>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="n">
+      <c r="A35" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B35" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" s="0" t="s">
+      <c r="B35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I35" s="2" t="s">
+      <c r="I35" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J35" s="2" t="s">
+      <c r="J35" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M35" s="3" t="str">
+      <c r="M35" s="4" t="str">
         <f aca="false">IF(A35-A34&lt;&gt;1,A35-A34,"")</f>
         <v/>
       </c>
-      <c r="N35" s="3" t="n">
+      <c r="N35" s="4" t="n">
         <f aca="false">COUNTA(H35:L35)</f>
         <v>2</v>
       </c>
-      <c r="O35" s="3" t="n">
+      <c r="O35" s="4" t="n">
         <v>998</v>
       </c>
-      <c r="P35" s="3" t="str">
+      <c r="P35" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D35,3),O35,LEFT(C35,3)))</f>
         <v>DIC998FIN</v>
       </c>
-      <c r="Q35" s="4" t="str">
+      <c r="Q35" s="5" t="str">
         <f aca="false">IF(H35&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N35&gt;1,"5",""),$O35), "")</f>
         <v/>
       </c>
-      <c r="R35" s="4" t="str">
+      <c r="R35" s="5" t="str">
         <f aca="false">IF(I35&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N35&gt;1,"4",""),$O35), "")</f>
         <v>Motion 4998</v>
       </c>
-      <c r="S35" s="4" t="str">
+      <c r="S35" s="5" t="str">
         <f aca="false">IF(J35&lt;&gt;"", _xlfn.CONCAT("Motion ",$O35), "")</f>
         <v>Motion 998</v>
       </c>
-      <c r="T35" s="4" t="str">
+      <c r="T35" s="5" t="str">
         <f aca="false">IF(K35&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N35&gt;1,"2",""),$O35), "")</f>
         <v/>
       </c>
-      <c r="U35" s="4" t="str">
+      <c r="U35" s="5" t="str">
         <f aca="false">IF(L35&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N35&gt;1,"1",""),$O35), "")</f>
         <v/>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="n">
+      <c r="A36" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B36" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="0" t="s">
+      <c r="B36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G36" s="10" t="n">
+      <c r="G36" s="11" t="n">
         <v>623</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="J36" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M36" s="3" t="str">
+      <c r="M36" s="4" t="str">
         <f aca="false">IF(A36-A35&lt;&gt;1,A36-A35,"")</f>
         <v/>
       </c>
-      <c r="N36" s="3" t="n">
+      <c r="N36" s="4" t="n">
         <f aca="false">COUNTA(H36:L36)</f>
         <v>1</v>
       </c>
-      <c r="O36" s="11" t="n">
+      <c r="O36" s="12" t="n">
         <f aca="false">G36</f>
         <v>623</v>
       </c>
-      <c r="P36" s="3" t="str">
+      <c r="P36" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D36,3),O36,LEFT(C36,3)))</f>
         <v>FUL623GEO</v>
       </c>
-      <c r="Q36" s="4" t="str">
+      <c r="Q36" s="5" t="str">
         <f aca="false">IF(H36&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N36&gt;1,"5",""),$O36), "")</f>
         <v/>
       </c>
-      <c r="R36" s="4" t="str">
+      <c r="R36" s="5" t="str">
         <f aca="false">IF(I36&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N36&gt;1,"4",""),$O36), "")</f>
         <v/>
       </c>
-      <c r="S36" s="4" t="str">
+      <c r="S36" s="5" t="str">
         <f aca="false">IF(J36&lt;&gt;"", _xlfn.CONCAT("Motion ",$O36), "")</f>
         <v>Motion 623</v>
       </c>
-      <c r="T36" s="4" t="str">
+      <c r="T36" s="5" t="str">
         <f aca="false">IF(K36&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N36&gt;1,"2",""),$O36), "")</f>
         <v/>
       </c>
-      <c r="U36" s="4" t="str">
+      <c r="U36" s="5" t="str">
         <f aca="false">IF(L36&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N36&gt;1,"1",""),$O36), "")</f>
         <v/>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="n">
+      <c r="A37" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B37" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" s="0" t="s">
+      <c r="B37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="J37" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M37" s="3" t="str">
+      <c r="M37" s="4" t="str">
         <f aca="false">IF(A37-A36&lt;&gt;1,A37-A36,"")</f>
         <v/>
       </c>
-      <c r="N37" s="3" t="n">
+      <c r="N37" s="4" t="n">
         <f aca="false">COUNTA(H37:L37)</f>
         <v>1</v>
       </c>
-      <c r="O37" s="3" t="n">
+      <c r="O37" s="4" t="n">
         <v>815</v>
       </c>
-      <c r="P37" s="3" t="str">
+      <c r="P37" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D37,3),O37,LEFT(C37,3)))</f>
         <v>SPA815BOB</v>
       </c>
-      <c r="Q37" s="4" t="str">
+      <c r="Q37" s="5" t="str">
         <f aca="false">IF(H37&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N37&gt;1,"5",""),$O37), "")</f>
         <v/>
       </c>
-      <c r="R37" s="4" t="str">
+      <c r="R37" s="5" t="str">
         <f aca="false">IF(I37&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N37&gt;1,"4",""),$O37), "")</f>
         <v/>
       </c>
-      <c r="S37" s="4" t="str">
+      <c r="S37" s="5" t="str">
         <f aca="false">IF(J37&lt;&gt;"", _xlfn.CONCAT("Motion ",$O37), "")</f>
         <v>Motion 815</v>
       </c>
-      <c r="T37" s="4" t="str">
+      <c r="T37" s="5" t="str">
         <f aca="false">IF(K37&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N37&gt;1,"2",""),$O37), "")</f>
         <v/>
       </c>
-      <c r="U37" s="4" t="str">
+      <c r="U37" s="5" t="str">
         <f aca="false">IF(L37&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N37&gt;1,"1",""),$O37), "")</f>
         <v/>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="n">
+      <c r="A38" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B38" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" s="0" t="s">
+      <c r="B38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J38" s="2" t="s">
+      <c r="J38" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M38" s="3" t="str">
+      <c r="M38" s="4" t="str">
         <f aca="false">IF(A38-A37&lt;&gt;1,A38-A37,"")</f>
         <v/>
       </c>
-      <c r="N38" s="3" t="n">
+      <c r="N38" s="4" t="n">
         <f aca="false">COUNTA(H38:L38)</f>
         <v>1</v>
       </c>
-      <c r="O38" s="3" t="n">
+      <c r="O38" s="4" t="n">
         <v>1033</v>
       </c>
-      <c r="P38" s="3" t="str">
+      <c r="P38" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D38,3),O38,LEFT(C38,3)))</f>
         <v>ARN1033PAU</v>
       </c>
-      <c r="Q38" s="4" t="str">
+      <c r="Q38" s="5" t="str">
         <f aca="false">IF(H38&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N38&gt;1,"5",""),$O38), "")</f>
         <v/>
       </c>
-      <c r="R38" s="4" t="str">
+      <c r="R38" s="5" t="str">
         <f aca="false">IF(I38&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N38&gt;1,"4",""),$O38), "")</f>
         <v/>
       </c>
-      <c r="S38" s="4" t="str">
+      <c r="S38" s="5" t="str">
         <f aca="false">IF(J38&lt;&gt;"", _xlfn.CONCAT("Motion ",$O38), "")</f>
         <v>Motion 1033</v>
       </c>
-      <c r="T38" s="4" t="str">
+      <c r="T38" s="5" t="str">
         <f aca="false">IF(K38&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N38&gt;1,"2",""),$O38), "")</f>
         <v/>
       </c>
-      <c r="U38" s="4" t="str">
+      <c r="U38" s="5" t="str">
         <f aca="false">IF(L38&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N38&gt;1,"1",""),$O38), "")</f>
         <v/>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="n">
+      <c r="A39" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B39" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" s="0" t="s">
+      <c r="B39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J39" s="2" t="s">
+      <c r="J39" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M39" s="3" t="str">
+      <c r="M39" s="4" t="str">
         <f aca="false">IF(A39-A38&lt;&gt;1,A39-A38,"")</f>
         <v/>
       </c>
-      <c r="N39" s="3" t="n">
+      <c r="N39" s="4" t="n">
         <f aca="false">COUNTA(H39:L39)</f>
         <v>1</v>
       </c>
-      <c r="O39" s="3" t="n">
+      <c r="O39" s="4" t="n">
         <v>838</v>
       </c>
-      <c r="P39" s="3" t="str">
+      <c r="P39" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D39,3),O39,LEFT(C39,3)))</f>
         <v>THO838STE</v>
       </c>
-      <c r="Q39" s="4" t="str">
+      <c r="Q39" s="5" t="str">
         <f aca="false">IF(H39&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N39&gt;1,"5",""),$O39), "")</f>
         <v/>
       </c>
-      <c r="R39" s="4" t="str">
+      <c r="R39" s="5" t="str">
         <f aca="false">IF(I39&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N39&gt;1,"4",""),$O39), "")</f>
         <v/>
       </c>
-      <c r="S39" s="4" t="str">
+      <c r="S39" s="5" t="str">
         <f aca="false">IF(J39&lt;&gt;"", _xlfn.CONCAT("Motion ",$O39), "")</f>
         <v>Motion 838</v>
       </c>
-      <c r="T39" s="4" t="str">
+      <c r="T39" s="5" t="str">
         <f aca="false">IF(K39&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N39&gt;1,"2",""),$O39), "")</f>
         <v/>
       </c>
-      <c r="U39" s="4" t="str">
+      <c r="U39" s="5" t="str">
         <f aca="false">IF(L39&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N39&gt;1,"1",""),$O39), "")</f>
         <v/>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="n">
+      <c r="A40" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J40" s="2" t="s">
+      <c r="J40" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M40" s="3" t="str">
+      <c r="M40" s="4" t="str">
         <f aca="false">IF(A40-A39&lt;&gt;1,A40-A39,"")</f>
         <v/>
       </c>
-      <c r="N40" s="3" t="n">
+      <c r="N40" s="4" t="n">
         <f aca="false">COUNTA(H40:L40)</f>
         <v>1</v>
       </c>
-      <c r="O40" s="3" t="n">
+      <c r="O40" s="4" t="n">
         <v>819</v>
       </c>
-      <c r="P40" s="3" t="str">
+      <c r="P40" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D40,3),O40,LEFT(C40,3)))</f>
         <v>WAT819JOE</v>
       </c>
-      <c r="Q40" s="4" t="str">
+      <c r="Q40" s="5" t="str">
         <f aca="false">IF(H40&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N40&gt;1,"5",""),$O40), "")</f>
         <v/>
       </c>
-      <c r="R40" s="4" t="str">
+      <c r="R40" s="5" t="str">
         <f aca="false">IF(I40&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N40&gt;1,"4",""),$O40), "")</f>
         <v/>
       </c>
-      <c r="S40" s="4" t="str">
+      <c r="S40" s="5" t="str">
         <f aca="false">IF(J40&lt;&gt;"", _xlfn.CONCAT("Motion ",$O40), "")</f>
         <v>Motion 819</v>
       </c>
-      <c r="T40" s="4" t="str">
+      <c r="T40" s="5" t="str">
         <f aca="false">IF(K40&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N40&gt;1,"2",""),$O40), "")</f>
         <v/>
       </c>
-      <c r="U40" s="4" t="str">
+      <c r="U40" s="5" t="str">
         <f aca="false">IF(L40&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N40&gt;1,"1",""),$O40), "")</f>
         <v/>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="n">
+      <c r="A41" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J41" s="2" t="s">
+      <c r="J41" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M41" s="3" t="str">
+      <c r="M41" s="4" t="str">
         <f aca="false">IF(A41-A40&lt;&gt;1,A41-A40,"")</f>
         <v/>
       </c>
-      <c r="N41" s="3" t="n">
+      <c r="N41" s="4" t="n">
         <f aca="false">COUNTA(H41:L41)</f>
         <v>1</v>
       </c>
-      <c r="O41" s="3" t="n">
+      <c r="O41" s="4" t="n">
         <v>853</v>
       </c>
-      <c r="P41" s="3" t="str">
+      <c r="P41" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D41,3),O41,LEFT(C41,3)))</f>
         <v>DAF853CHR</v>
       </c>
-      <c r="Q41" s="4" t="str">
+      <c r="Q41" s="5" t="str">
         <f aca="false">IF(H41&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N41&gt;1,"5",""),$O41), "")</f>
         <v/>
       </c>
-      <c r="R41" s="4" t="str">
+      <c r="R41" s="5" t="str">
         <f aca="false">IF(I41&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N41&gt;1,"4",""),$O41), "")</f>
         <v/>
       </c>
-      <c r="S41" s="4" t="str">
+      <c r="S41" s="5" t="str">
         <f aca="false">IF(J41&lt;&gt;"", _xlfn.CONCAT("Motion ",$O41), "")</f>
         <v>Motion 853</v>
       </c>
-      <c r="T41" s="4" t="str">
+      <c r="T41" s="5" t="str">
         <f aca="false">IF(K41&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N41&gt;1,"2",""),$O41), "")</f>
         <v/>
       </c>
-      <c r="U41" s="4" t="str">
+      <c r="U41" s="5" t="str">
         <f aca="false">IF(L41&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N41&gt;1,"1",""),$O41), "")</f>
         <v/>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="n">
+      <c r="A42" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="B42" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" s="0" t="s">
+      <c r="B42" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="D42" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J42" s="2" t="s">
+      <c r="J42" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M42" s="3" t="str">
+      <c r="M42" s="4" t="str">
         <f aca="false">IF(A42-A41&lt;&gt;1,A42-A41,"")</f>
         <v/>
       </c>
-      <c r="N42" s="3" t="n">
+      <c r="N42" s="4" t="n">
         <f aca="false">COUNTA(H42:L42)</f>
         <v>1</v>
       </c>
-      <c r="O42" s="3" t="n">
+      <c r="O42" s="4" t="n">
         <v>814</v>
       </c>
-      <c r="P42" s="3" t="str">
+      <c r="P42" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D42,3),O42,LEFT(C42,3)))</f>
         <v>WIL814JON</v>
       </c>
-      <c r="Q42" s="4" t="str">
+      <c r="Q42" s="5" t="str">
         <f aca="false">IF(H42&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N42&gt;1,"5",""),$O42), "")</f>
         <v/>
       </c>
-      <c r="R42" s="4" t="str">
+      <c r="R42" s="5" t="str">
         <f aca="false">IF(I42&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N42&gt;1,"4",""),$O42), "")</f>
         <v/>
       </c>
-      <c r="S42" s="4" t="str">
+      <c r="S42" s="5" t="str">
         <f aca="false">IF(J42&lt;&gt;"", _xlfn.CONCAT("Motion ",$O42), "")</f>
         <v>Motion 814</v>
       </c>
-      <c r="T42" s="4" t="str">
+      <c r="T42" s="5" t="str">
         <f aca="false">IF(K42&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N42&gt;1,"2",""),$O42), "")</f>
         <v/>
       </c>
-      <c r="U42" s="4" t="str">
+      <c r="U42" s="5" t="str">
         <f aca="false">IF(L42&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N42&gt;1,"1",""),$O42), "")</f>
         <v/>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="n">
+      <c r="A43" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="B43" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="0" t="s">
+      <c r="B43" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="H43" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M43" s="3" t="str">
+      <c r="M43" s="4" t="str">
         <f aca="false">IF(A43-A42&lt;&gt;1,A43-A42,"")</f>
         <v/>
       </c>
-      <c r="N43" s="3" t="n">
+      <c r="N43" s="4" t="n">
         <f aca="false">COUNTA(H43:L43)</f>
         <v>1</v>
       </c>
-      <c r="O43" s="3" t="n">
+      <c r="O43" s="4" t="n">
         <v>643</v>
       </c>
-      <c r="P43" s="3" t="str">
+      <c r="P43" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D43,3),O43,LEFT(C43,3)))</f>
         <v>SHE643IAN</v>
       </c>
-      <c r="Q43" s="4" t="str">
+      <c r="Q43" s="5" t="str">
         <f aca="false">IF(H43&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N43&gt;1,"5",""),$O43), "")</f>
         <v>Motion 643</v>
       </c>
-      <c r="R43" s="4" t="str">
+      <c r="R43" s="5" t="str">
         <f aca="false">IF(I43&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N43&gt;1,"4",""),$O43), "")</f>
         <v/>
       </c>
-      <c r="S43" s="4" t="str">
+      <c r="S43" s="5" t="str">
         <f aca="false">IF(J43&lt;&gt;"", _xlfn.CONCAT("Motion ",$O43), "")</f>
         <v/>
       </c>
-      <c r="T43" s="4" t="str">
+      <c r="T43" s="5" t="str">
         <f aca="false">IF(K43&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N43&gt;1,"2",""),$O43), "")</f>
         <v/>
       </c>
-      <c r="U43" s="4" t="str">
+      <c r="U43" s="5" t="str">
         <f aca="false">IF(L43&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N43&gt;1,"1",""),$O43), "")</f>
         <v/>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="n">
+      <c r="A44" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="B44" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" s="0" t="s">
+      <c r="B44" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D44" s="0" t="s">
+      <c r="D44" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G44" s="10" t="n">
+      <c r="G44" s="11" t="n">
         <v>846</v>
       </c>
-      <c r="K44" s="2" t="s">
+      <c r="K44" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M44" s="3" t="str">
+      <c r="M44" s="4" t="str">
         <f aca="false">IF(A44-A43&lt;&gt;1,A44-A43,"")</f>
         <v/>
       </c>
-      <c r="N44" s="3" t="n">
+      <c r="N44" s="4" t="n">
         <f aca="false">COUNTA(H44:L44)</f>
         <v>1</v>
       </c>
-      <c r="O44" s="11" t="n">
+      <c r="O44" s="12" t="n">
         <f aca="false">G44</f>
         <v>846</v>
       </c>
-      <c r="P44" s="3" t="str">
+      <c r="P44" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D44,3),O44,LEFT(C44,3)))</f>
         <v>BUR846EMI</v>
       </c>
-      <c r="Q44" s="4" t="str">
+      <c r="Q44" s="5" t="str">
         <f aca="false">IF(H44&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N44&gt;1,"5",""),$O44), "")</f>
         <v/>
       </c>
-      <c r="R44" s="4" t="str">
+      <c r="R44" s="5" t="str">
         <f aca="false">IF(I44&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N44&gt;1,"4",""),$O44), "")</f>
         <v/>
       </c>
-      <c r="S44" s="4" t="str">
+      <c r="S44" s="5" t="str">
         <f aca="false">IF(J44&lt;&gt;"", _xlfn.CONCAT("Motion ",$O44), "")</f>
         <v/>
       </c>
-      <c r="T44" s="4" t="str">
+      <c r="T44" s="5" t="str">
         <f aca="false">IF(K44&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N44&gt;1,"2",""),$O44), "")</f>
         <v>Motion 846</v>
       </c>
-      <c r="U44" s="4" t="str">
+      <c r="U44" s="5" t="str">
         <f aca="false">IF(L44&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N44&gt;1,"1",""),$O44), "")</f>
         <v/>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="n">
+      <c r="A45" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="B45" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" s="0" t="s">
+      <c r="B45" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="D45" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I45" s="2" t="s">
+      <c r="I45" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J45" s="2" t="s">
+      <c r="J45" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M45" s="3" t="str">
+      <c r="M45" s="4" t="str">
         <f aca="false">IF(A45-A44&lt;&gt;1,A45-A44,"")</f>
         <v/>
       </c>
-      <c r="N45" s="3" t="n">
+      <c r="N45" s="4" t="n">
         <f aca="false">COUNTA(H45:L45)</f>
         <v>2</v>
       </c>
-      <c r="O45" s="3" t="n">
+      <c r="O45" s="4" t="n">
         <v>854</v>
       </c>
-      <c r="P45" s="3" t="str">
+      <c r="P45" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D45,3),O45,LEFT(C45,3)))</f>
         <v>DVO854PAV</v>
       </c>
-      <c r="Q45" s="4" t="str">
+      <c r="Q45" s="5" t="str">
         <f aca="false">IF(H45&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N45&gt;1,"5",""),$O45), "")</f>
         <v/>
       </c>
-      <c r="R45" s="4" t="str">
+      <c r="R45" s="5" t="str">
         <f aca="false">IF(I45&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N45&gt;1,"4",""),$O45), "")</f>
         <v>Motion 4854</v>
       </c>
-      <c r="S45" s="4" t="str">
+      <c r="S45" s="5" t="str">
         <f aca="false">IF(J45&lt;&gt;"", _xlfn.CONCAT("Motion ",$O45), "")</f>
         <v>Motion 854</v>
       </c>
-      <c r="T45" s="4" t="str">
+      <c r="T45" s="5" t="str">
         <f aca="false">IF(K45&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N45&gt;1,"2",""),$O45), "")</f>
         <v/>
       </c>
-      <c r="U45" s="4" t="str">
+      <c r="U45" s="5" t="str">
         <f aca="false">IF(L45&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N45&gt;1,"1",""),$O45), "")</f>
         <v/>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="n">
+      <c r="A46" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="B46" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" s="0" t="s">
+      <c r="B46" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D46" s="0" t="s">
+      <c r="D46" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J46" s="2" t="s">
+      <c r="J46" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L46" s="2" t="s">
+      <c r="L46" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M46" s="3" t="str">
+      <c r="M46" s="4" t="str">
         <f aca="false">IF(A46-A45&lt;&gt;1,A46-A45,"")</f>
         <v/>
       </c>
-      <c r="N46" s="3" t="n">
+      <c r="N46" s="4" t="n">
         <f aca="false">COUNTA(H46:L46)</f>
         <v>2</v>
       </c>
-      <c r="O46" s="3" t="n">
+      <c r="O46" s="4" t="n">
         <v>641</v>
       </c>
-      <c r="P46" s="3" t="str">
+      <c r="P46" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D46,3),O46,LEFT(C46,3)))</f>
         <v>RUS641ROB</v>
       </c>
-      <c r="Q46" s="4" t="str">
+      <c r="Q46" s="5" t="str">
         <f aca="false">IF(H46&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N46&gt;1,"5",""),$O46), "")</f>
         <v/>
       </c>
-      <c r="R46" s="4" t="str">
+      <c r="R46" s="5" t="str">
         <f aca="false">IF(I46&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N46&gt;1,"4",""),$O46), "")</f>
         <v/>
       </c>
-      <c r="S46" s="4" t="str">
+      <c r="S46" s="5" t="str">
         <f aca="false">IF(J46&lt;&gt;"", _xlfn.CONCAT("Motion ",$O46), "")</f>
         <v>Motion 641</v>
       </c>
-      <c r="T46" s="4" t="str">
+      <c r="T46" s="5" t="str">
         <f aca="false">IF(K46&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N46&gt;1,"2",""),$O46), "")</f>
         <v/>
       </c>
-      <c r="U46" s="4" t="str">
+      <c r="U46" s="5" t="str">
         <f aca="false">IF(L46&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N46&gt;1,"1",""),$O46), "")</f>
         <v>Motion 1641</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="n">
+      <c r="A47" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="B47" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" s="0" t="s">
+      <c r="B47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D47" s="0" t="s">
+      <c r="D47" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J47" s="2" t="s">
+      <c r="J47" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M47" s="3" t="str">
+      <c r="M47" s="4" t="str">
         <f aca="false">IF(A47-A46&lt;&gt;1,A47-A46,"")</f>
         <v/>
       </c>
-      <c r="N47" s="3" t="n">
+      <c r="N47" s="4" t="n">
         <f aca="false">COUNTA(H47:L47)</f>
         <v>1</v>
       </c>
-      <c r="O47" s="3" t="n">
+      <c r="O47" s="4" t="n">
         <v>1020</v>
       </c>
-      <c r="P47" s="3" t="str">
+      <c r="P47" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D47,3),O47,LEFT(C47,3)))</f>
         <v>BRA1020JAM</v>
       </c>
-      <c r="Q47" s="4" t="str">
+      <c r="Q47" s="5" t="str">
         <f aca="false">IF(H47&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N47&gt;1,"5",""),$O47), "")</f>
         <v/>
       </c>
-      <c r="R47" s="4" t="str">
+      <c r="R47" s="5" t="str">
         <f aca="false">IF(I47&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N47&gt;1,"4",""),$O47), "")</f>
         <v/>
       </c>
-      <c r="S47" s="4" t="str">
+      <c r="S47" s="5" t="str">
         <f aca="false">IF(J47&lt;&gt;"", _xlfn.CONCAT("Motion ",$O47), "")</f>
         <v>Motion 1020</v>
       </c>
-      <c r="T47" s="4" t="str">
+      <c r="T47" s="5" t="str">
         <f aca="false">IF(K47&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N47&gt;1,"2",""),$O47), "")</f>
         <v/>
       </c>
-      <c r="U47" s="4" t="str">
+      <c r="U47" s="5" t="str">
         <f aca="false">IF(L47&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N47&gt;1,"1",""),$O47), "")</f>
         <v/>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="n">
+      <c r="A48" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="B48" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" s="0" t="s">
+      <c r="B48" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D48" s="0" t="s">
+      <c r="D48" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J48" s="2" t="s">
+      <c r="J48" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M48" s="3" t="str">
+      <c r="M48" s="4" t="str">
         <f aca="false">IF(A48-A47&lt;&gt;1,A48-A47,"")</f>
         <v/>
       </c>
-      <c r="N48" s="3" t="n">
+      <c r="N48" s="4" t="n">
         <f aca="false">COUNTA(H48:L48)</f>
         <v>1</v>
       </c>
-      <c r="O48" s="3" t="n">
+      <c r="O48" s="4" t="n">
         <v>858</v>
       </c>
-      <c r="P48" s="3" t="str">
+      <c r="P48" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D48,3),O48,LEFT(C48,3)))</f>
         <v>OLI858JOH</v>
       </c>
-      <c r="Q48" s="4" t="str">
+      <c r="Q48" s="5" t="str">
         <f aca="false">IF(H48&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N48&gt;1,"5",""),$O48), "")</f>
         <v/>
       </c>
-      <c r="R48" s="4" t="str">
+      <c r="R48" s="5" t="str">
         <f aca="false">IF(I48&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N48&gt;1,"4",""),$O48), "")</f>
         <v/>
       </c>
-      <c r="S48" s="4" t="str">
+      <c r="S48" s="5" t="str">
         <f aca="false">IF(J48&lt;&gt;"", _xlfn.CONCAT("Motion ",$O48), "")</f>
         <v>Motion 858</v>
       </c>
-      <c r="T48" s="4" t="str">
+      <c r="T48" s="5" t="str">
         <f aca="false">IF(K48&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N48&gt;1,"2",""),$O48), "")</f>
         <v/>
       </c>
-      <c r="U48" s="4" t="str">
+      <c r="U48" s="5" t="str">
         <f aca="false">IF(L48&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N48&gt;1,"1",""),$O48), "")</f>
         <v/>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="n">
+      <c r="A49" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="B49" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" s="0" t="s">
+      <c r="B49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D49" s="0" t="s">
+      <c r="D49" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J49" s="2" t="s">
+      <c r="J49" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M49" s="3" t="str">
+      <c r="M49" s="4" t="str">
         <f aca="false">IF(A49-A48&lt;&gt;1,A49-A48,"")</f>
         <v/>
       </c>
-      <c r="N49" s="3" t="n">
+      <c r="N49" s="4" t="n">
         <f aca="false">COUNTA(H49:L49)</f>
         <v>1</v>
       </c>
-      <c r="O49" s="3" t="n">
+      <c r="O49" s="4" t="n">
         <v>869</v>
       </c>
-      <c r="P49" s="3" t="str">
+      <c r="P49" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D49,3),O49,LEFT(C49,3)))</f>
         <v>BAR869ANT</v>
       </c>
-      <c r="Q49" s="4" t="str">
+      <c r="Q49" s="5" t="str">
         <f aca="false">IF(H49&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N49&gt;1,"5",""),$O49), "")</f>
         <v/>
       </c>
-      <c r="R49" s="4" t="str">
+      <c r="R49" s="5" t="str">
         <f aca="false">IF(I49&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N49&gt;1,"4",""),$O49), "")</f>
         <v/>
       </c>
-      <c r="S49" s="4" t="str">
+      <c r="S49" s="5" t="str">
         <f aca="false">IF(J49&lt;&gt;"", _xlfn.CONCAT("Motion ",$O49), "")</f>
         <v>Motion 869</v>
       </c>
-      <c r="T49" s="4" t="str">
+      <c r="T49" s="5" t="str">
         <f aca="false">IF(K49&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N49&gt;1,"2",""),$O49), "")</f>
         <v/>
       </c>
-      <c r="U49" s="4" t="str">
+      <c r="U49" s="5" t="str">
         <f aca="false">IF(L49&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N49&gt;1,"1",""),$O49), "")</f>
         <v/>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="n">
+      <c r="A50" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="B50" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" s="0" t="s">
+      <c r="B50" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D50" s="0" t="s">
+      <c r="D50" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="L50" s="2" t="s">
+      <c r="L50" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M50" s="3" t="str">
+      <c r="M50" s="4" t="str">
         <f aca="false">IF(A50-A49&lt;&gt;1,A50-A49,"")</f>
         <v/>
       </c>
-      <c r="N50" s="3" t="n">
+      <c r="N50" s="4" t="n">
         <f aca="false">COUNTA(H50:L50)</f>
         <v>1</v>
       </c>
-      <c r="O50" s="3" t="n">
+      <c r="O50" s="4" t="n">
         <v>618</v>
       </c>
-      <c r="P50" s="3" t="str">
+      <c r="P50" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D50,3),O50,LEFT(C50,3)))</f>
         <v>MAR618PET</v>
       </c>
-      <c r="Q50" s="4" t="str">
+      <c r="Q50" s="5" t="str">
         <f aca="false">IF(H50&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N50&gt;1,"5",""),$O50), "")</f>
         <v/>
       </c>
-      <c r="R50" s="4" t="str">
+      <c r="R50" s="5" t="str">
         <f aca="false">IF(I50&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N50&gt;1,"4",""),$O50), "")</f>
         <v/>
       </c>
-      <c r="S50" s="4" t="str">
+      <c r="S50" s="5" t="str">
         <f aca="false">IF(J50&lt;&gt;"", _xlfn.CONCAT("Motion ",$O50), "")</f>
         <v/>
       </c>
-      <c r="T50" s="4" t="str">
+      <c r="T50" s="5" t="str">
         <f aca="false">IF(K50&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N50&gt;1,"2",""),$O50), "")</f>
         <v/>
       </c>
-      <c r="U50" s="4" t="str">
+      <c r="U50" s="5" t="str">
         <f aca="false">IF(L50&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N50&gt;1,"1",""),$O50), "")</f>
         <v>Motion 618</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="n">
+      <c r="A51" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="B51" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" s="0" t="s">
+      <c r="B51" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D51" s="0" t="s">
+      <c r="D51" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H51" s="2" t="s">
+      <c r="H51" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M51" s="12" t="n">
+      <c r="M51" s="13" t="n">
         <f aca="false">IF(A51-A50&lt;&gt;1,A51-A50,"")</f>
         <v>2</v>
       </c>
-      <c r="N51" s="3" t="n">
+      <c r="N51" s="4" t="n">
         <f aca="false">COUNTA(H51:L51)</f>
         <v>1</v>
       </c>
-      <c r="O51" s="3" t="n">
+      <c r="O51" s="4" t="n">
         <v>827</v>
       </c>
-      <c r="P51" s="3" t="str">
+      <c r="P51" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D51,3),O51,LEFT(C51,3)))</f>
         <v>BER827FIN</v>
       </c>
-      <c r="Q51" s="4" t="str">
+      <c r="Q51" s="5" t="str">
         <f aca="false">IF(H51&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N51&gt;1,"5",""),$O51), "")</f>
         <v>Motion 827</v>
       </c>
-      <c r="R51" s="4" t="str">
+      <c r="R51" s="5" t="str">
         <f aca="false">IF(I51&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N51&gt;1,"4",""),$O51), "")</f>
         <v/>
       </c>
-      <c r="S51" s="4" t="str">
+      <c r="S51" s="5" t="str">
         <f aca="false">IF(J51&lt;&gt;"", _xlfn.CONCAT("Motion ",$O51), "")</f>
         <v/>
       </c>
-      <c r="T51" s="4" t="str">
+      <c r="T51" s="5" t="str">
         <f aca="false">IF(K51&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N51&gt;1,"2",""),$O51), "")</f>
         <v/>
       </c>
-      <c r="U51" s="4" t="str">
+      <c r="U51" s="5" t="str">
         <f aca="false">IF(L51&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N51&gt;1,"1",""),$O51), "")</f>
         <v/>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="n">
+      <c r="A52" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="B52" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" s="0" t="s">
+      <c r="B52" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D52" s="0" t="s">
+      <c r="D52" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H52" s="2" t="s">
+      <c r="H52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M52" s="3" t="str">
+      <c r="M52" s="4" t="str">
         <f aca="false">IF(A52-A51&lt;&gt;1,A52-A51,"")</f>
         <v/>
       </c>
-      <c r="N52" s="3" t="n">
+      <c r="N52" s="4" t="n">
         <f aca="false">COUNTA(H52:L52)</f>
         <v>1</v>
       </c>
-      <c r="O52" s="3" t="n">
+      <c r="O52" s="4" t="n">
         <v>639</v>
       </c>
-      <c r="P52" s="3" t="str">
+      <c r="P52" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D52,3),O52,LEFT(C52,3)))</f>
         <v>COL639AND</v>
       </c>
-      <c r="Q52" s="4" t="str">
+      <c r="Q52" s="5" t="str">
         <f aca="false">IF(H52&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N52&gt;1,"5",""),$O52), "")</f>
         <v>Motion 639</v>
       </c>
-      <c r="R52" s="4" t="str">
+      <c r="R52" s="5" t="str">
         <f aca="false">IF(I52&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N52&gt;1,"4",""),$O52), "")</f>
         <v/>
       </c>
-      <c r="S52" s="4" t="str">
+      <c r="S52" s="5" t="str">
         <f aca="false">IF(J52&lt;&gt;"", _xlfn.CONCAT("Motion ",$O52), "")</f>
         <v/>
       </c>
-      <c r="T52" s="4" t="str">
+      <c r="T52" s="5" t="str">
         <f aca="false">IF(K52&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N52&gt;1,"2",""),$O52), "")</f>
         <v/>
       </c>
-      <c r="U52" s="4" t="str">
+      <c r="U52" s="5" t="str">
         <f aca="false">IF(L52&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N52&gt;1,"1",""),$O52), "")</f>
         <v/>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="n">
+      <c r="A53" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C53" s="0" t="s">
+      <c r="C53" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D53" s="0" t="s">
+      <c r="D53" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H53" s="2" t="s">
+      <c r="H53" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M53" s="3" t="str">
+      <c r="M53" s="4" t="str">
         <f aca="false">IF(A53-A52&lt;&gt;1,A53-A52,"")</f>
         <v/>
       </c>
-      <c r="N53" s="3" t="n">
+      <c r="N53" s="4" t="n">
         <f aca="false">COUNTA(H53:L53)</f>
         <v>1</v>
       </c>
-      <c r="O53" s="3" t="n">
+      <c r="O53" s="4" t="n">
         <v>611</v>
       </c>
-      <c r="P53" s="3" t="str">
+      <c r="P53" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D53,3),O53,LEFT(C53,3)))</f>
         <v>COL611ANN</v>
       </c>
-      <c r="Q53" s="4" t="str">
+      <c r="Q53" s="5" t="str">
         <f aca="false">IF(H53&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N53&gt;1,"5",""),$O53), "")</f>
         <v>Motion 611</v>
       </c>
-      <c r="R53" s="4" t="str">
+      <c r="R53" s="5" t="str">
         <f aca="false">IF(I53&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N53&gt;1,"4",""),$O53), "")</f>
         <v/>
       </c>
-      <c r="S53" s="4" t="str">
+      <c r="S53" s="5" t="str">
         <f aca="false">IF(J53&lt;&gt;"", _xlfn.CONCAT("Motion ",$O53), "")</f>
         <v/>
       </c>
-      <c r="T53" s="4" t="str">
+      <c r="T53" s="5" t="str">
         <f aca="false">IF(K53&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N53&gt;1,"2",""),$O53), "")</f>
         <v/>
       </c>
-      <c r="U53" s="4" t="str">
+      <c r="U53" s="5" t="str">
         <f aca="false">IF(L53&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N53&gt;1,"1",""),$O53), "")</f>
         <v/>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="n">
+      <c r="A54" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="B54" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" s="0" t="s">
+      <c r="B54" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D54" s="0" t="s">
+      <c r="D54" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H54" s="2" t="s">
+      <c r="H54" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M54" s="3" t="str">
+      <c r="M54" s="4" t="str">
         <f aca="false">IF(A54-A53&lt;&gt;1,A54-A53,"")</f>
         <v/>
       </c>
-      <c r="N54" s="3" t="n">
+      <c r="N54" s="4" t="n">
         <f aca="false">COUNTA(H54:L54)</f>
         <v>1</v>
       </c>
-      <c r="O54" s="3" t="n">
+      <c r="O54" s="4" t="n">
         <v>826</v>
       </c>
-      <c r="P54" s="3" t="str">
+      <c r="P54" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D54,3),O54,LEFT(C54,3)))</f>
         <v>BER826ARL</v>
       </c>
-      <c r="Q54" s="4" t="str">
+      <c r="Q54" s="5" t="str">
         <f aca="false">IF(H54&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N54&gt;1,"5",""),$O54), "")</f>
         <v>Motion 826</v>
       </c>
-      <c r="R54" s="4" t="str">
+      <c r="R54" s="5" t="str">
         <f aca="false">IF(I54&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N54&gt;1,"4",""),$O54), "")</f>
         <v/>
       </c>
-      <c r="S54" s="4" t="str">
+      <c r="S54" s="5" t="str">
         <f aca="false">IF(J54&lt;&gt;"", _xlfn.CONCAT("Motion ",$O54), "")</f>
         <v/>
       </c>
-      <c r="T54" s="4" t="str">
+      <c r="T54" s="5" t="str">
         <f aca="false">IF(K54&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N54&gt;1,"2",""),$O54), "")</f>
         <v/>
       </c>
-      <c r="U54" s="4" t="str">
+      <c r="U54" s="5" t="str">
         <f aca="false">IF(L54&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N54&gt;1,"1",""),$O54), "")</f>
         <v/>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="n">
+      <c r="A55" s="1" t="n">
         <v>67</v>
       </c>
-      <c r="B55" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" s="0" t="s">
+      <c r="B55" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D55" s="0" t="s">
+      <c r="D55" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I55" s="2" t="s">
+      <c r="I55" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J55" s="2" t="s">
+      <c r="J55" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M55" s="3" t="str">
+      <c r="M55" s="4" t="str">
         <f aca="false">IF(A55-A54&lt;&gt;1,A55-A54,"")</f>
         <v/>
       </c>
-      <c r="N55" s="3" t="n">
+      <c r="N55" s="4" t="n">
         <f aca="false">COUNTA(H55:L55)</f>
         <v>2</v>
       </c>
-      <c r="O55" s="3" t="n">
+      <c r="O55" s="4" t="n">
         <v>821</v>
       </c>
-      <c r="P55" s="3" t="str">
+      <c r="P55" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D55,3),O55,LEFT(C55,3)))</f>
         <v>CON821GAR</v>
       </c>
-      <c r="Q55" s="4" t="str">
+      <c r="Q55" s="5" t="str">
         <f aca="false">IF(H55&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N55&gt;1,"5",""),$O55), "")</f>
         <v/>
       </c>
-      <c r="R55" s="4" t="str">
+      <c r="R55" s="5" t="str">
         <f aca="false">IF(I55&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N55&gt;1,"4",""),$O55), "")</f>
         <v>Motion 4821</v>
       </c>
-      <c r="S55" s="4" t="str">
+      <c r="S55" s="5" t="str">
         <f aca="false">IF(J55&lt;&gt;"", _xlfn.CONCAT("Motion ",$O55), "")</f>
         <v>Motion 821</v>
       </c>
-      <c r="T55" s="4" t="str">
+      <c r="T55" s="5" t="str">
         <f aca="false">IF(K55&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N55&gt;1,"2",""),$O55), "")</f>
         <v/>
       </c>
-      <c r="U55" s="4" t="str">
+      <c r="U55" s="5" t="str">
         <f aca="false">IF(L55&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N55&gt;1,"1",""),$O55), "")</f>
         <v/>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="n">
+      <c r="A56" s="1" t="n">
         <v>68</v>
       </c>
-      <c r="B56" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" s="0" t="s">
+      <c r="B56" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D56" s="0" t="s">
+      <c r="D56" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I56" s="2" t="s">
+      <c r="I56" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J56" s="2" t="s">
+      <c r="J56" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M56" s="3" t="str">
+      <c r="M56" s="4" t="str">
         <f aca="false">IF(A56-A55&lt;&gt;1,A56-A55,"")</f>
         <v/>
       </c>
-      <c r="N56" s="3" t="n">
+      <c r="N56" s="4" t="n">
         <f aca="false">COUNTA(H56:L56)</f>
         <v>2</v>
       </c>
-      <c r="O56" s="3" t="n">
+      <c r="O56" s="4" t="n">
         <v>812</v>
       </c>
-      <c r="P56" s="3" t="str">
+      <c r="P56" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D56,3),O56,LEFT(C56,3)))</f>
         <v>DIN812JAM</v>
       </c>
-      <c r="Q56" s="4" t="str">
+      <c r="Q56" s="5" t="str">
         <f aca="false">IF(H56&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N56&gt;1,"5",""),$O56), "")</f>
         <v/>
       </c>
-      <c r="R56" s="4" t="str">
+      <c r="R56" s="5" t="str">
         <f aca="false">IF(I56&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N56&gt;1,"4",""),$O56), "")</f>
         <v>Motion 4812</v>
       </c>
-      <c r="S56" s="4" t="str">
+      <c r="S56" s="5" t="str">
         <f aca="false">IF(J56&lt;&gt;"", _xlfn.CONCAT("Motion ",$O56), "")</f>
         <v>Motion 812</v>
       </c>
-      <c r="T56" s="4" t="str">
+      <c r="T56" s="5" t="str">
         <f aca="false">IF(K56&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N56&gt;1,"2",""),$O56), "")</f>
         <v/>
       </c>
-      <c r="U56" s="4" t="str">
+      <c r="U56" s="5" t="str">
         <f aca="false">IF(L56&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N56&gt;1,"1",""),$O56), "")</f>
         <v/>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="n">
+      <c r="A57" s="1" t="n">
         <v>69</v>
       </c>
-      <c r="B57" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" s="0" t="s">
+      <c r="B57" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D57" s="0" t="s">
+      <c r="D57" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J57" s="2" t="s">
+      <c r="J57" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M57" s="3" t="str">
+      <c r="M57" s="4" t="str">
         <f aca="false">IF(A57-A56&lt;&gt;1,A57-A56,"")</f>
         <v/>
       </c>
-      <c r="N57" s="3" t="n">
+      <c r="N57" s="4" t="n">
         <f aca="false">COUNTA(H57:L57)</f>
         <v>1</v>
       </c>
-      <c r="O57" s="3" t="n">
+      <c r="O57" s="4" t="n">
         <v>829</v>
       </c>
-      <c r="P57" s="3" t="str">
+      <c r="P57" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D57,3),O57,LEFT(C57,3)))</f>
         <v>TRO829WIL</v>
       </c>
-      <c r="Q57" s="4" t="str">
+      <c r="Q57" s="5" t="str">
         <f aca="false">IF(H57&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N57&gt;1,"5",""),$O57), "")</f>
         <v/>
       </c>
-      <c r="R57" s="4" t="str">
+      <c r="R57" s="5" t="str">
         <f aca="false">IF(I57&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N57&gt;1,"4",""),$O57), "")</f>
         <v/>
       </c>
-      <c r="S57" s="4" t="str">
+      <c r="S57" s="5" t="str">
         <f aca="false">IF(J57&lt;&gt;"", _xlfn.CONCAT("Motion ",$O57), "")</f>
         <v>Motion 829</v>
       </c>
-      <c r="T57" s="4" t="str">
+      <c r="T57" s="5" t="str">
         <f aca="false">IF(K57&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N57&gt;1,"2",""),$O57), "")</f>
         <v/>
       </c>
-      <c r="U57" s="4" t="str">
+      <c r="U57" s="5" t="str">
         <f aca="false">IF(L57&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N57&gt;1,"1",""),$O57), "")</f>
         <v/>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="n">
+      <c r="A58" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="B58" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" s="0" t="s">
+      <c r="B58" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D58" s="0" t="s">
+      <c r="D58" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H58" s="2" t="s">
+      <c r="H58" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K58" s="2" t="s">
+      <c r="K58" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M58" s="3" t="str">
+      <c r="M58" s="4" t="str">
         <f aca="false">IF(A58-A57&lt;&gt;1,A58-A57,"")</f>
         <v/>
       </c>
-      <c r="N58" s="3" t="n">
+      <c r="N58" s="4" t="n">
         <f aca="false">COUNTA(H58:L58)</f>
         <v>2</v>
       </c>
-      <c r="O58" s="3" t="n">
+      <c r="O58" s="4" t="n">
         <v>669</v>
       </c>
-      <c r="P58" s="3" t="str">
+      <c r="P58" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D58,3),O58,LEFT(C58,3)))</f>
         <v>WIL669DAV</v>
       </c>
-      <c r="Q58" s="4" t="str">
+      <c r="Q58" s="5" t="str">
         <f aca="false">IF(H58&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N58&gt;1,"5",""),$O58), "")</f>
         <v>Motion 5669</v>
       </c>
-      <c r="R58" s="4" t="str">
+      <c r="R58" s="5" t="str">
         <f aca="false">IF(I58&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N58&gt;1,"4",""),$O58), "")</f>
         <v/>
       </c>
-      <c r="S58" s="4" t="str">
+      <c r="S58" s="5" t="str">
         <f aca="false">IF(J58&lt;&gt;"", _xlfn.CONCAT("Motion ",$O58), "")</f>
         <v/>
       </c>
-      <c r="T58" s="4" t="str">
+      <c r="T58" s="5" t="str">
         <f aca="false">IF(K58&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N58&gt;1,"2",""),$O58), "")</f>
         <v>Motion 2669</v>
       </c>
-      <c r="U58" s="4" t="str">
+      <c r="U58" s="5" t="str">
         <f aca="false">IF(L58&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N58&gt;1,"1",""),$O58), "")</f>
         <v/>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="n">
+      <c r="A59" s="1" t="n">
         <v>71</v>
       </c>
-      <c r="B59" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" s="0" t="s">
+      <c r="B59" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D59" s="0" t="s">
+      <c r="D59" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G59" s="1" t="n">
+      <c r="G59" s="2" t="n">
         <v>920</v>
       </c>
-      <c r="J59" s="2" t="s">
+      <c r="J59" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M59" s="3" t="str">
+      <c r="M59" s="4" t="str">
         <f aca="false">IF(A59-A58&lt;&gt;1,A59-A58,"")</f>
         <v/>
       </c>
-      <c r="N59" s="3" t="n">
+      <c r="N59" s="4" t="n">
         <f aca="false">COUNTA(H59:L59)</f>
         <v>1</v>
       </c>
-      <c r="O59" s="11" t="n">
+      <c r="O59" s="12" t="n">
         <f aca="false">G59</f>
         <v>920</v>
       </c>
-      <c r="P59" s="3" t="str">
+      <c r="P59" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D59,3),O59,LEFT(C59,3)))</f>
         <v>PAL920MAR</v>
       </c>
-      <c r="Q59" s="4" t="str">
+      <c r="Q59" s="5" t="str">
         <f aca="false">IF(H59&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N59&gt;1,"5",""),$O59), "")</f>
         <v/>
       </c>
-      <c r="R59" s="4" t="str">
+      <c r="R59" s="5" t="str">
         <f aca="false">IF(I59&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N59&gt;1,"4",""),$O59), "")</f>
         <v/>
       </c>
-      <c r="S59" s="4" t="str">
+      <c r="S59" s="5" t="str">
         <f aca="false">IF(J59&lt;&gt;"", _xlfn.CONCAT("Motion ",$O59), "")</f>
         <v>Motion 920</v>
       </c>
-      <c r="T59" s="4" t="str">
+      <c r="T59" s="5" t="str">
         <f aca="false">IF(K59&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N59&gt;1,"2",""),$O59), "")</f>
         <v/>
       </c>
-      <c r="U59" s="4" t="str">
+      <c r="U59" s="5" t="str">
         <f aca="false">IF(L59&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N59&gt;1,"1",""),$O59), "")</f>
         <v/>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="n">
+      <c r="A60" s="1" t="n">
         <v>72</v>
       </c>
-      <c r="B60" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" s="0" t="s">
+      <c r="B60" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D60" s="0" t="s">
+      <c r="D60" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H60" s="2" t="s">
+      <c r="H60" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M60" s="3" t="str">
+      <c r="M60" s="4" t="str">
         <f aca="false">IF(A60-A59&lt;&gt;1,A60-A59,"")</f>
         <v/>
       </c>
-      <c r="N60" s="3" t="n">
+      <c r="N60" s="4" t="n">
         <f aca="false">COUNTA(H60:L60)</f>
         <v>1</v>
       </c>
-      <c r="O60" s="3" t="n">
+      <c r="O60" s="4" t="n">
         <v>631</v>
       </c>
-      <c r="P60" s="3" t="str">
+      <c r="P60" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D60,3),O60,LEFT(C60,3)))</f>
         <v>SAN631SIM</v>
       </c>
-      <c r="Q60" s="4" t="str">
+      <c r="Q60" s="5" t="str">
         <f aca="false">IF(H60&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N60&gt;1,"5",""),$O60), "")</f>
         <v>Motion 631</v>
       </c>
-      <c r="R60" s="4" t="str">
+      <c r="R60" s="5" t="str">
         <f aca="false">IF(I60&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N60&gt;1,"4",""),$O60), "")</f>
         <v/>
       </c>
-      <c r="S60" s="4" t="str">
+      <c r="S60" s="5" t="str">
         <f aca="false">IF(J60&lt;&gt;"", _xlfn.CONCAT("Motion ",$O60), "")</f>
         <v/>
       </c>
-      <c r="T60" s="4" t="str">
+      <c r="T60" s="5" t="str">
         <f aca="false">IF(K60&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N60&gt;1,"2",""),$O60), "")</f>
         <v/>
       </c>
-      <c r="U60" s="4" t="str">
+      <c r="U60" s="5" t="str">
         <f aca="false">IF(L60&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N60&gt;1,"1",""),$O60), "")</f>
         <v/>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="n">
+      <c r="A61" s="1" t="n">
         <v>73</v>
       </c>
-      <c r="B61" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" s="0" t="s">
+      <c r="B61" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D61" s="0" t="s">
+      <c r="D61" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I61" s="2" t="s">
+      <c r="I61" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J61" s="2" t="s">
+      <c r="J61" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M61" s="3" t="str">
+      <c r="M61" s="4" t="str">
         <f aca="false">IF(A61-A60&lt;&gt;1,A61-A60,"")</f>
         <v/>
       </c>
-      <c r="N61" s="3" t="n">
+      <c r="N61" s="4" t="n">
         <f aca="false">COUNTA(H61:L61)</f>
         <v>2</v>
       </c>
-      <c r="O61" s="3" t="n">
+      <c r="O61" s="4" t="n">
         <v>810</v>
       </c>
-      <c r="P61" s="3" t="str">
+      <c r="P61" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D61,3),O61,LEFT(C61,3)))</f>
         <v>NEW810MAR</v>
       </c>
-      <c r="Q61" s="4" t="str">
+      <c r="Q61" s="5" t="str">
         <f aca="false">IF(H61&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N61&gt;1,"5",""),$O61), "")</f>
         <v/>
       </c>
-      <c r="R61" s="4" t="str">
+      <c r="R61" s="5" t="str">
         <f aca="false">IF(I61&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N61&gt;1,"4",""),$O61), "")</f>
         <v>Motion 4810</v>
       </c>
-      <c r="S61" s="4" t="str">
+      <c r="S61" s="5" t="str">
         <f aca="false">IF(J61&lt;&gt;"", _xlfn.CONCAT("Motion ",$O61), "")</f>
         <v>Motion 810</v>
       </c>
-      <c r="T61" s="4" t="str">
+      <c r="T61" s="5" t="str">
         <f aca="false">IF(K61&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N61&gt;1,"2",""),$O61), "")</f>
         <v/>
       </c>
-      <c r="U61" s="4" t="str">
+      <c r="U61" s="5" t="str">
         <f aca="false">IF(L61&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N61&gt;1,"1",""),$O61), "")</f>
         <v/>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="n">
+      <c r="A62" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="B62" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" s="0" t="s">
+      <c r="B62" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D62" s="0" t="s">
+      <c r="D62" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J62" s="2" t="s">
+      <c r="J62" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M62" s="12" t="n">
+      <c r="M62" s="13" t="n">
         <f aca="false">IF(A62-A61&lt;&gt;1,A62-A61,"")</f>
         <v>2</v>
       </c>
-      <c r="N62" s="3" t="n">
+      <c r="N62" s="4" t="n">
         <f aca="false">COUNTA(H62:L62)</f>
         <v>1</v>
       </c>
-      <c r="O62" s="3" t="n">
+      <c r="O62" s="4" t="n">
         <v>817</v>
       </c>
-      <c r="P62" s="3" t="str">
+      <c r="P62" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D62,3),O62,LEFT(C62,3)))</f>
         <v>MAR817EDD</v>
       </c>
-      <c r="Q62" s="4" t="str">
+      <c r="Q62" s="5" t="str">
         <f aca="false">IF(H62&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N62&gt;1,"5",""),$O62), "")</f>
         <v/>
       </c>
-      <c r="R62" s="4" t="str">
+      <c r="R62" s="5" t="str">
         <f aca="false">IF(I62&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N62&gt;1,"4",""),$O62), "")</f>
         <v/>
       </c>
-      <c r="S62" s="4" t="str">
+      <c r="S62" s="5" t="str">
         <f aca="false">IF(J62&lt;&gt;"", _xlfn.CONCAT("Motion ",$O62), "")</f>
         <v>Motion 817</v>
       </c>
-      <c r="T62" s="4" t="str">
+      <c r="T62" s="5" t="str">
         <f aca="false">IF(K62&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N62&gt;1,"2",""),$O62), "")</f>
         <v/>
       </c>
-      <c r="U62" s="4" t="str">
+      <c r="U62" s="5" t="str">
         <f aca="false">IF(L62&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N62&gt;1,"1",""),$O62), "")</f>
         <v/>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="n">
+      <c r="A63" s="1" t="n">
         <v>76</v>
       </c>
-      <c r="B63" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" s="0" t="s">
+      <c r="B63" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D63" s="0" t="s">
+      <c r="D63" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J63" s="2" t="s">
+      <c r="J63" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M63" s="3" t="str">
+      <c r="M63" s="4" t="str">
         <f aca="false">IF(A63-A62&lt;&gt;1,A63-A62,"")</f>
         <v/>
       </c>
-      <c r="N63" s="3" t="n">
+      <c r="N63" s="4" t="n">
         <f aca="false">COUNTA(H63:L63)</f>
         <v>1</v>
       </c>
-      <c r="O63" s="3" t="n">
+      <c r="O63" s="4" t="n">
         <v>803</v>
       </c>
-      <c r="P63" s="3" t="str">
+      <c r="P63" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D63,3),O63,LEFT(C63,3)))</f>
         <v>STU803AND</v>
       </c>
-      <c r="Q63" s="4" t="str">
+      <c r="Q63" s="5" t="str">
         <f aca="false">IF(H63&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N63&gt;1,"5",""),$O63), "")</f>
         <v/>
       </c>
-      <c r="R63" s="4" t="str">
+      <c r="R63" s="5" t="str">
         <f aca="false">IF(I63&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N63&gt;1,"4",""),$O63), "")</f>
         <v/>
       </c>
-      <c r="S63" s="4" t="str">
+      <c r="S63" s="5" t="str">
         <f aca="false">IF(J63&lt;&gt;"", _xlfn.CONCAT("Motion ",$O63), "")</f>
         <v>Motion 803</v>
       </c>
-      <c r="T63" s="4" t="str">
+      <c r="T63" s="5" t="str">
         <f aca="false">IF(K63&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N63&gt;1,"2",""),$O63), "")</f>
         <v/>
       </c>
-      <c r="U63" s="4" t="str">
+      <c r="U63" s="5" t="str">
         <f aca="false">IF(L63&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N63&gt;1,"1",""),$O63), "")</f>
         <v/>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="n">
+      <c r="A64" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="B64" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" s="0" t="s">
+      <c r="B64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D64" s="0" t="s">
+      <c r="D64" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K64" s="2" t="s">
+      <c r="K64" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M64" s="3" t="str">
+      <c r="M64" s="4" t="str">
         <f aca="false">IF(A64-A63&lt;&gt;1,A64-A63,"")</f>
         <v/>
       </c>
-      <c r="N64" s="3" t="n">
+      <c r="N64" s="4" t="n">
         <f aca="false">COUNTA(H64:L64)</f>
         <v>1</v>
       </c>
-      <c r="O64" s="3" t="n">
+      <c r="O64" s="4" t="n">
         <v>699</v>
       </c>
-      <c r="P64" s="3" t="str">
+      <c r="P64" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D64,3),O64,LEFT(C64,3)))</f>
         <v>LON699JAM</v>
       </c>
-      <c r="Q64" s="4" t="str">
+      <c r="Q64" s="5" t="str">
         <f aca="false">IF(H64&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N64&gt;1,"5",""),$O64), "")</f>
         <v/>
       </c>
-      <c r="R64" s="4" t="str">
+      <c r="R64" s="5" t="str">
         <f aca="false">IF(I64&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N64&gt;1,"4",""),$O64), "")</f>
         <v/>
       </c>
-      <c r="S64" s="4" t="str">
+      <c r="S64" s="5" t="str">
         <f aca="false">IF(J64&lt;&gt;"", _xlfn.CONCAT("Motion ",$O64), "")</f>
         <v/>
       </c>
-      <c r="T64" s="4" t="str">
+      <c r="T64" s="5" t="str">
         <f aca="false">IF(K64&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N64&gt;1,"2",""),$O64), "")</f>
         <v>Motion 699</v>
       </c>
-      <c r="U64" s="4" t="str">
+      <c r="U64" s="5" t="str">
         <f aca="false">IF(L64&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N64&gt;1,"1",""),$O64), "")</f>
         <v/>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="n">
+      <c r="A65" s="1" t="n">
         <v>78</v>
       </c>
-      <c r="B65" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" s="0" t="s">
+      <c r="B65" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D65" s="0" t="s">
+      <c r="D65" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F65" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J65" s="2" t="s">
+      <c r="J65" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M65" s="3" t="str">
+      <c r="M65" s="4" t="str">
         <f aca="false">IF(A65-A64&lt;&gt;1,A65-A64,"")</f>
         <v/>
       </c>
-      <c r="N65" s="3" t="n">
+      <c r="N65" s="4" t="n">
         <f aca="false">COUNTA(H65:L65)</f>
         <v>1</v>
       </c>
-      <c r="O65" s="3" t="n">
+      <c r="O65" s="4" t="n">
         <v>656</v>
       </c>
-      <c r="P65" s="3" t="str">
+      <c r="P65" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D65,3),O65,LEFT(C65,3)))</f>
         <v>THO656RUS</v>
       </c>
-      <c r="Q65" s="4" t="str">
+      <c r="Q65" s="5" t="str">
         <f aca="false">IF(H65&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N65&gt;1,"5",""),$O65), "")</f>
         <v/>
       </c>
-      <c r="R65" s="4" t="str">
+      <c r="R65" s="5" t="str">
         <f aca="false">IF(I65&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N65&gt;1,"4",""),$O65), "")</f>
         <v/>
       </c>
-      <c r="S65" s="4" t="str">
+      <c r="S65" s="5" t="str">
         <f aca="false">IF(J65&lt;&gt;"", _xlfn.CONCAT("Motion ",$O65), "")</f>
         <v>Motion 656</v>
       </c>
-      <c r="T65" s="4" t="str">
+      <c r="T65" s="5" t="str">
         <f aca="false">IF(K65&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N65&gt;1,"2",""),$O65), "")</f>
         <v/>
       </c>
-      <c r="U65" s="4" t="str">
+      <c r="U65" s="5" t="str">
         <f aca="false">IF(L65&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N65&gt;1,"1",""),$O65), "")</f>
         <v/>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="n">
+      <c r="A66" s="1" t="n">
         <v>79</v>
       </c>
-      <c r="B66" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" s="0" t="s">
+      <c r="B66" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D66" s="0" t="s">
+      <c r="D66" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J66" s="2" t="s">
+      <c r="J66" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M66" s="3" t="str">
+      <c r="M66" s="4" t="str">
         <f aca="false">IF(A66-A65&lt;&gt;1,A66-A65,"")</f>
         <v/>
       </c>
-      <c r="N66" s="3" t="n">
+      <c r="N66" s="4" t="n">
         <f aca="false">COUNTA(H66:L66)</f>
         <v>1</v>
       </c>
-      <c r="O66" s="3" t="n">
+      <c r="O66" s="4" t="n">
         <v>651</v>
       </c>
-      <c r="P66" s="3" t="str">
+      <c r="P66" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D66,3),O66,LEFT(C66,3)))</f>
         <v>KIR651JON</v>
       </c>
-      <c r="Q66" s="4" t="str">
+      <c r="Q66" s="5" t="str">
         <f aca="false">IF(H66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"5",""),$O66), "")</f>
         <v/>
       </c>
-      <c r="R66" s="4" t="str">
+      <c r="R66" s="5" t="str">
         <f aca="false">IF(I66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"4",""),$O66), "")</f>
         <v/>
       </c>
-      <c r="S66" s="4" t="str">
+      <c r="S66" s="5" t="str">
         <f aca="false">IF(J66&lt;&gt;"", _xlfn.CONCAT("Motion ",$O66), "")</f>
         <v>Motion 651</v>
       </c>
-      <c r="T66" s="4" t="str">
+      <c r="T66" s="5" t="str">
         <f aca="false">IF(K66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"2",""),$O66), "")</f>
         <v/>
       </c>
-      <c r="U66" s="4" t="str">
+      <c r="U66" s="5" t="str">
         <f aca="false">IF(L66&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N66&gt;1,"1",""),$O66), "")</f>
         <v/>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="n">
+      <c r="A67" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="B67" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" s="0" t="s">
+      <c r="B67" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D67" s="0" t="s">
+      <c r="D67" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J67" s="2" t="s">
+      <c r="J67" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M67" s="3" t="str">
+      <c r="M67" s="4" t="str">
         <f aca="false">IF(A67-A66&lt;&gt;1,A67-A66,"")</f>
         <v/>
       </c>
-      <c r="N67" s="3" t="n">
+      <c r="N67" s="4" t="n">
         <f aca="false">COUNTA(H67:L67)</f>
         <v>1</v>
       </c>
-      <c r="O67" s="3" t="n">
+      <c r="O67" s="4" t="n">
         <v>836</v>
       </c>
-      <c r="P67" s="3" t="str">
+      <c r="P67" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D67,3),O67,LEFT(C67,3)))</f>
         <v>CRO836JIM</v>
       </c>
-      <c r="Q67" s="4" t="str">
+      <c r="Q67" s="5" t="str">
         <f aca="false">IF(H67&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N67&gt;1,"5",""),$O67), "")</f>
         <v/>
       </c>
-      <c r="R67" s="4" t="str">
+      <c r="R67" s="5" t="str">
         <f aca="false">IF(I67&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N67&gt;1,"4",""),$O67), "")</f>
         <v/>
       </c>
-      <c r="S67" s="4" t="str">
+      <c r="S67" s="5" t="str">
         <f aca="false">IF(J67&lt;&gt;"", _xlfn.CONCAT("Motion ",$O67), "")</f>
         <v>Motion 836</v>
       </c>
-      <c r="T67" s="4" t="str">
+      <c r="T67" s="5" t="str">
         <f aca="false">IF(K67&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N67&gt;1,"2",""),$O67), "")</f>
         <v/>
       </c>
-      <c r="U67" s="4" t="str">
+      <c r="U67" s="5" t="str">
         <f aca="false">IF(L67&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N67&gt;1,"1",""),$O67), "")</f>
         <v/>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="n">
+      <c r="A68" s="1" t="n">
         <v>81</v>
       </c>
-      <c r="B68" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" s="0" t="s">
+      <c r="B68" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D68" s="0" t="s">
+      <c r="D68" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E68" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J68" s="2" t="s">
+      <c r="J68" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M68" s="3" t="str">
+      <c r="M68" s="4" t="str">
         <f aca="false">IF(A68-A67&lt;&gt;1,A68-A67,"")</f>
         <v/>
       </c>
-      <c r="N68" s="3" t="n">
+      <c r="N68" s="4" t="n">
         <f aca="false">COUNTA(H68:L68)</f>
         <v>1</v>
       </c>
-      <c r="O68" s="3" t="n">
+      <c r="O68" s="4" t="n">
         <v>818</v>
       </c>
-      <c r="P68" s="3" t="str">
+      <c r="P68" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D68,3),O68,LEFT(C68,3)))</f>
         <v>CRO818GEO</v>
       </c>
-      <c r="Q68" s="4" t="str">
+      <c r="Q68" s="5" t="str">
         <f aca="false">IF(H68&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N68&gt;1,"5",""),$O68), "")</f>
         <v/>
       </c>
-      <c r="R68" s="4" t="str">
+      <c r="R68" s="5" t="str">
         <f aca="false">IF(I68&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N68&gt;1,"4",""),$O68), "")</f>
         <v/>
       </c>
-      <c r="S68" s="4" t="str">
+      <c r="S68" s="5" t="str">
         <f aca="false">IF(J68&lt;&gt;"", _xlfn.CONCAT("Motion ",$O68), "")</f>
         <v>Motion 818</v>
       </c>
-      <c r="T68" s="4" t="str">
+      <c r="T68" s="5" t="str">
         <f aca="false">IF(K68&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N68&gt;1,"2",""),$O68), "")</f>
         <v/>
       </c>
-      <c r="U68" s="4" t="str">
+      <c r="U68" s="5" t="str">
         <f aca="false">IF(L68&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N68&gt;1,"1",""),$O68), "")</f>
         <v/>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="n">
+      <c r="A69" s="1" t="n">
         <v>82</v>
       </c>
-      <c r="B69" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" s="0" t="s">
+      <c r="B69" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D69" s="0" t="s">
+      <c r="D69" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E69" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F69" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J69" s="2" t="s">
+      <c r="J69" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M69" s="3" t="str">
+      <c r="M69" s="4" t="str">
         <f aca="false">IF(A69-A68&lt;&gt;1,A69-A68,"")</f>
         <v/>
       </c>
-      <c r="N69" s="3" t="n">
+      <c r="N69" s="4" t="n">
         <f aca="false">COUNTA(H69:L69)</f>
         <v>1</v>
       </c>
-      <c r="O69" s="3" t="n">
+      <c r="O69" s="4" t="n">
         <v>816</v>
       </c>
-      <c r="P69" s="3" t="str">
+      <c r="P69" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D69,3),O69,LEFT(C69,3)))</f>
         <v>CRO816JAC</v>
       </c>
-      <c r="Q69" s="4" t="str">
+      <c r="Q69" s="5" t="str">
         <f aca="false">IF(H69&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N69&gt;1,"5",""),$O69), "")</f>
         <v/>
       </c>
-      <c r="R69" s="4" t="str">
+      <c r="R69" s="5" t="str">
         <f aca="false">IF(I69&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N69&gt;1,"4",""),$O69), "")</f>
         <v/>
       </c>
-      <c r="S69" s="4" t="str">
+      <c r="S69" s="5" t="str">
         <f aca="false">IF(J69&lt;&gt;"", _xlfn.CONCAT("Motion ",$O69), "")</f>
         <v>Motion 816</v>
       </c>
-      <c r="T69" s="4" t="str">
+      <c r="T69" s="5" t="str">
         <f aca="false">IF(K69&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N69&gt;1,"2",""),$O69), "")</f>
         <v/>
       </c>
-      <c r="U69" s="4" t="str">
+      <c r="U69" s="5" t="str">
         <f aca="false">IF(L69&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N69&gt;1,"1",""),$O69), "")</f>
         <v/>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="n">
+      <c r="A70" s="1" t="n">
         <v>83</v>
       </c>
-      <c r="B70" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" s="0" t="s">
+      <c r="B70" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D70" s="0" t="s">
+      <c r="D70" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I70" s="2" t="s">
+      <c r="I70" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J70" s="2" t="s">
+      <c r="J70" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M70" s="3" t="str">
+      <c r="M70" s="4" t="str">
         <f aca="false">IF(A70-A69&lt;&gt;1,A70-A69,"")</f>
         <v/>
       </c>
-      <c r="N70" s="3" t="n">
+      <c r="N70" s="4" t="n">
         <f aca="false">COUNTA(H70:L70)</f>
         <v>2</v>
       </c>
-      <c r="O70" s="3" t="n">
+      <c r="O70" s="4" t="n">
         <v>942</v>
       </c>
-      <c r="P70" s="3" t="str">
+      <c r="P70" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D70,3),O70,LEFT(C70,3)))</f>
         <v>NOR942SCO</v>
       </c>
-      <c r="Q70" s="4" t="str">
+      <c r="Q70" s="5" t="str">
         <f aca="false">IF(H70&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N70&gt;1,"5",""),$O70), "")</f>
         <v/>
       </c>
-      <c r="R70" s="4" t="str">
+      <c r="R70" s="5" t="str">
         <f aca="false">IF(I70&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N70&gt;1,"4",""),$O70), "")</f>
         <v>Motion 4942</v>
       </c>
-      <c r="S70" s="4" t="str">
+      <c r="S70" s="5" t="str">
         <f aca="false">IF(J70&lt;&gt;"", _xlfn.CONCAT("Motion ",$O70), "")</f>
         <v>Motion 942</v>
       </c>
-      <c r="T70" s="4" t="str">
+      <c r="T70" s="5" t="str">
         <f aca="false">IF(K70&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N70&gt;1,"2",""),$O70), "")</f>
         <v/>
       </c>
-      <c r="U70" s="4" t="str">
+      <c r="U70" s="5" t="str">
         <f aca="false">IF(L70&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N70&gt;1,"1",""),$O70), "")</f>
         <v/>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="n">
+      <c r="A71" s="1" t="n">
         <v>84</v>
       </c>
-      <c r="B71" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" s="0" t="s">
+      <c r="B71" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D71" s="0" t="s">
+      <c r="D71" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="K71" s="2" t="s">
+      <c r="K71" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M71" s="3" t="str">
+      <c r="M71" s="4" t="str">
         <f aca="false">IF(A71-A70&lt;&gt;1,A71-A70,"")</f>
         <v/>
       </c>
-      <c r="N71" s="3" t="n">
+      <c r="N71" s="4" t="n">
         <f aca="false">COUNTA(H71:L71)</f>
         <v>1</v>
       </c>
-      <c r="O71" s="3" t="n">
+      <c r="O71" s="4" t="n">
         <v>701</v>
       </c>
-      <c r="P71" s="3" t="str">
+      <c r="P71" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D71,3),O71,LEFT(C71,3)))</f>
         <v>CAM701SEB</v>
       </c>
-      <c r="Q71" s="4" t="str">
+      <c r="Q71" s="5" t="str">
         <f aca="false">IF(H71&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N71&gt;1,"5",""),$O71), "")</f>
         <v/>
       </c>
-      <c r="R71" s="4" t="str">
+      <c r="R71" s="5" t="str">
         <f aca="false">IF(I71&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N71&gt;1,"4",""),$O71), "")</f>
         <v/>
       </c>
-      <c r="S71" s="4" t="str">
+      <c r="S71" s="5" t="str">
         <f aca="false">IF(J71&lt;&gt;"", _xlfn.CONCAT("Motion ",$O71), "")</f>
         <v/>
       </c>
-      <c r="T71" s="4" t="str">
+      <c r="T71" s="5" t="str">
         <f aca="false">IF(K71&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N71&gt;1,"2",""),$O71), "")</f>
         <v>Motion 701</v>
       </c>
-      <c r="U71" s="4" t="str">
+      <c r="U71" s="5" t="str">
         <f aca="false">IF(L71&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N71&gt;1,"1",""),$O71), "")</f>
         <v/>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="n">
+      <c r="A72" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="B72" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" s="0" t="s">
+      <c r="B72" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D72" s="0" t="s">
+      <c r="D72" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="F72" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J72" s="2" t="s">
+      <c r="J72" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M72" s="3" t="str">
+      <c r="M72" s="4" t="str">
         <f aca="false">IF(A72-A71&lt;&gt;1,A72-A71,"")</f>
         <v/>
       </c>
-      <c r="N72" s="3" t="n">
+      <c r="N72" s="4" t="n">
         <f aca="false">COUNTA(H72:L72)</f>
         <v>1</v>
       </c>
-      <c r="O72" s="3" t="n">
+      <c r="O72" s="4" t="n">
         <v>718</v>
       </c>
-      <c r="P72" s="3" t="str">
+      <c r="P72" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D72,3),O72,LEFT(C72,3)))</f>
         <v>HIL718IAN</v>
       </c>
-      <c r="Q72" s="4" t="str">
+      <c r="Q72" s="5" t="str">
         <f aca="false">IF(H72&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N72&gt;1,"5",""),$O72), "")</f>
         <v/>
       </c>
-      <c r="R72" s="4" t="str">
+      <c r="R72" s="5" t="str">
         <f aca="false">IF(I72&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N72&gt;1,"4",""),$O72), "")</f>
         <v/>
       </c>
-      <c r="S72" s="4" t="str">
+      <c r="S72" s="5" t="str">
         <f aca="false">IF(J72&lt;&gt;"", _xlfn.CONCAT("Motion ",$O72), "")</f>
         <v>Motion 718</v>
       </c>
-      <c r="T72" s="4" t="str">
+      <c r="T72" s="5" t="str">
         <f aca="false">IF(K72&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N72&gt;1,"2",""),$O72), "")</f>
         <v/>
       </c>
-      <c r="U72" s="4" t="str">
+      <c r="U72" s="5" t="str">
         <f aca="false">IF(L72&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N72&gt;1,"1",""),$O72), "")</f>
         <v/>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="n">
+      <c r="A73" s="1" t="n">
         <v>86</v>
       </c>
-      <c r="B73" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" s="0" t="s">
+      <c r="B73" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D73" s="0" t="s">
+      <c r="D73" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="F73" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I73" s="2" t="s">
+      <c r="I73" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J73" s="2" t="s">
+      <c r="J73" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M73" s="3" t="str">
+      <c r="M73" s="4" t="str">
         <f aca="false">IF(A73-A72&lt;&gt;1,A73-A72,"")</f>
         <v/>
       </c>
-      <c r="N73" s="3" t="n">
+      <c r="N73" s="4" t="n">
         <f aca="false">COUNTA(H73:L73)</f>
         <v>2</v>
       </c>
-      <c r="O73" s="3" t="n">
+      <c r="O73" s="4" t="n">
         <v>833</v>
       </c>
-      <c r="P73" s="3" t="str">
+      <c r="P73" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D73,3),O73,LEFT(C73,3)))</f>
         <v>TWI833AND</v>
       </c>
-      <c r="Q73" s="4" t="str">
+      <c r="Q73" s="5" t="str">
         <f aca="false">IF(H73&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N73&gt;1,"5",""),$O73), "")</f>
         <v/>
       </c>
-      <c r="R73" s="4" t="str">
+      <c r="R73" s="5" t="str">
         <f aca="false">IF(I73&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N73&gt;1,"4",""),$O73), "")</f>
         <v>Motion 4833</v>
       </c>
-      <c r="S73" s="4" t="str">
+      <c r="S73" s="5" t="str">
         <f aca="false">IF(J73&lt;&gt;"", _xlfn.CONCAT("Motion ",$O73), "")</f>
         <v>Motion 833</v>
       </c>
-      <c r="T73" s="4" t="str">
+      <c r="T73" s="5" t="str">
         <f aca="false">IF(K73&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N73&gt;1,"2",""),$O73), "")</f>
         <v/>
       </c>
-      <c r="U73" s="4" t="str">
+      <c r="U73" s="5" t="str">
         <f aca="false">IF(L73&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N73&gt;1,"1",""),$O73), "")</f>
         <v/>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="n">
+      <c r="A74" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="B74" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" s="0" t="s">
+      <c r="B74" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D74" s="0" t="s">
+      <c r="D74" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F74" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J74" s="2" t="s">
+      <c r="J74" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M74" s="3" t="str">
+      <c r="M74" s="4" t="str">
         <f aca="false">IF(A74-A73&lt;&gt;1,A74-A73,"")</f>
         <v/>
       </c>
-      <c r="N74" s="3" t="n">
+      <c r="N74" s="4" t="n">
         <f aca="false">COUNTA(H74:L74)</f>
         <v>1</v>
       </c>
-      <c r="O74" s="3" t="n">
+      <c r="O74" s="4" t="n">
         <v>811</v>
       </c>
-      <c r="P74" s="3" t="str">
+      <c r="P74" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D74,3),O74,LEFT(C74,3)))</f>
         <v>HUM811TIM</v>
       </c>
-      <c r="Q74" s="4" t="str">
+      <c r="Q74" s="5" t="str">
         <f aca="false">IF(H74&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N74&gt;1,"5",""),$O74), "")</f>
         <v/>
       </c>
-      <c r="R74" s="4" t="str">
+      <c r="R74" s="5" t="str">
         <f aca="false">IF(I74&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N74&gt;1,"4",""),$O74), "")</f>
         <v/>
       </c>
-      <c r="S74" s="4" t="str">
+      <c r="S74" s="5" t="str">
         <f aca="false">IF(J74&lt;&gt;"", _xlfn.CONCAT("Motion ",$O74), "")</f>
         <v>Motion 811</v>
       </c>
-      <c r="T74" s="4" t="str">
+      <c r="T74" s="5" t="str">
         <f aca="false">IF(K74&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N74&gt;1,"2",""),$O74), "")</f>
         <v/>
       </c>
-      <c r="U74" s="4" t="str">
+      <c r="U74" s="5" t="str">
         <f aca="false">IF(L74&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N74&gt;1,"1",""),$O74), "")</f>
         <v/>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="n">
+      <c r="A75" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="B75" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" s="0" t="s">
+      <c r="B75" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D75" s="0" t="s">
+      <c r="D75" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F75" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G75" s="1" t="n">
+      <c r="G75" s="2" t="n">
         <v>1002</v>
       </c>
-      <c r="J75" s="2" t="s">
+      <c r="J75" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M75" s="3" t="str">
+      <c r="M75" s="4" t="str">
         <f aca="false">IF(A75-A74&lt;&gt;1,A75-A74,"")</f>
         <v/>
       </c>
-      <c r="N75" s="3" t="n">
+      <c r="N75" s="4" t="n">
         <f aca="false">COUNTA(H75:L75)</f>
         <v>1</v>
       </c>
-      <c r="O75" s="11" t="n">
+      <c r="O75" s="12" t="n">
         <v>1001</v>
       </c>
-      <c r="P75" s="3" t="str">
+      <c r="P75" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D75,3),O75,LEFT(C75,3)))</f>
         <v>GOO1001GAR</v>
       </c>
-      <c r="Q75" s="4" t="str">
+      <c r="Q75" s="5" t="str">
         <f aca="false">IF(H75&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N75&gt;1,"5",""),$O75), "")</f>
         <v/>
       </c>
-      <c r="R75" s="4" t="str">
+      <c r="R75" s="5" t="str">
         <f aca="false">IF(I75&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N75&gt;1,"4",""),$O75), "")</f>
         <v/>
       </c>
-      <c r="S75" s="4" t="str">
+      <c r="S75" s="5" t="str">
         <f aca="false">IF(J75&lt;&gt;"", _xlfn.CONCAT("Motion ",$O75), "")</f>
         <v>Motion 1001</v>
       </c>
-      <c r="T75" s="4" t="str">
+      <c r="T75" s="5" t="str">
         <f aca="false">IF(K75&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N75&gt;1,"2",""),$O75), "")</f>
         <v/>
       </c>
-      <c r="U75" s="4" t="str">
+      <c r="U75" s="5" t="str">
         <f aca="false">IF(L75&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N75&gt;1,"1",""),$O75), "")</f>
         <v/>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="n">
+      <c r="A76" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="B76" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" s="0" t="s">
+      <c r="B76" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D76" s="0" t="s">
+      <c r="D76" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F76" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J76" s="2" t="s">
+      <c r="J76" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M76" s="3" t="str">
+      <c r="M76" s="4" t="str">
         <f aca="false">IF(A76-A75&lt;&gt;1,A76-A75,"")</f>
         <v/>
       </c>
-      <c r="N76" s="3" t="n">
+      <c r="N76" s="4" t="n">
         <f aca="false">COUNTA(H76:L76)</f>
         <v>1</v>
       </c>
-      <c r="O76" s="3" t="n">
+      <c r="O76" s="4" t="n">
         <v>647</v>
       </c>
-      <c r="P76" s="3" t="str">
+      <c r="P76" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D76,3),O76,LEFT(C76,3)))</f>
         <v>WHA647TRE</v>
       </c>
-      <c r="Q76" s="4" t="str">
+      <c r="Q76" s="5" t="str">
         <f aca="false">IF(H76&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N76&gt;1,"5",""),$O76), "")</f>
         <v/>
       </c>
-      <c r="R76" s="4" t="str">
+      <c r="R76" s="5" t="str">
         <f aca="false">IF(I76&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N76&gt;1,"4",""),$O76), "")</f>
         <v/>
       </c>
-      <c r="S76" s="4" t="str">
+      <c r="S76" s="5" t="str">
         <f aca="false">IF(J76&lt;&gt;"", _xlfn.CONCAT("Motion ",$O76), "")</f>
         <v>Motion 647</v>
       </c>
-      <c r="T76" s="4" t="str">
+      <c r="T76" s="5" t="str">
         <f aca="false">IF(K76&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N76&gt;1,"2",""),$O76), "")</f>
         <v/>
       </c>
-      <c r="U76" s="4" t="str">
+      <c r="U76" s="5" t="str">
         <f aca="false">IF(L76&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N76&gt;1,"1",""),$O76), "")</f>
         <v/>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="n">
+      <c r="A77" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="B77" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" s="0" t="s">
+      <c r="B77" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D77" s="0" t="s">
+      <c r="D77" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E77" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="F77" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J77" s="2" t="s">
+      <c r="J77" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M77" s="3" t="str">
+      <c r="M77" s="4" t="str">
         <f aca="false">IF(A77-A76&lt;&gt;1,A77-A76,"")</f>
         <v/>
       </c>
-      <c r="N77" s="3" t="n">
+      <c r="N77" s="4" t="n">
         <f aca="false">COUNTA(H77:L77)</f>
         <v>1</v>
       </c>
-      <c r="O77" s="3" t="n">
+      <c r="O77" s="4" t="n">
         <v>1040</v>
       </c>
-      <c r="P77" s="3" t="str">
+      <c r="P77" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D77,3),O77,LEFT(C77,3)))</f>
         <v>KIE1040OLI</v>
       </c>
-      <c r="Q77" s="4" t="str">
+      <c r="Q77" s="5" t="str">
         <f aca="false">IF(H77&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N77&gt;1,"5",""),$O77), "")</f>
         <v/>
       </c>
-      <c r="R77" s="4" t="str">
+      <c r="R77" s="5" t="str">
         <f aca="false">IF(I77&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N77&gt;1,"4",""),$O77), "")</f>
         <v/>
       </c>
-      <c r="S77" s="4" t="str">
+      <c r="S77" s="5" t="str">
         <f aca="false">IF(J77&lt;&gt;"", _xlfn.CONCAT("Motion ",$O77), "")</f>
         <v>Motion 1040</v>
       </c>
-      <c r="T77" s="4" t="str">
+      <c r="T77" s="5" t="str">
         <f aca="false">IF(K77&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N77&gt;1,"2",""),$O77), "")</f>
         <v/>
       </c>
-      <c r="U77" s="4" t="str">
+      <c r="U77" s="5" t="str">
         <f aca="false">IF(L77&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N77&gt;1,"1",""),$O77), "")</f>
         <v/>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="n">
+      <c r="A78" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="B78" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" s="0" t="s">
+      <c r="B78" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D78" s="0" t="s">
+      <c r="D78" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F78" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G78" s="1" t="n">
+      <c r="G78" s="2" t="n">
         <v>676</v>
       </c>
-      <c r="J78" s="2" t="s">
+      <c r="J78" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M78" s="3" t="str">
+      <c r="M78" s="4" t="str">
         <f aca="false">IF(A78-A77&lt;&gt;1,A78-A77,"")</f>
         <v/>
       </c>
-      <c r="N78" s="3" t="n">
+      <c r="N78" s="4" t="n">
         <f aca="false">COUNTA(H78:L78)</f>
         <v>1</v>
       </c>
-      <c r="O78" s="11" t="n">
+      <c r="O78" s="12" t="n">
         <f aca="false">G78</f>
         <v>676</v>
       </c>
-      <c r="P78" s="3" t="str">
+      <c r="P78" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D78,3),O78,LEFT(C78,3)))</f>
         <v>NEA676IAI</v>
       </c>
-      <c r="Q78" s="4" t="str">
+      <c r="Q78" s="5" t="str">
         <f aca="false">IF(H78&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N78&gt;1,"5",""),$O78), "")</f>
         <v/>
       </c>
-      <c r="R78" s="4" t="str">
+      <c r="R78" s="5" t="str">
         <f aca="false">IF(I78&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N78&gt;1,"4",""),$O78), "")</f>
         <v/>
       </c>
-      <c r="S78" s="4" t="str">
+      <c r="S78" s="5" t="str">
         <f aca="false">IF(J78&lt;&gt;"", _xlfn.CONCAT("Motion ",$O78), "")</f>
         <v>Motion 676</v>
       </c>
-      <c r="T78" s="4" t="str">
+      <c r="T78" s="5" t="str">
         <f aca="false">IF(K78&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N78&gt;1,"2",""),$O78), "")</f>
         <v/>
       </c>
-      <c r="U78" s="4" t="str">
+      <c r="U78" s="5" t="str">
         <f aca="false">IF(L78&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N78&gt;1,"1",""),$O78), "")</f>
         <v/>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="n">
+      <c r="A79" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="B79" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" s="0" t="s">
+      <c r="B79" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D79" s="0" t="s">
+      <c r="D79" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="K79" s="2" t="s">
+      <c r="K79" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M79" s="3" t="str">
+      <c r="M79" s="4" t="str">
         <f aca="false">IF(A79-A78&lt;&gt;1,A79-A78,"")</f>
         <v/>
       </c>
-      <c r="N79" s="3" t="n">
+      <c r="N79" s="4" t="n">
         <f aca="false">COUNTA(H79:L79)</f>
         <v>1</v>
       </c>
-      <c r="O79" s="3" t="n">
+      <c r="O79" s="4" t="n">
         <v>660</v>
       </c>
-      <c r="P79" s="3" t="str">
+      <c r="P79" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D79,3),O79,LEFT(C79,3)))</f>
         <v>CAR660MAR</v>
       </c>
-      <c r="Q79" s="4" t="str">
+      <c r="Q79" s="5" t="str">
         <f aca="false">IF(H79&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N79&gt;1,"5",""),$O79), "")</f>
         <v/>
       </c>
-      <c r="R79" s="4" t="str">
+      <c r="R79" s="5" t="str">
         <f aca="false">IF(I79&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N79&gt;1,"4",""),$O79), "")</f>
         <v/>
       </c>
-      <c r="S79" s="4" t="str">
+      <c r="S79" s="5" t="str">
         <f aca="false">IF(J79&lt;&gt;"", _xlfn.CONCAT("Motion ",$O79), "")</f>
         <v/>
       </c>
-      <c r="T79" s="4" t="str">
+      <c r="T79" s="5" t="str">
         <f aca="false">IF(K79&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N79&gt;1,"2",""),$O79), "")</f>
         <v>Motion 660</v>
       </c>
-      <c r="U79" s="4" t="str">
+      <c r="U79" s="5" t="str">
         <f aca="false">IF(L79&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N79&gt;1,"1",""),$O79), "")</f>
         <v/>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="n">
+      <c r="A80" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="B80" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" s="0" t="s">
+      <c r="B80" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D80" s="0" t="s">
+      <c r="D80" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F80" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G80" s="1" t="n">
+      <c r="G80" s="2" t="n">
         <v>704</v>
       </c>
-      <c r="J80" s="2" t="s">
+      <c r="J80" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M80" s="3" t="str">
+      <c r="M80" s="4" t="str">
         <f aca="false">IF(A80-A79&lt;&gt;1,A80-A79,"")</f>
         <v/>
       </c>
-      <c r="N80" s="3" t="n">
+      <c r="N80" s="4" t="n">
         <f aca="false">COUNTA(H80:L80)</f>
         <v>1</v>
       </c>
-      <c r="O80" s="11" t="n">
+      <c r="O80" s="12" t="n">
         <f aca="false">G80</f>
         <v>704</v>
       </c>
-      <c r="P80" s="3" t="str">
+      <c r="P80" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D80,3),O80,LEFT(C80,3)))</f>
         <v>VER704SHA</v>
       </c>
-      <c r="Q80" s="4" t="str">
+      <c r="Q80" s="5" t="str">
         <f aca="false">IF(H80&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N80&gt;1,"5",""),$O80), "")</f>
         <v/>
       </c>
-      <c r="R80" s="4" t="str">
+      <c r="R80" s="5" t="str">
         <f aca="false">IF(I80&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N80&gt;1,"4",""),$O80), "")</f>
         <v/>
       </c>
-      <c r="S80" s="4" t="str">
+      <c r="S80" s="5" t="str">
         <f aca="false">IF(J80&lt;&gt;"", _xlfn.CONCAT("Motion ",$O80), "")</f>
         <v>Motion 704</v>
       </c>
-      <c r="T80" s="4" t="str">
+      <c r="T80" s="5" t="str">
         <f aca="false">IF(K80&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N80&gt;1,"2",""),$O80), "")</f>
         <v/>
       </c>
-      <c r="U80" s="4" t="str">
+      <c r="U80" s="5" t="str">
         <f aca="false">IF(L80&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N80&gt;1,"1",""),$O80), "")</f>
         <v/>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="n">
+      <c r="A81" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="B81" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" s="0" t="s">
+      <c r="B81" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D81" s="0" t="s">
+      <c r="D81" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F81" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J81" s="2" t="s">
+      <c r="J81" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M81" s="3" t="str">
+      <c r="M81" s="4" t="str">
         <f aca="false">IF(A81-A80&lt;&gt;1,A81-A80,"")</f>
         <v/>
       </c>
-      <c r="N81" s="3" t="n">
+      <c r="N81" s="4" t="n">
         <f aca="false">COUNTA(H81:L81)</f>
         <v>1</v>
       </c>
-      <c r="O81" s="3" t="n">
+      <c r="O81" s="4" t="n">
         <v>661</v>
       </c>
-      <c r="P81" s="3" t="str">
+      <c r="P81" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D81,3),O81,LEFT(C81,3)))</f>
         <v>BRA661PAU</v>
       </c>
-      <c r="Q81" s="4" t="str">
+      <c r="Q81" s="5" t="str">
         <f aca="false">IF(H81&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N81&gt;1,"5",""),$O81), "")</f>
         <v/>
       </c>
-      <c r="R81" s="4" t="str">
+      <c r="R81" s="5" t="str">
         <f aca="false">IF(I81&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N81&gt;1,"4",""),$O81), "")</f>
         <v/>
       </c>
-      <c r="S81" s="4" t="str">
+      <c r="S81" s="5" t="str">
         <f aca="false">IF(J81&lt;&gt;"", _xlfn.CONCAT("Motion ",$O81), "")</f>
         <v>Motion 661</v>
       </c>
-      <c r="T81" s="4" t="str">
+      <c r="T81" s="5" t="str">
         <f aca="false">IF(K81&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N81&gt;1,"2",""),$O81), "")</f>
         <v/>
       </c>
-      <c r="U81" s="4" t="str">
+      <c r="U81" s="5" t="str">
         <f aca="false">IF(L81&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N81&gt;1,"1",""),$O81), "")</f>
         <v/>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="n">
+      <c r="A82" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="B82" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" s="0" t="s">
+      <c r="B82" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D82" s="0" t="s">
+      <c r="D82" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="F82" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I82" s="2" t="s">
+      <c r="I82" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J82" s="2" t="s">
+      <c r="J82" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M82" s="12" t="n">
+      <c r="M82" s="13" t="n">
         <f aca="false">IF(A82-A81&lt;&gt;1,A82-A81,"")</f>
         <v>2</v>
       </c>
-      <c r="N82" s="3" t="n">
+      <c r="N82" s="4" t="n">
         <f aca="false">COUNTA(H82:L82)</f>
         <v>2</v>
       </c>
-      <c r="O82" s="3" t="n">
+      <c r="O82" s="4" t="n">
         <v>866</v>
       </c>
-      <c r="P82" s="3" t="str">
+      <c r="P82" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D82,3),O82,LEFT(C82,3)))</f>
         <v>CRO866ALL</v>
       </c>
-      <c r="Q82" s="4" t="str">
+      <c r="Q82" s="5" t="str">
         <f aca="false">IF(H82&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N82&gt;1,"5",""),$O82), "")</f>
         <v/>
       </c>
-      <c r="R82" s="4" t="str">
+      <c r="R82" s="5" t="str">
         <f aca="false">IF(I82&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N82&gt;1,"4",""),$O82), "")</f>
         <v>Motion 4866</v>
       </c>
-      <c r="S82" s="4" t="str">
+      <c r="S82" s="5" t="str">
         <f aca="false">IF(J82&lt;&gt;"", _xlfn.CONCAT("Motion ",$O82), "")</f>
         <v>Motion 866</v>
       </c>
-      <c r="T82" s="4" t="str">
+      <c r="T82" s="5" t="str">
         <f aca="false">IF(K82&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N82&gt;1,"2",""),$O82), "")</f>
         <v/>
       </c>
-      <c r="U82" s="4" t="str">
+      <c r="U82" s="5" t="str">
         <f aca="false">IF(L82&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N82&gt;1,"1",""),$O82), "")</f>
         <v/>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="n">
+      <c r="A83" s="1" t="n">
         <v>97</v>
       </c>
-      <c r="B83" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" s="0" t="s">
+      <c r="B83" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D83" s="0" t="s">
+      <c r="D83" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E83" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F83" s="1" t="s">
+      <c r="F83" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H83" s="2" t="s">
+      <c r="H83" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="M83" s="3" t="str">
+      <c r="M83" s="4" t="str">
         <f aca="false">IF(A83-A82&lt;&gt;1,A83-A82,"")</f>
         <v/>
       </c>
-      <c r="N83" s="3" t="n">
+      <c r="N83" s="4" t="n">
         <f aca="false">COUNTA(H83:L83)</f>
         <v>1</v>
       </c>
-      <c r="O83" s="3" t="n">
+      <c r="O83" s="4" t="n">
         <v>825</v>
       </c>
-      <c r="P83" s="3" t="str">
+      <c r="P83" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D83,3),O83,LEFT(C83,3)))</f>
         <v>MIL825JAY</v>
       </c>
-      <c r="Q83" s="4" t="str">
+      <c r="Q83" s="5" t="str">
         <f aca="false">IF(H83&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N83&gt;1,"5",""),$O83), "")</f>
         <v>Motion 825</v>
       </c>
-      <c r="R83" s="4" t="str">
+      <c r="R83" s="5" t="str">
         <f aca="false">IF(I83&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N83&gt;1,"4",""),$O83), "")</f>
         <v/>
       </c>
-      <c r="S83" s="4" t="str">
+      <c r="S83" s="5" t="str">
         <f aca="false">IF(J83&lt;&gt;"", _xlfn.CONCAT("Motion ",$O83), "")</f>
         <v/>
       </c>
-      <c r="T83" s="4" t="str">
+      <c r="T83" s="5" t="str">
         <f aca="false">IF(K83&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N83&gt;1,"2",""),$O83), "")</f>
         <v/>
       </c>
-      <c r="U83" s="4" t="str">
+      <c r="U83" s="5" t="str">
         <f aca="false">IF(L83&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N83&gt;1,"1",""),$O83), "")</f>
         <v/>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="n">
+      <c r="A84" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="B84" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" s="0" t="s">
+      <c r="B84" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D84" s="0" t="s">
+      <c r="D84" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="F84" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J84" s="2" t="s">
+      <c r="J84" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M84" s="3" t="str">
+      <c r="M84" s="4" t="str">
         <f aca="false">IF(A84-A83&lt;&gt;1,A84-A83,"")</f>
         <v/>
       </c>
-      <c r="N84" s="3" t="n">
+      <c r="N84" s="4" t="n">
         <f aca="false">COUNTA(H84:L84)</f>
         <v>1</v>
       </c>
-      <c r="O84" s="3" t="n">
+      <c r="O84" s="4" t="n">
         <v>633</v>
       </c>
-      <c r="P84" s="3" t="str">
+      <c r="P84" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D84,3),O84,LEFT(C84,3)))</f>
         <v>PEN633ROB</v>
       </c>
-      <c r="Q84" s="4" t="str">
+      <c r="Q84" s="5" t="str">
         <f aca="false">IF(H84&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N84&gt;1,"5",""),$O84), "")</f>
         <v/>
       </c>
-      <c r="R84" s="4" t="str">
+      <c r="R84" s="5" t="str">
         <f aca="false">IF(I84&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N84&gt;1,"4",""),$O84), "")</f>
         <v/>
       </c>
-      <c r="S84" s="4" t="str">
+      <c r="S84" s="5" t="str">
         <f aca="false">IF(J84&lt;&gt;"", _xlfn.CONCAT("Motion ",$O84), "")</f>
         <v>Motion 633</v>
       </c>
-      <c r="T84" s="4" t="str">
+      <c r="T84" s="5" t="str">
         <f aca="false">IF(K84&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N84&gt;1,"2",""),$O84), "")</f>
         <v/>
       </c>
-      <c r="U84" s="4" t="str">
+      <c r="U84" s="5" t="str">
         <f aca="false">IF(L84&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N84&gt;1,"1",""),$O84), "")</f>
         <v/>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="n">
+      <c r="A85" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="B85" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" s="0" t="s">
+      <c r="B85" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D85" s="0" t="s">
+      <c r="D85" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="F85" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J85" s="2" t="s">
+      <c r="J85" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K85" s="2" t="s">
+      <c r="K85" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M85" s="3" t="str">
+      <c r="M85" s="4" t="str">
         <f aca="false">IF(A85-A84&lt;&gt;1,A85-A84,"")</f>
         <v/>
       </c>
-      <c r="N85" s="3" t="n">
+      <c r="N85" s="4" t="n">
         <f aca="false">COUNTA(H85:L85)</f>
         <v>2</v>
       </c>
-      <c r="O85" s="3" t="n">
+      <c r="O85" s="4" t="n">
         <v>695</v>
       </c>
-      <c r="P85" s="3" t="str">
+      <c r="P85" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D85,3),O85,LEFT(C85,3)))</f>
         <v>DAV695STE</v>
       </c>
-      <c r="Q85" s="4" t="str">
+      <c r="Q85" s="5" t="str">
         <f aca="false">IF(H85&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N85&gt;1,"5",""),$O85), "")</f>
         <v/>
       </c>
-      <c r="R85" s="4" t="str">
+      <c r="R85" s="5" t="str">
         <f aca="false">IF(I85&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N85&gt;1,"4",""),$O85), "")</f>
         <v/>
       </c>
-      <c r="S85" s="4" t="str">
+      <c r="S85" s="5" t="str">
         <f aca="false">IF(J85&lt;&gt;"", _xlfn.CONCAT("Motion ",$O85), "")</f>
         <v>Motion 695</v>
       </c>
-      <c r="T85" s="4" t="str">
+      <c r="T85" s="5" t="str">
         <f aca="false">IF(K85&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N85&gt;1,"2",""),$O85), "")</f>
         <v>Motion 2695</v>
       </c>
-      <c r="U85" s="4" t="str">
+      <c r="U85" s="5" t="str">
         <f aca="false">IF(L85&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N85&gt;1,"1",""),$O85), "")</f>
         <v/>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="n">
+      <c r="A86" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="B86" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" s="0" t="s">
+      <c r="B86" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D86" s="0" t="s">
+      <c r="D86" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E86" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F86" s="1" t="s">
+      <c r="F86" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J86" s="2" t="s">
+      <c r="J86" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M86" s="3" t="str">
+      <c r="M86" s="4" t="str">
         <f aca="false">IF(A86-A85&lt;&gt;1,A86-A85,"")</f>
         <v/>
       </c>
-      <c r="N86" s="3" t="n">
+      <c r="N86" s="4" t="n">
         <f aca="false">COUNTA(H86:L86)</f>
         <v>1</v>
       </c>
-      <c r="O86" s="3" t="n">
+      <c r="O86" s="4" t="n">
         <v>823</v>
       </c>
-      <c r="P86" s="3" t="str">
+      <c r="P86" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D86,3),O86,LEFT(C86,3)))</f>
         <v>VIC823MIT</v>
       </c>
-      <c r="Q86" s="4" t="str">
+      <c r="Q86" s="5" t="str">
         <f aca="false">IF(H86&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N86&gt;1,"5",""),$O86), "")</f>
         <v/>
       </c>
-      <c r="R86" s="4" t="str">
+      <c r="R86" s="5" t="str">
         <f aca="false">IF(I86&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N86&gt;1,"4",""),$O86), "")</f>
         <v/>
       </c>
-      <c r="S86" s="4" t="str">
+      <c r="S86" s="5" t="str">
         <f aca="false">IF(J86&lt;&gt;"", _xlfn.CONCAT("Motion ",$O86), "")</f>
         <v>Motion 823</v>
       </c>
-      <c r="T86" s="4" t="str">
+      <c r="T86" s="5" t="str">
         <f aca="false">IF(K86&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N86&gt;1,"2",""),$O86), "")</f>
         <v/>
       </c>
-      <c r="U86" s="4" t="str">
+      <c r="U86" s="5" t="str">
         <f aca="false">IF(L86&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N86&gt;1,"1",""),$O86), "")</f>
         <v/>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="n">
+      <c r="A87" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="B87" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" s="0" t="s">
+      <c r="B87" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D87" s="0" t="s">
+      <c r="D87" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E87" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="F87" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H87" s="2" t="s">
+      <c r="H87" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="N87" s="3" t="n">
+      <c r="N87" s="4" t="n">
         <f aca="false">COUNTA(H87:L87)</f>
         <v>1</v>
       </c>
-      <c r="O87" s="3" t="n">
+      <c r="O87" s="4" t="n">
         <v>601</v>
       </c>
-      <c r="P87" s="3" t="str">
+      <c r="P87" s="4" t="str">
         <f aca="false">UPPER(_xlfn.CONCAT(LEFT(D87,3),O87,LEFT(C87,3)))</f>
         <v>DEM601OSC</v>
       </c>
-      <c r="Q87" s="4" t="str">
+      <c r="Q87" s="5" t="str">
         <f aca="false">IF(H87&lt;&gt;"", _xlfn.CONCAT("Motion ",$O87), "")</f>
         <v>Motion 601</v>
       </c>
-      <c r="R87" s="4" t="str">
+      <c r="R87" s="5" t="str">
         <f aca="false">IF(I87&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N87&gt;1,"4",""),$O87), "")</f>
         <v/>
       </c>
-      <c r="T87" s="4" t="str">
+      <c r="T87" s="5" t="str">
         <f aca="false">IF(K87&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N87&gt;1,"2",""),$O87), "")</f>
         <v/>
       </c>
-      <c r="U87" s="4" t="str">
+      <c r="U87" s="5" t="str">
         <f aca="false">IF(L87&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N87&gt;1,"1",""),$O87), "")</f>
         <v/>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C94" s="13" t="s">
+      <c r="C94" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="D94" s="0" t="s">
+      <c r="D94" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E94" s="0" t="n">
+      <c r="E94" s="2" t="n">
         <v>724</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C95" s="13" t="s">
+      <c r="C95" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="D95" s="0" t="s">
+      <c r="D95" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E95" s="0" t="n">
+      <c r="E95" s="2" t="n">
         <v>705</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C96" s="13" t="s">
+      <c r="C96" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="D96" s="0" t="s">
+      <c r="D96" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E96" s="0" t="n">
+      <c r="E96" s="2" t="n">
         <v>619</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C97" s="13" t="s">
+      <c r="C97" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D97" s="0" t="s">
+      <c r="D97" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E97" s="0" t="n">
+      <c r="E97" s="2" t="n">
         <v>946</v>
       </c>
     </row>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C98" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <autoFilter ref="A:U"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6325,786 +6350,786 @@
   <dimension ref="A1:F92"/>
   <sheetFormatPr defaultColWidth="8.6015625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="5.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="20.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="24.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="23.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="19.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="14.57"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>169</v>
+      <c r="C2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>171</v>
+      <c r="C3" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>173</v>
+      <c r="C4" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>174</v>
+      <c r="A5" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>175</v>
+      <c r="E6" s="2" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>177</v>
+      <c r="C7" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>178</v>
+      <c r="D8" s="2" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>179</v>
+      <c r="B9" s="2" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>180</v>
+      <c r="D10" s="2" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>182</v>
+      <c r="C11" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>183</v>
+      <c r="D12" s="2" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>184</v>
+      <c r="B13" s="2" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>185</v>
+      <c r="D14" s="2" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>187</v>
+      <c r="C15" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>188</v>
+      <c r="B16" s="2" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>189</v>
+      <c r="D17" s="2" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>190</v>
+      <c r="D18" s="2" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>192</v>
+      <c r="C19" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>193</v>
+      <c r="D20" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>194</v>
+      <c r="D21" s="2" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>196</v>
+      <c r="C22" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>198</v>
+      <c r="C23" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>199</v>
+      <c r="D24" s="2" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>201</v>
+      <c r="C25" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>202</v>
+      <c r="D26" s="2" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>203</v>
+      <c r="D27" s="2" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>204</v>
+      <c r="B28" s="2" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>205</v>
+      <c r="D29" s="2" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>206</v>
+      <c r="D30" s="2" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>207</v>
+      <c r="D31" s="2" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>208</v>
+      <c r="D32" s="2" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>210</v>
+      <c r="C33" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>211</v>
+      <c r="D34" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>213</v>
+      <c r="C35" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>214</v>
+      <c r="D36" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>215</v>
+      <c r="D37" s="2" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>216</v>
+      <c r="D38" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>217</v>
+      <c r="D39" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>218</v>
+      <c r="D40" s="2" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>219</v>
+      <c r="D41" s="2" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>220</v>
+      <c r="D42" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>221</v>
+      <c r="B43" s="2" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>222</v>
+      <c r="E44" s="2" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>224</v>
+      <c r="C45" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>226</v>
+      <c r="D46" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>227</v>
+      <c r="D47" s="2" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>228</v>
+      <c r="D48" s="2" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>229</v>
+      <c r="D49" s="2" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>230</v>
+      <c r="F50" s="2" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>231</v>
+      <c r="B51" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>232</v>
+      <c r="B52" s="2" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>233</v>
+      <c r="B53" s="2" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>234</v>
+      <c r="B54" s="2" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>236</v>
+      <c r="C55" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>238</v>
+      <c r="C56" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>239</v>
+      <c r="D57" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>241</v>
+      <c r="B58" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>242</v>
+      <c r="D59" s="2" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>243</v>
+      <c r="B60" s="2" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>245</v>
+      <c r="C61" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>246</v>
+      <c r="D62" s="2" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>247</v>
+      <c r="D63" s="2" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>248</v>
+      <c r="E64" s="2" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>78</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>249</v>
+      <c r="D65" s="2" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>250</v>
+      <c r="D66" s="2" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>251</v>
+      <c r="D67" s="2" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>252</v>
+      <c r="D68" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>253</v>
+      <c r="D69" s="2" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>255</v>
+      <c r="C70" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>84</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>256</v>
+      <c r="E71" s="2" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>257</v>
+      <c r="D72" s="2" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>86</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>259</v>
+      <c r="C73" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>260</v>
+      <c r="D74" s="2" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>261</v>
+      <c r="D75" s="2" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>262</v>
+      <c r="D76" s="2" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="D77" s="1" t="s">
-        <v>263</v>
+      <c r="D77" s="2" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>91</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>264</v>
+      <c r="D78" s="2" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>265</v>
+      <c r="E79" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>266</v>
+      <c r="D80" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>94</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>267</v>
+      <c r="D81" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>269</v>
+      <c r="C82" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>270</v>
+      <c r="B83" s="2" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>98</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>271</v>
+      <c r="D84" s="2" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="D85" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>273</v>
+      <c r="D85" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>274</v>
+      <c r="D86" s="2" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>275</v>
+      <c r="B87" s="2" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/events/2026/config/motions-ids.xlsx
+++ b/events/2026/config/motions-ids.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="280">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -509,6 +509,15 @@
     <t xml:space="preserve">Dempsey</t>
   </si>
   <si>
+    <t xml:space="preserve">Hobson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maciej</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bukholt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sam</t>
   </si>
   <si>
@@ -521,19 +530,16 @@
     <t xml:space="preserve">Stallman</t>
   </si>
   <si>
-    <t xml:space="preserve">Maciej</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bukholt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hobson</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lilia</t>
   </si>
   <si>
     <t xml:space="preserve">Yelland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State</t>
   </si>
   <si>
     <t xml:space="preserve">Motion 4871</t>
@@ -1366,7 +1372,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U102"/>
+  <dimension ref="A1:U1048576"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.29"/>
@@ -6270,65 +6276,85 @@
         <v/>
       </c>
     </row>
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C92" s="0"/>
+      <c r="D92" s="0"/>
+      <c r="E92" s="0"/>
+    </row>
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C93" s="0"/>
+      <c r="D93" s="0"/>
+      <c r="E93" s="0"/>
+    </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C94" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="E94" s="2" t="n">
-        <v>724</v>
+        <v>946</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C95" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="E95" s="2" t="n">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C96" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E96" s="2" t="n">
         <v>619</v>
       </c>
     </row>
+    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C97" s="14" t="s">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C98" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E97" s="2" t="n">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C98" s="1" t="s">
+      <c r="E98" s="2" t="n">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C99" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D99" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E98" s="2" t="n">
+      <c r="E99" s="2" t="n">
         <v>700</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C100" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>617</v>
+      </c>
+    </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <autoFilter ref="A:U"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6383,10 +6409,10 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6394,10 +6420,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6405,10 +6431,10 @@
         <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6416,7 +6442,7 @@
         <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6424,7 +6450,7 @@
         <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6432,10 +6458,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6443,7 +6469,7 @@
         <v>19</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6451,7 +6477,7 @@
         <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6459,7 +6485,7 @@
         <v>21</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6467,10 +6493,10 @@
         <v>22</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6478,7 +6504,7 @@
         <v>23</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6486,7 +6512,7 @@
         <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6494,7 +6520,7 @@
         <v>25</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6502,10 +6528,10 @@
         <v>26</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6513,7 +6539,7 @@
         <v>27</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6521,7 +6547,7 @@
         <v>28</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6529,7 +6555,7 @@
         <v>29</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6537,10 +6563,10 @@
         <v>30</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6548,7 +6574,7 @@
         <v>31</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6556,7 +6582,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6564,10 +6590,10 @@
         <v>33</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6575,10 +6601,10 @@
         <v>34</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6586,7 +6612,7 @@
         <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6594,10 +6620,10 @@
         <v>36</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6605,7 +6631,7 @@
         <v>37</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6613,7 +6639,7 @@
         <v>38</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6621,7 +6647,7 @@
         <v>39</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6629,7 +6655,7 @@
         <v>40</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6637,7 +6663,7 @@
         <v>41</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6645,7 +6671,7 @@
         <v>42</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6653,7 +6679,7 @@
         <v>43</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6661,10 +6687,10 @@
         <v>44</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6672,7 +6698,7 @@
         <v>45</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6680,10 +6706,10 @@
         <v>46</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6691,7 +6717,7 @@
         <v>47</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6699,7 +6725,7 @@
         <v>48</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6707,7 +6733,7 @@
         <v>49</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6715,7 +6741,7 @@
         <v>50</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6723,7 +6749,7 @@
         <v>51</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6731,7 +6757,7 @@
         <v>52</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6739,7 +6765,7 @@
         <v>53</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6747,7 +6773,7 @@
         <v>54</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6755,7 +6781,7 @@
         <v>55</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6763,10 +6789,10 @@
         <v>56</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6774,10 +6800,10 @@
         <v>57</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6785,7 +6811,7 @@
         <v>58</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6793,7 +6819,7 @@
         <v>59</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6801,7 +6827,7 @@
         <v>60</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6809,7 +6835,7 @@
         <v>61</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6817,7 +6843,7 @@
         <v>63</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6825,7 +6851,7 @@
         <v>64</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6833,7 +6859,7 @@
         <v>65</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6841,7 +6867,7 @@
         <v>66</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6849,10 +6875,10 @@
         <v>67</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6860,10 +6886,10 @@
         <v>68</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6871,7 +6897,7 @@
         <v>69</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6879,10 +6905,10 @@
         <v>70</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6890,7 +6916,7 @@
         <v>71</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6898,7 +6924,7 @@
         <v>72</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6906,10 +6932,10 @@
         <v>73</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6917,7 +6943,7 @@
         <v>75</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6925,7 +6951,7 @@
         <v>76</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6933,7 +6959,7 @@
         <v>77</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6941,7 +6967,7 @@
         <v>78</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6949,7 +6975,7 @@
         <v>79</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6957,7 +6983,7 @@
         <v>80</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6965,7 +6991,7 @@
         <v>81</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6973,7 +6999,7 @@
         <v>82</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6981,10 +7007,10 @@
         <v>83</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6992,7 +7018,7 @@
         <v>84</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7000,7 +7026,7 @@
         <v>85</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7008,10 +7034,10 @@
         <v>86</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7019,7 +7045,7 @@
         <v>87</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7027,7 +7053,7 @@
         <v>88</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7035,7 +7061,7 @@
         <v>89</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7043,7 +7069,7 @@
         <v>90</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7051,7 +7077,7 @@
         <v>91</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7059,7 +7085,7 @@
         <v>92</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7067,7 +7093,7 @@
         <v>93</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7075,7 +7101,7 @@
         <v>94</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7083,10 +7109,10 @@
         <v>96</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7094,7 +7120,7 @@
         <v>97</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7102,7 +7128,7 @@
         <v>98</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7110,10 +7136,10 @@
         <v>99</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7121,7 +7147,7 @@
         <v>100</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7129,7 +7155,7 @@
         <v>101</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
